--- a/Results/Hydrogen/hydrogen water use results.xlsx
+++ b/Results/Hydrogen/hydrogen water use results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.439624231261389</v>
+        <v>3.439624231261436</v>
       </c>
       <c r="C2" t="n">
-        <v>11.12159826602235</v>
+        <v>11.1215982660223</v>
       </c>
       <c r="D2" t="n">
-        <v>6.349099451425016</v>
+        <v>6.349099451425015</v>
       </c>
       <c r="E2" t="n">
-        <v>11.12159826602235</v>
+        <v>11.1215982660223</v>
       </c>
       <c r="F2" t="n">
-        <v>11.12159826602235</v>
+        <v>11.1215982660223</v>
       </c>
       <c r="G2" t="n">
-        <v>11.62370516325145</v>
+        <v>11.62370516325154</v>
       </c>
       <c r="H2" t="n">
-        <v>13.88600276223243</v>
+        <v>13.88600276223235</v>
       </c>
       <c r="I2" t="n">
-        <v>11.12159826602235</v>
+        <v>11.1215982660223</v>
       </c>
       <c r="J2" t="n">
-        <v>9.768892795319578</v>
+        <v>9.768892795319555</v>
       </c>
       <c r="K2" t="n">
-        <v>5.519665081932748</v>
+        <v>5.519665081932722</v>
       </c>
       <c r="L2" t="n">
-        <v>5.166196394550681</v>
+        <v>60.83597155084687</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1326954221235296</v>
+        <v>0.1326954221235301</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1342994351034811</v>
+        <v>0.1342994351034808</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1326954221235296</v>
+        <v>0.1326954221235301</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1350207924592651</v>
+        <v>0.1350207924592659</v>
       </c>
       <c r="F3" t="n">
-        <v>0.135020792459265</v>
+        <v>0.1350207924592648</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1328425964323176</v>
+        <v>0.1328425964323178</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1326954221235296</v>
+        <v>0.1326954221235301</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1332124444142255</v>
+        <v>0.1332124444142265</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1326954221235296</v>
+        <v>0.1326954221235301</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1326954221235296</v>
+        <v>0.1326954221235301</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1326954221235296</v>
+        <v>0.1326954221235301</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>88.01378025386281</v>
+        <v>7.258533098663344</v>
       </c>
       <c r="C4" t="n">
-        <v>7.350603112330792</v>
+        <v>7.35060311233078</v>
       </c>
       <c r="D4" t="n">
-        <v>7.23565330183851</v>
+        <v>7.235654266080064</v>
       </c>
       <c r="E4" t="n">
-        <v>7.326322319997771</v>
+        <v>7.326322319997776</v>
       </c>
       <c r="F4" t="n">
-        <v>7.350809588467323</v>
+        <v>7.350809588467327</v>
       </c>
       <c r="G4" t="n">
-        <v>88.01392742817167</v>
+        <v>88.01392742817166</v>
       </c>
       <c r="H4" t="n">
-        <v>88.00268980547108</v>
+        <v>88.00268980547105</v>
       </c>
       <c r="I4" t="n">
-        <v>88.01429727615353</v>
+        <v>7.259050120954027</v>
       </c>
       <c r="J4" t="n">
         <v>7.260828123245609</v>
       </c>
       <c r="K4" t="n">
-        <v>7.14144426429488</v>
+        <v>7.141444264294877</v>
       </c>
       <c r="L4" t="n">
-        <v>7.242955024532693</v>
+        <v>7.242955024532694</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5333670001299314</v>
+        <v>0.5333670001299298</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5338840224206284</v>
+        <v>0.5338840224206293</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5333383863704657</v>
+        <v>0.5333383863704656</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5338289742157479</v>
+        <v>0.5338289742157486</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5338289742157479</v>
+        <v>0.5338289742157486</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5335141744387191</v>
+        <v>0.5335141744387192</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5333670001299314</v>
+        <v>0.5333670001299298</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5338840224206284</v>
+        <v>0.5338840224206293</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5333670001299314</v>
+        <v>0.5333670001299298</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5333670001299314</v>
+        <v>0.5333670001299298</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5333670001299314</v>
+        <v>0.5333670001299298</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5948421360649253</v>
+        <v>0.5948421360649256</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9204113996034919</v>
+        <v>0.9204113996034943</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9872391198765198</v>
+        <v>0.9872391198765218</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8315128439041946</v>
+        <v>0.8315128439041963</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6056455477046109</v>
+        <v>0.605645547704611</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9199943765131664</v>
+        <v>0.9199943765131666</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9198472022043532</v>
+        <v>0.9198472022043537</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9203642244950768</v>
+        <v>0.9203642244950765</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9199110749746447</v>
+        <v>0.9199110749746459</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5888050001077253</v>
+        <v>0.5888050001077247</v>
       </c>
       <c r="L6" t="n">
-        <v>1.25934217023181</v>
+        <v>1.259342170231813</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.609862027412146</v>
+        <v>3.609862027412149</v>
       </c>
       <c r="C7" t="n">
-        <v>4.585657795974373</v>
+        <v>4.58565779597437</v>
       </c>
       <c r="D7" t="n">
-        <v>4.585140695944692</v>
+        <v>4.585140695944696</v>
       </c>
       <c r="E7" t="n">
-        <v>5.711107969243982</v>
+        <v>5.711107969243986</v>
       </c>
       <c r="F7" t="n">
-        <v>4.58565719565097</v>
+        <v>4.585657195650964</v>
       </c>
       <c r="G7" t="n">
-        <v>4.585287947992466</v>
+        <v>4.585287947992467</v>
       </c>
       <c r="H7" t="n">
-        <v>4.585140773683675</v>
+        <v>4.585140773683679</v>
       </c>
       <c r="I7" t="n">
-        <v>4.585657795974373</v>
+        <v>4.58565779597437</v>
       </c>
       <c r="J7" t="n">
-        <v>4.585140773683675</v>
+        <v>4.585140773683679</v>
       </c>
       <c r="K7" t="n">
-        <v>3.357090765635856</v>
+        <v>4.020060405182281</v>
       </c>
       <c r="L7" t="n">
-        <v>4.585140773683675</v>
+        <v>4.585140773683679</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1263338467248756</v>
+        <v>0.1263338467248824</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.001383743702258848</v>
+        <v>-0.001383743702258953</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06542128041424634</v>
+        <v>0.06542128041424598</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.001383743702258848</v>
+        <v>-0.001383743702258953</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.001383743702258848</v>
+        <v>-0.001383743702258953</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.04182941074572051</v>
+        <v>-0.04182941074571987</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.06255020930605802</v>
+        <v>-0.06255020930605829</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.001383743702258848</v>
+        <v>-0.001383743702258953</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00296767047662938</v>
+        <v>0.002967670476629723</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08320971260854575</v>
+        <v>0.0832097126085459</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.9701730720139548</v>
+        <v>-0.9701730720139558</v>
       </c>
     </row>
     <row r="9">
@@ -795,34 +795,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1667675943895592</v>
+        <v>0.166767594389559</v>
       </c>
       <c r="C9" t="n">
-        <v>0.137687470141777</v>
+        <v>0.1376874701417771</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1419618026248571</v>
+        <v>0.1419618026248573</v>
       </c>
       <c r="E9" t="n">
-        <v>0.137687470141777</v>
+        <v>0.1376874701417771</v>
       </c>
       <c r="F9" t="n">
-        <v>0.137687470141777</v>
+        <v>0.1376874701417771</v>
       </c>
       <c r="G9" t="n">
-        <v>0.09838358379481786</v>
+        <v>0.09838358379481844</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09007856925249623</v>
+        <v>0.09007856925249616</v>
       </c>
       <c r="I9" t="n">
-        <v>0.137687470141777</v>
+        <v>0.1376874701417771</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1165956129310424</v>
+        <v>0.1165956129310425</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1492094639417721</v>
+        <v>0.149209463941772</v>
       </c>
       <c r="L9" t="n">
         <v>-0.2789610159703704</v>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7118535288306267</v>
+        <v>0.7118535288306241</v>
       </c>
       <c r="C2" t="n">
-        <v>6.655692650504918</v>
+        <v>6.655692650504908</v>
       </c>
       <c r="D2" t="n">
-        <v>2.820634643327073</v>
+        <v>2.820634643327078</v>
       </c>
       <c r="E2" t="n">
-        <v>6.655692650504918</v>
+        <v>6.655692650504908</v>
       </c>
       <c r="F2" t="n">
-        <v>6.655692650504918</v>
+        <v>6.655692650504908</v>
       </c>
       <c r="G2" t="n">
-        <v>7.288786600455413</v>
+        <v>7.288786600455305</v>
       </c>
       <c r="H2" t="n">
         <v>12.91212733602356</v>
       </c>
       <c r="I2" t="n">
-        <v>6.655692650504918</v>
+        <v>6.655692650504908</v>
       </c>
       <c r="J2" t="n">
-        <v>5.065990580515674</v>
+        <v>5.065990580515678</v>
       </c>
       <c r="K2" t="n">
-        <v>1.799225528863999</v>
+        <v>1.799225528864002</v>
       </c>
       <c r="L2" t="n">
-        <v>9.159935703445125</v>
+        <v>5.164481121185355</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1145712481990986</v>
+        <v>0.1145712481990981</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1157740130120048</v>
+        <v>0.1157740130120039</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1145712481990986</v>
+        <v>0.1145712481990981</v>
       </c>
       <c r="E3" t="n">
-        <v>0.116341936075573</v>
+        <v>0.1163419360755719</v>
       </c>
       <c r="F3" t="n">
-        <v>0.116341936075573</v>
+        <v>0.116341936075572</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1147075538157965</v>
+        <v>0.1147075538157962</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1145712481990986</v>
+        <v>0.1145712481990981</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1150171810686173</v>
+        <v>0.1150171810686164</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1145712481990986</v>
+        <v>0.1145712481990981</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1145712481990986</v>
+        <v>0.1145712481990981</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1145712481990986</v>
+        <v>0.1145712481990981</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.71266880094448</v>
+        <v>76.71266880094456</v>
       </c>
       <c r="C4" t="n">
-        <v>6.393631814616912</v>
+        <v>6.39363181461691</v>
       </c>
       <c r="D4" t="n">
-        <v>6.293882390700772</v>
+        <v>76.70396440073259</v>
       </c>
       <c r="E4" t="n">
-        <v>6.373020638388403</v>
+        <v>6.373020638388404</v>
       </c>
       <c r="F4" t="n">
-        <v>6.39435720273474</v>
+        <v>6.394357202734737</v>
       </c>
       <c r="G4" t="n">
-        <v>76.71280510656122</v>
+        <v>6.309662431009874</v>
       </c>
       <c r="H4" t="n">
-        <v>76.70350266186426</v>
+        <v>76.70350266186414</v>
       </c>
       <c r="I4" t="n">
-        <v>6.309972058262713</v>
+        <v>6.30997205826271</v>
       </c>
       <c r="J4" t="n">
         <v>76.70487661142803</v>
       </c>
       <c r="K4" t="n">
-        <v>6.210976313201616</v>
+        <v>6.21097631320161</v>
       </c>
       <c r="L4" t="n">
-        <v>6.301523920819234</v>
+        <v>6.301523920819232</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4564729133722897</v>
+        <v>0.4564729133722887</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4569188462418103</v>
+        <v>0.4569188462418082</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4564479264436372</v>
+        <v>0.4564479264436359</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4569069855778627</v>
+        <v>0.4569069855778612</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4569069855778627</v>
+        <v>0.4569069855778612</v>
       </c>
       <c r="G5" t="n">
-        <v>0.456609218988988</v>
+        <v>0.4566092189889868</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4564729133722897</v>
+        <v>0.4564729133722887</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4569188462418103</v>
+        <v>0.4569188462418082</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4564729133722897</v>
+        <v>0.4564729133722887</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4564729133722897</v>
+        <v>0.4564729133722887</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4564729133722897</v>
+        <v>0.4564729133722887</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5049580246660943</v>
+        <v>0.5049580246660916</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7807390583232833</v>
+        <v>0.7807390583232781</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8372960394462859</v>
+        <v>0.8372960394462834</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7054431074730199</v>
+        <v>0.7054431074730159</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5141371328314469</v>
+        <v>0.5141371328314448</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7803552087567701</v>
+        <v>0.7803552087567657</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7802189031400895</v>
+        <v>0.7802189031400867</v>
       </c>
       <c r="I6" t="n">
-        <v>0.780664836009591</v>
+        <v>0.7806648360095879</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7802729997487846</v>
+        <v>0.7802729997487807</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4998449125336706</v>
+        <v>0.4998449125336688</v>
       </c>
       <c r="L6" t="n">
-        <v>1.067751907606607</v>
+        <v>1.067751907606604</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.232140214137566</v>
+        <v>2.23214021413756</v>
       </c>
       <c r="C7" t="n">
-        <v>2.830055567786531</v>
+        <v>2.830055567786525</v>
       </c>
       <c r="D7" t="n">
-        <v>2.829609493587986</v>
+        <v>2.82960949358798</v>
       </c>
       <c r="E7" t="n">
-        <v>3.519521793887519</v>
+        <v>3.519521793887515</v>
       </c>
       <c r="F7" t="n">
-        <v>2.830055016328398</v>
+        <v>2.830055016328394</v>
       </c>
       <c r="G7" t="n">
-        <v>2.829745940533705</v>
+        <v>2.8297459405337</v>
       </c>
       <c r="H7" t="n">
-        <v>2.829609634917014</v>
+        <v>2.829609634917012</v>
       </c>
       <c r="I7" t="n">
-        <v>2.830055567786531</v>
+        <v>2.830055567786525</v>
       </c>
       <c r="J7" t="n">
-        <v>2.829609634917014</v>
+        <v>2.829609634917012</v>
       </c>
       <c r="K7" t="n">
-        <v>2.483433446631704</v>
+        <v>2.483433446631701</v>
       </c>
       <c r="L7" t="n">
-        <v>2.829609634917014</v>
+        <v>2.829609634917012</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1721194478490143</v>
+        <v>0.1721194478490138</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05434705816927187</v>
+        <v>0.05434705816927164</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1165527825626763</v>
+        <v>0.116552782562676</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05434705816927187</v>
+        <v>0.05434705816927164</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05434705816927187</v>
+        <v>0.05434705816927164</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004588838981103313</v>
+        <v>0.004588838981103498</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1095200301691666</v>
+        <v>-0.1095200301691669</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05434705816927187</v>
+        <v>0.05434705816927164</v>
       </c>
       <c r="J8" t="n">
-        <v>0.07039512462822864</v>
+        <v>0.07039512462822818</v>
       </c>
       <c r="K8" t="n">
-        <v>0.14252766794791</v>
+        <v>0.1425276679479096</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.02600370013967963</v>
+        <v>0.07765472176836023</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.178382609460309</v>
+        <v>0.1783826094603088</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1528032890046517</v>
+        <v>0.1528032890046519</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1557524918424427</v>
+        <v>0.1557524918424419</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1528032890046517</v>
+        <v>0.1528032890046519</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1528032890046517</v>
+        <v>0.1528032890046519</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1101990785857041</v>
+        <v>0.1101990785857036</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06394737487717582</v>
+        <v>0.06394737487717543</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1528032890046517</v>
+        <v>0.1528032890046519</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1369948831519553</v>
+        <v>0.1369948831519547</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1663323434294186</v>
+        <v>0.1663323434294181</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09784623639815485</v>
+        <v>0.09784623639815405</v>
       </c>
     </row>
   </sheetData>
@@ -1307,34 +1307,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.51258613069281</v>
+        <v>31.51258613069285</v>
       </c>
       <c r="C2" t="n">
-        <v>31.14700304910591</v>
+        <v>31.14700304910594</v>
       </c>
       <c r="D2" t="n">
-        <v>4.161346424092894</v>
+        <v>4.161346424092904</v>
       </c>
       <c r="E2" t="n">
-        <v>5.385823060346422</v>
+        <v>5.385823060346453</v>
       </c>
       <c r="F2" t="n">
-        <v>5.385823060346422</v>
+        <v>5.385823060346453</v>
       </c>
       <c r="G2" t="n">
-        <v>9.52874357937468</v>
+        <v>9.528743579374673</v>
       </c>
       <c r="H2" t="n">
         <v>11.78613593958424</v>
       </c>
       <c r="I2" t="n">
-        <v>5.385823060346422</v>
+        <v>5.385823060346453</v>
       </c>
       <c r="J2" t="n">
-        <v>7.272197841527305</v>
+        <v>7.272197841527317</v>
       </c>
       <c r="K2" t="n">
-        <v>3.576855571447755</v>
+        <v>3.576855571447788</v>
       </c>
       <c r="L2" t="n">
         <v>22.88219238623097</v>
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1384784270671002</v>
+        <v>0.1384784270671027</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1543650625339992</v>
+        <v>0.1543650625339987</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1384784270671002</v>
+        <v>0.1384784270671028</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1399521649656474</v>
+        <v>0.1399521649656471</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1399521649656474</v>
+        <v>0.1399521649656471</v>
       </c>
       <c r="G3" t="n">
-        <v>0.138484553398112</v>
+        <v>0.1384845533981114</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1384784270671002</v>
+        <v>0.1384784270671028</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1380877518516956</v>
+        <v>0.1380877518516942</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1384784270671001</v>
+        <v>0.1384784270671028</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1384784270671002</v>
+        <v>0.1384784270671028</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1384784270671002</v>
+        <v>0.1384784270671028</v>
       </c>
     </row>
     <row r="4">
@@ -1387,31 +1387,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>81.06373347234383</v>
+        <v>6.713773802921841</v>
       </c>
       <c r="C4" t="n">
-        <v>6.846811482937484</v>
+        <v>6.846811482937482</v>
       </c>
       <c r="D4" t="n">
-        <v>6.697795672400785</v>
+        <v>6.697796422192252</v>
       </c>
       <c r="E4" t="n">
-        <v>6.771269933863171</v>
+        <v>6.771269933863173</v>
       </c>
       <c r="F4" t="n">
-        <v>6.801045541566102</v>
+        <v>6.801045541566104</v>
       </c>
       <c r="G4" t="n">
-        <v>81.06373959867494</v>
+        <v>81.0637395986749</v>
       </c>
       <c r="H4" t="n">
-        <v>81.06014079130662</v>
+        <v>81.06014079130671</v>
       </c>
       <c r="I4" t="n">
-        <v>81.06334279712853</v>
+        <v>81.06334279712856</v>
       </c>
       <c r="J4" t="n">
-        <v>81.05922614823017</v>
+        <v>81.0592261482302</v>
       </c>
       <c r="K4" t="n">
         <v>6.611812573007168</v>
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5010376166168456</v>
+        <v>0.5010376166168492</v>
       </c>
       <c r="C5" t="n">
         <v>0.5023204149031725</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5010113859165989</v>
+        <v>0.5010113859166012</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5014795932909455</v>
+        <v>0.5014795932909457</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5014795932909455</v>
+        <v>0.5014795932909457</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5010437429478576</v>
+        <v>0.5010437429478581</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5010376166168456</v>
+        <v>0.5010376166168492</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5006469414014421</v>
+        <v>0.5006469414014416</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5010376166168456</v>
+        <v>0.5010376166168492</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5010376166168456</v>
+        <v>0.5010376166168492</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5010376166168456</v>
+        <v>0.5010376166168492</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5582012827884336</v>
+        <v>0.5582012827884353</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8566984653837947</v>
+        <v>0.8566984653851724</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9159734420130126</v>
+        <v>0.9159734420130122</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7738810168502049</v>
+        <v>0.7738810168502029</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5677160765136824</v>
+        <v>0.5677160765136821</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8545342644950044</v>
+        <v>0.8545342644950048</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8545281381641467</v>
+        <v>0.8545281381641456</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8541374629485883</v>
+        <v>0.8541374629485868</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8545863748298247</v>
+        <v>0.8545863748298248</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5526968593199442</v>
+        <v>0.5526968593199451</v>
       </c>
       <c r="L6" t="n">
-        <v>1.164066317004994</v>
+        <v>1.164066317004991</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.912316434754233</v>
+        <v>2.912316434754236</v>
       </c>
       <c r="C7" t="n">
-        <v>3.693619253980631</v>
+        <v>3.693619253980632</v>
       </c>
       <c r="D7" t="n">
-        <v>3.692336249129768</v>
+        <v>3.692336249129769</v>
       </c>
       <c r="E7" t="n">
-        <v>4.592071269113798</v>
+        <v>4.592071269113804</v>
       </c>
       <c r="F7" t="n">
-        <v>3.691945068715194</v>
+        <v>3.691945068715195</v>
       </c>
       <c r="G7" t="n">
         <v>3.692342582025328</v>
       </c>
       <c r="H7" t="n">
-        <v>3.692336455694308</v>
+        <v>3.692336455694306</v>
       </c>
       <c r="I7" t="n">
-        <v>3.691945780478898</v>
+        <v>3.691945780478899</v>
       </c>
       <c r="J7" t="n">
-        <v>3.692336455694308</v>
+        <v>3.692336455694306</v>
       </c>
       <c r="K7" t="n">
-        <v>2.710152069786762</v>
+        <v>3.240389705306613</v>
       </c>
       <c r="L7" t="n">
-        <v>3.692336455694308</v>
+        <v>3.692336455694306</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.5159576527335726</v>
+        <v>-0.5159576527335724</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.4736856320672792</v>
+        <v>-0.4736856320672789</v>
       </c>
       <c r="D8" t="n">
-        <v>0.125548292154608</v>
+        <v>0.1255482921546076</v>
       </c>
       <c r="E8" t="n">
-        <v>0.103304376963091</v>
+        <v>0.1033043769630915</v>
       </c>
       <c r="F8" t="n">
-        <v>0.103304376963091</v>
+        <v>0.1033043769630915</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.01982907376810075</v>
+        <v>-0.01982907376810003</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.01884904215593426</v>
+        <v>-0.01884904215593347</v>
       </c>
       <c r="I8" t="n">
-        <v>0.103304376963091</v>
+        <v>0.1033043769630915</v>
       </c>
       <c r="J8" t="n">
-        <v>0.08562074474926613</v>
+        <v>0.08562074474926556</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1436105725870181</v>
+        <v>0.1436105725870183</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2609662896058105</v>
+        <v>-0.2609662896058104</v>
       </c>
     </row>
     <row r="9">
@@ -1587,13 +1587,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.1013064032292416</v>
+        <v>-0.1013064032292409</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.06318668751478432</v>
+        <v>-0.0631866875147858</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1780579855020234</v>
+        <v>0.1780579855020243</v>
       </c>
       <c r="E9" t="n">
         <v>0.1717686551815937</v>
@@ -1602,22 +1602,22 @@
         <v>0.1717686551815937</v>
       </c>
       <c r="G9" t="n">
-        <v>0.10289528121478</v>
+        <v>0.1028952812147804</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1194640290876007</v>
+        <v>0.1194640290876019</v>
       </c>
       <c r="I9" t="n">
         <v>0.1717686551815937</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1754783024297609</v>
+        <v>0.175478302429762</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1878514825645768</v>
+        <v>0.1878514825645781</v>
       </c>
       <c r="L9" t="n">
-        <v>0.006478266012904592</v>
+        <v>0.006478266012904948</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26.8762483719977</v>
+        <v>26.87624837199768</v>
       </c>
       <c r="C2" t="n">
-        <v>25.76209792933404</v>
+        <v>25.76209792933399</v>
       </c>
       <c r="D2" t="n">
-        <v>3.433094723222052</v>
+        <v>3.433094723222047</v>
       </c>
       <c r="E2" t="n">
-        <v>3.859926473209595</v>
+        <v>3.859926473209583</v>
       </c>
       <c r="F2" t="n">
-        <v>3.859926473209595</v>
+        <v>3.859926473209583</v>
       </c>
       <c r="G2" t="n">
-        <v>7.294177192859975</v>
+        <v>7.294177192859855</v>
       </c>
       <c r="H2" t="n">
-        <v>8.759883420382838</v>
+        <v>8.759883420382835</v>
       </c>
       <c r="I2" t="n">
-        <v>3.859926473209595</v>
+        <v>3.859926473209583</v>
       </c>
       <c r="J2" t="n">
-        <v>5.035907294438378</v>
+        <v>5.035907294438374</v>
       </c>
       <c r="K2" t="n">
-        <v>2.459873347612433</v>
+        <v>2.459873347612426</v>
       </c>
       <c r="L2" t="n">
-        <v>15.47557977994029</v>
+        <v>15.47557977994028</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1327651491708669</v>
+        <v>0.1327651491708629</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1446769134324144</v>
+        <v>0.1446769134324142</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1327651491708669</v>
+        <v>0.1327651491708629</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1492253812475908</v>
+        <v>0.14922538124759</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1492253812475907</v>
+        <v>0.1492253812475904</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1328077448277207</v>
+        <v>0.1328077448277189</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1327651491708669</v>
+        <v>0.1327651491708629</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1325999138544271</v>
+        <v>0.1325999138544267</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1327651491708669</v>
+        <v>0.1327651491708629</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1327651491708669</v>
+        <v>0.1327651491708629</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1327651491708669</v>
+        <v>0.1327651491708629</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.76578189773774</v>
+        <v>76.76578189773775</v>
       </c>
       <c r="C4" t="n">
-        <v>6.473198922361664</v>
+        <v>6.473198922361655</v>
       </c>
       <c r="D4" t="n">
-        <v>6.33814619505949</v>
+        <v>76.76347942331797</v>
       </c>
       <c r="E4" t="n">
-        <v>6.409329729042335</v>
+        <v>6.409329729042336</v>
       </c>
       <c r="F4" t="n">
-        <v>6.435575107539367</v>
+        <v>6.435575107539365</v>
       </c>
       <c r="G4" t="n">
-        <v>6.35120909236147</v>
+        <v>6.351209092361463</v>
       </c>
       <c r="H4" t="n">
-        <v>76.76718094209852</v>
+        <v>76.76718094209853</v>
       </c>
       <c r="I4" t="n">
-        <v>6.351001261388152</v>
+        <v>6.35100126138815</v>
       </c>
       <c r="J4" t="n">
-        <v>6.358736332975113</v>
+        <v>6.358736332975106</v>
       </c>
       <c r="K4" t="n">
-        <v>6.255937354030816</v>
+        <v>6.25593735403081</v>
       </c>
       <c r="L4" t="n">
-        <v>6.346755004634744</v>
+        <v>6.346755004634733</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4782484487262397</v>
+        <v>0.4782484487262416</v>
       </c>
       <c r="C5" t="n">
         <v>0.4795085285769677</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4782237286953436</v>
+        <v>0.4782237286953454</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4830857920777322</v>
+        <v>0.483085792077732</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4830857920777322</v>
+        <v>0.483085792077732</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4782910443830964</v>
+        <v>0.478291044383098</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4782484487262397</v>
+        <v>0.4782484487262416</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4780832134098033</v>
+        <v>0.4780832134098031</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4782484487262397</v>
+        <v>0.4782484487262416</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4782484487262397</v>
+        <v>0.4782484487262416</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4782484487262397</v>
+        <v>0.4782484487262416</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5302104860085231</v>
+        <v>0.5302104860085178</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8189715355371502</v>
+        <v>0.8189715355392454</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8714485973338003</v>
+        <v>0.8714485973337972</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7397271898901399</v>
+        <v>0.7397271898901379</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5420032902093852</v>
+        <v>0.5420032902093844</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8128855164629434</v>
+        <v>0.8128855164629425</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8128429208068039</v>
+        <v>0.8128429208067981</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8126776854896487</v>
+        <v>0.8126776854896478</v>
       </c>
       <c r="J6" t="n">
-        <v>0.81289846608464</v>
+        <v>0.8128984660846397</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5249604434354912</v>
+        <v>0.5249604434354841</v>
       </c>
       <c r="L6" t="n">
-        <v>1.108076132208396</v>
+        <v>1.108076132208389</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.453714945889834</v>
+        <v>2.453714945889832</v>
       </c>
       <c r="C7" t="n">
-        <v>3.109946878782846</v>
+        <v>3.109946878782843</v>
       </c>
       <c r="D7" t="n">
-        <v>3.108686642004115</v>
+        <v>3.108686642004112</v>
       </c>
       <c r="E7" t="n">
-        <v>3.864344306151412</v>
+        <v>3.86434430615141</v>
       </c>
       <c r="F7" t="n">
-        <v>3.108520966520038</v>
+        <v>3.108520966520036</v>
       </c>
       <c r="G7" t="n">
-        <v>3.108729394588971</v>
+        <v>3.108729394588965</v>
       </c>
       <c r="H7" t="n">
-        <v>3.108686798932117</v>
+        <v>3.108686798932111</v>
       </c>
       <c r="I7" t="n">
-        <v>3.108521563615676</v>
+        <v>3.108521563615674</v>
       </c>
       <c r="J7" t="n">
-        <v>3.108686798932117</v>
+        <v>3.108686798932111</v>
       </c>
       <c r="K7" t="n">
-        <v>2.729193469003377</v>
+        <v>2.729193469003372</v>
       </c>
       <c r="L7" t="n">
-        <v>3.108686798932117</v>
+        <v>3.108686798932111</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.4541500058592514</v>
+        <v>-0.4541500058592498</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.3946561694398145</v>
+        <v>-0.3946561694398132</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1341980926772324</v>
+        <v>0.1341980926772337</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1355986892530425</v>
+        <v>0.1355986892530429</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1355986892530425</v>
+        <v>0.1355986892530429</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01790183161302281</v>
+        <v>0.01790183161302218</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02912395165459511</v>
+        <v>0.02912395165459311</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1355986892530425</v>
+        <v>0.1355986892530429</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1355971541960872</v>
+        <v>0.1355971541960847</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1738196232214941</v>
+        <v>0.1738196232214909</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1285058707677878</v>
+        <v>-0.1285058707677892</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.08094786093439256</v>
+        <v>-0.08094786093439418</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.03655390794187886</v>
+        <v>-0.03655390794187766</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1794836066168654</v>
+        <v>0.1794836066168643</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1863277045237182</v>
+        <v>0.1863277045237186</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1863277045237182</v>
+        <v>0.1863277045237186</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1164378101339445</v>
+        <v>0.1164378101339422</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1368579479862884</v>
+        <v>0.1368579479862851</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1863277045237182</v>
+        <v>0.1863277045237186</v>
       </c>
       <c r="J9" t="n">
         <v>0.1999665151467923</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2046448448180998</v>
+        <v>0.2046448448180988</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0613913231723856</v>
+        <v>0.06139132317238408</v>
       </c>
     </row>
   </sheetData>
@@ -2099,34 +2099,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24.73508748989611</v>
+        <v>24.7350874898961</v>
       </c>
       <c r="C2" t="n">
-        <v>23.06506662457045</v>
+        <v>23.06506662457047</v>
       </c>
       <c r="D2" t="n">
-        <v>2.994876042036971</v>
+        <v>2.994876042036964</v>
       </c>
       <c r="E2" t="n">
-        <v>2.860892284464406</v>
+        <v>2.860892284464398</v>
       </c>
       <c r="F2" t="n">
-        <v>2.860892284464406</v>
+        <v>2.860892284464398</v>
       </c>
       <c r="G2" t="n">
-        <v>6.178776269820466</v>
+        <v>6.178776269820382</v>
       </c>
       <c r="H2" t="n">
-        <v>6.953570353833198</v>
+        <v>6.953570353833189</v>
       </c>
       <c r="I2" t="n">
-        <v>2.860892284464406</v>
+        <v>2.860892284464398</v>
       </c>
       <c r="J2" t="n">
-        <v>3.738696769585227</v>
+        <v>3.738696769585222</v>
       </c>
       <c r="K2" t="n">
-        <v>1.904947391413661</v>
+        <v>1.904947391413664</v>
       </c>
       <c r="L2" t="n">
         <v>11.3768823596719</v>
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1297091303454101</v>
+        <v>0.1297091303454125</v>
       </c>
       <c r="C3" t="n">
-        <v>0.139954447419614</v>
+        <v>0.1399544474196139</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1297091303454101</v>
+        <v>0.1297091303454125</v>
       </c>
       <c r="E3" t="n">
-        <v>0.148564195503168</v>
+        <v>0.1485641955031673</v>
       </c>
       <c r="F3" t="n">
-        <v>0.148564195503168</v>
+        <v>0.1485641955031673</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1297552238740855</v>
+        <v>0.1297552238740875</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1297091303454101</v>
+        <v>0.1297091303454125</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1295701762468536</v>
+        <v>0.1295701762468544</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1297091303454101</v>
+        <v>0.1297091303454125</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1297091303454101</v>
+        <v>0.1297091303454125</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1297091303454101</v>
+        <v>0.1297091303454125</v>
       </c>
     </row>
     <row r="4">
@@ -2179,34 +2179,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.75003124969351</v>
+        <v>6.340918053472512</v>
       </c>
       <c r="C4" t="n">
-        <v>6.459958837214308</v>
+        <v>6.45995883721428</v>
       </c>
       <c r="D4" t="n">
-        <v>6.329307927604691</v>
+        <v>6.32930792760466</v>
       </c>
       <c r="E4" t="n">
-        <v>6.400273928905201</v>
+        <v>6.400273928905198</v>
       </c>
       <c r="F4" t="n">
         <v>6.425929326720243</v>
       </c>
       <c r="G4" t="n">
-        <v>6.340964147001187</v>
+        <v>76.75007734322223</v>
       </c>
       <c r="H4" t="n">
-        <v>76.75392831738583</v>
+        <v>76.75392831738586</v>
       </c>
       <c r="I4" t="n">
-        <v>6.340779099373967</v>
+        <v>76.749892295595</v>
       </c>
       <c r="J4" t="n">
-        <v>6.348446454917257</v>
+        <v>76.74924894087522</v>
       </c>
       <c r="K4" t="n">
-        <v>6.246738888559149</v>
+        <v>6.246738888559154</v>
       </c>
       <c r="L4" t="n">
         <v>6.335940129756301</v>
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4732848649879602</v>
+        <v>0.4732848649879643</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4744993475914962</v>
+        <v>0.4744993475914952</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4732595213872449</v>
+        <v>0.4732595213872459</v>
       </c>
       <c r="E5" t="n">
-        <v>0.479050229728489</v>
+        <v>0.4790502297284879</v>
       </c>
       <c r="F5" t="n">
-        <v>0.479050229728489</v>
+        <v>0.4790502297284879</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4733309585166404</v>
+        <v>0.4733309585166389</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4732848649879602</v>
+        <v>0.4732848649879643</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4731459108894076</v>
+        <v>0.4731459108894057</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4732848649879602</v>
+        <v>0.4732848649879643</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4732848649879602</v>
+        <v>0.4732848649879643</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4732848649879602</v>
+        <v>0.4732848649879643</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5232147970132096</v>
+        <v>0.5232147970132054</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8107589173253071</v>
+        <v>0.8107589173220715</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8619954248724249</v>
+        <v>0.8619954248724255</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7320499877301119</v>
+        <v>0.7320499877301117</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5355076663877288</v>
+        <v>0.5355076663877283</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8038579004793635</v>
+        <v>0.8038579004793617</v>
       </c>
       <c r="H6" t="n">
-        <v>0.803811806952029</v>
+        <v>0.8038118069520315</v>
       </c>
       <c r="I6" t="n">
-        <v>0.80367285285213</v>
+        <v>0.803672852852129</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8038669521899865</v>
+        <v>0.8038669521899874</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5180025635020491</v>
+        <v>0.5180025635020511</v>
       </c>
       <c r="L6" t="n">
-        <v>1.096918846871884</v>
+        <v>1.096918846871885</v>
       </c>
     </row>
     <row r="7">
@@ -2302,34 +2302,34 @@
         <v>2.214015271017563</v>
       </c>
       <c r="C7" t="n">
-        <v>2.804960187616993</v>
+        <v>2.80496018761699</v>
       </c>
       <c r="D7" t="n">
-        <v>2.803745572552451</v>
+        <v>2.80374557255245</v>
       </c>
       <c r="E7" t="n">
-        <v>3.484142359889756</v>
+        <v>3.48414235988975</v>
       </c>
       <c r="F7" t="n">
-        <v>2.803606200666808</v>
+        <v>2.803606200666807</v>
       </c>
       <c r="G7" t="n">
-        <v>2.803791798542151</v>
+        <v>2.803791798542144</v>
       </c>
       <c r="H7" t="n">
-        <v>2.803745705013463</v>
+        <v>2.803745705013462</v>
       </c>
       <c r="I7" t="n">
-        <v>2.803606750914905</v>
+        <v>2.803606750914902</v>
       </c>
       <c r="J7" t="n">
-        <v>2.803745705013463</v>
+        <v>2.803745705013462</v>
       </c>
       <c r="K7" t="n">
-        <v>2.448190641591651</v>
+        <v>2.061169856433697</v>
       </c>
       <c r="L7" t="n">
-        <v>2.803745705013463</v>
+        <v>2.803745705013462</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.4111604507785614</v>
+        <v>-0.4111604507785594</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.3404578193460724</v>
+        <v>-0.3404578193460725</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1383664852721187</v>
+        <v>0.1383664852721207</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1554609700163893</v>
+        <v>0.1554609700163896</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1554609700163893</v>
+        <v>0.1554609700163896</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03864698058137238</v>
+        <v>0.03864698058137375</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06148078385761695</v>
+        <v>0.06148078385761965</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1554609700163893</v>
+        <v>0.1554609700163896</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1643355279341238</v>
+        <v>0.1643355279341265</v>
       </c>
       <c r="K8" t="n">
         <v>0.1847667552433436</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.04546115484777394</v>
+        <v>-0.04546115484777272</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.06779081350421406</v>
+        <v>-0.06779081350421287</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.02009345548732214</v>
+        <v>-0.02009345548732249</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1774756437225908</v>
+        <v>0.1774756437225935</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1920127179835844</v>
+        <v>0.1920127179835845</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1920127179835844</v>
+        <v>0.1920127179835845</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1216664462795093</v>
+        <v>0.1216664462795108</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1462951288578494</v>
+        <v>0.1462951288578512</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1920127179835844</v>
+        <v>0.1920127179835845</v>
       </c>
       <c r="J9" t="n">
-        <v>0.210959569733578</v>
+        <v>0.2109595697335789</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2076984294631829</v>
+        <v>0.207698429463184</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09323227821083886</v>
+        <v>0.09323227821083882</v>
       </c>
     </row>
   </sheetData>
@@ -2498,31 +2498,31 @@
         <v>30.81470464908816</v>
       </c>
       <c r="C2" t="n">
-        <v>35.08388161014174</v>
+        <v>35.08388161014172</v>
       </c>
       <c r="D2" t="n">
-        <v>3.295046119469539</v>
+        <v>3.29504611946955</v>
       </c>
       <c r="E2" t="n">
-        <v>4.805547517367093</v>
+        <v>4.805547517367105</v>
       </c>
       <c r="F2" t="n">
-        <v>4.805547517367093</v>
+        <v>4.805547517367105</v>
       </c>
       <c r="G2" t="n">
-        <v>8.732529400572679</v>
+        <v>8.732529400572673</v>
       </c>
       <c r="H2" t="n">
-        <v>15.17799135064064</v>
+        <v>15.17799135064065</v>
       </c>
       <c r="I2" t="n">
-        <v>4.805547517367093</v>
+        <v>4.805547517367105</v>
       </c>
       <c r="J2" t="n">
-        <v>7.555274227267769</v>
+        <v>7.555274227267759</v>
       </c>
       <c r="K2" t="n">
-        <v>3.134076738781787</v>
+        <v>3.134076738781784</v>
       </c>
       <c r="L2" t="n">
         <v>23.49723536925034</v>
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1462122988859541</v>
+        <v>0.1462122988859539</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1638606180693068</v>
+        <v>0.163860618069307</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1462122988859541</v>
+        <v>0.1462122988859539</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1719007804427292</v>
+        <v>0.1719007804427276</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1719007804427282</v>
+        <v>0.1719007804427277</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1462581816832836</v>
+        <v>0.1462581816832832</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1462122988859541</v>
+        <v>0.1462122988859539</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1460594071208096</v>
+        <v>0.1460594071208081</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1462122988859541</v>
+        <v>0.1462122988859539</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1462122988859541</v>
+        <v>0.1462122988859539</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1462122988859541</v>
+        <v>0.1462122988859539</v>
       </c>
     </row>
     <row r="4">
@@ -2575,34 +2575,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>81.07823525420623</v>
+        <v>6.726915301106686</v>
       </c>
       <c r="C4" t="n">
-        <v>6.868763560247993</v>
+        <v>6.868763560247989</v>
       </c>
       <c r="D4" t="n">
-        <v>6.710026533465082</v>
+        <v>6.710026533465078</v>
       </c>
       <c r="E4" t="n">
-        <v>6.78749868585743</v>
+        <v>6.78749868585744</v>
       </c>
       <c r="F4" t="n">
-        <v>6.815932200112884</v>
+        <v>6.815932200112885</v>
       </c>
       <c r="G4" t="n">
-        <v>6.726961183904013</v>
+        <v>6.726961183904008</v>
       </c>
       <c r="H4" t="n">
-        <v>81.07697134665206</v>
+        <v>81.07697134665209</v>
       </c>
       <c r="I4" t="n">
-        <v>81.07808236244107</v>
+        <v>6.726762409341567</v>
       </c>
       <c r="J4" t="n">
         <v>81.07650680287041</v>
       </c>
       <c r="K4" t="n">
-        <v>6.625292793614189</v>
+        <v>6.62529279361418</v>
       </c>
       <c r="L4" t="n">
         <v>6.723586492141632</v>
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5146954679153918</v>
+        <v>0.514695467915391</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5161574967846607</v>
+        <v>0.5161574967846597</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5146695440811647</v>
+        <v>0.5146695440811638</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5220454404022943</v>
+        <v>0.5220454404022923</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5220454404022943</v>
+        <v>0.5220454404022923</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5147413507127231</v>
+        <v>0.5147413507127223</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5146954679153918</v>
+        <v>0.514695467915391</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5145425761502469</v>
+        <v>0.5145425761502462</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5146954679153918</v>
+        <v>0.514695467915391</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5146954679153918</v>
+        <v>0.514695467915391</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5146954679153918</v>
+        <v>0.514695467915391</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5718758024452714</v>
+        <v>0.5718758024452715</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8830143287801535</v>
+        <v>0.8830143287801513</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9369974908436615</v>
+        <v>0.9369974908436592</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7979181318466306</v>
+        <v>0.7979181318466292</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5858002597201953</v>
+        <v>0.5858002597201949</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8743358305695081</v>
+        <v>0.8743358305695063</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8742899477717486</v>
+        <v>0.8742899477717463</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8741370560070345</v>
+        <v>0.8741370560070312</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8743493807207341</v>
+        <v>0.8743493807207331</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5662583044457444</v>
+        <v>0.5662583044457435</v>
       </c>
       <c r="L6" t="n">
-        <v>1.190186809934958</v>
+        <v>1.190186809934954</v>
       </c>
     </row>
     <row r="7">
@@ -2695,34 +2695,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.912287153493611</v>
+        <v>2.912287153493612</v>
       </c>
       <c r="C7" t="n">
-        <v>3.69262893961945</v>
+        <v>3.692628939619451</v>
       </c>
       <c r="D7" t="n">
-        <v>3.691166626755368</v>
+        <v>3.69116662675537</v>
       </c>
       <c r="E7" t="n">
-        <v>4.589823522183215</v>
+        <v>4.589823522183217</v>
       </c>
       <c r="F7" t="n">
-        <v>3.691013246958823</v>
+        <v>3.691013246958822</v>
       </c>
       <c r="G7" t="n">
-        <v>3.691212793547513</v>
+        <v>3.691212793547515</v>
       </c>
       <c r="H7" t="n">
         <v>3.691166910750182</v>
       </c>
       <c r="I7" t="n">
-        <v>3.691014018985045</v>
+        <v>3.691014018985042</v>
       </c>
       <c r="J7" t="n">
         <v>3.691166910750182</v>
       </c>
       <c r="K7" t="n">
-        <v>2.710418340424767</v>
+        <v>2.710418340424769</v>
       </c>
       <c r="L7" t="n">
         <v>3.691166910750182</v>
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.4688273106779927</v>
+        <v>-0.4688273106779933</v>
       </c>
       <c r="C8" t="n">
         <v>-0.5439634024872804</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1531359023831039</v>
+        <v>0.153135902383104</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1331790276453614</v>
+        <v>0.1331790276453611</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1331790276453614</v>
+        <v>0.1331790276453611</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009608488110972459</v>
+        <v>0.009608488110972003</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.08042223661382258</v>
+        <v>-0.08042223661382299</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1331790276453614</v>
+        <v>0.1331790276453611</v>
       </c>
       <c r="J8" t="n">
-        <v>0.09701789943959677</v>
+        <v>0.09701789943959702</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1755583540278204</v>
+        <v>0.1755583540278197</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2587399368448151</v>
+        <v>-0.2587399368448149</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.06391350029450826</v>
+        <v>-0.06391350029450829</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0812599724797787</v>
+        <v>-0.08125997247977886</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1936815479949685</v>
+        <v>0.1936815479949686</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1935404486000528</v>
+        <v>0.1935404486000532</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1935404486000528</v>
+        <v>0.1935404486000532</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1215858620661993</v>
+        <v>0.1215858620661994</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09883773083182469</v>
+        <v>0.09883773083182464</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1935404486000528</v>
+        <v>0.1935404486000532</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1903072562173786</v>
+        <v>0.1903072562173787</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2134399953557467</v>
+        <v>0.213439995355745</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01579807968081714</v>
+        <v>0.0157980796808169</v>
       </c>
     </row>
   </sheetData>
@@ -2891,34 +2891,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.24284021624035</v>
+        <v>23.24284021624032</v>
       </c>
       <c r="C2" t="n">
-        <v>25.94408674137237</v>
+        <v>25.94408674137241</v>
       </c>
       <c r="D2" t="n">
-        <v>2.051989558327121</v>
+        <v>2.051989558327118</v>
       </c>
       <c r="E2" t="n">
-        <v>3.292189369532512</v>
+        <v>3.292189369532539</v>
       </c>
       <c r="F2" t="n">
-        <v>3.292189369532512</v>
+        <v>3.292189369532539</v>
       </c>
       <c r="G2" t="n">
-        <v>5.910601428314053</v>
+        <v>5.91060142831403</v>
       </c>
       <c r="H2" t="n">
         <v>16.9438948403348</v>
       </c>
       <c r="I2" t="n">
-        <v>3.292189369532512</v>
+        <v>3.292189369532539</v>
       </c>
       <c r="J2" t="n">
-        <v>4.51907475463289</v>
+        <v>4.519074754632887</v>
       </c>
       <c r="K2" t="n">
-        <v>1.854704315786541</v>
+        <v>1.854704315786538</v>
       </c>
       <c r="L2" t="n">
         <v>12.49280973234907</v>
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1358554524261276</v>
+        <v>0.1358554524261277</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1505539702387418</v>
+        <v>0.1505539702387408</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1358554524261276</v>
+        <v>0.1358554524261277</v>
       </c>
       <c r="E3" t="n">
-        <v>0.167611391058879</v>
+        <v>0.1676113910588778</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1676113910588793</v>
+        <v>0.1676113910588778</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1359437110230356</v>
+        <v>0.1359437110230343</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1358554524261276</v>
+        <v>0.1358554524261277</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1359726367049819</v>
+        <v>0.1359726367049806</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1358554524261276</v>
+        <v>0.1358554524261277</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1358554524261276</v>
+        <v>0.1358554524261277</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1358554524261276</v>
+        <v>0.1358554524261277</v>
       </c>
     </row>
     <row r="4">
@@ -2971,34 +2971,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.352210650780772</v>
+        <v>6.35221065078077</v>
       </c>
       <c r="C4" t="n">
-        <v>6.477985774789695</v>
+        <v>6.477985774789696</v>
       </c>
       <c r="D4" t="n">
-        <v>76.76119537022092</v>
+        <v>6.339004487223415</v>
       </c>
       <c r="E4" t="n">
-        <v>6.414504768154182</v>
+        <v>6.414504768154179</v>
       </c>
       <c r="F4" t="n">
-        <v>6.438932034782992</v>
+        <v>6.438932034782988</v>
       </c>
       <c r="G4" t="n">
-        <v>6.35229890937766</v>
+        <v>76.761811454628</v>
       </c>
       <c r="H4" t="n">
-        <v>76.77233806941386</v>
+        <v>76.77233806941382</v>
       </c>
       <c r="I4" t="n">
-        <v>6.352327835059629</v>
+        <v>76.76184038030988</v>
       </c>
       <c r="J4" t="n">
-        <v>6.36072201140661</v>
+        <v>6.360722011406611</v>
       </c>
       <c r="K4" t="n">
-        <v>6.258889439512552</v>
+        <v>6.258889439512555</v>
       </c>
       <c r="L4" t="n">
         <v>6.348030132420071</v>
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4825823413820272</v>
+        <v>0.4825823413820206</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4839288784260773</v>
+        <v>0.4839288784260701</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4825569195392589</v>
+        <v>0.4825569195392526</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4918811563242266</v>
+        <v>0.4918811563242201</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4918811563242266</v>
+        <v>0.4918811563242201</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4826705999789361</v>
+        <v>0.4826705999789296</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4825823413820272</v>
+        <v>0.4825823413820206</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4826995256608823</v>
+        <v>0.4826995256608753</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4825823413820272</v>
+        <v>0.4825823413820206</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4825823413820272</v>
+        <v>0.4825823413820206</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4825823413820272</v>
+        <v>0.4825823413820206</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5315982614028685</v>
+        <v>0.5315982614028666</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8243448929897096</v>
+        <v>0.8243448929897068</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8727198602742163</v>
+        <v>0.8727198602742119</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7449000083129631</v>
+        <v>0.7449000083129587</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5461638522753588</v>
+        <v>0.5461638522753557</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8142224526873466</v>
+        <v>0.8142224526873427</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8141341940927361</v>
+        <v>0.8141341940927321</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8142513783692931</v>
+        <v>0.8142513783692895</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8141897203775452</v>
+        <v>0.8141897203775412</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5263500114099864</v>
+        <v>0.5263500114099834</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1092666009445</v>
+        <v>1.109266600944493</v>
       </c>
     </row>
     <row r="7">
@@ -3094,34 +3094,34 @@
         <v>2.432676107765424</v>
       </c>
       <c r="C7" t="n">
-        <v>3.082750428141297</v>
+        <v>3.082750428141293</v>
       </c>
       <c r="D7" t="n">
-        <v>3.081403607167103</v>
+        <v>3.0814036071671</v>
       </c>
       <c r="E7" t="n">
-        <v>3.830138065749113</v>
+        <v>3.830138065749106</v>
       </c>
       <c r="F7" t="n">
-        <v>3.081520387636248</v>
+        <v>3.081520387636246</v>
       </c>
       <c r="G7" t="n">
-        <v>3.081492149694158</v>
+        <v>3.081492149694153</v>
       </c>
       <c r="H7" t="n">
-        <v>3.081403891097249</v>
+        <v>3.081403891097248</v>
       </c>
       <c r="I7" t="n">
-        <v>3.081521075376096</v>
+        <v>3.081521075376093</v>
       </c>
       <c r="J7" t="n">
-        <v>3.081403891097249</v>
+        <v>3.081403891097248</v>
       </c>
       <c r="K7" t="n">
-        <v>2.70552834626449</v>
+        <v>2.264539887971486</v>
       </c>
       <c r="L7" t="n">
-        <v>3.081403891097249</v>
+        <v>3.081403891097248</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.3428932635610039</v>
+        <v>-0.3428932635610045</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.3960516272805254</v>
+        <v>-0.3960516272805265</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1680661343369831</v>
+        <v>0.1680661343369822</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1555539752870355</v>
+        <v>0.1555539752870347</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1555539752870355</v>
+        <v>0.1555539752870347</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0536343044320802</v>
+        <v>0.05363430443208005</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1468090116485305</v>
+        <v>-0.1468090116485309</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1555539752870355</v>
+        <v>0.1555539752870347</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1542688220903085</v>
+        <v>0.1542688220903076</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1984232892821598</v>
+        <v>0.1984232892821615</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.06121554430476726</v>
+        <v>-0.06121554430476787</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.02097284354423421</v>
+        <v>-0.02097284354423488</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.03540742496684633</v>
+        <v>-0.03540742496684678</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1934028123653194</v>
+        <v>0.1934028123653185</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1980909312248452</v>
+        <v>0.1980909312248446</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1980909312248452</v>
+        <v>0.1980909312248446</v>
       </c>
       <c r="G9" t="n">
-        <v>0.132725759311503</v>
+        <v>0.1327257593115027</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06549129591672806</v>
+        <v>0.06549129591672745</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1980909312248452</v>
+        <v>0.1980909312248446</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2114609055257833</v>
+        <v>0.2114609055257823</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2204055109376309</v>
+        <v>0.2204055109376331</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09130364868555162</v>
+        <v>0.09130364868555098</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.23237525578736</v>
+        <v>18.23237525578735</v>
       </c>
       <c r="C2" t="n">
-        <v>18.46029996164139</v>
+        <v>18.4602999616414</v>
       </c>
       <c r="D2" t="n">
-        <v>1.955762135466063</v>
+        <v>1.955762135466061</v>
       </c>
       <c r="E2" t="n">
-        <v>2.228753001965684</v>
+        <v>2.228753001965636</v>
       </c>
       <c r="F2" t="n">
-        <v>2.228753001965684</v>
+        <v>2.228753001965636</v>
       </c>
       <c r="G2" t="n">
-        <v>4.284928090237127</v>
+        <v>4.284928090237054</v>
       </c>
       <c r="H2" t="n">
-        <v>12.2002251601855</v>
+        <v>12.20022516018549</v>
       </c>
       <c r="I2" t="n">
-        <v>2.228753001965684</v>
+        <v>2.228753001965636</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3174471797453</v>
+        <v>3.317447179745302</v>
       </c>
       <c r="K2" t="n">
-        <v>1.332616340614094</v>
+        <v>1.332616340614091</v>
       </c>
       <c r="L2" t="n">
-        <v>6.445622033449772</v>
+        <v>6.445622033449764</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1391335276045443</v>
+        <v>0.1391335276045439</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1596259300411805</v>
+        <v>0.1596259300411801</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1391335276045443</v>
+        <v>0.1391335276045439</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1611177525187248</v>
+        <v>0.1611177525187233</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1611177525187247</v>
+        <v>0.1611177525187233</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1392236609644559</v>
+        <v>0.1392236609644724</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1391335276045443</v>
+        <v>0.1391335276045439</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1392771244287614</v>
+        <v>0.1392771244287735</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1391335276045443</v>
+        <v>0.1391335276045439</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1391335276045443</v>
+        <v>0.1391335276045439</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1391335276045443</v>
+        <v>0.1391335276045439</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.74753729326974</v>
+        <v>76.7475372932697</v>
       </c>
       <c r="C4" t="n">
-        <v>6.458948571685501</v>
+        <v>6.458948571685505</v>
       </c>
       <c r="D4" t="n">
         <v>6.332126941167274</v>
       </c>
       <c r="E4" t="n">
-        <v>6.405191874601215</v>
+        <v>6.405191874601218</v>
       </c>
       <c r="F4" t="n">
-        <v>6.429499245541997</v>
+        <v>6.429499245542</v>
       </c>
       <c r="G4" t="n">
-        <v>76.74762742662942</v>
+        <v>76.74762742662938</v>
       </c>
       <c r="H4" t="n">
-        <v>76.76211893646385</v>
+        <v>76.76211893646382</v>
       </c>
       <c r="I4" t="n">
-        <v>6.342076803805957</v>
+        <v>6.342076803805953</v>
       </c>
       <c r="J4" t="n">
-        <v>76.74672674370466</v>
+        <v>76.74672674370463</v>
       </c>
       <c r="K4" t="n">
-        <v>6.251075060226365</v>
+        <v>6.251075060226354</v>
       </c>
       <c r="L4" t="n">
-        <v>6.337626322371247</v>
+        <v>6.337626322371244</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4816504379433343</v>
+        <v>0.4816504379433337</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4828111053386925</v>
+        <v>0.4828111053386916</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4816223378004009</v>
+        <v>0.4816223378004006</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4884067960851829</v>
+        <v>0.4884067960851813</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4884067960851829</v>
+        <v>0.4884067960851813</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4817405713032464</v>
+        <v>0.4817405713032454</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4816504379433343</v>
+        <v>0.4816504379433337</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4817940347675514</v>
+        <v>0.4817940347675495</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4816504379433343</v>
+        <v>0.4816504379433337</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4816504379433343</v>
+        <v>0.4816504379433337</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4816504379433343</v>
+        <v>0.4816504379433337</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5306957422698293</v>
+        <v>0.5306957422698289</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8209713771476428</v>
+        <v>0.8209713771476413</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8720142562721984</v>
+        <v>0.8720142562721964</v>
       </c>
       <c r="E6" t="n">
-        <v>0.741948904573318</v>
+        <v>0.7419489045733154</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5437620581097949</v>
+        <v>0.5437620581097922</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8134849044163213</v>
+        <v>0.8134849044163186</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8133947710598968</v>
+        <v>0.8133947710598952</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8135383678806269</v>
+        <v>0.8135383678806238</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8134503293100014</v>
+        <v>0.8134503293099994</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5254444626867592</v>
+        <v>0.5254444626867572</v>
       </c>
       <c r="L6" t="n">
-        <v>1.108697545347561</v>
+        <v>1.108697545347557</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.188809715128932</v>
+        <v>2.188809715128931</v>
       </c>
       <c r="C7" t="n">
-        <v>2.771576181157963</v>
+        <v>2.771576181157964</v>
       </c>
       <c r="D7" t="n">
         <v>2.770415310004593</v>
       </c>
       <c r="E7" t="n">
-        <v>3.441718969122904</v>
+        <v>3.441718969122903</v>
       </c>
       <c r="F7" t="n">
-        <v>2.770558537098838</v>
+        <v>2.77055853709884</v>
       </c>
       <c r="G7" t="n">
-        <v>2.770505647122526</v>
+        <v>2.770505647122525</v>
       </c>
       <c r="H7" t="n">
-        <v>2.770415513762604</v>
+        <v>2.770415513762603</v>
       </c>
       <c r="I7" t="n">
-        <v>2.770559110586829</v>
+        <v>2.770559110586828</v>
       </c>
       <c r="J7" t="n">
-        <v>2.770415513762604</v>
+        <v>2.770415513762603</v>
       </c>
       <c r="K7" t="n">
-        <v>2.433430744192417</v>
+        <v>2.419758854682204</v>
       </c>
       <c r="L7" t="n">
-        <v>2.770415513762604</v>
+        <v>2.770415513762603</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.2294268626238095</v>
+        <v>-0.2294268626238096</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2429941011833171</v>
+        <v>-0.2429941011833176</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1627812377070058</v>
+        <v>0.1627812377070055</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1725329820120479</v>
+        <v>0.1725329820120476</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1725329820120479</v>
+        <v>0.1725329820120476</v>
       </c>
       <c r="G8" t="n">
-        <v>0.08366710504076534</v>
+        <v>0.08366710504076506</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.05236313255967731</v>
+        <v>-0.05236313255967759</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1725329820120479</v>
+        <v>0.1725329820120476</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1813302611186214</v>
+        <v>0.1813302611186203</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2029632122863734</v>
+        <v>0.2029632122863698</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05687967600106586</v>
+        <v>0.05687967600106557</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02235459980814772</v>
+        <v>0.02235459980814735</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01272454213115431</v>
+        <v>0.01272454213115414</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1868402652810433</v>
+        <v>0.1868402652810426</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1999763558603616</v>
+        <v>0.1999763558603612</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1999763558603616</v>
+        <v>0.1999763558603612</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1400570894191691</v>
+        <v>0.1400570894191694</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09945354341936807</v>
+        <v>0.09945354341936766</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1999763558603616</v>
+        <v>0.1999763558603612</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2220189353214333</v>
+        <v>0.222018935321433</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2175481756682543</v>
+        <v>0.217548175668252</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1338385567445775</v>
+        <v>0.1338385567445773</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.28574012372845</v>
+        <v>30.28574012372843</v>
       </c>
       <c r="C2" t="n">
-        <v>34.44664993509611</v>
+        <v>34.44664993509616</v>
       </c>
       <c r="D2" t="n">
-        <v>2.506323844104075</v>
+        <v>2.506323844104058</v>
       </c>
       <c r="E2" t="n">
-        <v>4.714031495958479</v>
+        <v>4.714031495958485</v>
       </c>
       <c r="F2" t="n">
-        <v>4.714031495958479</v>
+        <v>4.714031495958485</v>
       </c>
       <c r="G2" t="n">
-        <v>8.59473306454437</v>
+        <v>8.594733064544339</v>
       </c>
       <c r="H2" t="n">
-        <v>14.95423915548299</v>
+        <v>14.954239155483</v>
       </c>
       <c r="I2" t="n">
-        <v>4.714031495958479</v>
+        <v>4.714031495958485</v>
       </c>
       <c r="J2" t="n">
-        <v>6.376977613286529</v>
+        <v>6.37697761328652</v>
       </c>
       <c r="K2" t="n">
-        <v>2.791504839028545</v>
+        <v>2.791504839028537</v>
       </c>
       <c r="L2" t="n">
-        <v>24.51606542264503</v>
+        <v>24.51606542264502</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1466612766503031</v>
+        <v>0.1466612766502933</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1632631611715463</v>
+        <v>0.1632631611715459</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1466612766503031</v>
+        <v>0.1466612766502933</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1767001899085888</v>
+        <v>0.1767001899085893</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1767001899085889</v>
+        <v>0.1767001899085893</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1467131957766316</v>
+        <v>0.1467131957766304</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1466612766503031</v>
+        <v>0.1466612766502933</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1465440266048815</v>
+        <v>0.1465440266048825</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1466612766503031</v>
+        <v>0.1466612766502933</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1466612766503031</v>
+        <v>0.1466612766502933</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1466612766503031</v>
+        <v>0.1466612766502933</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>81.0781987270469</v>
+        <v>6.725692546726544</v>
       </c>
       <c r="C4" t="n">
-        <v>6.866558870852852</v>
+        <v>6.866558870852862</v>
       </c>
       <c r="D4" t="n">
-        <v>6.707556952996369</v>
+        <v>6.707556952996324</v>
       </c>
       <c r="E4" t="n">
-        <v>6.787168578069132</v>
+        <v>6.787168578069131</v>
       </c>
       <c r="F4" t="n">
-        <v>6.815154506834849</v>
+        <v>6.81515450683485</v>
       </c>
       <c r="G4" t="n">
-        <v>81.07825064617336</v>
+        <v>81.07825064617334</v>
       </c>
       <c r="H4" t="n">
-        <v>81.07696603189301</v>
+        <v>81.07696603189299</v>
       </c>
       <c r="I4" t="n">
-        <v>6.725575296681142</v>
+        <v>81.07808147700142</v>
       </c>
       <c r="J4" t="n">
-        <v>81.07680414809799</v>
+        <v>81.07680414809798</v>
       </c>
       <c r="K4" t="n">
-        <v>6.623701006830898</v>
+        <v>6.623701006830917</v>
       </c>
       <c r="L4" t="n">
-        <v>6.722811399695058</v>
+        <v>6.722811399695055</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5169122000373692</v>
+        <v>0.5169122000373619</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5183680287040699</v>
+        <v>0.5183680287040703</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5168864509726183</v>
+        <v>0.5168864509726129</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5254975138331754</v>
+        <v>0.5254975138331753</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5254975138331754</v>
+        <v>0.5254975138331753</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5169641191636969</v>
+        <v>0.5169641191636896</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5169122000373692</v>
+        <v>0.5169122000373619</v>
       </c>
       <c r="I5" t="n">
-        <v>0.516794949991949</v>
+        <v>0.5167949499919484</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5169122000373692</v>
+        <v>0.5169122000373619</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5169122000373692</v>
+        <v>0.5169122000373619</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5169122000373692</v>
+        <v>0.5169122000373619</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5745319097544506</v>
+        <v>0.574531909754441</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8890227202241883</v>
+        <v>0.8890227202241886</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9423241744604189</v>
+        <v>0.9423241744604054</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8032425740728999</v>
+        <v>0.8032425740729011</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5892776979915718</v>
+        <v>0.5892776979915731</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8792098944455889</v>
+        <v>0.8792098944455835</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8791579753187063</v>
+        <v>0.8791579753187083</v>
       </c>
       <c r="I6" t="n">
-        <v>0.87904072527384</v>
+        <v>0.879040725273843</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8792178429611446</v>
+        <v>0.8792178429611374</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5688733242021569</v>
+        <v>0.5688733242021573</v>
       </c>
       <c r="L6" t="n">
-        <v>1.197365373116323</v>
+        <v>1.197365373116321</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.910911979707614</v>
+        <v>2.910911979707605</v>
       </c>
       <c r="C7" t="n">
-        <v>3.69109543717853</v>
+        <v>3.691095437178523</v>
       </c>
       <c r="D7" t="n">
-        <v>3.689639327867417</v>
+        <v>3.68963932786741</v>
       </c>
       <c r="E7" t="n">
-        <v>4.588156319499307</v>
+        <v>4.588156319499304</v>
       </c>
       <c r="F7" t="n">
-        <v>3.689521592691737</v>
+        <v>3.689521592691736</v>
       </c>
       <c r="G7" t="n">
-        <v>3.68969152763817</v>
+        <v>3.689691527638161</v>
       </c>
       <c r="H7" t="n">
-        <v>3.689639608511836</v>
+        <v>3.689639608511823</v>
       </c>
       <c r="I7" t="n">
-        <v>3.689522358466423</v>
+        <v>3.689522358466419</v>
       </c>
       <c r="J7" t="n">
-        <v>3.689639608511836</v>
+        <v>3.689639608511823</v>
       </c>
       <c r="K7" t="n">
-        <v>3.220135984064924</v>
+        <v>3.238441644045552</v>
       </c>
       <c r="L7" t="n">
-        <v>3.689639608511836</v>
+        <v>3.689639608511825</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.447695270492164</v>
+        <v>-0.4476952704921693</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.5268128120983623</v>
+        <v>-0.5268128120983617</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1723633085844342</v>
+        <v>0.1723633085844308</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1373171823950313</v>
+        <v>0.1373171823950315</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1373171823950313</v>
+        <v>0.1373171823950315</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01515130293544907</v>
+        <v>0.01515130293544618</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.07485988016463227</v>
+        <v>-0.07485988016463446</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1373171823950313</v>
+        <v>0.1373171823950315</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1252229444961606</v>
+        <v>0.1252229444961636</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1865109316898073</v>
+        <v>0.1865109316898028</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2768715602034485</v>
+        <v>-0.2768715602034514</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.04991932015957556</v>
+        <v>-0.04991932015958284</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.07262015421393039</v>
+        <v>-0.07262015421393025</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2021164346744783</v>
+        <v>0.2021164346744705</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1964334941909418</v>
+        <v>0.1964334941909421</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1964334941909418</v>
+        <v>0.1964334941909421</v>
       </c>
       <c r="G9" t="n">
-        <v>0.125284724753368</v>
+        <v>0.1252847247533657</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1017031339703105</v>
+        <v>0.1017031339703026</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1964334941909418</v>
+        <v>0.1964334941909421</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2031691694169874</v>
+        <v>0.2031691694169825</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2196985956425498</v>
+        <v>0.2196985956425469</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009737448668895539</v>
+        <v>0.009737448668892749</v>
       </c>
     </row>
   </sheetData>
@@ -4082,34 +4082,34 @@
         <v>21.79674557890819</v>
       </c>
       <c r="C2" t="n">
-        <v>24.50526679126416</v>
+        <v>24.50526679126414</v>
       </c>
       <c r="D2" t="n">
         <v>2.243367361856434</v>
       </c>
       <c r="E2" t="n">
-        <v>3.109356983650853</v>
+        <v>3.109356983650827</v>
       </c>
       <c r="F2" t="n">
-        <v>3.109356983650853</v>
+        <v>3.109356983650827</v>
       </c>
       <c r="G2" t="n">
-        <v>5.880465660992145</v>
+        <v>5.880465660992131</v>
       </c>
       <c r="H2" t="n">
-        <v>15.40880326332605</v>
+        <v>15.40880326332603</v>
       </c>
       <c r="I2" t="n">
-        <v>3.109356983650853</v>
+        <v>3.109356983650827</v>
       </c>
       <c r="J2" t="n">
-        <v>4.42968109431628</v>
+        <v>4.429681094316273</v>
       </c>
       <c r="K2" t="n">
-        <v>1.866531213560383</v>
+        <v>1.866531213560369</v>
       </c>
       <c r="L2" t="n">
-        <v>13.30627862131535</v>
+        <v>13.30627862131533</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1333469041433906</v>
+        <v>0.1333469041433901</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1439061270313208</v>
+        <v>0.1439061270313204</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1333469041433906</v>
+        <v>0.1333469041433901</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1720136229570543</v>
+        <v>0.1720136229570538</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1720136229570542</v>
+        <v>0.1720136229570539</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1334327628047211</v>
+        <v>0.1334327628047201</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1333469041433906</v>
+        <v>0.1333469041433901</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1334440452113223</v>
+        <v>0.1334440452113217</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1333469041433906</v>
+        <v>0.1333469041433901</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1333469041433906</v>
+        <v>0.1333469041433901</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1333469041433906</v>
+        <v>0.1333469041433901</v>
       </c>
     </row>
     <row r="4">
@@ -4159,31 +4159,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.75857894332609</v>
+        <v>6.348425902196644</v>
       </c>
       <c r="C4" t="n">
-        <v>6.471307259692439</v>
+        <v>6.471307259692447</v>
       </c>
       <c r="D4" t="n">
-        <v>6.336009454519596</v>
+        <v>6.336009967276821</v>
       </c>
       <c r="E4" t="n">
-        <v>6.411815957315865</v>
+        <v>6.411815957315858</v>
       </c>
       <c r="F4" t="n">
-        <v>6.435951711578251</v>
+        <v>6.435951711578249</v>
       </c>
       <c r="G4" t="n">
-        <v>6.348511760857965</v>
+        <v>6.348511760857962</v>
       </c>
       <c r="H4" t="n">
-        <v>76.76855981498387</v>
+        <v>76.76855981498386</v>
       </c>
       <c r="I4" t="n">
-        <v>6.348523043264581</v>
+        <v>76.75867608439404</v>
       </c>
       <c r="J4" t="n">
-        <v>6.357381742186302</v>
+        <v>76.75972862929358</v>
       </c>
       <c r="K4" t="n">
         <v>6.255856120576964</v>
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4823595038696986</v>
+        <v>0.4823595038696953</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4836704506047102</v>
+        <v>0.4836704506047103</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4823350720384193</v>
+        <v>0.482335072038418</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4936380428558417</v>
+        <v>0.4936380428558425</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4936380428558417</v>
+        <v>0.4936380428558425</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4824453625310243</v>
+        <v>0.4824453625310245</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4823595038696986</v>
+        <v>0.4823595038696953</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4824566449376261</v>
+        <v>0.4824566449376269</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4823595038696986</v>
+        <v>0.4823595038696953</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4823595038696986</v>
+        <v>0.4823595038696953</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4823595038696986</v>
+        <v>0.4823595038696953</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5314797251907537</v>
+        <v>0.5314797251907518</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8285821088724264</v>
+        <v>0.8285821088724249</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8755973317175212</v>
+        <v>0.8755973317175174</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7482731742076852</v>
+        <v>0.7482731742076839</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5472962989775598</v>
+        <v>0.5472962989775582</v>
       </c>
       <c r="G6" t="n">
-        <v>0.816582977169526</v>
+        <v>0.8165829771695226</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8164971185101669</v>
+        <v>0.8164971185101627</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8165942595761291</v>
+        <v>0.8165942595761272</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8165531324563351</v>
+        <v>0.8165531324563303</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5261853807945626</v>
+        <v>0.5261853807945632</v>
       </c>
       <c r="L6" t="n">
-        <v>1.114221618470447</v>
+        <v>1.114221618470445</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.430975590644089</v>
+        <v>2.430975590644086</v>
       </c>
       <c r="C7" t="n">
-        <v>3.081656850391174</v>
+        <v>3.081656850391169</v>
       </c>
       <c r="D7" t="n">
-        <v>3.080345649758586</v>
+        <v>3.080345649758581</v>
       </c>
       <c r="E7" t="n">
-        <v>3.829801563585974</v>
+        <v>3.829801563585971</v>
       </c>
       <c r="F7" t="n">
-        <v>3.080442385554548</v>
+        <v>3.080442385554542</v>
       </c>
       <c r="G7" t="n">
-        <v>3.080431762317491</v>
+        <v>3.080431762317489</v>
       </c>
       <c r="H7" t="n">
-        <v>3.080345903656167</v>
+        <v>3.080345903656162</v>
       </c>
       <c r="I7" t="n">
-        <v>3.080443044724093</v>
+        <v>3.080443044724088</v>
       </c>
       <c r="J7" t="n">
-        <v>3.080345903656167</v>
+        <v>3.080345903656162</v>
       </c>
       <c r="K7" t="n">
-        <v>2.262672833188045</v>
+        <v>2.704098087234841</v>
       </c>
       <c r="L7" t="n">
-        <v>3.080345903656167</v>
+        <v>3.080345903656162</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.2263434137196922</v>
+        <v>-0.226343413719692</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.3593968279549217</v>
+        <v>-0.3593968279549221</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1638896290053637</v>
+        <v>0.163889629005364</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1630136118483971</v>
+        <v>0.163013611848397</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1630136118483971</v>
+        <v>0.163013611848397</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06449425711101844</v>
+        <v>0.06449425711101792</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1132728550910066</v>
+        <v>-0.1132728550910075</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1630136118483971</v>
+        <v>0.163013611848397</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1609460067967553</v>
+        <v>0.1609460067967532</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2064877875565375</v>
+        <v>0.2064877875565404</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.07567349621345187</v>
+        <v>-0.07567349621345243</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07411330153737539</v>
+        <v>0.07411330153737448</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.01895691295721429</v>
+        <v>-0.01895691295721443</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1920699905306541</v>
+        <v>0.1920699905306552</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2029686032691332</v>
+        <v>0.2029686032691328</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2029686032691332</v>
+        <v>0.2029686032691328</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1430856231590924</v>
+        <v>0.1430856231590915</v>
       </c>
       <c r="H9" t="n">
-        <v>0.07948781509702818</v>
+        <v>0.07948781509702796</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2029686032691332</v>
+        <v>0.2029686032691328</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2169186755369999</v>
+        <v>0.2169186755369995</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2285930240866867</v>
+        <v>0.2285930240866868</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08706255964203025</v>
+        <v>0.08706255964202997</v>
       </c>
     </row>
   </sheetData>
@@ -4478,34 +4478,34 @@
         <v>18.56323573392874</v>
       </c>
       <c r="C2" t="n">
-        <v>19.49045220533289</v>
+        <v>19.49045220533286</v>
       </c>
       <c r="D2" t="n">
         <v>2.250973647433747</v>
       </c>
       <c r="E2" t="n">
-        <v>2.216901702127087</v>
+        <v>2.21690170212708</v>
       </c>
       <c r="F2" t="n">
-        <v>2.216901702127087</v>
+        <v>2.21690170212708</v>
       </c>
       <c r="G2" t="n">
-        <v>4.532030104334918</v>
+        <v>4.532030104334947</v>
       </c>
       <c r="H2" t="n">
-        <v>11.76299656493493</v>
+        <v>11.76299656493495</v>
       </c>
       <c r="I2" t="n">
-        <v>2.216901702127087</v>
+        <v>2.21690170212708</v>
       </c>
       <c r="J2" t="n">
-        <v>3.374418687264199</v>
+        <v>3.374418687264202</v>
       </c>
       <c r="K2" t="n">
-        <v>1.499619719946259</v>
+        <v>1.49961971994626</v>
       </c>
       <c r="L2" t="n">
-        <v>7.532431484942075</v>
+        <v>7.53243148494207</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1345585301547494</v>
+        <v>0.1345585301547497</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1502200360167625</v>
+        <v>0.1502200360167555</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1345585301547494</v>
+        <v>0.1345585301547497</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1625825782126967</v>
+        <v>0.1625825782126972</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1625825782126965</v>
+        <v>0.1625825782126972</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1346314062753504</v>
+        <v>0.1346314062753508</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1345585301547494</v>
+        <v>0.1345585301547497</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1345846856891028</v>
+        <v>0.1345846856891032</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1345585301547494</v>
+        <v>0.1345585301547497</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1345585301547494</v>
+        <v>0.1345585301547497</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1345585301547494</v>
+        <v>0.1345585301547497</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.74353586683692</v>
+        <v>6.339000390797188</v>
       </c>
       <c r="C4" t="n">
-        <v>6.45656970393489</v>
+        <v>6.456569703934896</v>
       </c>
       <c r="D4" t="n">
-        <v>6.329607580974369</v>
+        <v>6.32960758097437</v>
       </c>
       <c r="E4" t="n">
-        <v>6.402653284730215</v>
+        <v>6.402653284730218</v>
       </c>
       <c r="F4" t="n">
-        <v>6.426690854578575</v>
+        <v>6.426690854578577</v>
       </c>
       <c r="G4" t="n">
-        <v>76.74360874295772</v>
+        <v>76.74360874295762</v>
       </c>
       <c r="H4" t="n">
-        <v>76.75513810626317</v>
+        <v>76.75513810626313</v>
       </c>
       <c r="I4" t="n">
-        <v>6.339026546331525</v>
+        <v>76.74356202237129</v>
       </c>
       <c r="J4" t="n">
-        <v>76.74337373066106</v>
+        <v>6.348203784917564</v>
       </c>
       <c r="K4" t="n">
-        <v>6.24854699631828</v>
+        <v>6.248546996318283</v>
       </c>
       <c r="L4" t="n">
-        <v>6.335125657967449</v>
+        <v>6.335125657967445</v>
       </c>
     </row>
     <row r="5">
@@ -4598,25 +4598,25 @@
         <v>0.4782597973865615</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4794452175143928</v>
+        <v>0.4794452175143883</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4782325792099615</v>
+        <v>0.4782325792099612</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4867267850603597</v>
+        <v>0.4867267850603599</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4867267850603597</v>
+        <v>0.4867267850603599</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4783326735071631</v>
+        <v>0.4783326735071627</v>
       </c>
       <c r="H5" t="n">
         <v>0.4782597973865615</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4782859529209139</v>
+        <v>0.4782859529209136</v>
       </c>
       <c r="J5" t="n">
         <v>0.4782597973865615</v>
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5253733875085734</v>
+        <v>0.5253733875085742</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8158011537214249</v>
+        <v>0.8158011537214229</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8647382936768598</v>
+        <v>0.8647382936768603</v>
       </c>
       <c r="E6" t="n">
-        <v>0.736895104942156</v>
+        <v>0.7368951049421576</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5393609780237598</v>
+        <v>0.5393609780237604</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8065272054518089</v>
+        <v>0.8065272054518092</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8064543293341431</v>
+        <v>0.8064543293341436</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8064804848655612</v>
+        <v>0.8064804848655613</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8065095696194415</v>
+        <v>0.8065095696194418</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5201521647206512</v>
+        <v>0.5201521647206514</v>
       </c>
       <c r="L6" t="n">
-        <v>1.100066876518034</v>
+        <v>1.100066876518035</v>
       </c>
     </row>
     <row r="7">
@@ -4675,19 +4675,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.189834888509452</v>
+        <v>2.189834888509451</v>
       </c>
       <c r="C7" t="n">
-        <v>2.773677270646925</v>
+        <v>2.77367727064692</v>
       </c>
       <c r="D7" t="n">
-        <v>2.772491646412442</v>
+        <v>2.772491646412444</v>
       </c>
       <c r="E7" t="n">
-        <v>3.444890877154037</v>
+        <v>3.444890877154033</v>
       </c>
       <c r="F7" t="n">
-        <v>2.772517426671105</v>
+        <v>2.772517426671103</v>
       </c>
       <c r="G7" t="n">
         <v>2.7725647266397</v>
@@ -4696,13 +4696,13 @@
         <v>2.772491850519102</v>
       </c>
       <c r="I7" t="n">
-        <v>2.772518006053456</v>
+        <v>2.772518006053455</v>
       </c>
       <c r="J7" t="n">
         <v>2.772491850519102</v>
       </c>
       <c r="K7" t="n">
-        <v>2.421201433257638</v>
+        <v>2.421201433257637</v>
       </c>
       <c r="L7" t="n">
         <v>2.772491850519102</v>
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04176656312889038</v>
+        <v>0.0417665631288894</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2585394677163754</v>
+        <v>-0.258539467716377</v>
       </c>
       <c r="D8" t="n">
         <v>0.1543205280215443</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1732405636354438</v>
+        <v>0.1732405636354437</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1732405636354438</v>
+        <v>0.1732405636354437</v>
       </c>
       <c r="G8" t="n">
         <v>0.1041511237281451</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.04420481701643164</v>
+        <v>-0.04420481701643161</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1732405636354438</v>
+        <v>0.1732405636354437</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1783064656586352</v>
+        <v>0.1783064656586357</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2030723736255983</v>
+        <v>0.2030723736255943</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03546675915810492</v>
+        <v>0.03546675915810476</v>
       </c>
     </row>
     <row r="9">
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2938743947490615</v>
+        <v>0.2938743947490607</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01158644039315639</v>
+        <v>0.01158644039315472</v>
       </c>
       <c r="D9" t="n">
         <v>0.182722832455606</v>
@@ -4770,22 +4770,22 @@
         <v>0.2005622353254784</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1636516870568072</v>
+        <v>0.1636516870568069</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1020960564216616</v>
+        <v>0.1020960564216617</v>
       </c>
       <c r="I9" t="n">
         <v>0.2005622353254784</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2198567653593181</v>
+        <v>0.219856765359318</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2200513309092755</v>
+        <v>0.2200513309092706</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1260557257450644</v>
+        <v>0.126055725745064</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.705326743846688</v>
+        <v>2.70532674384668</v>
       </c>
       <c r="C2" t="n">
-        <v>10.9048458838603</v>
+        <v>10.90484588386031</v>
       </c>
       <c r="D2" t="n">
-        <v>5.618512043260422</v>
+        <v>5.618512043260417</v>
       </c>
       <c r="E2" t="n">
-        <v>10.9048458838603</v>
+        <v>10.90484588386031</v>
       </c>
       <c r="F2" t="n">
-        <v>10.9048458838603</v>
+        <v>10.90484588386031</v>
       </c>
       <c r="G2" t="n">
         <v>10.95471983319387</v>
       </c>
       <c r="H2" t="n">
-        <v>12.91651369996431</v>
+        <v>12.91651369996435</v>
       </c>
       <c r="I2" t="n">
-        <v>10.9048458838603</v>
+        <v>10.90484588386031</v>
       </c>
       <c r="J2" t="n">
-        <v>7.753204000752329</v>
+        <v>7.753204000752314</v>
       </c>
       <c r="K2" t="n">
-        <v>4.970815362863634</v>
+        <v>4.970815362863648</v>
       </c>
       <c r="L2" t="n">
-        <v>35.34354695400378</v>
+        <v>35.34354695400381</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1339233690897053</v>
+        <v>0.1339233690897062</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1360555213132331</v>
+        <v>0.1360555213132328</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1339233690897053</v>
+        <v>0.1339233690897062</v>
       </c>
       <c r="E3" t="n">
-        <v>0.136745249317046</v>
+        <v>0.1367452493170456</v>
       </c>
       <c r="F3" t="n">
-        <v>0.136745249317046</v>
+        <v>0.1367452493170456</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1340955314355507</v>
+        <v>0.134095531435551</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1339233690897053</v>
+        <v>0.1339233690897062</v>
       </c>
       <c r="I3" t="n">
         <v>0.1346001200363499</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1339233690897053</v>
+        <v>0.1339233690897062</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1339233690897053</v>
+        <v>0.1339233690897062</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1339233690897053</v>
+        <v>0.1339233690897062</v>
       </c>
     </row>
     <row r="4">
@@ -4954,25 +4954,25 @@
         <v>82.37047481525154</v>
       </c>
       <c r="C4" t="n">
-        <v>6.890528693572323</v>
+        <v>6.890528693572321</v>
       </c>
       <c r="D4" t="n">
-        <v>6.780334133189195</v>
+        <v>6.780334133189188</v>
       </c>
       <c r="E4" t="n">
         <v>6.86772341071064</v>
       </c>
       <c r="F4" t="n">
-        <v>6.889677362212417</v>
+        <v>6.889677362212414</v>
       </c>
       <c r="G4" t="n">
-        <v>6.80228449323323</v>
+        <v>82.37064697759737</v>
       </c>
       <c r="H4" t="n">
-        <v>6.790689741866502</v>
+        <v>82.35967190382887</v>
       </c>
       <c r="I4" t="n">
-        <v>82.37115156619831</v>
+        <v>82.37115156619826</v>
       </c>
       <c r="J4" t="n">
         <v>82.36269081366676</v>
@@ -4981,7 +4981,7 @@
         <v>6.692305870471019</v>
       </c>
       <c r="L4" t="n">
-        <v>6.788095595629553</v>
+        <v>6.788095595629559</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5115120796661341</v>
+        <v>0.5115120796661351</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5121888306127785</v>
+        <v>0.5121888306127784</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5114850211536852</v>
+        <v>0.5114850211536862</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5121129208213911</v>
+        <v>0.5121129208213901</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5121129208213911</v>
+        <v>0.5121129208213901</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5116842420119773</v>
+        <v>0.5116842420119784</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5115120796661341</v>
+        <v>0.5115120796661351</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5121888306127785</v>
+        <v>0.5121888306127784</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5115120796661341</v>
+        <v>0.5115120796661351</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5115120796661341</v>
+        <v>0.5115120796661351</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5115120796661341</v>
+        <v>0.5115120796661351</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5716518752796006</v>
+        <v>0.5716518752796007</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8806699357069523</v>
+        <v>0.8806699357069533</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9439032046005804</v>
+        <v>0.9439032046005827</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7963378641558075</v>
+        <v>0.7963378641558088</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5820727301919891</v>
+        <v>0.5820727301919899</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8801433491842359</v>
+        <v>0.8801433491842372</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8799711868382945</v>
+        <v>0.879971186838298</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8806479377850341</v>
+        <v>0.8806479377850334</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8800317803767824</v>
+        <v>0.8800317803767844</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5659246857804036</v>
+        <v>0.5659246857804054</v>
       </c>
       <c r="L6" t="n">
-        <v>1.202036488963477</v>
+        <v>1.20203648896348</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.011464469107863</v>
+        <v>3.011464469107864</v>
       </c>
       <c r="C7" t="n">
-        <v>3.821080927408417</v>
+        <v>3.821080927408416</v>
       </c>
       <c r="D7" t="n">
-        <v>3.82040410530715</v>
+        <v>3.820404105307153</v>
       </c>
       <c r="E7" t="n">
-        <v>4.754579440438872</v>
+        <v>4.75457944043887</v>
       </c>
       <c r="F7" t="n">
         <v>3.821080373294888</v>
       </c>
       <c r="G7" t="n">
-        <v>3.820576338807623</v>
+        <v>3.820576338807624</v>
       </c>
       <c r="H7" t="n">
-        <v>3.820404176461777</v>
+        <v>3.820404176461778</v>
       </c>
       <c r="I7" t="n">
-        <v>3.821080927408417</v>
+        <v>3.821080927408416</v>
       </c>
       <c r="J7" t="n">
-        <v>3.820404176461777</v>
+        <v>3.820404176461778</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3517013031424</v>
+        <v>3.351701303142403</v>
       </c>
       <c r="L7" t="n">
-        <v>3.820404176461777</v>
+        <v>3.820404176461778</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.140928150061406</v>
+        <v>0.1409281500614064</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0173911216123152</v>
+        <v>-0.01739112161231463</v>
       </c>
       <c r="D8" t="n">
-        <v>0.07459393395709589</v>
+        <v>0.07459393395709629</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0173911216123152</v>
+        <v>-0.01739112161231463</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0173911216123152</v>
+        <v>-0.01739112161231463</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.04280252451234366</v>
+        <v>-0.04280252451234285</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.05962099340135116</v>
+        <v>-0.05962099340135162</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0173911216123152</v>
+        <v>-0.01739112161231463</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03579569310923978</v>
+        <v>0.03579569310923996</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08966214721502383</v>
+        <v>0.08966214721502352</v>
       </c>
       <c r="L8" t="n">
-        <v>0.110939356745713</v>
+        <v>-0.5234320600049172</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1741827433419282</v>
+        <v>0.1741827433419285</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1339523480464417</v>
+        <v>0.1339523480464418</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1471685717526683</v>
+        <v>0.1471685717526684</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1339523480464417</v>
+        <v>0.1339523480464418</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1339523480464417</v>
+        <v>0.1339523480464418</v>
       </c>
       <c r="G9" t="n">
-        <v>0.09953318181895715</v>
+        <v>0.09953318181895739</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09274222898178983</v>
+        <v>0.09274222898179031</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1339523480464417</v>
+        <v>0.1339523480464418</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1314256795134238</v>
+        <v>0.1314256795134249</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1533082738781537</v>
+        <v>0.1533082738781539</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1620360944070458</v>
+        <v>-0.09586682859069737</v>
       </c>
     </row>
   </sheetData>
@@ -5267,13 +5267,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.247130452331417</v>
+        <v>2.247130452331419</v>
       </c>
       <c r="C2" t="n">
         <v>9.270388210250511</v>
       </c>
       <c r="D2" t="n">
-        <v>4.826965699331538</v>
+        <v>4.826965699331505</v>
       </c>
       <c r="E2" t="n">
         <v>9.270388210250511</v>
@@ -5282,22 +5282,22 @@
         <v>9.270388210250511</v>
       </c>
       <c r="G2" t="n">
-        <v>8.767781490031911</v>
+        <v>8.767781490032029</v>
       </c>
       <c r="H2" t="n">
-        <v>9.480120824729218</v>
+        <v>9.480120824729216</v>
       </c>
       <c r="I2" t="n">
         <v>9.270388210250511</v>
       </c>
       <c r="J2" t="n">
-        <v>6.515377363363993</v>
+        <v>6.51537736336399</v>
       </c>
       <c r="K2" t="n">
-        <v>3.920624751474529</v>
+        <v>3.920624751474536</v>
       </c>
       <c r="L2" t="n">
-        <v>5.238019310750468</v>
+        <v>20.43826984150618</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1269783441924902</v>
+        <v>0.1269783441924913</v>
       </c>
       <c r="C3" t="n">
-        <v>0.129928872353827</v>
+        <v>0.1299288723538271</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1269783441924902</v>
+        <v>0.1269783441924914</v>
       </c>
       <c r="E3" t="n">
+        <v>0.1305088300992693</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.1305088300992694</v>
       </c>
-      <c r="F3" t="n">
-        <v>0.1305088300992696</v>
-      </c>
       <c r="G3" t="n">
-        <v>0.127172415710611</v>
+        <v>0.1271724157106117</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1269783441924902</v>
+        <v>0.1269783441924914</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1277933547763803</v>
+        <v>0.1277933547763802</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1269783441924902</v>
+        <v>0.1269783441924914</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1269783441924902</v>
+        <v>0.1269783441924914</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1269783441924902</v>
+        <v>0.1269783441924914</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.331593084549699</v>
+        <v>76.74022670835109</v>
       </c>
       <c r="C4" t="n">
-        <v>6.418556847620968</v>
+        <v>6.418556847620962</v>
       </c>
       <c r="D4" t="n">
-        <v>6.316406060451586</v>
+        <v>6.316406060451584</v>
       </c>
       <c r="E4" t="n">
         <v>6.397461290145317</v>
       </c>
       <c r="F4" t="n">
-        <v>6.417073209328368</v>
+        <v>6.417073209328367</v>
       </c>
       <c r="G4" t="n">
-        <v>6.33178715606778</v>
+        <v>76.7404207798691</v>
       </c>
       <c r="H4" t="n">
-        <v>76.73024043272125</v>
+        <v>76.73024043272122</v>
       </c>
       <c r="I4" t="n">
-        <v>6.332408095133584</v>
+        <v>76.74104171893485</v>
       </c>
       <c r="J4" t="n">
-        <v>6.337178416030537</v>
+        <v>76.73340103003122</v>
       </c>
       <c r="K4" t="n">
-        <v>6.234037452751248</v>
+        <v>6.234037452751253</v>
       </c>
       <c r="L4" t="n">
-        <v>6.322626350117827</v>
+        <v>6.322626350117829</v>
       </c>
     </row>
     <row r="5">
@@ -5387,13 +5387,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.474975508617729</v>
+        <v>0.4749755086177305</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4757905192016201</v>
+        <v>0.4757905192016189</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4749501770827873</v>
+        <v>0.474950177082788</v>
       </c>
       <c r="E5" t="n">
         <v>0.4758479646583103</v>
@@ -5405,19 +5405,19 @@
         <v>0.4751695801358504</v>
       </c>
       <c r="H5" t="n">
-        <v>0.474975508617729</v>
+        <v>0.4749755086177304</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4757905192016201</v>
+        <v>0.4757905192016189</v>
       </c>
       <c r="J5" t="n">
-        <v>0.474975508617729</v>
+        <v>0.4749755086177304</v>
       </c>
       <c r="K5" t="n">
-        <v>0.474975508617729</v>
+        <v>0.4749755086177304</v>
       </c>
       <c r="L5" t="n">
-        <v>0.474975508617729</v>
+        <v>0.4749755086177304</v>
       </c>
     </row>
     <row r="6">
@@ -5427,34 +5427,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5272302648058518</v>
+        <v>0.527230264805852</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8104396519088962</v>
+        <v>0.810439651910008</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8680091910505798</v>
+        <v>0.8680091910505792</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7332243851065336</v>
+        <v>0.733224385106533</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5370416120358537</v>
+        <v>0.5370416120358533</v>
       </c>
       <c r="G6" t="n">
-        <v>0.809676448425956</v>
+        <v>0.8096764484259578</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8094823769077369</v>
+        <v>0.8094823769077361</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8102973874917273</v>
+        <v>0.8102973874917263</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8095378474941454</v>
+        <v>0.8095378474941481</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5219872869194467</v>
+        <v>0.5219872869194473</v>
       </c>
       <c r="L6" t="n">
         <v>1.104318309496201</v>
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.499564627062839</v>
+        <v>2.49956462706284</v>
       </c>
       <c r="C7" t="n">
-        <v>3.168690004364129</v>
+        <v>3.168690004364124</v>
       </c>
       <c r="D7" t="n">
-        <v>3.167874943772686</v>
+        <v>3.167874943772685</v>
       </c>
       <c r="E7" t="n">
-        <v>3.939905369301891</v>
+        <v>3.939905369301883</v>
       </c>
       <c r="F7" t="n">
-        <v>3.168689538299939</v>
+        <v>3.168689538299931</v>
       </c>
       <c r="G7" t="n">
-        <v>3.168069065298358</v>
+        <v>3.168069065298359</v>
       </c>
       <c r="H7" t="n">
-        <v>3.167874993780244</v>
+        <v>3.167874993780238</v>
       </c>
       <c r="I7" t="n">
-        <v>3.168690004364129</v>
+        <v>3.168690004364124</v>
       </c>
       <c r="J7" t="n">
-        <v>3.167874993780244</v>
+        <v>3.167874993780238</v>
       </c>
       <c r="K7" t="n">
-        <v>2.326352962065558</v>
+        <v>2.326352962065559</v>
       </c>
       <c r="L7" t="n">
-        <v>3.167874993780244</v>
+        <v>3.167874993780238</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1434888631378138</v>
+        <v>0.1434888631378148</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.001535903851206274</v>
+        <v>-0.001535903851205857</v>
       </c>
       <c r="D8" t="n">
-        <v>0.07834965608197431</v>
+        <v>0.07834965608197518</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.001535903851206274</v>
+        <v>-0.001535903851205857</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.001535903851206274</v>
+        <v>-0.001535903851205857</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.01524764953487487</v>
+        <v>-0.01524764953487529</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.008137771406577406</v>
+        <v>-0.008137771406576129</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.001535903851206274</v>
+        <v>-0.001535903851205857</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04751110401043343</v>
+        <v>0.04751110401043337</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09744543074321865</v>
+        <v>0.09744543074321958</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08909759360299642</v>
+        <v>-0.2568864054921711</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1724064553930852</v>
+        <v>0.1724064553930859</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1380524924832889</v>
+        <v>0.138052492483289</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1458787754053107</v>
+        <v>0.1458787754053118</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1380524924832889</v>
+        <v>0.138052492483289</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1380524924832889</v>
+        <v>0.138052492483289</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1079850930125937</v>
+        <v>0.1079850930125933</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1108393348941147</v>
+        <v>0.1108393348941154</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1380524924832889</v>
+        <v>0.138052492483289</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1333717271325522</v>
+        <v>0.1333717271325533</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1536584380446214</v>
+        <v>0.1536584380446217</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009673707944356225</v>
+        <v>0.009673707944356062</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.074281276725861</v>
+        <v>2.07428127672582</v>
       </c>
       <c r="C2" t="n">
-        <v>7.842661517065323</v>
+        <v>7.842661517065296</v>
       </c>
       <c r="D2" t="n">
-        <v>4.254049723493997</v>
+        <v>4.25404972349399</v>
       </c>
       <c r="E2" t="n">
-        <v>7.842661517065323</v>
+        <v>7.842661517065296</v>
       </c>
       <c r="F2" t="n">
-        <v>7.842661517065323</v>
+        <v>7.842661517065296</v>
       </c>
       <c r="G2" t="n">
-        <v>7.440897490698641</v>
+        <v>7.440897490698569</v>
       </c>
       <c r="H2" t="n">
-        <v>10.62074098886564</v>
+        <v>10.6207409888657</v>
       </c>
       <c r="I2" t="n">
-        <v>7.842661517065323</v>
+        <v>7.842661517065296</v>
       </c>
       <c r="J2" t="n">
-        <v>5.404323889710537</v>
+        <v>5.404323889710493</v>
       </c>
       <c r="K2" t="n">
-        <v>2.940202443545266</v>
+        <v>2.940202443545181</v>
       </c>
       <c r="L2" t="n">
-        <v>5.079776159107588</v>
+        <v>5.079776159107578</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1204103578024436</v>
+        <v>0.1204103578024434</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1233638614907748</v>
+        <v>0.1233638614907733</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1204103578024436</v>
+        <v>0.1204103578024437</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1238929397977583</v>
+        <v>0.1238929397977588</v>
       </c>
       <c r="F3" t="n">
-        <v>0.123892939797758</v>
+        <v>0.1238929397977581</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1205944831698614</v>
+        <v>0.1205944831698615</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1204103578024436</v>
+        <v>0.1204103578024437</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1211605604579108</v>
+        <v>0.1211605604579089</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1204103578024436</v>
+        <v>0.1204103578024437</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1204103578024436</v>
+        <v>0.1204103578024437</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1204103578024436</v>
+        <v>0.1204103578024437</v>
       </c>
     </row>
     <row r="4">
@@ -5746,34 +5746,34 @@
         <v>6.318304761460984</v>
       </c>
       <c r="C4" t="n">
-        <v>6.40517734460368</v>
+        <v>6.405177344603676</v>
       </c>
       <c r="D4" t="n">
-        <v>76.71413613810392</v>
+        <v>76.7141361381039</v>
       </c>
       <c r="E4" t="n">
-        <v>6.384356294071024</v>
+        <v>6.384356294071019</v>
       </c>
       <c r="F4" t="n">
-        <v>6.404142062177028</v>
+        <v>6.404142062177031</v>
       </c>
       <c r="G4" t="n">
-        <v>6.318488886828375</v>
+        <v>6.318488886828372</v>
       </c>
       <c r="H4" t="n">
-        <v>76.71244100422685</v>
+        <v>76.71244100422686</v>
       </c>
       <c r="I4" t="n">
-        <v>76.72278088601438</v>
+        <v>76.72278088601433</v>
       </c>
       <c r="J4" t="n">
-        <v>76.71472714365348</v>
+        <v>6.324141923139504</v>
       </c>
       <c r="K4" t="n">
-        <v>6.221780297414934</v>
+        <v>6.22178029741493</v>
       </c>
       <c r="L4" t="n">
-        <v>6.310252043172887</v>
+        <v>6.310252043172885</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4647805470766588</v>
+        <v>0.4647805470766634</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4655307497321342</v>
+        <v>0.4655307497321277</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4647553243895881</v>
+        <v>0.4647553243895899</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4656764483924854</v>
+        <v>0.4656764483924842</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4656764483924854</v>
+        <v>0.4656764483924842</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4649646724440835</v>
+        <v>0.4649646724440796</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4647805470766588</v>
+        <v>0.4647805470766628</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4655307497321342</v>
+        <v>0.4655307497321277</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4647805470766588</v>
+        <v>0.4647805470766628</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4647805470766588</v>
+        <v>0.4647805470766628</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4647805470766588</v>
+        <v>0.4647805470766628</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.513104976838434</v>
+        <v>0.5131049768384328</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7911434841786257</v>
+        <v>0.7911434841786227</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8476185100668998</v>
+        <v>0.8476185100668963</v>
       </c>
       <c r="E6" t="n">
-        <v>0.715338611936308</v>
+        <v>0.7153386119363037</v>
       </c>
       <c r="F6" t="n">
-        <v>0.522739604210726</v>
+        <v>0.5227396042107266</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7903518663882398</v>
+        <v>0.7903518663882377</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7901677410207764</v>
+        <v>0.790167741020776</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7909179436762886</v>
+        <v>0.7909179436762853</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7902221917511892</v>
+        <v>0.7902221917511832</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5079583937538896</v>
+        <v>0.5079583937538855</v>
       </c>
       <c r="L6" t="n">
-        <v>1.079582965780586</v>
+        <v>1.07958296578057</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.247702305914453</v>
+        <v>2.247702305914451</v>
       </c>
       <c r="C7" t="n">
-        <v>2.848756860522426</v>
+        <v>2.848756860522425</v>
       </c>
       <c r="D7" t="n">
-        <v>2.848006557031474</v>
+        <v>2.848006557031472</v>
       </c>
       <c r="E7" t="n">
-        <v>3.541494642173302</v>
+        <v>3.541494642173294</v>
       </c>
       <c r="F7" t="n">
-        <v>2.84875636384919</v>
+        <v>2.848756363849187</v>
       </c>
       <c r="G7" t="n">
-        <v>2.848190783234383</v>
+        <v>2.848190783234394</v>
       </c>
       <c r="H7" t="n">
-        <v>2.84800665786697</v>
+        <v>2.848006657866967</v>
       </c>
       <c r="I7" t="n">
-        <v>2.848756860522426</v>
+        <v>2.848756860522425</v>
       </c>
       <c r="J7" t="n">
-        <v>2.84800665786697</v>
+        <v>2.848006657866967</v>
       </c>
       <c r="K7" t="n">
-        <v>2.500187916357773</v>
+        <v>2.50018791635777</v>
       </c>
       <c r="L7" t="n">
-        <v>2.84800665786697</v>
+        <v>2.848006657866967</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1408688580147515</v>
+        <v>0.1408688580147525</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02701381579792825</v>
+        <v>0.02701381579792948</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08394687964340539</v>
+        <v>0.08394687964340643</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02701381579792825</v>
+        <v>0.02701381579792948</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02701381579792825</v>
+        <v>0.02701381579792948</v>
       </c>
       <c r="G8" t="n">
-        <v>0.007098261748696095</v>
+        <v>0.007098261748692276</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.04872298171117451</v>
+        <v>-0.04872298171117456</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02701381579792825</v>
+        <v>0.02701381579792948</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0675708533060223</v>
+        <v>0.0675708533060229</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1140573457428135</v>
+        <v>0.1140573457428141</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0850858965938659</v>
+        <v>0.08508589659386546</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1679751822681153</v>
+        <v>0.1679751822681171</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1455027334391706</v>
+        <v>0.1455027334391708</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1447940255312535</v>
+        <v>0.1447940255312527</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1455027334391706</v>
+        <v>0.1455027334391708</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1455027334391706</v>
+        <v>0.1455027334391708</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1136836276267615</v>
+        <v>0.1136836276267596</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09097748394136213</v>
+        <v>0.0909774839413619</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1455027334391706</v>
+        <v>0.1455027334391708</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1381679171910278</v>
+        <v>0.1381679171910272</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1570590193389186</v>
+        <v>0.1570590193389183</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1453342796918847</v>
+        <v>0.1453342796918852</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9738103776214676</v>
+        <v>0.9738103776214667</v>
       </c>
       <c r="C2" t="n">
-        <v>11.26128283889701</v>
+        <v>11.261282838897</v>
       </c>
       <c r="D2" t="n">
-        <v>3.426276936508332</v>
+        <v>3.426276936508326</v>
       </c>
       <c r="E2" t="n">
-        <v>11.26128283889701</v>
+        <v>11.261282838897</v>
       </c>
       <c r="F2" t="n">
-        <v>11.26128283889701</v>
+        <v>11.261282838897</v>
       </c>
       <c r="G2" t="n">
-        <v>13.68287810816894</v>
+        <v>13.68287810816893</v>
       </c>
       <c r="H2" t="n">
-        <v>23.59525059989438</v>
+        <v>23.59525059989437</v>
       </c>
       <c r="I2" t="n">
-        <v>11.26128283889701</v>
+        <v>11.261282838897</v>
       </c>
       <c r="J2" t="n">
-        <v>10.43528480254211</v>
+        <v>10.43528480254209</v>
       </c>
       <c r="K2" t="n">
-        <v>4.413306761055487</v>
+        <v>4.41330676105548</v>
       </c>
       <c r="L2" t="n">
-        <v>20.90973718932252</v>
+        <v>16.19750656167275</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1421940271475463</v>
+        <v>0.1421940271475451</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1416464046020249</v>
+        <v>0.1416464046020248</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1421940271475463</v>
+        <v>0.1421940271475451</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1425516922625362</v>
+        <v>0.1425516922625363</v>
       </c>
       <c r="F3" t="n">
         <v>0.1425516922625363</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1422617524686411</v>
+        <v>0.1422617524686404</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1421940271475463</v>
+        <v>0.1421940271475451</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1422074643102212</v>
+        <v>0.142207464310221</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1421940271475463</v>
+        <v>0.1421940271475451</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1421940271475463</v>
+        <v>0.1421940271475451</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1421940271475463</v>
+        <v>0.1421940271475451</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.820177142836801</v>
+        <v>6.820177142836793</v>
       </c>
       <c r="C4" t="n">
-        <v>6.902313781223246</v>
+        <v>6.902313781223252</v>
       </c>
       <c r="D4" t="n">
-        <v>6.788376261638279</v>
+        <v>82.40017027473155</v>
       </c>
       <c r="E4" t="n">
-        <v>6.879146722521159</v>
+        <v>6.879146722521153</v>
       </c>
       <c r="F4" t="n">
         <v>6.905412226480188</v>
       </c>
       <c r="G4" t="n">
-        <v>82.41089992391939</v>
+        <v>6.820244868157912</v>
       </c>
       <c r="H4" t="n">
-        <v>82.40155006640383</v>
+        <v>82.40155006640386</v>
       </c>
       <c r="I4" t="n">
-        <v>82.41084563576091</v>
+        <v>6.820190579999466</v>
       </c>
       <c r="J4" t="n">
-        <v>82.40259053404371</v>
+        <v>82.40259053404365</v>
       </c>
       <c r="K4" t="n">
-        <v>6.703708252154939</v>
+        <v>6.703708252154938</v>
       </c>
       <c r="L4" t="n">
-        <v>6.808406787934487</v>
+        <v>6.808406787934492</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5310243012858875</v>
+        <v>0.5310243012858874</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5310377384485609</v>
+        <v>0.5310377384485616</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5309970903602507</v>
+        <v>0.5309970903602499</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5309700778377239</v>
+        <v>0.5309700778377244</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5309700778377239</v>
+        <v>0.5309700778377244</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5310920266069804</v>
+        <v>0.5310920266069793</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5310243012858875</v>
+        <v>0.5310243012858874</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5310377384485609</v>
+        <v>0.5310377384485616</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5310243012858875</v>
+        <v>0.5310243012858874</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5310243012858875</v>
+        <v>0.5310243012858874</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5310243012858875</v>
+        <v>0.5310243012858874</v>
       </c>
     </row>
     <row r="6">
@@ -6219,34 +6219,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6039695617829315</v>
+        <v>0.6039695617829307</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9301841567293337</v>
+        <v>0.9301841567280642</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9977701234204159</v>
+        <v>0.9977701234204152</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8409694914027359</v>
+        <v>0.840969491402737</v>
       </c>
       <c r="F6" t="n">
-        <v>0.614297877667867</v>
+        <v>0.6142978776678675</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9302048746780029</v>
+        <v>0.9302048746780046</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9301371493568276</v>
+        <v>0.9301371493568286</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9301505865195843</v>
+        <v>0.9301505865195854</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9302012505799467</v>
+        <v>0.9302012505799477</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5979108313947746</v>
+        <v>0.5979108313947736</v>
       </c>
       <c r="L6" t="n">
         <v>1.270846468215954</v>
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.100427179945933</v>
+        <v>3.100427179945928</v>
       </c>
       <c r="C7" t="n">
-        <v>3.93281441379722</v>
+        <v>3.932814413797213</v>
       </c>
       <c r="D7" t="n">
-        <v>3.93280081082138</v>
+        <v>3.932800810821376</v>
       </c>
       <c r="E7" t="n">
-        <v>4.893355028175508</v>
+        <v>4.893355028175503</v>
       </c>
       <c r="F7" t="n">
-        <v>3.932813655449944</v>
+        <v>3.93281365544994</v>
       </c>
       <c r="G7" t="n">
-        <v>3.932868701955645</v>
+        <v>3.932868701955642</v>
       </c>
       <c r="H7" t="n">
-        <v>3.932800976634563</v>
+        <v>3.932800976634558</v>
       </c>
       <c r="I7" t="n">
-        <v>3.93281441379722</v>
+        <v>3.932814413797213</v>
       </c>
       <c r="J7" t="n">
-        <v>3.932800976634563</v>
+        <v>3.932800976634558</v>
       </c>
       <c r="K7" t="n">
-        <v>2.884693831381789</v>
+        <v>3.450520260108856</v>
       </c>
       <c r="L7" t="n">
-        <v>3.932800976634563</v>
+        <v>3.932800976634558</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1940847823108278</v>
+        <v>0.1940847823108272</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.01879252995971297</v>
+        <v>-0.0187925299597128</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1329769415799848</v>
+        <v>0.1329769415799841</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.01879252995971297</v>
+        <v>-0.0187925299597128</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.01879252995971297</v>
+        <v>-0.0187925299597128</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1120881549538519</v>
+        <v>-0.1120881549538524</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.319364831270098</v>
+        <v>-0.3193648312700987</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01879252995971297</v>
+        <v>-0.0187925299597128</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.01078913979672783</v>
+        <v>-0.01078913979672883</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1090582759344537</v>
+        <v>0.1090582759344529</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.115422355989526</v>
+        <v>-0.221827280031133</v>
       </c>
     </row>
     <row r="9">
@@ -6339,13 +6339,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.202529573607948</v>
+        <v>0.202529573607947</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1382159527056752</v>
+        <v>0.138215952705675</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1776428267550476</v>
+        <v>0.1776428267550468</v>
       </c>
       <c r="E9" t="n">
         <v>0.1382159527056752</v>
@@ -6354,22 +6354,22 @@
         <v>0.1382159527056752</v>
       </c>
       <c r="G9" t="n">
-        <v>0.07771952162634874</v>
+        <v>0.07771952162634842</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.006100806919994275</v>
+        <v>-0.006100806919995039</v>
       </c>
       <c r="I9" t="n">
         <v>0.1382159527056752</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1191705965006465</v>
+        <v>0.1191705965006458</v>
       </c>
       <c r="K9" t="n">
-        <v>0.167904246488055</v>
+        <v>0.1679042464880541</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03345479417038606</v>
+        <v>0.07671703978872184</v>
       </c>
     </row>
   </sheetData>
@@ -6455,34 +6455,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9342620945146526</v>
+        <v>0.934262094514654</v>
       </c>
       <c r="C2" t="n">
-        <v>8.511844238662565</v>
+        <v>8.511844238662562</v>
       </c>
       <c r="D2" t="n">
         <v>2.461380163304673</v>
       </c>
       <c r="E2" t="n">
-        <v>8.511844238662565</v>
+        <v>8.511844238662562</v>
       </c>
       <c r="F2" t="n">
-        <v>8.511844238662565</v>
+        <v>8.511844238662562</v>
       </c>
       <c r="G2" t="n">
-        <v>8.988878822372943</v>
+        <v>8.988878822372921</v>
       </c>
       <c r="H2" t="n">
-        <v>12.7024727133575</v>
+        <v>12.70247271335751</v>
       </c>
       <c r="I2" t="n">
-        <v>8.511844238662565</v>
+        <v>8.511844238662562</v>
       </c>
       <c r="J2" t="n">
         <v>6.3698101593966</v>
       </c>
       <c r="K2" t="n">
-        <v>2.385639812330804</v>
+        <v>2.385639812330807</v>
       </c>
       <c r="L2" t="n">
         <v>10.27265588918169</v>
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.125215258320956</v>
+        <v>0.1252152583209571</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1266015259975827</v>
+        <v>0.1266015259975825</v>
       </c>
       <c r="D3" t="n">
-        <v>0.125215258320956</v>
+        <v>0.1252152583209571</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1272116692090987</v>
+        <v>0.1272116692090986</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1272116692090987</v>
+        <v>0.1272116692090988</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1253554355928822</v>
+        <v>0.1253554355928821</v>
       </c>
       <c r="H3" t="n">
-        <v>0.125215258320956</v>
+        <v>0.1252152583209571</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1256873527021027</v>
+        <v>0.1256873527021025</v>
       </c>
       <c r="J3" t="n">
-        <v>0.125215258320956</v>
+        <v>0.1252152583209571</v>
       </c>
       <c r="K3" t="n">
-        <v>0.125215258320956</v>
+        <v>0.1252152583209571</v>
       </c>
       <c r="L3" t="n">
-        <v>0.125215258320956</v>
+        <v>0.1252152583209571</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.329216276939953</v>
+        <v>76.74334858560698</v>
       </c>
       <c r="C4" t="n">
-        <v>6.414379777657317</v>
+        <v>6.414379777657314</v>
       </c>
       <c r="D4" t="n">
-        <v>6.309576305766674</v>
+        <v>6.309577200948139</v>
       </c>
       <c r="E4" t="n">
-        <v>6.393316171408907</v>
+        <v>6.393316171408906</v>
       </c>
       <c r="F4" t="n">
-        <v>6.414836557607243</v>
+        <v>6.414836557607244</v>
       </c>
       <c r="G4" t="n">
-        <v>6.329356454211904</v>
+        <v>6.329356454211911</v>
       </c>
       <c r="H4" t="n">
-        <v>76.73471429435139</v>
+        <v>6.32435392029941</v>
       </c>
       <c r="I4" t="n">
-        <v>6.329688371321092</v>
+        <v>6.329688371321093</v>
       </c>
       <c r="J4" t="n">
-        <v>6.33586960343012</v>
+        <v>76.73644620519752</v>
       </c>
       <c r="K4" t="n">
-        <v>6.228563027378058</v>
+        <v>6.22856302737806</v>
       </c>
       <c r="L4" t="n">
-        <v>6.322853039867248</v>
+        <v>6.322853039867256</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4736852233319924</v>
+        <v>0.4736852233319923</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4741573177131396</v>
+        <v>0.4741573177131391</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4736599864629672</v>
+        <v>0.4736599864629666</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4741498575291316</v>
+        <v>0.4741498575291313</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4741498575291316</v>
+        <v>0.4741498575291313</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4738254006039179</v>
+        <v>0.4738254006039183</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4736852233319924</v>
+        <v>0.4736852233319923</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4741573177131396</v>
+        <v>0.4741573177131391</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4736852233319924</v>
+        <v>0.4736852233319923</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4736852233319924</v>
+        <v>0.4736852233319923</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4736852233319924</v>
+        <v>0.4736852233319923</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5278168899260778</v>
+        <v>0.527816889926078</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8124817229807062</v>
+        <v>0.8124817229807059</v>
       </c>
       <c r="D6" t="n">
-        <v>0.870841718869093</v>
+        <v>0.8708417188690916</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7347642994855883</v>
+        <v>0.7347642994855871</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5373055100108231</v>
+        <v>0.5373055100108223</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8120693611699989</v>
+        <v>0.8120693611699991</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8119291838980608</v>
+        <v>0.8119291838980601</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8124012782792187</v>
+        <v>0.8124012782792189</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8119850200594128</v>
+        <v>0.8119850200594118</v>
       </c>
       <c r="K6" t="n">
-        <v>0.522539358206858</v>
+        <v>0.5225393582068588</v>
       </c>
       <c r="L6" t="n">
-        <v>1.108708231991747</v>
+        <v>1.108708231991746</v>
       </c>
     </row>
     <row r="7">
@@ -6658,34 +6658,34 @@
         <v>2.509254587984112</v>
       </c>
       <c r="C7" t="n">
-        <v>3.18136433047301</v>
+        <v>3.181364330473007</v>
       </c>
       <c r="D7" t="n">
-        <v>3.180892129200466</v>
+        <v>3.180892129200462</v>
       </c>
       <c r="E7" t="n">
-        <v>3.95641913945813</v>
+        <v>3.956419139458125</v>
       </c>
       <c r="F7" t="n">
-        <v>3.181363771044342</v>
+        <v>3.181363771044338</v>
       </c>
       <c r="G7" t="n">
-        <v>3.181032413363794</v>
+        <v>3.181032413363793</v>
       </c>
       <c r="H7" t="n">
-        <v>3.180892236091871</v>
+        <v>3.180892236091867</v>
       </c>
       <c r="I7" t="n">
-        <v>3.18136433047301</v>
+        <v>3.181364330473007</v>
       </c>
       <c r="J7" t="n">
-        <v>3.180892236091871</v>
+        <v>3.180892236091867</v>
       </c>
       <c r="K7" t="n">
-        <v>2.775954416187671</v>
+        <v>2.775954416187672</v>
       </c>
       <c r="L7" t="n">
-        <v>3.180892236091871</v>
+        <v>3.180892236091867</v>
       </c>
     </row>
     <row r="8">
@@ -6695,13 +6695,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1758988178198627</v>
+        <v>0.1758988178198626</v>
       </c>
       <c r="C8" t="n">
         <v>0.01277568595044616</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1343511816176306</v>
+        <v>0.1343511816176307</v>
       </c>
       <c r="E8" t="n">
         <v>0.01277568595044616</v>
@@ -6710,7 +6710,7 @@
         <v>0.01277568595044616</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.03826475080024545</v>
+        <v>-0.03826475080024568</v>
       </c>
       <c r="H8" t="n">
         <v>-0.1311853888070971</v>
@@ -6719,13 +6719,13 @@
         <v>0.01277568595044616</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04215065213432877</v>
+        <v>0.04215065213432873</v>
       </c>
       <c r="K8" t="n">
         <v>0.1370264358991947</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.02787076266907459</v>
+        <v>-0.0278707626690745</v>
       </c>
     </row>
     <row r="9">
@@ -6735,13 +6735,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1852936041419395</v>
+        <v>0.1852936041419396</v>
       </c>
       <c r="C9" t="n">
         <v>0.1426271757159337</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1683731200780243</v>
+        <v>0.1683731200780245</v>
       </c>
       <c r="E9" t="n">
         <v>0.1426271757159337</v>
@@ -6750,10 +6750,10 @@
         <v>0.1426271757159337</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0981335743171609</v>
+        <v>0.09813357431716037</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06052363774800855</v>
+        <v>0.0605236377480086</v>
       </c>
       <c r="I9" t="n">
         <v>0.1426271757159337</v>
@@ -6762,10 +6762,10 @@
         <v>0.1308770601190095</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1694641861920374</v>
+        <v>0.1694641861920375</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09490078364375493</v>
+        <v>0.1024682051670029</v>
       </c>
     </row>
   </sheetData>
@@ -6854,34 +6854,34 @@
         <v>1.057376452676942</v>
       </c>
       <c r="C2" t="n">
-        <v>6.285629862530848</v>
+        <v>6.285629862530855</v>
       </c>
       <c r="D2" t="n">
-        <v>1.635104016210316</v>
+        <v>1.635104016210322</v>
       </c>
       <c r="E2" t="n">
-        <v>6.285629862530848</v>
+        <v>6.285629862530855</v>
       </c>
       <c r="F2" t="n">
-        <v>6.285629862530848</v>
+        <v>6.285629862530855</v>
       </c>
       <c r="G2" t="n">
-        <v>5.848258743992544</v>
+        <v>5.848258743992585</v>
       </c>
       <c r="H2" t="n">
-        <v>10.14350019899162</v>
+        <v>10.14350019899164</v>
       </c>
       <c r="I2" t="n">
-        <v>6.285629862530848</v>
+        <v>6.285629862530855</v>
       </c>
       <c r="J2" t="n">
-        <v>3.712817612385198</v>
+        <v>3.712817612385196</v>
       </c>
       <c r="K2" t="n">
-        <v>1.313979829268308</v>
+        <v>1.313979829268313</v>
       </c>
       <c r="L2" t="n">
-        <v>8.601062491604328</v>
+        <v>6.04168104074221</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1097539390624849</v>
+        <v>0.1097539390624866</v>
       </c>
       <c r="C3" t="n">
-        <v>0.111965285108128</v>
+        <v>0.1119652851081286</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1097539390624849</v>
+        <v>0.1097539390624866</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1124083053094791</v>
+        <v>0.1124083053094799</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1124083053094792</v>
+        <v>0.1124083053094796</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1099313927684207</v>
+        <v>0.1099313927684223</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1097539390624849</v>
+        <v>0.1097539390624866</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1104600942969519</v>
+        <v>0.1104600942969527</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1097539390624849</v>
+        <v>0.1097539390624866</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1097539390624849</v>
+        <v>0.1097539390624866</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1097539390624849</v>
+        <v>0.1097539390624866</v>
       </c>
     </row>
     <row r="4">
@@ -6934,34 +6934,34 @@
         <v>6.295406702229701</v>
       </c>
       <c r="C4" t="n">
-        <v>6.386445299036725</v>
+        <v>6.386445299036729</v>
       </c>
       <c r="D4" t="n">
-        <v>76.68175208727961</v>
+        <v>6.284475865102093</v>
       </c>
       <c r="E4" t="n">
-        <v>6.366022226397444</v>
+        <v>6.36602222639744</v>
       </c>
       <c r="F4" t="n">
-        <v>6.385797721381627</v>
+        <v>6.385797721381632</v>
       </c>
       <c r="G4" t="n">
-        <v>6.295584155935631</v>
+        <v>76.69028749169556</v>
       </c>
       <c r="H4" t="n">
-        <v>76.68115386599675</v>
+        <v>76.68115386599669</v>
       </c>
       <c r="I4" t="n">
-        <v>6.296112857464177</v>
+        <v>6.296112857464182</v>
       </c>
       <c r="J4" t="n">
-        <v>6.305538008288076</v>
+        <v>76.68261827353919</v>
       </c>
       <c r="K4" t="n">
-        <v>6.203085458912573</v>
+        <v>6.203085458912575</v>
       </c>
       <c r="L4" t="n">
-        <v>6.292987927282445</v>
+        <v>6.292987927282444</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4450211781781048</v>
+        <v>0.445021178178109</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4457273334125739</v>
+        <v>0.4457273334125748</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4449962529063807</v>
+        <v>0.4449962529063849</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4457176950425318</v>
+        <v>0.4457176950425327</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4457176950425318</v>
+        <v>0.4457176950425327</v>
       </c>
       <c r="G5" t="n">
-        <v>0.445198631884046</v>
+        <v>0.4451986318840467</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4450211781781048</v>
+        <v>0.445021178178109</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4457273334125739</v>
+        <v>0.4457273334125748</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4450211781781048</v>
+        <v>0.445021178178109</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4450211781781048</v>
+        <v>0.445021178178109</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4450211781781048</v>
+        <v>0.445021178178109</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4861488086372677</v>
+        <v>0.4861488086372704</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7520022234645041</v>
+        <v>0.7520022234654696</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8061864014675404</v>
+        <v>0.8061864014675416</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6794925706552964</v>
+        <v>0.6794925706552972</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4952664875351874</v>
+        <v>0.4952664875351877</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7513992453583489</v>
+        <v>0.751399245358349</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7512217916524705</v>
+        <v>0.7512217916524742</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7519279468868791</v>
+        <v>0.7519279468868811</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7512738860515686</v>
+        <v>0.7512738860515691</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4812249418930741</v>
+        <v>0.4812249418930765</v>
       </c>
       <c r="L6" t="n">
-        <v>1.028112687417959</v>
+        <v>1.028112687417961</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.196134742285408</v>
+        <v>2.196134742285412</v>
       </c>
       <c r="C7" t="n">
-        <v>2.785120288197885</v>
+        <v>2.785120288197886</v>
       </c>
       <c r="D7" t="n">
-        <v>2.784413992148109</v>
+        <v>2.784413992148111</v>
       </c>
       <c r="E7" t="n">
-        <v>3.46398146982434</v>
+        <v>3.463981469824342</v>
       </c>
       <c r="F7" t="n">
-        <v>2.785119780690164</v>
+        <v>2.785119780690166</v>
       </c>
       <c r="G7" t="n">
-        <v>2.784591586669351</v>
+        <v>2.784591586669348</v>
       </c>
       <c r="H7" t="n">
-        <v>2.784414132963413</v>
+        <v>2.784414132963415</v>
       </c>
       <c r="I7" t="n">
-        <v>2.785120288197885</v>
+        <v>2.785120288197886</v>
       </c>
       <c r="J7" t="n">
-        <v>2.784414132963413</v>
+        <v>2.784414132963415</v>
       </c>
       <c r="K7" t="n">
-        <v>2.443562684426982</v>
+        <v>2.42973391631309</v>
       </c>
       <c r="L7" t="n">
-        <v>2.784414132963413</v>
+        <v>2.784414132963415</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1551329300517643</v>
+        <v>0.155132930051764</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05876899542765232</v>
+        <v>0.05876899542765249</v>
       </c>
       <c r="D8" t="n">
         <v>0.1402669799149822</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05876899542765232</v>
+        <v>0.05876899542765249</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05876899542765232</v>
+        <v>0.05876899542765249</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03223509121888155</v>
+        <v>0.03223509121888054</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.05884252829894025</v>
+        <v>-0.05884252829894066</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05876899542765232</v>
+        <v>0.05876899542765249</v>
       </c>
       <c r="J8" t="n">
-        <v>0.09185997356891586</v>
+        <v>0.09185997356891581</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1478624662736342</v>
+        <v>0.1478624662736343</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.01968881952231797</v>
+        <v>-0.01968881952231809</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1669034152827514</v>
+        <v>0.166903415282752</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1512165545996624</v>
+        <v>0.1512165545996625</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1608496030455105</v>
+        <v>0.16084960304551</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1512165545996624</v>
+        <v>0.1512165545996625</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1512165545996624</v>
+        <v>0.1512165545996625</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1170012468850651</v>
+        <v>0.1170012468850652</v>
       </c>
       <c r="H9" t="n">
-        <v>0.07997282804653222</v>
+        <v>0.0799728280465328</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1512165545996624</v>
+        <v>0.1512165545996625</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1411655065308517</v>
+        <v>0.1411655065308522</v>
       </c>
       <c r="K9" t="n">
-        <v>0.163943782541668</v>
+        <v>0.1639437825416672</v>
       </c>
       <c r="L9" t="n">
-        <v>0.095846990168677</v>
+        <v>0.1236548995783286</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.935596775540818</v>
+        <v>1.935596775540825</v>
       </c>
       <c r="C2" t="n">
-        <v>11.24097633360988</v>
+        <v>11.24097633360986</v>
       </c>
       <c r="D2" t="n">
-        <v>5.366935205520281</v>
+        <v>5.366935205520275</v>
       </c>
       <c r="E2" t="n">
-        <v>11.24097633360988</v>
+        <v>11.24097633360986</v>
       </c>
       <c r="F2" t="n">
-        <v>11.24097633360988</v>
+        <v>11.24097633360986</v>
       </c>
       <c r="G2" t="n">
-        <v>11.25967116556027</v>
+        <v>11.25967116556026</v>
       </c>
       <c r="H2" t="n">
-        <v>12.216025775349</v>
+        <v>12.21602577534901</v>
       </c>
       <c r="I2" t="n">
-        <v>11.24097633360988</v>
+        <v>11.24097633360986</v>
       </c>
       <c r="J2" t="n">
-        <v>9.8022639183569</v>
+        <v>9.802263918356921</v>
       </c>
       <c r="K2" t="n">
-        <v>4.763451613095168</v>
+        <v>4.763451613095184</v>
       </c>
       <c r="L2" t="n">
-        <v>9.162610375396797</v>
+        <v>9.162610375396804</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1363881210936265</v>
+        <v>0.1363881210936266</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1385702295647685</v>
+        <v>0.1385702295647688</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1363881210936265</v>
+        <v>0.1363881210936266</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1392690694197543</v>
+        <v>0.1392690694197547</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1392690694197543</v>
+        <v>0.1392690694197547</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1365542216370123</v>
+        <v>0.1365542216370129</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1363881210936265</v>
+        <v>0.1363881210936266</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1370273645063698</v>
+        <v>0.1370273645063703</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1363881210936265</v>
+        <v>0.1363881210936266</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1363881210936265</v>
+        <v>0.1363881210936266</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1363881210936265</v>
+        <v>0.1363881210936266</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.808100465057573</v>
+        <v>6.808100465057571</v>
       </c>
       <c r="C4" t="n">
-        <v>6.895829064712697</v>
+        <v>6.895829064712698</v>
       </c>
       <c r="D4" t="n">
-        <v>6.784711774524936</v>
+        <v>6.784711774524935</v>
       </c>
       <c r="E4" t="n">
         <v>6.872834972064436</v>
       </c>
       <c r="F4" t="n">
-        <v>6.89519413431949</v>
+        <v>6.895194134319492</v>
       </c>
       <c r="G4" t="n">
-        <v>82.38115071380848</v>
+        <v>82.38115071380844</v>
       </c>
       <c r="H4" t="n">
-        <v>82.36950406739656</v>
+        <v>82.36950406739658</v>
       </c>
       <c r="I4" t="n">
-        <v>6.808739708470334</v>
+        <v>82.38162385667775</v>
       </c>
       <c r="J4" t="n">
-        <v>82.37258098045179</v>
+        <v>82.3725809804517</v>
       </c>
       <c r="K4" t="n">
         <v>6.6966026545627</v>
       </c>
       <c r="L4" t="n">
-        <v>6.794858072435635</v>
+        <v>6.794858072435636</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5156887312146379</v>
+        <v>0.5156887312146384</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5163279746273816</v>
+        <v>0.5163279746273829</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5156615797736879</v>
+        <v>0.5156615797736883</v>
       </c>
       <c r="E5" t="n">
-        <v>0.516305206197734</v>
+        <v>0.5163052061977337</v>
       </c>
       <c r="F5" t="n">
-        <v>0.516305206197734</v>
+        <v>0.5163052061977337</v>
       </c>
       <c r="G5" t="n">
-        <v>0.515854831758025</v>
+        <v>0.515854831758026</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5156887312146379</v>
+        <v>0.5156887312146384</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5163279746273816</v>
+        <v>0.5163279746273829</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5156887312146379</v>
+        <v>0.5156887312146384</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5156887312146379</v>
+        <v>0.5156887312146384</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5156887312146379</v>
+        <v>0.5156887312146384</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.578170763305929</v>
+        <v>0.5781707633059302</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8901011422405739</v>
+        <v>0.8901011422417132</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9539214029144323</v>
+        <v>0.9539214029144333</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8049709163045697</v>
+        <v>0.8049709163045704</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5886777399176814</v>
+        <v>0.5886777399176822</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8895544993464276</v>
+        <v>0.8895544993464283</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8893883988029482</v>
+        <v>0.8893883988029491</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8900276422157832</v>
+        <v>0.8900276422157859</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8894495619424094</v>
+        <v>0.8894495619424124</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5723897359518531</v>
+        <v>0.5723897359518544</v>
       </c>
       <c r="L6" t="n">
-        <v>1.21448124263303</v>
+        <v>1.214481242633033</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.030148633076926</v>
+        <v>3.030148633076928</v>
       </c>
       <c r="C7" t="n">
-        <v>3.84435346498298</v>
+        <v>3.844353464982982</v>
       </c>
       <c r="D7" t="n">
-        <v>3.843714143901876</v>
+        <v>3.84371414390188</v>
       </c>
       <c r="E7" t="n">
-        <v>4.783190114780478</v>
+        <v>4.783190114780483</v>
       </c>
       <c r="F7" t="n">
-        <v>3.844352889993408</v>
+        <v>3.844352889993415</v>
       </c>
       <c r="G7" t="n">
-        <v>3.843880322113621</v>
+        <v>3.843880322113627</v>
       </c>
       <c r="H7" t="n">
-        <v>3.843714221570232</v>
+        <v>3.843714221570241</v>
       </c>
       <c r="I7" t="n">
-        <v>3.84435346498298</v>
+        <v>3.844353464982982</v>
       </c>
       <c r="J7" t="n">
-        <v>3.843714221570232</v>
+        <v>3.843714221570241</v>
       </c>
       <c r="K7" t="n">
-        <v>3.353206485942588</v>
+        <v>3.37233109181181</v>
       </c>
       <c r="L7" t="n">
-        <v>3.843714221570232</v>
+        <v>3.843714221570241</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1618666254982376</v>
+        <v>0.1618666254982379</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0237496263984806</v>
+        <v>-0.02374962639848077</v>
       </c>
       <c r="D8" t="n">
-        <v>0.07891792579542227</v>
+        <v>0.07891792579542328</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0237496263984806</v>
+        <v>-0.02374962639848077</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0237496263984806</v>
+        <v>-0.02374962639848077</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0542327218418921</v>
+        <v>-0.0542327218418916</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.06260928453641637</v>
+        <v>-0.0626092845364162</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0237496263984806</v>
+        <v>-0.02374962639848077</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.006037562813864184</v>
+        <v>-0.006037562813863835</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09490350862254279</v>
+        <v>0.09490350862254303</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5801370743997158</v>
+        <v>0.02610958177376049</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1842278494442251</v>
+        <v>0.1842278494442253</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1330208559588485</v>
+        <v>0.1330208559588489</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1504466585347383</v>
+        <v>0.150446658534739</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1330208559588485</v>
+        <v>0.1330208559588489</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1330208559588485</v>
+        <v>0.1330208559588489</v>
       </c>
       <c r="G9" t="n">
-        <v>0.09637744990544142</v>
+        <v>0.09637744990544191</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09304731854497231</v>
+        <v>0.09304731854497247</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1330208559588485</v>
+        <v>0.1330208559588489</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1159212113862655</v>
+        <v>0.1159212113862658</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1569599054726671</v>
+        <v>0.1569599054726674</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1174011554139569</v>
+        <v>0.1290686927471591</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7816677952031369</v>
+        <v>0.7816677952031362</v>
       </c>
       <c r="C2" t="n">
-        <v>8.653798097605126</v>
+        <v>8.653798097605105</v>
       </c>
       <c r="D2" t="n">
-        <v>4.055356773767122</v>
+        <v>4.055356773767141</v>
       </c>
       <c r="E2" t="n">
-        <v>8.653798097605124</v>
+        <v>8.653798097605105</v>
       </c>
       <c r="F2" t="n">
-        <v>8.653798097605124</v>
+        <v>8.653798097605105</v>
       </c>
       <c r="G2" t="n">
-        <v>8.684206566460707</v>
+        <v>8.68420656646075</v>
       </c>
       <c r="H2" t="n">
-        <v>20.01715371401263</v>
+        <v>20.01715371401261</v>
       </c>
       <c r="I2" t="n">
-        <v>8.653798097605126</v>
+        <v>8.653798097605105</v>
       </c>
       <c r="J2" t="n">
-        <v>7.073155172853325</v>
+        <v>7.073155172853319</v>
       </c>
       <c r="K2" t="n">
-        <v>2.709423653727304</v>
+        <v>2.709423653727302</v>
       </c>
       <c r="L2" t="n">
-        <v>8.251767688993361</v>
+        <v>16.6105278682193</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1251160959910735</v>
+        <v>0.1251160959910738</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1270352716762632</v>
+        <v>0.1270352716762625</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1251160959910735</v>
+        <v>0.1251160959910738</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1276362898016564</v>
+        <v>0.127636289801656</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1276362898016564</v>
+        <v>0.1276362898016559</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1252746608712634</v>
+        <v>0.1252746608712633</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1251160959910735</v>
+        <v>0.1251160959910738</v>
       </c>
       <c r="I3" t="n">
-        <v>0.125705047331626</v>
+        <v>0.1257050473316259</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1251160959910735</v>
+        <v>0.1251160959910738</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1251160959910735</v>
+        <v>0.1251160959910738</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1251160959910735</v>
+        <v>0.1251160959910738</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.330152088726252</v>
+        <v>76.74202006092014</v>
       </c>
       <c r="C4" t="n">
         <v>6.414586642359975</v>
       </c>
       <c r="D4" t="n">
-        <v>6.312902561857117</v>
+        <v>6.312902561857101</v>
       </c>
       <c r="E4" t="n">
         <v>6.393534306927027</v>
       </c>
       <c r="F4" t="n">
-        <v>6.414315756225553</v>
+        <v>6.414315756225554</v>
       </c>
       <c r="G4" t="n">
-        <v>76.74217862580034</v>
+        <v>6.33031065360643</v>
       </c>
       <c r="H4" t="n">
-        <v>76.73441838248155</v>
+        <v>76.73441838248156</v>
       </c>
       <c r="I4" t="n">
-        <v>76.7426090122607</v>
+        <v>76.74260901226069</v>
       </c>
       <c r="J4" t="n">
-        <v>76.73443788378961</v>
+        <v>6.335184170508335</v>
       </c>
       <c r="K4" t="n">
-        <v>6.229128527027517</v>
+        <v>6.229128527027519</v>
       </c>
       <c r="L4" t="n">
-        <v>6.321421243734709</v>
+        <v>6.321421243734705</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4737975788391111</v>
+        <v>0.4737975788391101</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4743865301796618</v>
+        <v>0.4743865301796612</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4737723417296021</v>
+        <v>0.4737723417296008</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4743911174898881</v>
+        <v>0.4743911174898875</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4743911174898881</v>
+        <v>0.4743911174898877</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4739561437192995</v>
+        <v>0.4739561437192986</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4737975788391111</v>
+        <v>0.4737975788391101</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4743865301796618</v>
+        <v>0.4743865301796612</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4737975788391111</v>
+        <v>0.4737975788391101</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4737975788391111</v>
+        <v>0.4737975788391101</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4737975788391111</v>
+        <v>0.4737975788391101</v>
       </c>
     </row>
     <row r="6">
@@ -7803,22 +7803,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5274928277395253</v>
+        <v>0.5274928277395254</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8119421736110116</v>
+        <v>0.8119421736121127</v>
       </c>
       <c r="D6" t="n">
-        <v>0.870102567657084</v>
+        <v>0.870102567657082</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7343175581756676</v>
+        <v>0.7343175581756671</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5370945939154756</v>
+        <v>0.5370945939154749</v>
       </c>
       <c r="G6" t="n">
-        <v>0.811419886710938</v>
+        <v>0.8114198867109383</v>
       </c>
       <c r="H6" t="n">
         <v>0.8112613218307608</v>
@@ -7827,10 +7827,10 @@
         <v>0.8118502731713026</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8113170904278441</v>
+        <v>0.8113170904278445</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5222216822793692</v>
+        <v>0.5222216822793693</v>
       </c>
       <c r="L6" t="n">
         <v>1.107681242203034</v>
@@ -7858,7 +7858,7 @@
         <v>3.170002546669376</v>
       </c>
       <c r="G7" t="n">
-        <v>3.16957281964342</v>
+        <v>3.169572819643418</v>
       </c>
       <c r="H7" t="n">
         <v>3.169414254763234</v>
@@ -7870,7 +7870,7 @@
         <v>3.169414254763234</v>
       </c>
       <c r="K7" t="n">
-        <v>2.781732607135464</v>
+        <v>2.326892797068828</v>
       </c>
       <c r="L7" t="n">
         <v>3.169414254763234</v>
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1796247761187994</v>
+        <v>0.1796247761187996</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01164206160555393</v>
+        <v>0.01164206160555377</v>
       </c>
       <c r="D8" t="n">
-        <v>0.09189956218826717</v>
+        <v>0.09189956218826728</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01164206160555393</v>
+        <v>0.01164206160555377</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01164206160555393</v>
+        <v>0.01164206160555377</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.02367976757673168</v>
+        <v>-0.02367976757673215</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.289113337286837</v>
+        <v>-0.2891133372868371</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01164206160555393</v>
+        <v>0.01164206160555377</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03375729726814557</v>
+        <v>0.0337572972681456</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1283011324233336</v>
+        <v>0.1283011324233339</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1821746635404057</v>
+        <v>0.01994915364911504</v>
       </c>
     </row>
     <row r="9">
@@ -7929,7 +7929,7 @@
         <v>0.1423324119803571</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1509806856470386</v>
+        <v>0.1509806856470385</v>
       </c>
       <c r="E9" t="n">
         <v>0.1423324119803571</v>
@@ -7938,22 +7938,22 @@
         <v>0.1423324119803571</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1040364734336209</v>
+        <v>0.1040364734336208</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.003755814764222959</v>
+        <v>-0.003755814764223042</v>
       </c>
       <c r="I9" t="n">
         <v>0.1423324119803571</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1273583578232879</v>
+        <v>0.127358357823288</v>
       </c>
       <c r="K9" t="n">
         <v>0.1658075967381862</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03963051538215524</v>
+        <v>0.1218053231733345</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen water use results.xlsx
+++ b/Results/Hydrogen/hydrogen water use results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.439624231261436</v>
+        <v>3.439624231261468</v>
       </c>
       <c r="C2" t="n">
-        <v>11.1215982660223</v>
+        <v>11.12159826602231</v>
       </c>
       <c r="D2" t="n">
-        <v>6.349099451425015</v>
+        <v>6.349099451425012</v>
       </c>
       <c r="E2" t="n">
-        <v>11.1215982660223</v>
+        <v>11.12159826602231</v>
       </c>
       <c r="F2" t="n">
-        <v>11.1215982660223</v>
+        <v>11.12159826602231</v>
       </c>
       <c r="G2" t="n">
-        <v>11.62370516325154</v>
+        <v>11.62370516325139</v>
       </c>
       <c r="H2" t="n">
         <v>13.88600276223235</v>
       </c>
       <c r="I2" t="n">
-        <v>11.1215982660223</v>
+        <v>11.12159826602231</v>
       </c>
       <c r="J2" t="n">
-        <v>9.768892795319555</v>
+        <v>9.768892795319571</v>
       </c>
       <c r="K2" t="n">
-        <v>5.519665081932722</v>
+        <v>5.519665081932723</v>
       </c>
       <c r="L2" t="n">
-        <v>60.83597155084687</v>
+        <v>5.166196394550684</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1326954221235301</v>
+        <v>0.1326954221235297</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1342994351034808</v>
+        <v>0.134299435103481</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1326954221235301</v>
+        <v>0.1326954221235297</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1350207924592659</v>
+        <v>0.135020792459265</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1350207924592648</v>
+        <v>0.135020792459265</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1328425964323178</v>
+        <v>0.1328425964323179</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1326954221235301</v>
+        <v>0.1326954221235297</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1332124444142265</v>
+        <v>0.1332124444142258</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1326954221235301</v>
+        <v>0.1326954221235297</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1326954221235301</v>
+        <v>0.1326954221235297</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1326954221235301</v>
+        <v>0.1326954221235297</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.258533098663344</v>
+        <v>7.258533098663348</v>
       </c>
       <c r="C4" t="n">
-        <v>7.35060311233078</v>
+        <v>7.350603112330774</v>
       </c>
       <c r="D4" t="n">
-        <v>7.235654266080064</v>
+        <v>7.235653301838506</v>
       </c>
       <c r="E4" t="n">
-        <v>7.326322319997776</v>
+        <v>7.326322319997771</v>
       </c>
       <c r="F4" t="n">
-        <v>7.350809588467327</v>
+        <v>7.350809588467324</v>
       </c>
       <c r="G4" t="n">
-        <v>88.01392742817166</v>
+        <v>88.0139274281717</v>
       </c>
       <c r="H4" t="n">
-        <v>88.00268980547105</v>
+        <v>88.00268980547104</v>
       </c>
       <c r="I4" t="n">
-        <v>7.259050120954027</v>
+        <v>88.01429727615353</v>
       </c>
       <c r="J4" t="n">
-        <v>7.260828123245609</v>
+        <v>88.00565904674765</v>
       </c>
       <c r="K4" t="n">
-        <v>7.141444264294877</v>
+        <v>7.14144426429487</v>
       </c>
       <c r="L4" t="n">
-        <v>7.242955024532694</v>
+        <v>7.242955024532695</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5333670001299298</v>
+        <v>0.5333670001299307</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5338840224206293</v>
+        <v>0.5338840224206273</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5333383863704656</v>
+        <v>0.5333383863704655</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5338289742157486</v>
+        <v>0.5338289742157477</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5338289742157486</v>
+        <v>0.5338289742157477</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5335141744387192</v>
+        <v>0.5335141744387183</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5333670001299298</v>
+        <v>0.5333670001299307</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5338840224206293</v>
+        <v>0.5338840224206273</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5333670001299298</v>
+        <v>0.5333670001299307</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5333670001299298</v>
+        <v>0.5333670001299307</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5333670001299298</v>
+        <v>0.5333670001299307</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5948421360649256</v>
+        <v>0.5948421360649236</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9204113996034943</v>
+        <v>0.9204113996044128</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9872391198765218</v>
+        <v>0.9872391198765184</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8315128439041963</v>
+        <v>0.831512843904193</v>
       </c>
       <c r="F6" t="n">
-        <v>0.605645547704611</v>
+        <v>0.6056455477046099</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9199943765131666</v>
+        <v>0.919994376513165</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9198472022043537</v>
+        <v>0.919847202204352</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9203642244950765</v>
+        <v>0.9203642244950748</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9199110749746459</v>
+        <v>0.919911074974642</v>
       </c>
       <c r="K6" t="n">
         <v>0.5888050001077247</v>
       </c>
       <c r="L6" t="n">
-        <v>1.259342170231813</v>
+        <v>1.259342170231809</v>
       </c>
     </row>
     <row r="7">
@@ -718,34 +718,34 @@
         <v>3.609862027412149</v>
       </c>
       <c r="C7" t="n">
-        <v>4.58565779597437</v>
+        <v>4.585657795974369</v>
       </c>
       <c r="D7" t="n">
-        <v>4.585140695944696</v>
+        <v>4.585140695944693</v>
       </c>
       <c r="E7" t="n">
-        <v>5.711107969243986</v>
+        <v>5.711107969243984</v>
       </c>
       <c r="F7" t="n">
         <v>4.585657195650964</v>
       </c>
       <c r="G7" t="n">
-        <v>4.585287947992467</v>
+        <v>4.585287947992464</v>
       </c>
       <c r="H7" t="n">
-        <v>4.585140773683679</v>
+        <v>4.585140773683677</v>
       </c>
       <c r="I7" t="n">
-        <v>4.58565779597437</v>
+        <v>4.585657795974369</v>
       </c>
       <c r="J7" t="n">
-        <v>4.585140773683679</v>
+        <v>4.585140773683677</v>
       </c>
       <c r="K7" t="n">
-        <v>4.020060405182281</v>
+        <v>3.357090765635855</v>
       </c>
       <c r="L7" t="n">
-        <v>4.585140773683679</v>
+        <v>4.585140773683677</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1263338467248824</v>
+        <v>0.1263338467248802</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.001383743702258953</v>
+        <v>-0.001383743702259518</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06542128041424598</v>
+        <v>0.06542128041424546</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.001383743702258953</v>
+        <v>-0.001383743702259518</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.001383743702258953</v>
+        <v>-0.001383743702259518</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.04182941074571987</v>
+        <v>-0.04182941074571948</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.06255020930605829</v>
+        <v>-0.06255020930605792</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.001383743702258953</v>
+        <v>-0.001383743702259518</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002967670476629723</v>
+        <v>0.00296767047662938</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0832097126085459</v>
+        <v>0.08320971260854661</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.9701730720139558</v>
+        <v>-0.9701730720139556</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.166767594389559</v>
+        <v>0.1667675943895594</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1376874701417771</v>
+        <v>0.1376874701417768</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1419618026248573</v>
+        <v>0.1419618026248569</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1376874701417771</v>
+        <v>0.1376874701417768</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1376874701417771</v>
+        <v>0.1376874701417768</v>
       </c>
       <c r="G9" t="n">
-        <v>0.09838358379481844</v>
+        <v>0.09838358379481724</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09007856925249616</v>
+        <v>0.09007856925249601</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1376874701417771</v>
+        <v>0.1376874701417768</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1165956129310425</v>
+        <v>0.1165956129310424</v>
       </c>
       <c r="K9" t="n">
-        <v>0.149209463941772</v>
+        <v>0.1492094639417718</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2789610159703704</v>
+        <v>0.1586872849558668</v>
       </c>
     </row>
   </sheetData>
@@ -911,31 +911,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7118535288306241</v>
+        <v>0.7118535288306262</v>
       </c>
       <c r="C2" t="n">
-        <v>6.655692650504908</v>
+        <v>6.655692650504924</v>
       </c>
       <c r="D2" t="n">
-        <v>2.820634643327078</v>
+        <v>2.820634643327075</v>
       </c>
       <c r="E2" t="n">
-        <v>6.655692650504908</v>
+        <v>6.655692650504924</v>
       </c>
       <c r="F2" t="n">
-        <v>6.655692650504908</v>
+        <v>6.655692650504924</v>
       </c>
       <c r="G2" t="n">
-        <v>7.288786600455305</v>
+        <v>7.288786600455294</v>
       </c>
       <c r="H2" t="n">
-        <v>12.91212733602356</v>
+        <v>12.91212733602359</v>
       </c>
       <c r="I2" t="n">
-        <v>6.655692650504908</v>
+        <v>6.655692650504924</v>
       </c>
       <c r="J2" t="n">
-        <v>5.065990580515678</v>
+        <v>5.065990580515675</v>
       </c>
       <c r="K2" t="n">
         <v>1.799225528864002</v>
@@ -954,25 +954,25 @@
         <v>0.1145712481990981</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1157740130120039</v>
+        <v>0.1157740130120042</v>
       </c>
       <c r="D3" t="n">
         <v>0.1145712481990981</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1163419360755719</v>
+        <v>0.1163419360755726</v>
       </c>
       <c r="F3" t="n">
-        <v>0.116341936075572</v>
+        <v>0.1163419360755725</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1147075538157962</v>
+        <v>0.1147075538157959</v>
       </c>
       <c r="H3" t="n">
         <v>0.1145712481990981</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1150171810686164</v>
+        <v>0.1150171810686167</v>
       </c>
       <c r="J3" t="n">
         <v>0.1145712481990981</v>
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.71266880094456</v>
+        <v>6.309526125393175</v>
       </c>
       <c r="C4" t="n">
-        <v>6.39363181461691</v>
+        <v>6.39363181461692</v>
       </c>
       <c r="D4" t="n">
-        <v>76.70396440073259</v>
+        <v>76.70396440073247</v>
       </c>
       <c r="E4" t="n">
-        <v>6.373020638388404</v>
+        <v>6.373020638388395</v>
       </c>
       <c r="F4" t="n">
-        <v>6.394357202734737</v>
+        <v>6.394357202734736</v>
       </c>
       <c r="G4" t="n">
-        <v>6.309662431009874</v>
+        <v>76.71280510656125</v>
       </c>
       <c r="H4" t="n">
-        <v>76.70350266186414</v>
+        <v>76.70350266186425</v>
       </c>
       <c r="I4" t="n">
-        <v>6.30997205826271</v>
+        <v>6.309972058262712</v>
       </c>
       <c r="J4" t="n">
-        <v>76.70487661142803</v>
+        <v>6.315093604000207</v>
       </c>
       <c r="K4" t="n">
-        <v>6.21097631320161</v>
+        <v>6.210976313201614</v>
       </c>
       <c r="L4" t="n">
-        <v>6.301523920819232</v>
+        <v>6.301523920819235</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4564729133722887</v>
+        <v>0.4564729133722897</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4569188462418082</v>
+        <v>0.4569188462418085</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4564479264436359</v>
+        <v>0.4564479264436366</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4569069855778612</v>
+        <v>0.4569069855778615</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4569069855778612</v>
+        <v>0.4569069855778615</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4566092189889868</v>
+        <v>0.4566092189889872</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4564729133722887</v>
+        <v>0.4564729133722897</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4569188462418082</v>
+        <v>0.4569188462418085</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4564729133722887</v>
+        <v>0.4564729133722897</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4564729133722887</v>
+        <v>0.4564729133722897</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4564729133722887</v>
+        <v>0.4564729133722897</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5049580246660916</v>
+        <v>0.504958024666092</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7807390583232781</v>
+        <v>0.7807390583243143</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8372960394462834</v>
+        <v>0.8372960394462839</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7054431074730159</v>
+        <v>0.7054431074730166</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5141371328314448</v>
+        <v>0.5141371328314451</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7803552087567657</v>
+        <v>0.7803552087567679</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7802189031400867</v>
+        <v>0.7802189031400875</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7806648360095879</v>
+        <v>0.7806648360095887</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7802729997487807</v>
+        <v>0.7802729997487816</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4998449125336688</v>
+        <v>0.4998449125336695</v>
       </c>
       <c r="L6" t="n">
-        <v>1.067751907606604</v>
+        <v>1.067751907606605</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.23214021413756</v>
+        <v>2.232140214137559</v>
       </c>
       <c r="C7" t="n">
-        <v>2.830055567786525</v>
+        <v>2.830055567786526</v>
       </c>
       <c r="D7" t="n">
         <v>2.82960949358798</v>
       </c>
       <c r="E7" t="n">
-        <v>3.519521793887515</v>
+        <v>3.519521793887518</v>
       </c>
       <c r="F7" t="n">
-        <v>2.830055016328394</v>
+        <v>2.830055016328391</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8297459405337</v>
+        <v>2.829745940533702</v>
       </c>
       <c r="H7" t="n">
-        <v>2.829609634917012</v>
+        <v>2.829609634917014</v>
       </c>
       <c r="I7" t="n">
-        <v>2.830055567786525</v>
+        <v>2.830055567786526</v>
       </c>
       <c r="J7" t="n">
-        <v>2.829609634917012</v>
+        <v>2.829609634917014</v>
       </c>
       <c r="K7" t="n">
         <v>2.483433446631701</v>
       </c>
       <c r="L7" t="n">
-        <v>2.829609634917012</v>
+        <v>2.829609634917014</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1721194478490138</v>
+        <v>0.1721194478490135</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05434705816927164</v>
+        <v>0.05434705816927196</v>
       </c>
       <c r="D8" t="n">
-        <v>0.116552782562676</v>
+        <v>0.1165527825626753</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05434705816927164</v>
+        <v>0.05434705816927196</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05434705816927164</v>
+        <v>0.05434705816927196</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004588838981103498</v>
+        <v>0.00458883898110295</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1095200301691669</v>
+        <v>-0.1095200301691682</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05434705816927164</v>
+        <v>0.05434705816927196</v>
       </c>
       <c r="J8" t="n">
-        <v>0.07039512462822818</v>
+        <v>0.07039512462822833</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1425276679479096</v>
+        <v>0.1425276679479086</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07765472176836023</v>
+        <v>0.07765472176835879</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1783826094603088</v>
+        <v>0.1783826094603082</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1528032890046519</v>
+        <v>0.1528032890046521</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1557524918424419</v>
+        <v>0.1557524918424414</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1528032890046519</v>
+        <v>0.1528032890046521</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1528032890046519</v>
+        <v>0.1528032890046521</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1101990785857036</v>
+        <v>0.1101990785857037</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06394737487717543</v>
+        <v>0.06394737487717436</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1528032890046519</v>
+        <v>0.1528032890046521</v>
       </c>
       <c r="J9" t="n">
         <v>0.1369948831519547</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1663323434294181</v>
+        <v>0.1663323434294177</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09784623639815405</v>
+        <v>0.1399894717486868</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.51258613069285</v>
+        <v>31.51258613069282</v>
       </c>
       <c r="C2" t="n">
-        <v>31.14700304910594</v>
+        <v>31.14700304910593</v>
       </c>
       <c r="D2" t="n">
-        <v>4.161346424092904</v>
+        <v>4.161346424092906</v>
       </c>
       <c r="E2" t="n">
-        <v>5.385823060346453</v>
+        <v>5.385823060346454</v>
       </c>
       <c r="F2" t="n">
-        <v>5.385823060346453</v>
+        <v>5.385823060346454</v>
       </c>
       <c r="G2" t="n">
         <v>9.528743579374673</v>
       </c>
       <c r="H2" t="n">
-        <v>11.78613593958424</v>
+        <v>11.78613593958423</v>
       </c>
       <c r="I2" t="n">
-        <v>5.385823060346453</v>
+        <v>5.385823060346454</v>
       </c>
       <c r="J2" t="n">
-        <v>7.272197841527317</v>
+        <v>7.272197841527303</v>
       </c>
       <c r="K2" t="n">
-        <v>3.576855571447788</v>
+        <v>3.576855571447756</v>
       </c>
       <c r="L2" t="n">
-        <v>22.88219238623097</v>
+        <v>22.88219238623095</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1384784270671027</v>
+        <v>0.138478427067102</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1543650625339987</v>
+        <v>0.1543650625339988</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1384784270671028</v>
+        <v>0.138478427067102</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1399521649656471</v>
+        <v>0.139952164965647</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1399521649656471</v>
+        <v>0.1399521649656469</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1384845533981114</v>
+        <v>0.1384845533981125</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1384784270671028</v>
+        <v>0.1384784270671022</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1380877518516942</v>
+        <v>0.138087751851694</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1384784270671028</v>
+        <v>0.1384784270671022</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1384784270671028</v>
+        <v>0.138478427067102</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1384784270671028</v>
+        <v>0.138478427067102</v>
       </c>
     </row>
     <row r="4">
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.713773802921841</v>
+        <v>81.06373347234387</v>
       </c>
       <c r="C4" t="n">
-        <v>6.846811482937482</v>
+        <v>6.846811482937483</v>
       </c>
       <c r="D4" t="n">
-        <v>6.697796422192252</v>
+        <v>6.697795672400777</v>
       </c>
       <c r="E4" t="n">
         <v>6.771269933863173</v>
@@ -1402,13 +1402,13 @@
         <v>6.801045541566104</v>
       </c>
       <c r="G4" t="n">
-        <v>81.0637395986749</v>
+        <v>6.713779929252857</v>
       </c>
       <c r="H4" t="n">
-        <v>81.06014079130671</v>
+        <v>81.06014079130672</v>
       </c>
       <c r="I4" t="n">
-        <v>81.06334279712856</v>
+        <v>6.713383127706468</v>
       </c>
       <c r="J4" t="n">
         <v>81.0592261482302</v>
@@ -1417,7 +1417,7 @@
         <v>6.611812573007168</v>
       </c>
       <c r="L4" t="n">
-        <v>6.71016136221049</v>
+        <v>6.710161362210495</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5010376166168492</v>
+        <v>0.501037616616849</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5023204149031725</v>
+        <v>0.5023204149031735</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5010113859166012</v>
+        <v>0.5010113859166004</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5014795932909457</v>
+        <v>0.5014795932909454</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5014795932909457</v>
+        <v>0.5014795932909454</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5010437429478581</v>
+        <v>0.5010437429478584</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5010376166168492</v>
+        <v>0.501037616616849</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5006469414014416</v>
+        <v>0.5006469414014421</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5010376166168492</v>
+        <v>0.501037616616849</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5010376166168492</v>
+        <v>0.501037616616849</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5010376166168492</v>
+        <v>0.501037616616849</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5582012827884353</v>
+        <v>0.5582012827884367</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8566984653851724</v>
+        <v>0.8566984653851716</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9159734420130122</v>
+        <v>0.9159734420130131</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7738810168502029</v>
+        <v>0.7738810168502043</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5677160765136821</v>
+        <v>0.5677160765136824</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8545342644950048</v>
+        <v>0.8545342644950051</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8545281381641456</v>
+        <v>0.8545281381641464</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8541374629485868</v>
+        <v>0.8541374629485875</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8545863748298248</v>
+        <v>0.8545863748298258</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5526968593199451</v>
+        <v>0.5526968593199448</v>
       </c>
       <c r="L6" t="n">
-        <v>1.164066317004991</v>
+        <v>1.164066317004995</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.912316434754236</v>
+        <v>2.912316434754235</v>
       </c>
       <c r="C7" t="n">
-        <v>3.693619253980632</v>
+        <v>3.693619253980628</v>
       </c>
       <c r="D7" t="n">
-        <v>3.692336249129769</v>
+        <v>3.692336249129771</v>
       </c>
       <c r="E7" t="n">
-        <v>4.592071269113804</v>
+        <v>4.592071269113797</v>
       </c>
       <c r="F7" t="n">
-        <v>3.691945068715195</v>
+        <v>3.691945068715192</v>
       </c>
       <c r="G7" t="n">
-        <v>3.692342582025328</v>
+        <v>3.692342582025329</v>
       </c>
       <c r="H7" t="n">
-        <v>3.692336455694306</v>
+        <v>3.692336455694309</v>
       </c>
       <c r="I7" t="n">
-        <v>3.691945780478899</v>
+        <v>3.691945780478897</v>
       </c>
       <c r="J7" t="n">
-        <v>3.692336455694306</v>
+        <v>3.692336455694309</v>
       </c>
       <c r="K7" t="n">
-        <v>3.240389705306613</v>
+        <v>3.24038970530661</v>
       </c>
       <c r="L7" t="n">
-        <v>3.692336455694306</v>
+        <v>3.692336455694309</v>
       </c>
     </row>
     <row r="8">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.5159576527335724</v>
+        <v>-0.5159576527335714</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.4736856320672789</v>
+        <v>-0.4736856320672787</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1255482921546076</v>
+        <v>0.1255482921546074</v>
       </c>
       <c r="E8" t="n">
         <v>0.1033043769630915</v>
@@ -1562,22 +1562,22 @@
         <v>0.1033043769630915</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.01982907376810003</v>
+        <v>-0.01982907376809934</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.01884904215593347</v>
+        <v>-0.01884904215593358</v>
       </c>
       <c r="I8" t="n">
         <v>0.1033043769630915</v>
       </c>
       <c r="J8" t="n">
-        <v>0.08562074474926556</v>
+        <v>0.08562074474926547</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1436105725870183</v>
+        <v>0.143610572587019</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2609662896058104</v>
+        <v>-0.2609662896058101</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.1013064032292409</v>
+        <v>-0.1013064032292402</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0631866875147858</v>
+        <v>-0.06318668751478593</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1780579855020243</v>
+        <v>0.1780579855020244</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1717686551815937</v>
+        <v>0.1717686551815935</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1717686551815937</v>
+        <v>0.1717686551815935</v>
       </c>
       <c r="G9" t="n">
         <v>0.1028952812147804</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1194640290876019</v>
+        <v>0.1194640290876018</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1717686551815937</v>
+        <v>0.1717686551815935</v>
       </c>
       <c r="J9" t="n">
-        <v>0.175478302429762</v>
+        <v>0.1754783024297619</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1878514825645781</v>
+        <v>0.1878514825645785</v>
       </c>
       <c r="L9" t="n">
-        <v>0.006478266012904948</v>
+        <v>0.006478266012905306</v>
       </c>
     </row>
   </sheetData>
@@ -1703,34 +1703,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26.87624837199768</v>
+        <v>26.87624837199769</v>
       </c>
       <c r="C2" t="n">
-        <v>25.76209792933399</v>
+        <v>25.76209792933401</v>
       </c>
       <c r="D2" t="n">
-        <v>3.433094723222047</v>
+        <v>3.433094723222044</v>
       </c>
       <c r="E2" t="n">
-        <v>3.859926473209583</v>
+        <v>3.859926473209593</v>
       </c>
       <c r="F2" t="n">
-        <v>3.859926473209583</v>
+        <v>3.859926473209593</v>
       </c>
       <c r="G2" t="n">
-        <v>7.294177192859855</v>
+        <v>7.294177192859902</v>
       </c>
       <c r="H2" t="n">
-        <v>8.759883420382835</v>
+        <v>8.759883420382838</v>
       </c>
       <c r="I2" t="n">
-        <v>3.859926473209583</v>
+        <v>3.859926473209593</v>
       </c>
       <c r="J2" t="n">
-        <v>5.035907294438374</v>
+        <v>5.035907294438378</v>
       </c>
       <c r="K2" t="n">
-        <v>2.459873347612426</v>
+        <v>2.459873347612429</v>
       </c>
       <c r="L2" t="n">
         <v>15.47557977994028</v>
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1327651491708629</v>
+        <v>0.1327651491708655</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1446769134324142</v>
+        <v>0.1446769134324144</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1327651491708629</v>
+        <v>0.1327651491708654</v>
       </c>
       <c r="E3" t="n">
-        <v>0.14922538124759</v>
+        <v>0.1492253812475904</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1492253812475904</v>
+        <v>0.1492253812475901</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1328077448277189</v>
+        <v>0.1328077448277207</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1327651491708629</v>
+        <v>0.1327651491708654</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1325999138544267</v>
+        <v>0.1325999138544263</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1327651491708629</v>
+        <v>0.1327651491708655</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1327651491708629</v>
+        <v>0.1327651491708654</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1327651491708629</v>
+        <v>0.1327651491708654</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.76578189773775</v>
+        <v>76.76578189773774</v>
       </c>
       <c r="C4" t="n">
-        <v>6.473198922361655</v>
+        <v>6.473198922361651</v>
       </c>
       <c r="D4" t="n">
         <v>76.76347942331797</v>
       </c>
       <c r="E4" t="n">
-        <v>6.409329729042336</v>
+        <v>6.409329729042335</v>
       </c>
       <c r="F4" t="n">
-        <v>6.435575107539365</v>
+        <v>6.435575107539364</v>
       </c>
       <c r="G4" t="n">
-        <v>6.351209092361463</v>
+        <v>76.76582449339472</v>
       </c>
       <c r="H4" t="n">
-        <v>76.76718094209853</v>
+        <v>76.76718094209851</v>
       </c>
       <c r="I4" t="n">
-        <v>6.35100126138815</v>
+        <v>6.351001261388147</v>
       </c>
       <c r="J4" t="n">
-        <v>6.358736332975106</v>
+        <v>6.358736332975104</v>
       </c>
       <c r="K4" t="n">
-        <v>6.25593735403081</v>
+        <v>6.255937354030812</v>
       </c>
       <c r="L4" t="n">
-        <v>6.346755004634733</v>
+        <v>6.346755004634739</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4782484487262416</v>
+        <v>0.4782484487262429</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4795085285769677</v>
+        <v>0.4795085285769676</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4782237286953454</v>
+        <v>0.4782237286953442</v>
       </c>
       <c r="E5" t="n">
-        <v>0.483085792077732</v>
+        <v>0.4830857920777325</v>
       </c>
       <c r="F5" t="n">
-        <v>0.483085792077732</v>
+        <v>0.4830857920777325</v>
       </c>
       <c r="G5" t="n">
-        <v>0.478291044383098</v>
+        <v>0.4782910443830968</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4782484487262416</v>
+        <v>0.4782484487262429</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4780832134098031</v>
+        <v>0.478083213409803</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4782484487262416</v>
+        <v>0.4782484487262429</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4782484487262416</v>
+        <v>0.4782484487262429</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4782484487262416</v>
+        <v>0.4782484487262429</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5302104860085178</v>
+        <v>0.5302104860085226</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8189715355392454</v>
+        <v>0.8189715355371507</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8714485973337972</v>
+        <v>0.8714485973337975</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7397271898901379</v>
+        <v>0.7397271898901386</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5420032902093844</v>
+        <v>0.5420032902093841</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8128855164629425</v>
+        <v>0.8128855164629424</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8128429208067981</v>
+        <v>0.8128429208068028</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8126776854896478</v>
+        <v>0.812677685489647</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8128984660846397</v>
+        <v>0.8128984660846411</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5249604434354841</v>
+        <v>0.5249604434354859</v>
       </c>
       <c r="L6" t="n">
-        <v>1.108076132208389</v>
+        <v>1.108076132208395</v>
       </c>
     </row>
     <row r="7">
@@ -1903,16 +1903,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.453714945889832</v>
+        <v>2.453714945889836</v>
       </c>
       <c r="C7" t="n">
-        <v>3.109946878782843</v>
+        <v>3.109946878782845</v>
       </c>
       <c r="D7" t="n">
-        <v>3.108686642004112</v>
+        <v>3.108686642004116</v>
       </c>
       <c r="E7" t="n">
-        <v>3.86434430615141</v>
+        <v>3.864344306151412</v>
       </c>
       <c r="F7" t="n">
         <v>3.108520966520036</v>
@@ -1924,13 +1924,13 @@
         <v>3.108686798932111</v>
       </c>
       <c r="I7" t="n">
-        <v>3.108521563615674</v>
+        <v>3.108521563615677</v>
       </c>
       <c r="J7" t="n">
         <v>3.108686798932111</v>
       </c>
       <c r="K7" t="n">
-        <v>2.729193469003372</v>
+        <v>2.729193469003374</v>
       </c>
       <c r="L7" t="n">
         <v>3.108686798932111</v>
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.4541500058592498</v>
+        <v>-0.4541500058592491</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.3946561694398132</v>
+        <v>-0.3946561694398136</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1341980926772337</v>
+        <v>0.1341980926772343</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1355986892530429</v>
+        <v>0.1355986892530431</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1355986892530429</v>
+        <v>0.1355986892530431</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01790183161302218</v>
+        <v>0.01790183161302242</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02912395165459311</v>
+        <v>0.02912395165459515</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1355986892530429</v>
+        <v>0.1355986892530431</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1355971541960847</v>
+        <v>0.1355971541960868</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1738196232214909</v>
+        <v>0.173819623221495</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1285058707677892</v>
+        <v>-0.1285058707677876</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.08094786093439418</v>
+        <v>-0.08094786093439318</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.03655390794187766</v>
+        <v>-0.03655390794187817</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1794836066168643</v>
+        <v>0.1794836066168638</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1863277045237186</v>
+        <v>0.186327704523719</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1863277045237186</v>
+        <v>0.186327704523719</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1164378101339422</v>
+        <v>0.1164378101339429</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1368579479862851</v>
+        <v>0.1368579479862873</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1863277045237186</v>
+        <v>0.186327704523719</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1999665151467923</v>
+        <v>0.199966515146793</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2046448448180988</v>
+        <v>0.2046448448181022</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06139132317238408</v>
+        <v>0.06139132317238483</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24.7350874898961</v>
+        <v>24.73508748989613</v>
       </c>
       <c r="C2" t="n">
-        <v>23.06506662457047</v>
+        <v>23.06506662457045</v>
       </c>
       <c r="D2" t="n">
-        <v>2.994876042036964</v>
+        <v>2.994876042036948</v>
       </c>
       <c r="E2" t="n">
-        <v>2.860892284464398</v>
+        <v>2.860892284464396</v>
       </c>
       <c r="F2" t="n">
-        <v>2.860892284464398</v>
+        <v>2.860892284464396</v>
       </c>
       <c r="G2" t="n">
-        <v>6.178776269820382</v>
+        <v>6.178776269820399</v>
       </c>
       <c r="H2" t="n">
-        <v>6.953570353833189</v>
+        <v>6.953570353833179</v>
       </c>
       <c r="I2" t="n">
-        <v>2.860892284464398</v>
+        <v>2.860892284464396</v>
       </c>
       <c r="J2" t="n">
-        <v>3.738696769585222</v>
+        <v>3.73869676958522</v>
       </c>
       <c r="K2" t="n">
-        <v>1.904947391413664</v>
+        <v>1.904947391413651</v>
       </c>
       <c r="L2" t="n">
-        <v>11.3768823596719</v>
+        <v>11.37688235967189</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1297091303454125</v>
+        <v>0.1297091303454118</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1399544474196139</v>
+        <v>0.1399544474196147</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1297091303454125</v>
+        <v>0.1297091303454118</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1485641955031673</v>
+        <v>0.1485641955031667</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1485641955031673</v>
+        <v>0.148564195503167</v>
       </c>
       <c r="G3" t="n">
         <v>0.1297552238740875</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1297091303454125</v>
+        <v>0.1297091303454118</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1295701762468544</v>
+        <v>0.1295701762468545</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1297091303454125</v>
+        <v>0.1297091303454118</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1297091303454125</v>
+        <v>0.1297091303454118</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1297091303454125</v>
+        <v>0.1297091303454118</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.340918053472512</v>
+        <v>6.340918053472508</v>
       </c>
       <c r="C4" t="n">
-        <v>6.45995883721428</v>
+        <v>6.459958837214288</v>
       </c>
       <c r="D4" t="n">
-        <v>6.32930792760466</v>
+        <v>6.329308444727283</v>
       </c>
       <c r="E4" t="n">
-        <v>6.400273928905198</v>
+        <v>6.400273928905199</v>
       </c>
       <c r="F4" t="n">
-        <v>6.425929326720243</v>
+        <v>6.425929326720244</v>
       </c>
       <c r="G4" t="n">
-        <v>76.75007734322223</v>
+        <v>76.75007734322222</v>
       </c>
       <c r="H4" t="n">
-        <v>76.75392831738586</v>
+        <v>76.75392831738584</v>
       </c>
       <c r="I4" t="n">
-        <v>76.749892295595</v>
+        <v>76.74989229559507</v>
       </c>
       <c r="J4" t="n">
         <v>76.74924894087522</v>
       </c>
       <c r="K4" t="n">
-        <v>6.246738888559154</v>
+        <v>6.246738888559136</v>
       </c>
       <c r="L4" t="n">
-        <v>6.335940129756301</v>
+        <v>6.335940129756302</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4732848649879643</v>
+        <v>0.4732848649879634</v>
       </c>
       <c r="C5" t="n">
         <v>0.4744993475914952</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4732595213872459</v>
+        <v>0.4732595213872446</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4790502297284879</v>
+        <v>0.4790502297284866</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4790502297284879</v>
+        <v>0.4790502297284866</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4733309585166389</v>
+        <v>0.4733309585166383</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4732848649879643</v>
+        <v>0.4732848649879634</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4731459108894057</v>
+        <v>0.4731459108894047</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4732848649879643</v>
+        <v>0.4732848649879634</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4732848649879643</v>
+        <v>0.4732848649879634</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4732848649879643</v>
+        <v>0.4732848649879634</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5232147970132054</v>
+        <v>0.5232147970132044</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8107589173220715</v>
+        <v>0.8107589173253034</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8619954248724255</v>
+        <v>0.8619954248724209</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7320499877301117</v>
+        <v>0.7320499877301103</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5355076663877283</v>
+        <v>0.5355076663877267</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8038579004793617</v>
+        <v>0.8038579004793605</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8038118069520315</v>
+        <v>0.8038118069520317</v>
       </c>
       <c r="I6" t="n">
-        <v>0.803672852852129</v>
+        <v>0.8036728528521275</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8038669521899874</v>
+        <v>0.8038669521899846</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5180025635020511</v>
+        <v>0.5180025635020493</v>
       </c>
       <c r="L6" t="n">
-        <v>1.096918846871885</v>
+        <v>1.096918846871883</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.214015271017563</v>
+        <v>2.214015271017558</v>
       </c>
       <c r="C7" t="n">
-        <v>2.80496018761699</v>
+        <v>2.804960187616981</v>
       </c>
       <c r="D7" t="n">
-        <v>2.80374557255245</v>
+        <v>2.803745572552442</v>
       </c>
       <c r="E7" t="n">
-        <v>3.48414235988975</v>
+        <v>3.484142359889744</v>
       </c>
       <c r="F7" t="n">
-        <v>2.803606200666807</v>
+        <v>2.803606200666801</v>
       </c>
       <c r="G7" t="n">
-        <v>2.803791798542144</v>
+        <v>2.803791798542136</v>
       </c>
       <c r="H7" t="n">
-        <v>2.803745705013462</v>
+        <v>2.80374570501346</v>
       </c>
       <c r="I7" t="n">
-        <v>2.803606750914902</v>
+        <v>2.803606750914896</v>
       </c>
       <c r="J7" t="n">
-        <v>2.803745705013462</v>
+        <v>2.80374570501346</v>
       </c>
       <c r="K7" t="n">
-        <v>2.061169856433697</v>
+        <v>2.44819064159165</v>
       </c>
       <c r="L7" t="n">
-        <v>2.803745705013462</v>
+        <v>2.80374570501346</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.4111604507785594</v>
+        <v>-0.4111604507785595</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.3404578193460725</v>
+        <v>-0.3404578193460734</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1383664852721207</v>
+        <v>0.1383664852721201</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1554609700163896</v>
+        <v>0.1554609700163891</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1554609700163896</v>
+        <v>0.1554609700163891</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03864698058137375</v>
+        <v>0.03864698058137439</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06148078385761965</v>
+        <v>0.06148078385761918</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1554609700163896</v>
+        <v>0.1554609700163891</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1643355279341265</v>
+        <v>0.1643355279341254</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1847667552433436</v>
+        <v>0.1847667552433425</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.04546115484777272</v>
+        <v>-0.04546115484777317</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.06779081350421287</v>
+        <v>-0.0677908135042132</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.02009345548732249</v>
+        <v>-0.02009345548732284</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1774756437225935</v>
+        <v>0.1774756437225924</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1920127179835845</v>
+        <v>0.1920127179835838</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1920127179835845</v>
+        <v>0.1920127179835838</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1216664462795108</v>
+        <v>0.1216664462795107</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1462951288578512</v>
+        <v>0.1462951288578508</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1920127179835845</v>
+        <v>0.1920127179835838</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2109595697335789</v>
+        <v>0.2109595697335783</v>
       </c>
       <c r="K9" t="n">
-        <v>0.207698429463184</v>
+        <v>0.2076984294631838</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09323227821083882</v>
+        <v>0.09323227821083832</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.81470464908816</v>
+        <v>30.81470464908815</v>
       </c>
       <c r="C2" t="n">
-        <v>35.08388161014172</v>
+        <v>35.08388161014173</v>
       </c>
       <c r="D2" t="n">
-        <v>3.29504611946955</v>
+        <v>3.295046119469534</v>
       </c>
       <c r="E2" t="n">
-        <v>4.805547517367105</v>
+        <v>4.805547517367089</v>
       </c>
       <c r="F2" t="n">
-        <v>4.805547517367105</v>
+        <v>4.805547517367089</v>
       </c>
       <c r="G2" t="n">
-        <v>8.732529400572673</v>
+        <v>8.732529400572705</v>
       </c>
       <c r="H2" t="n">
         <v>15.17799135064065</v>
       </c>
       <c r="I2" t="n">
-        <v>4.805547517367105</v>
+        <v>4.805547517367089</v>
       </c>
       <c r="J2" t="n">
-        <v>7.555274227267759</v>
+        <v>7.55527422726776</v>
       </c>
       <c r="K2" t="n">
-        <v>3.134076738781784</v>
+        <v>3.134076738781791</v>
       </c>
       <c r="L2" t="n">
-        <v>23.49723536925034</v>
+        <v>23.49723536925033</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1462122988859539</v>
+        <v>0.1462122988859561</v>
       </c>
       <c r="C3" t="n">
-        <v>0.163860618069307</v>
+        <v>0.1638606180693062</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1462122988859539</v>
+        <v>0.1462122988859561</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1719007804427276</v>
+        <v>0.1719007804427286</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1719007804427277</v>
+        <v>0.1719007804427286</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1462581816832832</v>
+        <v>0.1462581816832842</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1462122988859539</v>
+        <v>0.1462122988859561</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1460594071208081</v>
+        <v>0.1460594071208085</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1462122988859539</v>
+        <v>0.1462122988859561</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1462122988859539</v>
+        <v>0.1462122988859561</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1462122988859539</v>
+        <v>0.1462122988859561</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.726915301106686</v>
+        <v>6.726915301106692</v>
       </c>
       <c r="C4" t="n">
-        <v>6.868763560247989</v>
+        <v>6.868763560247974</v>
       </c>
       <c r="D4" t="n">
-        <v>6.710026533465078</v>
+        <v>6.710027236842297</v>
       </c>
       <c r="E4" t="n">
-        <v>6.78749868585744</v>
+        <v>6.787498685857435</v>
       </c>
       <c r="F4" t="n">
         <v>6.815932200112885</v>
       </c>
       <c r="G4" t="n">
-        <v>6.726961183904008</v>
+        <v>6.726961183904015</v>
       </c>
       <c r="H4" t="n">
-        <v>81.07697134665209</v>
+        <v>81.07697134665212</v>
       </c>
       <c r="I4" t="n">
-        <v>6.726762409341567</v>
+        <v>81.07808236244108</v>
       </c>
       <c r="J4" t="n">
-        <v>81.07650680287041</v>
+        <v>6.735527261833595</v>
       </c>
       <c r="K4" t="n">
-        <v>6.62529279361418</v>
+        <v>6.625292793614184</v>
       </c>
       <c r="L4" t="n">
-        <v>6.723586492141632</v>
+        <v>6.723586492141636</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.514695467915391</v>
+        <v>0.5146954679153961</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5161574967846597</v>
+        <v>0.5161574967846561</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5146695440811638</v>
+        <v>0.5146695440811668</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5220454404022923</v>
+        <v>0.5220454404022935</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5220454404022923</v>
+        <v>0.5220454404022935</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5147413507127223</v>
+        <v>0.5147413507127253</v>
       </c>
       <c r="H5" t="n">
-        <v>0.514695467915391</v>
+        <v>0.5146954679153961</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5145425761502462</v>
+        <v>0.5145425761502468</v>
       </c>
       <c r="J5" t="n">
-        <v>0.514695467915391</v>
+        <v>0.5146954679153961</v>
       </c>
       <c r="K5" t="n">
-        <v>0.514695467915391</v>
+        <v>0.5146954679153961</v>
       </c>
       <c r="L5" t="n">
-        <v>0.514695467915391</v>
+        <v>0.5146954679153961</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5718758024452715</v>
+        <v>0.5718758024452734</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8830143287801513</v>
+        <v>0.8830143287816513</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9369974908436592</v>
+        <v>0.9369974908436568</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7979181318466292</v>
+        <v>0.7979181318466303</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5858002597201949</v>
+        <v>0.5858002597201954</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8743358305695063</v>
+        <v>0.8743358305695093</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8742899477717463</v>
+        <v>0.8742899477717535</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8741370560070312</v>
+        <v>0.8741370560070338</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8743493807207331</v>
+        <v>0.8743493807207355</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5662583044457435</v>
+        <v>0.5662583044457413</v>
       </c>
       <c r="L6" t="n">
-        <v>1.190186809934954</v>
+        <v>1.190186809934959</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.912287153493612</v>
+        <v>2.912287153493609</v>
       </c>
       <c r="C7" t="n">
-        <v>3.692628939619451</v>
+        <v>3.692628939619454</v>
       </c>
       <c r="D7" t="n">
-        <v>3.69116662675537</v>
+        <v>3.691166626755366</v>
       </c>
       <c r="E7" t="n">
-        <v>4.589823522183217</v>
+        <v>4.58982352218321</v>
       </c>
       <c r="F7" t="n">
-        <v>3.691013246958822</v>
+        <v>3.691013246958818</v>
       </c>
       <c r="G7" t="n">
-        <v>3.691212793547515</v>
+        <v>3.691212793547511</v>
       </c>
       <c r="H7" t="n">
-        <v>3.691166910750182</v>
+        <v>3.691166910750184</v>
       </c>
       <c r="I7" t="n">
         <v>3.691014018985042</v>
       </c>
       <c r="J7" t="n">
-        <v>3.691166910750182</v>
+        <v>3.691166910750183</v>
       </c>
       <c r="K7" t="n">
-        <v>2.710418340424769</v>
+        <v>3.239880801051978</v>
       </c>
       <c r="L7" t="n">
-        <v>3.691166910750182</v>
+        <v>3.691166910750183</v>
       </c>
     </row>
     <row r="8">
@@ -2738,34 +2738,34 @@
         <v>-0.4688273106779933</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.5439634024872804</v>
+        <v>-0.54396340248728</v>
       </c>
       <c r="D8" t="n">
-        <v>0.153135902383104</v>
+        <v>0.1531359023831042</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1331790276453611</v>
+        <v>0.1331790276453616</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1331790276453611</v>
+        <v>0.1331790276453616</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009608488110972003</v>
+        <v>0.009608488110972018</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.08042223661382299</v>
+        <v>-0.08042223661382228</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1331790276453611</v>
+        <v>0.1331790276453616</v>
       </c>
       <c r="J8" t="n">
-        <v>0.09701789943959702</v>
+        <v>0.09701789943959681</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1755583540278197</v>
+        <v>0.1755583540278175</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2587399368448149</v>
+        <v>-0.2587399368448147</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.06391350029450829</v>
+        <v>-0.06391350029450783</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.08125997247977886</v>
+        <v>-0.08125997247977894</v>
       </c>
       <c r="D9" t="n">
         <v>0.1936815479949686</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1935404486000532</v>
+        <v>0.1935404486000527</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1935404486000532</v>
+        <v>0.1935404486000527</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1215858620661994</v>
+        <v>0.121585862066199</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09883773083182464</v>
+        <v>0.09883773083182465</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1935404486000532</v>
+        <v>0.1935404486000527</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1903072562173787</v>
+        <v>0.1903072562173783</v>
       </c>
       <c r="K9" t="n">
-        <v>0.213439995355745</v>
+        <v>0.2134399953557439</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0157980796808169</v>
+        <v>0.01579807968081709</v>
       </c>
     </row>
   </sheetData>
@@ -2891,31 +2891,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.24284021624032</v>
+        <v>23.24284021624031</v>
       </c>
       <c r="C2" t="n">
-        <v>25.94408674137241</v>
+        <v>25.94408674137239</v>
       </c>
       <c r="D2" t="n">
-        <v>2.051989558327118</v>
+        <v>2.051989558327119</v>
       </c>
       <c r="E2" t="n">
-        <v>3.292189369532539</v>
+        <v>3.292189369532506</v>
       </c>
       <c r="F2" t="n">
-        <v>3.292189369532539</v>
+        <v>3.292189369532506</v>
       </c>
       <c r="G2" t="n">
-        <v>5.91060142831403</v>
+        <v>5.910601428314033</v>
       </c>
       <c r="H2" t="n">
-        <v>16.9438948403348</v>
+        <v>16.94389484033477</v>
       </c>
       <c r="I2" t="n">
-        <v>3.292189369532539</v>
+        <v>3.292189369532506</v>
       </c>
       <c r="J2" t="n">
-        <v>4.519074754632887</v>
+        <v>4.519074754632888</v>
       </c>
       <c r="K2" t="n">
         <v>1.854704315786538</v>
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1358554524261277</v>
+        <v>0.1358554524261274</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1505539702387408</v>
+        <v>0.1505539702387416</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1358554524261277</v>
+        <v>0.1358554524261274</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1676113910588778</v>
+        <v>0.167611391058878</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1676113910588778</v>
+        <v>0.167611391058878</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1359437110230343</v>
+        <v>0.1359437110230351</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1358554524261277</v>
+        <v>0.1358554524261274</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1359726367049806</v>
+        <v>0.1359726367049809</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1358554524261277</v>
+        <v>0.1358554524261274</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1358554524261277</v>
+        <v>0.1358554524261274</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1358554524261277</v>
+        <v>0.1358554524261274</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.35221065078077</v>
+        <v>6.352210650780775</v>
       </c>
       <c r="C4" t="n">
-        <v>6.477985774789696</v>
+        <v>6.477985774789691</v>
       </c>
       <c r="D4" t="n">
-        <v>6.339004487223415</v>
+        <v>76.7611953702209</v>
       </c>
       <c r="E4" t="n">
-        <v>6.414504768154179</v>
+        <v>6.414504768154183</v>
       </c>
       <c r="F4" t="n">
         <v>6.438932034782988</v>
       </c>
       <c r="G4" t="n">
-        <v>76.761811454628</v>
+        <v>6.352298909377658</v>
       </c>
       <c r="H4" t="n">
-        <v>76.77233806941382</v>
+        <v>76.77233806941383</v>
       </c>
       <c r="I4" t="n">
-        <v>76.76184038030988</v>
+        <v>76.76184038030991</v>
       </c>
       <c r="J4" t="n">
-        <v>6.360722011406611</v>
+        <v>76.76211805267224</v>
       </c>
       <c r="K4" t="n">
-        <v>6.258889439512555</v>
+        <v>6.258889439512564</v>
       </c>
       <c r="L4" t="n">
-        <v>6.348030132420071</v>
+        <v>6.348030132420069</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4825823413820206</v>
+        <v>0.4825823413820202</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4839288784260701</v>
+        <v>0.4839288784260702</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4825569195392526</v>
+        <v>0.4825569195392517</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4918811563242201</v>
+        <v>0.4918811563242194</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4918811563242201</v>
+        <v>0.4918811563242194</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4826705999789296</v>
+        <v>0.4826705999789293</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4825823413820206</v>
+        <v>0.4825823413820202</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4826995256608753</v>
+        <v>0.4826995256608754</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4825823413820206</v>
+        <v>0.4825823413820202</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4825823413820206</v>
+        <v>0.4825823413820202</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4825823413820206</v>
+        <v>0.4825823413820202</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5315982614028666</v>
+        <v>0.531598261402866</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8243448929897068</v>
+        <v>0.82434489298668</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8727198602742119</v>
+        <v>0.872719860274212</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7449000083129587</v>
+        <v>0.7449000083129582</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5461638522753557</v>
+        <v>0.5461638522753552</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8142224526873427</v>
+        <v>0.8142224526873423</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8141341940927321</v>
+        <v>0.814134194092731</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8142513783692895</v>
+        <v>0.8142513783692883</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8141897203775412</v>
+        <v>0.8141897203775407</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5263500114099834</v>
+        <v>0.5263500114099838</v>
       </c>
       <c r="L6" t="n">
-        <v>1.109266600944493</v>
+        <v>1.109266600944494</v>
       </c>
     </row>
     <row r="7">
@@ -3091,16 +3091,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.432676107765424</v>
+        <v>2.432676107765425</v>
       </c>
       <c r="C7" t="n">
         <v>3.082750428141293</v>
       </c>
       <c r="D7" t="n">
-        <v>3.0814036071671</v>
+        <v>3.081403607167098</v>
       </c>
       <c r="E7" t="n">
-        <v>3.830138065749106</v>
+        <v>3.830138065749107</v>
       </c>
       <c r="F7" t="n">
         <v>3.081520387636246</v>
@@ -3109,19 +3109,19 @@
         <v>3.081492149694153</v>
       </c>
       <c r="H7" t="n">
-        <v>3.081403891097248</v>
+        <v>3.081403891097246</v>
       </c>
       <c r="I7" t="n">
-        <v>3.081521075376093</v>
+        <v>3.081521075376092</v>
       </c>
       <c r="J7" t="n">
-        <v>3.081403891097248</v>
+        <v>3.081403891097246</v>
       </c>
       <c r="K7" t="n">
-        <v>2.264539887971486</v>
+        <v>2.705528346264487</v>
       </c>
       <c r="L7" t="n">
-        <v>3.081403891097248</v>
+        <v>3.081403891097246</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.3428932635610045</v>
+        <v>-0.3428932635610042</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.3960516272805265</v>
+        <v>-0.3960516272805267</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1680661343369822</v>
+        <v>0.1680661343369823</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1555539752870347</v>
+        <v>0.1555539752870349</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1555539752870347</v>
+        <v>0.1555539752870349</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05363430443208005</v>
+        <v>0.0536343044320796</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1468090116485309</v>
+        <v>-0.1468090116485307</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1555539752870347</v>
+        <v>0.1555539752870349</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1542688220903076</v>
+        <v>0.154268822090308</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1984232892821615</v>
+        <v>0.1984232892821576</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.06121554430476787</v>
+        <v>-0.0612155443047682</v>
       </c>
     </row>
     <row r="9">
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.02097284354423488</v>
+        <v>-0.0209728435442346</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.03540742496684678</v>
+        <v>-0.03540742496684581</v>
       </c>
       <c r="D9" t="n">
         <v>0.1934028123653185</v>
@@ -3186,22 +3186,22 @@
         <v>0.1980909312248446</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1327257593115027</v>
+        <v>0.1327257593115021</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06549129591672745</v>
+        <v>0.06549129591672742</v>
       </c>
       <c r="I9" t="n">
         <v>0.1980909312248446</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2114609055257823</v>
+        <v>0.2114609055257822</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2204055109376331</v>
+        <v>0.2204055109376292</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09130364868555098</v>
+        <v>0.0913036486855508</v>
       </c>
     </row>
   </sheetData>
@@ -3290,34 +3290,34 @@
         <v>18.23237525578735</v>
       </c>
       <c r="C2" t="n">
-        <v>18.4602999616414</v>
+        <v>18.46029996164138</v>
       </c>
       <c r="D2" t="n">
-        <v>1.955762135466061</v>
+        <v>1.955762135466052</v>
       </c>
       <c r="E2" t="n">
-        <v>2.228753001965636</v>
+        <v>2.228753001965655</v>
       </c>
       <c r="F2" t="n">
-        <v>2.228753001965636</v>
+        <v>2.228753001965655</v>
       </c>
       <c r="G2" t="n">
-        <v>4.284928090237054</v>
+        <v>4.284928090237121</v>
       </c>
       <c r="H2" t="n">
-        <v>12.20022516018549</v>
+        <v>12.20022516018548</v>
       </c>
       <c r="I2" t="n">
-        <v>2.228753001965636</v>
+        <v>2.228753001965655</v>
       </c>
       <c r="J2" t="n">
-        <v>3.317447179745302</v>
+        <v>3.317447179745303</v>
       </c>
       <c r="K2" t="n">
-        <v>1.332616340614091</v>
+        <v>1.332616340614077</v>
       </c>
       <c r="L2" t="n">
-        <v>6.445622033449764</v>
+        <v>6.445622033449754</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1391335276045439</v>
+        <v>0.1391335276045327</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1596259300411801</v>
+        <v>0.1596259300411809</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1391335276045439</v>
+        <v>0.1391335276045327</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1611177525187233</v>
+        <v>0.1611177525187243</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1611177525187233</v>
+        <v>0.1611177525187243</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1392236609644724</v>
+        <v>0.1392236609644558</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1391335276045439</v>
+        <v>0.1391335276045327</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1392771244287735</v>
+        <v>0.1392771244287599</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1391335276045439</v>
+        <v>0.1391335276045327</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1391335276045439</v>
+        <v>0.1391335276045327</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1391335276045439</v>
+        <v>0.1391335276045327</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.7475372932697</v>
+        <v>76.74753729326967</v>
       </c>
       <c r="C4" t="n">
-        <v>6.458948571685505</v>
+        <v>6.458948571685498</v>
       </c>
       <c r="D4" t="n">
-        <v>6.332126941167274</v>
+        <v>6.332126941167284</v>
       </c>
       <c r="E4" t="n">
-        <v>6.405191874601218</v>
+        <v>6.405191874601216</v>
       </c>
       <c r="F4" t="n">
-        <v>6.429499245542</v>
+        <v>6.429499245542001</v>
       </c>
       <c r="G4" t="n">
-        <v>76.74762742662938</v>
+        <v>76.74762742662936</v>
       </c>
       <c r="H4" t="n">
-        <v>76.76211893646382</v>
+        <v>6.339676092467684</v>
       </c>
       <c r="I4" t="n">
-        <v>6.342076803805953</v>
+        <v>76.74768089009362</v>
       </c>
       <c r="J4" t="n">
-        <v>76.74672674370463</v>
+        <v>6.351296519635558</v>
       </c>
       <c r="K4" t="n">
-        <v>6.251075060226354</v>
+        <v>6.251075060226341</v>
       </c>
       <c r="L4" t="n">
-        <v>6.337626322371244</v>
+        <v>6.337626322371222</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4816504379433337</v>
+        <v>0.4816504379433283</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4828111053386916</v>
+        <v>0.4828111053386921</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4816223378004006</v>
+        <v>0.4816223378003942</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4884067960851813</v>
+        <v>0.4884067960851827</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4884067960851813</v>
+        <v>0.4884067960851827</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4817405713032454</v>
+        <v>0.4817405713032424</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4816504379433337</v>
+        <v>0.4816504379433283</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4817940347675495</v>
+        <v>0.4817940347675511</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4816504379433337</v>
+        <v>0.4816504379433283</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4816504379433337</v>
+        <v>0.4816504379433283</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4816504379433337</v>
+        <v>0.4816504379433283</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5306957422698289</v>
+        <v>0.5306957422698271</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8209713771476413</v>
+        <v>0.8209713771538735</v>
       </c>
       <c r="D6" t="n">
         <v>0.8720142562721964</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7419489045733154</v>
+        <v>0.7419489045733169</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5437620581097922</v>
+        <v>0.5437620581097938</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8134849044163186</v>
+        <v>0.8134849044163217</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8133947710598952</v>
+        <v>0.8133947710598944</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8135383678806238</v>
+        <v>0.8135383678806251</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8134503293099994</v>
+        <v>0.8134503293099907</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5254444626867572</v>
+        <v>0.5254444626867533</v>
       </c>
       <c r="L6" t="n">
-        <v>1.108697545347557</v>
+        <v>1.108697545347566</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.188809715128931</v>
+        <v>2.188809715128929</v>
       </c>
       <c r="C7" t="n">
-        <v>2.771576181157964</v>
+        <v>2.771576181157965</v>
       </c>
       <c r="D7" t="n">
         <v>2.770415310004593</v>
       </c>
       <c r="E7" t="n">
-        <v>3.441718969122903</v>
+        <v>3.441718969122906</v>
       </c>
       <c r="F7" t="n">
-        <v>2.77055853709884</v>
+        <v>2.770558537098842</v>
       </c>
       <c r="G7" t="n">
-        <v>2.770505647122525</v>
+        <v>2.770505647122524</v>
       </c>
       <c r="H7" t="n">
-        <v>2.770415513762603</v>
+        <v>2.770415513762599</v>
       </c>
       <c r="I7" t="n">
-        <v>2.770559110586828</v>
+        <v>2.770559110586829</v>
       </c>
       <c r="J7" t="n">
-        <v>2.770415513762603</v>
+        <v>2.770415513762599</v>
       </c>
       <c r="K7" t="n">
-        <v>2.419758854682204</v>
+        <v>2.433430744192423</v>
       </c>
       <c r="L7" t="n">
-        <v>2.770415513762603</v>
+        <v>2.770415513762599</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.2294268626238096</v>
+        <v>-0.229426862623811</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2429941011833176</v>
+        <v>-0.2429941011833173</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1627812377070055</v>
+        <v>0.1627812377070043</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1725329820120476</v>
+        <v>0.172532982012048</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1725329820120476</v>
+        <v>0.172532982012048</v>
       </c>
       <c r="G8" t="n">
-        <v>0.08366710504076506</v>
+        <v>0.0836671050407624</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.05236313255967759</v>
+        <v>-0.05236313255968056</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1725329820120476</v>
+        <v>0.172532982012048</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1813302611186203</v>
+        <v>0.1813302611186188</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2029632122863698</v>
+        <v>0.2029632122863688</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05687967600106557</v>
+        <v>0.05687967600106755</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02235459980814735</v>
+        <v>0.02235459980814685</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01272454213115414</v>
+        <v>0.01272454213115452</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1868402652810426</v>
+        <v>0.1868402652810461</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1999763558603612</v>
+        <v>0.1999763558603615</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1999763558603612</v>
+        <v>0.1999763558603615</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1400570894191694</v>
+        <v>0.1400570894191658</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09945354341936766</v>
+        <v>0.0994535434193649</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1999763558603612</v>
+        <v>0.1999763558603615</v>
       </c>
       <c r="J9" t="n">
-        <v>0.222018935321433</v>
+        <v>0.2220189353214339</v>
       </c>
       <c r="K9" t="n">
-        <v>0.217548175668252</v>
+        <v>0.2175481756682478</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1338385567445773</v>
+        <v>0.1338385567445735</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.28574012372843</v>
+        <v>30.28574012372844</v>
       </c>
       <c r="C2" t="n">
-        <v>34.44664993509616</v>
+        <v>34.44664993509612</v>
       </c>
       <c r="D2" t="n">
-        <v>2.506323844104058</v>
+        <v>2.506323844104069</v>
       </c>
       <c r="E2" t="n">
-        <v>4.714031495958485</v>
+        <v>4.714031495958487</v>
       </c>
       <c r="F2" t="n">
-        <v>4.714031495958485</v>
+        <v>4.714031495958487</v>
       </c>
       <c r="G2" t="n">
-        <v>8.594733064544339</v>
+        <v>8.594733064544306</v>
       </c>
       <c r="H2" t="n">
-        <v>14.954239155483</v>
+        <v>14.95423915548302</v>
       </c>
       <c r="I2" t="n">
-        <v>4.714031495958485</v>
+        <v>4.714031495958487</v>
       </c>
       <c r="J2" t="n">
-        <v>6.37697761328652</v>
+        <v>6.376977613286511</v>
       </c>
       <c r="K2" t="n">
-        <v>2.791504839028537</v>
+        <v>2.791504839028549</v>
       </c>
       <c r="L2" t="n">
-        <v>24.51606542264502</v>
+        <v>24.51606542264501</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1466612766502933</v>
+        <v>0.1466612766503034</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1632631611715459</v>
+        <v>0.1632631611715462</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1466612766502933</v>
+        <v>0.1466612766503034</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1767001899085893</v>
+        <v>0.176700189908589</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1767001899085893</v>
+        <v>0.176700189908589</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1467131957766304</v>
+        <v>0.1467131957766288</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1466612766502933</v>
+        <v>0.1466612766503034</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1465440266048825</v>
+        <v>0.1465440266048826</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1466612766502933</v>
+        <v>0.1466612766503034</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1466612766502933</v>
+        <v>0.1466612766503034</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1466612766502933</v>
+        <v>0.1466612766503034</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.725692546726544</v>
+        <v>6.725692546726555</v>
       </c>
       <c r="C4" t="n">
-        <v>6.866558870852862</v>
+        <v>6.866558870852853</v>
       </c>
       <c r="D4" t="n">
-        <v>6.707556952996324</v>
+        <v>6.707556952996337</v>
       </c>
       <c r="E4" t="n">
         <v>6.787168578069131</v>
       </c>
       <c r="F4" t="n">
-        <v>6.81515450683485</v>
+        <v>6.815154506834849</v>
       </c>
       <c r="G4" t="n">
-        <v>81.07825064617334</v>
+        <v>6.725744465852893</v>
       </c>
       <c r="H4" t="n">
-        <v>81.07696603189299</v>
+        <v>81.07696603189292</v>
       </c>
       <c r="I4" t="n">
-        <v>81.07808147700142</v>
+        <v>6.725575296681141</v>
       </c>
       <c r="J4" t="n">
-        <v>81.07680414809798</v>
+        <v>6.734055004395605</v>
       </c>
       <c r="K4" t="n">
-        <v>6.623701006830917</v>
+        <v>6.623701006830934</v>
       </c>
       <c r="L4" t="n">
-        <v>6.722811399695055</v>
+        <v>6.722811399695058</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5169122000373619</v>
+        <v>0.5169122000373708</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5183680287040703</v>
+        <v>0.5183680287040686</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5168864509726129</v>
+        <v>0.5168864509726188</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5254975138331753</v>
+        <v>0.5254975138331751</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5254975138331753</v>
+        <v>0.5254975138331751</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5169641191636896</v>
+        <v>0.5169641191636967</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5169122000373619</v>
+        <v>0.5169122000373708</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5167949499919484</v>
+        <v>0.5167949499919487</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5169122000373619</v>
+        <v>0.5169122000373708</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5169122000373619</v>
+        <v>0.5169122000373708</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5169122000373619</v>
+        <v>0.5169122000373708</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.574531909754441</v>
+        <v>0.5745319097544502</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8890227202241886</v>
+        <v>0.8890227202226642</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9423241744604054</v>
+        <v>0.9423241744604205</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8032425740729011</v>
+        <v>0.803242574072901</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5892776979915731</v>
+        <v>0.5892776979915725</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8792098944455835</v>
+        <v>0.8792098944455938</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8791579753187083</v>
+        <v>0.8791579753187063</v>
       </c>
       <c r="I6" t="n">
-        <v>0.879040725273843</v>
+        <v>0.8790407252738416</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8792178429611374</v>
+        <v>0.8792178429611456</v>
       </c>
       <c r="K6" t="n">
         <v>0.5688733242021573</v>
       </c>
       <c r="L6" t="n">
-        <v>1.197365373116321</v>
+        <v>1.197365373116327</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.910911979707605</v>
+        <v>2.910911979707612</v>
       </c>
       <c r="C7" t="n">
-        <v>3.691095437178523</v>
+        <v>3.691095437178526</v>
       </c>
       <c r="D7" t="n">
-        <v>3.68963932786741</v>
+        <v>3.689639327867419</v>
       </c>
       <c r="E7" t="n">
-        <v>4.588156319499304</v>
+        <v>4.588156319499299</v>
       </c>
       <c r="F7" t="n">
-        <v>3.689521592691736</v>
+        <v>3.689521592691737</v>
       </c>
       <c r="G7" t="n">
-        <v>3.689691527638161</v>
+        <v>3.689691527638166</v>
       </c>
       <c r="H7" t="n">
-        <v>3.689639608511823</v>
+        <v>3.689639608511836</v>
       </c>
       <c r="I7" t="n">
-        <v>3.689522358466419</v>
+        <v>3.689522358466416</v>
       </c>
       <c r="J7" t="n">
-        <v>3.689639608511823</v>
+        <v>3.689639608511836</v>
       </c>
       <c r="K7" t="n">
-        <v>3.238441644045552</v>
+        <v>3.238441644045554</v>
       </c>
       <c r="L7" t="n">
-        <v>3.689639608511825</v>
+        <v>3.689639608511836</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.4476952704921693</v>
+        <v>-0.4476952704921637</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.5268128120983617</v>
+        <v>-0.5268128120983628</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1723633085844308</v>
+        <v>0.172363308584434</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1373171823950315</v>
+        <v>0.1373171823950311</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1373171823950315</v>
+        <v>0.1373171823950311</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01515130293544618</v>
+        <v>0.01515130293544995</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.07485988016463446</v>
+        <v>-0.07485988016463174</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1373171823950315</v>
+        <v>0.1373171823950311</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1252229444961636</v>
+        <v>0.1252229444961593</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1865109316898028</v>
+        <v>0.186510931689807</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2768715602034514</v>
+        <v>-0.2768715602034478</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.04991932015958284</v>
+        <v>-0.04991932015957471</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.07262015421393025</v>
+        <v>-0.07262015421393057</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2021164346744705</v>
+        <v>0.2021164346744781</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1964334941909421</v>
+        <v>0.1964334941909419</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1964334941909421</v>
+        <v>0.1964334941909419</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1252847247533657</v>
+        <v>0.1252847247533671</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1017031339703026</v>
+        <v>0.1017031339703109</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1964334941909421</v>
+        <v>0.1964334941909419</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2031691694169825</v>
+        <v>0.2031691694169867</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2196985956425469</v>
+        <v>0.2196985956425498</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009737448668892749</v>
+        <v>0.009737448668895723</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.79674557890819</v>
+        <v>21.79674557890818</v>
       </c>
       <c r="C2" t="n">
-        <v>24.50526679126414</v>
+        <v>24.50526679126413</v>
       </c>
       <c r="D2" t="n">
-        <v>2.243367361856434</v>
+        <v>2.243367361856426</v>
       </c>
       <c r="E2" t="n">
-        <v>3.109356983650827</v>
+        <v>3.109356983650831</v>
       </c>
       <c r="F2" t="n">
-        <v>3.109356983650827</v>
+        <v>3.109356983650831</v>
       </c>
       <c r="G2" t="n">
-        <v>5.880465660992131</v>
+        <v>5.88046566099208</v>
       </c>
       <c r="H2" t="n">
         <v>15.40880326332603</v>
       </c>
       <c r="I2" t="n">
-        <v>3.109356983650827</v>
+        <v>3.109356983650831</v>
       </c>
       <c r="J2" t="n">
-        <v>4.429681094316273</v>
+        <v>4.429681094316272</v>
       </c>
       <c r="K2" t="n">
-        <v>1.866531213560369</v>
+        <v>1.866531213560365</v>
       </c>
       <c r="L2" t="n">
-        <v>13.30627862131533</v>
+        <v>13.30627862131534</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1333469041433901</v>
+        <v>0.1333469041433896</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1439061270313204</v>
+        <v>0.1439061270313195</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1333469041433901</v>
+        <v>0.1333469041433896</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1720136229570538</v>
+        <v>0.1720136229570539</v>
       </c>
       <c r="F3" t="n">
         <v>0.1720136229570539</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1334327628047201</v>
+        <v>0.1334327628047198</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1333469041433901</v>
+        <v>0.1333469041433896</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1334440452113217</v>
+        <v>0.1334440452113219</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1333469041433901</v>
+        <v>0.1333469041433896</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1333469041433901</v>
+        <v>0.1333469041433896</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1333469041433901</v>
+        <v>0.1333469041433896</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.348425902196644</v>
+        <v>76.75857894332596</v>
       </c>
       <c r="C4" t="n">
-        <v>6.471307259692447</v>
+        <v>6.471307259692434</v>
       </c>
       <c r="D4" t="n">
-        <v>6.336009967276821</v>
+        <v>6.3360094545196</v>
       </c>
       <c r="E4" t="n">
-        <v>6.411815957315858</v>
+        <v>6.411815957315865</v>
       </c>
       <c r="F4" t="n">
-        <v>6.435951711578249</v>
+        <v>6.435951711578246</v>
       </c>
       <c r="G4" t="n">
-        <v>6.348511760857962</v>
+        <v>6.348511760857961</v>
       </c>
       <c r="H4" t="n">
-        <v>76.76855981498386</v>
+        <v>76.76855981498385</v>
       </c>
       <c r="I4" t="n">
-        <v>76.75867608439404</v>
+        <v>76.75867608439398</v>
       </c>
       <c r="J4" t="n">
-        <v>76.75972862929358</v>
+        <v>6.357381742186295</v>
       </c>
       <c r="K4" t="n">
-        <v>6.255856120576964</v>
+        <v>6.255856120576954</v>
       </c>
       <c r="L4" t="n">
-        <v>6.344928293065857</v>
+        <v>6.344928293065855</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4823595038696953</v>
+        <v>0.4823595038696946</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4836704506047103</v>
+        <v>0.4836704506047088</v>
       </c>
       <c r="D5" t="n">
-        <v>0.482335072038418</v>
+        <v>0.4823350720384171</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4936380428558425</v>
+        <v>0.4936380428558415</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4936380428558425</v>
+        <v>0.4936380428558415</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4824453625310245</v>
+        <v>0.4824453625310233</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4823595038696953</v>
+        <v>0.4823595038696946</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4824566449376269</v>
+        <v>0.4824566449376256</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4823595038696953</v>
+        <v>0.4823595038696946</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4823595038696953</v>
+        <v>0.4823595038696946</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4823595038696953</v>
+        <v>0.4823595038696946</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5314797251907518</v>
+        <v>0.5314797251907507</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8285821088724249</v>
+        <v>0.8285821088724226</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8755973317175174</v>
+        <v>0.8755973317175135</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7482731742076839</v>
+        <v>0.748273174207683</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5472962989775582</v>
+        <v>0.5472962989775575</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8165829771695226</v>
+        <v>0.8165829771695214</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8164971185101627</v>
+        <v>0.8164971185101609</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8165942595761272</v>
+        <v>0.8165942595761254</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8165531324563303</v>
+        <v>0.816553132456328</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5261853807945632</v>
+        <v>0.5261853807945615</v>
       </c>
       <c r="L6" t="n">
-        <v>1.114221618470445</v>
+        <v>1.114221618470443</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.430975590644086</v>
+        <v>2.430975590644078</v>
       </c>
       <c r="C7" t="n">
-        <v>3.081656850391169</v>
+        <v>3.081656850391164</v>
       </c>
       <c r="D7" t="n">
-        <v>3.080345649758581</v>
+        <v>3.080345649758574</v>
       </c>
       <c r="E7" t="n">
-        <v>3.829801563585971</v>
+        <v>3.829801563585962</v>
       </c>
       <c r="F7" t="n">
-        <v>3.080442385554542</v>
+        <v>3.080442385554539</v>
       </c>
       <c r="G7" t="n">
-        <v>3.080431762317489</v>
+        <v>3.080431762317484</v>
       </c>
       <c r="H7" t="n">
-        <v>3.080345903656162</v>
+        <v>3.080345903656156</v>
       </c>
       <c r="I7" t="n">
-        <v>3.080443044724088</v>
+        <v>3.080443044724083</v>
       </c>
       <c r="J7" t="n">
-        <v>3.080345903656162</v>
+        <v>3.080345903656156</v>
       </c>
       <c r="K7" t="n">
-        <v>2.704098087234841</v>
+        <v>2.262672833188039</v>
       </c>
       <c r="L7" t="n">
-        <v>3.080345903656162</v>
+        <v>3.080345903656156</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.226343413719692</v>
+        <v>-0.226343413719693</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.3593968279549221</v>
+        <v>-0.3593968279549215</v>
       </c>
       <c r="D8" t="n">
-        <v>0.163889629005364</v>
+        <v>0.1638896290053637</v>
       </c>
       <c r="E8" t="n">
-        <v>0.163013611848397</v>
+        <v>0.1630136118483965</v>
       </c>
       <c r="F8" t="n">
-        <v>0.163013611848397</v>
+        <v>0.1630136118483965</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06449425711101792</v>
+        <v>0.06449425711101772</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1132728550910075</v>
+        <v>-0.113272855091008</v>
       </c>
       <c r="I8" t="n">
-        <v>0.163013611848397</v>
+        <v>0.1630136118483965</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1609460067967532</v>
+        <v>0.1609460067967527</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2064877875565404</v>
+        <v>0.2064877875565376</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.07567349621345243</v>
+        <v>-0.07567349621345267</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07411330153737448</v>
+        <v>0.07411330153737414</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.01895691295721443</v>
+        <v>-0.01895691295721474</v>
       </c>
       <c r="D9" t="n">
         <v>0.1920699905306552</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2029686032691328</v>
+        <v>0.202968603269132</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2029686032691328</v>
+        <v>0.202968603269132</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1430856231590915</v>
+        <v>0.1430856231590907</v>
       </c>
       <c r="H9" t="n">
-        <v>0.07948781509702796</v>
+        <v>0.07948781509702769</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2029686032691328</v>
+        <v>0.202968603269132</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2169186755369995</v>
+        <v>0.2169186755369984</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2285930240866868</v>
+        <v>0.2285930240866851</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08706255964202997</v>
+        <v>0.08706255964202976</v>
       </c>
     </row>
   </sheetData>
@@ -4478,34 +4478,34 @@
         <v>18.56323573392874</v>
       </c>
       <c r="C2" t="n">
-        <v>19.49045220533286</v>
+        <v>19.49045220533285</v>
       </c>
       <c r="D2" t="n">
-        <v>2.250973647433747</v>
+        <v>2.250973647433744</v>
       </c>
       <c r="E2" t="n">
-        <v>2.21690170212708</v>
+        <v>2.216901702127076</v>
       </c>
       <c r="F2" t="n">
-        <v>2.21690170212708</v>
+        <v>2.216901702127076</v>
       </c>
       <c r="G2" t="n">
-        <v>4.532030104334947</v>
+        <v>4.532030104334916</v>
       </c>
       <c r="H2" t="n">
-        <v>11.76299656493495</v>
+        <v>11.76299656493493</v>
       </c>
       <c r="I2" t="n">
-        <v>2.21690170212708</v>
+        <v>2.216901702127076</v>
       </c>
       <c r="J2" t="n">
-        <v>3.374418687264202</v>
+        <v>3.374418687264197</v>
       </c>
       <c r="K2" t="n">
-        <v>1.49961971994626</v>
+        <v>1.499619719946263</v>
       </c>
       <c r="L2" t="n">
-        <v>7.53243148494207</v>
+        <v>7.532431484942081</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1345585301547497</v>
+        <v>0.1345585301547509</v>
       </c>
       <c r="C3" t="n">
         <v>0.1502200360167555</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1345585301547497</v>
+        <v>0.1345585301547509</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1625825782126972</v>
+        <v>0.1625825782126966</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1625825782126972</v>
+        <v>0.1625825782126966</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1346314062753508</v>
+        <v>0.1346314062753515</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1345585301547497</v>
+        <v>0.1345585301547509</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1345846856891032</v>
+        <v>0.1345846856891028</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1345585301547497</v>
+        <v>0.1345585301547509</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1345585301547497</v>
+        <v>0.1345585301547509</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1345585301547497</v>
+        <v>0.1345585301547509</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.339000390797188</v>
+        <v>76.74353586683694</v>
       </c>
       <c r="C4" t="n">
-        <v>6.456569703934896</v>
+        <v>6.456569703934898</v>
       </c>
       <c r="D4" t="n">
-        <v>6.32960758097437</v>
+        <v>6.329607991970727</v>
       </c>
       <c r="E4" t="n">
-        <v>6.402653284730218</v>
+        <v>6.402653284730219</v>
       </c>
       <c r="F4" t="n">
         <v>6.426690854578577</v>
       </c>
       <c r="G4" t="n">
-        <v>76.74360874295762</v>
+        <v>6.339073266917763</v>
       </c>
       <c r="H4" t="n">
-        <v>76.75513810626313</v>
+        <v>76.7551381062631</v>
       </c>
       <c r="I4" t="n">
-        <v>76.74356202237129</v>
+        <v>6.339026546331524</v>
       </c>
       <c r="J4" t="n">
-        <v>6.348203784917564</v>
+        <v>76.74337373066105</v>
       </c>
       <c r="K4" t="n">
-        <v>6.248546996318283</v>
+        <v>6.248546996318279</v>
       </c>
       <c r="L4" t="n">
-        <v>6.335125657967445</v>
+        <v>6.335125657967446</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4782597973865615</v>
+        <v>0.4782597973865622</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4794452175143883</v>
+        <v>0.4794452175143887</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4782325792099612</v>
+        <v>0.4782325792099664</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4867267850603599</v>
+        <v>0.4867267850603602</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4867267850603599</v>
+        <v>0.4867267850603602</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4783326735071627</v>
+        <v>0.4783326735071649</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4782597973865615</v>
+        <v>0.4782597973865622</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4782859529209136</v>
+        <v>0.4782859529209137</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4782597973865615</v>
+        <v>0.4782597973865622</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4782597973865615</v>
+        <v>0.4782597973865622</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4782597973865615</v>
+        <v>0.4782597973865622</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5253733875085742</v>
+        <v>0.5253733875085758</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8158011537214229</v>
+        <v>0.8158011537160932</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8647382936768603</v>
+        <v>0.8647382936768595</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7368951049421576</v>
+        <v>0.7368951049421559</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5393609780237604</v>
+        <v>0.5393609780237595</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8065272054518092</v>
+        <v>0.8065272054518121</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8064543293341436</v>
+        <v>0.8064543293341445</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8064804848655613</v>
+        <v>0.8064804848655611</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8065095696194418</v>
+        <v>0.8065095696194413</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5201521647206514</v>
+        <v>0.5201521647206508</v>
       </c>
       <c r="L6" t="n">
-        <v>1.100066876518035</v>
+        <v>1.100066876518038</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.189834888509451</v>
+        <v>2.189834888509453</v>
       </c>
       <c r="C7" t="n">
-        <v>2.77367727064692</v>
+        <v>2.773677270646922</v>
       </c>
       <c r="D7" t="n">
         <v>2.772491646412444</v>
       </c>
       <c r="E7" t="n">
-        <v>3.444890877154033</v>
+        <v>3.444890877154032</v>
       </c>
       <c r="F7" t="n">
-        <v>2.772517426671103</v>
+        <v>2.772517426671106</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7725647266397</v>
+        <v>2.772564726639701</v>
       </c>
       <c r="H7" t="n">
-        <v>2.772491850519102</v>
+        <v>2.772491850519105</v>
       </c>
       <c r="I7" t="n">
-        <v>2.772518006053455</v>
+        <v>2.772518006053454</v>
       </c>
       <c r="J7" t="n">
-        <v>2.772491850519102</v>
+        <v>2.772491850519105</v>
       </c>
       <c r="K7" t="n">
-        <v>2.421201433257637</v>
+        <v>2.421201433257643</v>
       </c>
       <c r="L7" t="n">
-        <v>2.772491850519102</v>
+        <v>2.772491850519105</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0417665631288894</v>
+        <v>0.04176656312889183</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.258539467716377</v>
+        <v>-0.2585394677163773</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1543205280215443</v>
+        <v>0.1543205280215445</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1732405636354437</v>
+        <v>0.1732405636354435</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1732405636354437</v>
+        <v>0.1732405636354435</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1041511237281451</v>
+        <v>0.1041511237281435</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.04420481701643161</v>
+        <v>-0.0442048170164297</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1732405636354437</v>
+        <v>0.1732405636354435</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1783064656586357</v>
+        <v>0.1783064656586379</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2030723736255943</v>
+        <v>0.2030723736255987</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03546675915810476</v>
+        <v>0.03546675915810382</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2938743947490607</v>
+        <v>0.2938743947490621</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01158644039315472</v>
+        <v>0.0115864403931549</v>
       </c>
       <c r="D9" t="n">
-        <v>0.182722832455606</v>
+        <v>0.1827228324556065</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2005622353254784</v>
+        <v>0.2005622353254783</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2005622353254784</v>
+        <v>0.2005622353254783</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1636516870568069</v>
+        <v>0.1636516870568078</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1020960564216617</v>
+        <v>0.1020960564216615</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2005622353254784</v>
+        <v>0.2005622353254783</v>
       </c>
       <c r="J9" t="n">
-        <v>0.219856765359318</v>
+        <v>0.2198567653593198</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2200513309092706</v>
+        <v>0.2200513309092744</v>
       </c>
       <c r="L9" t="n">
-        <v>0.126055725745064</v>
+        <v>0.126055725745066</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.70532674384668</v>
+        <v>2.70532674384672</v>
       </c>
       <c r="C2" t="n">
-        <v>10.90484588386031</v>
+        <v>10.90484588386029</v>
       </c>
       <c r="D2" t="n">
-        <v>5.618512043260417</v>
+        <v>5.618512043260413</v>
       </c>
       <c r="E2" t="n">
-        <v>10.90484588386031</v>
+        <v>10.90484588386029</v>
       </c>
       <c r="F2" t="n">
-        <v>10.90484588386031</v>
+        <v>10.90484588386029</v>
       </c>
       <c r="G2" t="n">
         <v>10.95471983319387</v>
       </c>
       <c r="H2" t="n">
-        <v>12.91651369996435</v>
+        <v>12.91651369996433</v>
       </c>
       <c r="I2" t="n">
-        <v>10.90484588386031</v>
+        <v>10.90484588386029</v>
       </c>
       <c r="J2" t="n">
-        <v>7.753204000752314</v>
+        <v>7.753204000752302</v>
       </c>
       <c r="K2" t="n">
         <v>4.970815362863648</v>
       </c>
       <c r="L2" t="n">
-        <v>35.34354695400381</v>
+        <v>35.3435469540038</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1339233690897062</v>
+        <v>0.1339233690897061</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1360555213132328</v>
+        <v>0.136055521313233</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1339233690897062</v>
+        <v>0.1339233690897061</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1367452493170456</v>
+        <v>0.1367452493170459</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1367452493170456</v>
+        <v>0.1367452493170459</v>
       </c>
       <c r="G3" t="n">
-        <v>0.134095531435551</v>
+        <v>0.1340955314355511</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1339233690897062</v>
+        <v>0.1339233690897061</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1346001200363499</v>
+        <v>0.1346001200363502</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1339233690897062</v>
+        <v>0.1339233690897061</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1339233690897062</v>
+        <v>0.1339233690897061</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1339233690897062</v>
+        <v>0.1339233690897061</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>82.37047481525154</v>
+        <v>6.802112330887377</v>
       </c>
       <c r="C4" t="n">
-        <v>6.890528693572321</v>
+        <v>6.890528693572319</v>
       </c>
       <c r="D4" t="n">
-        <v>6.780334133189188</v>
+        <v>6.780333217722753</v>
       </c>
       <c r="E4" t="n">
-        <v>6.86772341071064</v>
+        <v>6.867723410710639</v>
       </c>
       <c r="F4" t="n">
         <v>6.889677362212414</v>
       </c>
       <c r="G4" t="n">
-        <v>82.37064697759737</v>
+        <v>6.802284493233229</v>
       </c>
       <c r="H4" t="n">
         <v>82.35967190382887</v>
       </c>
       <c r="I4" t="n">
-        <v>82.37115156619826</v>
+        <v>82.37115156619828</v>
       </c>
       <c r="J4" t="n">
-        <v>82.36269081366676</v>
+        <v>6.804508706933245</v>
       </c>
       <c r="K4" t="n">
-        <v>6.692305870471019</v>
+        <v>6.692305870471017</v>
       </c>
       <c r="L4" t="n">
-        <v>6.788095595629559</v>
+        <v>6.788095595629558</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5115120796661351</v>
+        <v>0.5115120796661317</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5121888306127784</v>
+        <v>0.5121888306127782</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5114850211536862</v>
+        <v>0.5114850211536865</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5121129208213901</v>
+        <v>0.5121129208213906</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5121129208213901</v>
+        <v>0.5121129208213906</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5116842420119784</v>
+        <v>0.5116842420119767</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5115120796661351</v>
+        <v>0.5115120796661317</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5121888306127784</v>
+        <v>0.5121888306127782</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5115120796661351</v>
+        <v>0.5115120796661317</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5115120796661351</v>
+        <v>0.5115120796661317</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5115120796661351</v>
+        <v>0.5115120796661317</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5716518752796007</v>
+        <v>0.5716518752795984</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8806699357069533</v>
+        <v>0.8806699357080148</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9439032046005827</v>
+        <v>0.9439032046005804</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7963378641558088</v>
+        <v>0.7963378641558081</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5820727301919899</v>
+        <v>0.5820727301919892</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8801433491842372</v>
+        <v>0.8801433491842353</v>
       </c>
       <c r="H6" t="n">
-        <v>0.879971186838298</v>
+        <v>0.8799711868382964</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8806479377850334</v>
+        <v>0.8806479377850329</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8800317803767844</v>
+        <v>0.8800317803767835</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5659246857804054</v>
+        <v>0.5659246857804032</v>
       </c>
       <c r="L6" t="n">
-        <v>1.20203648896348</v>
+        <v>1.202036488963474</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.011464469107864</v>
+        <v>3.011464469107857</v>
       </c>
       <c r="C7" t="n">
         <v>3.821080927408416</v>
       </c>
       <c r="D7" t="n">
-        <v>3.820404105307153</v>
+        <v>3.82040410530715</v>
       </c>
       <c r="E7" t="n">
-        <v>4.75457944043887</v>
+        <v>4.754579440438872</v>
       </c>
       <c r="F7" t="n">
         <v>3.821080373294888</v>
       </c>
       <c r="G7" t="n">
-        <v>3.820576338807624</v>
+        <v>3.820576338807621</v>
       </c>
       <c r="H7" t="n">
-        <v>3.820404176461778</v>
+        <v>3.820404176461776</v>
       </c>
       <c r="I7" t="n">
         <v>3.821080927408416</v>
       </c>
       <c r="J7" t="n">
-        <v>3.820404176461778</v>
+        <v>3.820404176461776</v>
       </c>
       <c r="K7" t="n">
-        <v>3.351701303142403</v>
+        <v>3.351701303142401</v>
       </c>
       <c r="L7" t="n">
-        <v>3.820404176461778</v>
+        <v>3.820404176461776</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1409281500614064</v>
+        <v>0.1409281500614069</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.01739112161231463</v>
+        <v>-0.01739112161231481</v>
       </c>
       <c r="D8" t="n">
-        <v>0.07459393395709629</v>
+        <v>0.07459393395709699</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.01739112161231463</v>
+        <v>-0.01739112161231481</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.01739112161231463</v>
+        <v>-0.01739112161231481</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.04280252451234285</v>
+        <v>-0.04280252451234409</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.05962099340135162</v>
+        <v>-0.0596209934013504</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01739112161231463</v>
+        <v>-0.01739112161231481</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03579569310923996</v>
+        <v>0.03579569310923969</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08966214721502352</v>
+        <v>0.08966214721502411</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5234320600049172</v>
+        <v>-0.5234320600049159</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1741827433419285</v>
+        <v>0.1741827433419278</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1339523480464418</v>
+        <v>0.1339523480464417</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1471685717526684</v>
+        <v>0.1471685717526681</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1339523480464418</v>
+        <v>0.1339523480464417</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1339523480464418</v>
+        <v>0.1339523480464417</v>
       </c>
       <c r="G9" t="n">
-        <v>0.09953318181895739</v>
+        <v>0.09953318181895685</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09274222898179031</v>
+        <v>0.09274222898178937</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1339523480464418</v>
+        <v>0.1339523480464417</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1314256795134249</v>
+        <v>0.131425679513425</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1533082738781539</v>
+        <v>0.1533082738781529</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.09586682859069737</v>
+        <v>0.1620360944070451</v>
       </c>
     </row>
   </sheetData>
@@ -5267,34 +5267,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.247130452331419</v>
+        <v>2.247130452331414</v>
       </c>
       <c r="C2" t="n">
-        <v>9.270388210250511</v>
+        <v>9.2703882102505</v>
       </c>
       <c r="D2" t="n">
-        <v>4.826965699331505</v>
+        <v>4.826965699331532</v>
       </c>
       <c r="E2" t="n">
-        <v>9.270388210250511</v>
+        <v>9.2703882102505</v>
       </c>
       <c r="F2" t="n">
-        <v>9.270388210250511</v>
+        <v>9.2703882102505</v>
       </c>
       <c r="G2" t="n">
-        <v>8.767781490032029</v>
+        <v>8.767781490032066</v>
       </c>
       <c r="H2" t="n">
-        <v>9.480120824729216</v>
+        <v>9.480120824729195</v>
       </c>
       <c r="I2" t="n">
-        <v>9.270388210250511</v>
+        <v>9.2703882102505</v>
       </c>
       <c r="J2" t="n">
-        <v>6.51537736336399</v>
+        <v>6.515377363364002</v>
       </c>
       <c r="K2" t="n">
-        <v>3.920624751474536</v>
+        <v>3.920624751474533</v>
       </c>
       <c r="L2" t="n">
         <v>20.43826984150618</v>
@@ -5310,34 +5310,34 @@
         <v>0.1269783441924913</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1299288723538271</v>
+        <v>0.1299288723538272</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1269783441924914</v>
+        <v>0.1269783441924912</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1305088300992693</v>
+        <v>0.1305088300992694</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1305088300992694</v>
+        <v>0.1305088300992695</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1271724157106117</v>
+        <v>0.127172415710612</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1269783441924914</v>
+        <v>0.1269783441924912</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1277933547763802</v>
+        <v>0.1277933547763803</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1269783441924914</v>
+        <v>0.1269783441924912</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1269783441924914</v>
+        <v>0.1269783441924912</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1269783441924914</v>
+        <v>0.1269783441924912</v>
       </c>
     </row>
     <row r="4">
@@ -5347,34 +5347,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.74022670835109</v>
+        <v>6.331593084549692</v>
       </c>
       <c r="C4" t="n">
-        <v>6.418556847620962</v>
+        <v>6.418556847620956</v>
       </c>
       <c r="D4" t="n">
-        <v>6.316406060451584</v>
+        <v>6.316406060451587</v>
       </c>
       <c r="E4" t="n">
-        <v>6.397461290145317</v>
+        <v>6.397461290145311</v>
       </c>
       <c r="F4" t="n">
-        <v>6.417073209328367</v>
+        <v>6.417073209328366</v>
       </c>
       <c r="G4" t="n">
-        <v>76.7404207798691</v>
+        <v>6.331787156067772</v>
       </c>
       <c r="H4" t="n">
-        <v>76.73024043272122</v>
+        <v>76.7302404327212</v>
       </c>
       <c r="I4" t="n">
-        <v>76.74104171893485</v>
+        <v>76.74104171893494</v>
       </c>
       <c r="J4" t="n">
-        <v>76.73340103003122</v>
+        <v>6.337178416030533</v>
       </c>
       <c r="K4" t="n">
-        <v>6.234037452751253</v>
+        <v>6.234037452751229</v>
       </c>
       <c r="L4" t="n">
         <v>6.322626350117829</v>
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4749755086177305</v>
+        <v>0.4749755086177314</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4757905192016189</v>
+        <v>0.4757905192016197</v>
       </c>
       <c r="D5" t="n">
-        <v>0.474950177082788</v>
+        <v>0.4749501770827879</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4758479646583103</v>
+        <v>0.4758479646583106</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4758479646583103</v>
+        <v>0.4758479646583105</v>
       </c>
       <c r="G5" t="n">
         <v>0.4751695801358504</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4749755086177304</v>
+        <v>0.4749755086177314</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4757905192016189</v>
+        <v>0.4757905192016197</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4749755086177304</v>
+        <v>0.4749755086177314</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4749755086177304</v>
+        <v>0.4749755086177314</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4749755086177304</v>
+        <v>0.4749755086177314</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.527230264805852</v>
+        <v>0.5272302648058531</v>
       </c>
       <c r="C6" t="n">
-        <v>0.810439651910008</v>
+        <v>0.8104396519100103</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8680091910505792</v>
+        <v>0.8680091910505809</v>
       </c>
       <c r="E6" t="n">
-        <v>0.733224385106533</v>
+        <v>0.7332243851065359</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5370416120358533</v>
+        <v>0.5370416120358555</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8096764484259578</v>
+        <v>0.8096764484259592</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8094823769077361</v>
+        <v>0.8094823769077371</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8102973874917263</v>
+        <v>0.8102973874917272</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8095378474941481</v>
+        <v>0.8095378474941505</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5219872869194473</v>
+        <v>0.5219872869194481</v>
       </c>
       <c r="L6" t="n">
-        <v>1.104318309496201</v>
+        <v>1.104318309496205</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.49956462706284</v>
+        <v>2.499564627062842</v>
       </c>
       <c r="C7" t="n">
-        <v>3.168690004364124</v>
+        <v>3.168690004364129</v>
       </c>
       <c r="D7" t="n">
-        <v>3.167874943772685</v>
+        <v>3.167874943772688</v>
       </c>
       <c r="E7" t="n">
-        <v>3.939905369301883</v>
+        <v>3.939905369301889</v>
       </c>
       <c r="F7" t="n">
-        <v>3.168689538299931</v>
+        <v>3.168689538299938</v>
       </c>
       <c r="G7" t="n">
-        <v>3.168069065298359</v>
+        <v>3.168069065298361</v>
       </c>
       <c r="H7" t="n">
-        <v>3.167874993780238</v>
+        <v>3.167874993780245</v>
       </c>
       <c r="I7" t="n">
-        <v>3.168690004364124</v>
+        <v>3.168690004364129</v>
       </c>
       <c r="J7" t="n">
-        <v>3.167874993780238</v>
+        <v>3.167874993780245</v>
       </c>
       <c r="K7" t="n">
-        <v>2.326352962065559</v>
+        <v>2.780653321614079</v>
       </c>
       <c r="L7" t="n">
-        <v>3.167874993780238</v>
+        <v>3.167874993780245</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1434888631378148</v>
+        <v>0.1434888631378151</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.001535903851205857</v>
+        <v>-0.001535903851205492</v>
       </c>
       <c r="D8" t="n">
-        <v>0.07834965608197518</v>
+        <v>0.07834965608197426</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.001535903851205857</v>
+        <v>-0.001535903851205492</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.001535903851205857</v>
+        <v>-0.001535903851205492</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.01524764953487529</v>
+        <v>-0.01524764953487582</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.008137771406576129</v>
+        <v>-0.008137771406575803</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.001535903851205857</v>
+        <v>-0.001535903851205492</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04751110401043337</v>
+        <v>0.04751110401043358</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09744543074321958</v>
+        <v>0.09744543074321997</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2568864054921711</v>
+        <v>-0.2568864054921712</v>
       </c>
     </row>
     <row r="9">
@@ -5550,34 +5550,34 @@
         <v>0.1724064553930859</v>
       </c>
       <c r="C9" t="n">
-        <v>0.138052492483289</v>
+        <v>0.1380524924832892</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1458787754053118</v>
+        <v>0.1458787754053114</v>
       </c>
       <c r="E9" t="n">
-        <v>0.138052492483289</v>
+        <v>0.1380524924832892</v>
       </c>
       <c r="F9" t="n">
-        <v>0.138052492483289</v>
+        <v>0.1380524924832892</v>
       </c>
       <c r="G9" t="n">
         <v>0.1079850930125933</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1108393348941154</v>
+        <v>0.1108393348941155</v>
       </c>
       <c r="I9" t="n">
-        <v>0.138052492483289</v>
+        <v>0.1380524924832892</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1333717271325533</v>
+        <v>0.1333717271325536</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1536584380446217</v>
+        <v>0.1536584380446221</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009673707944356062</v>
+        <v>0.1503337153844229</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.07428127672582</v>
+        <v>2.074281276725833</v>
       </c>
       <c r="C2" t="n">
-        <v>7.842661517065296</v>
+        <v>7.842661517065317</v>
       </c>
       <c r="D2" t="n">
-        <v>4.25404972349399</v>
+        <v>4.254049723494</v>
       </c>
       <c r="E2" t="n">
-        <v>7.842661517065296</v>
+        <v>7.842661517065317</v>
       </c>
       <c r="F2" t="n">
-        <v>7.842661517065296</v>
+        <v>7.842661517065317</v>
       </c>
       <c r="G2" t="n">
-        <v>7.440897490698569</v>
+        <v>7.440897490698586</v>
       </c>
       <c r="H2" t="n">
-        <v>10.6207409888657</v>
+        <v>10.62074098886567</v>
       </c>
       <c r="I2" t="n">
-        <v>7.842661517065296</v>
+        <v>7.842661517065317</v>
       </c>
       <c r="J2" t="n">
-        <v>5.404323889710493</v>
+        <v>5.404323889710499</v>
       </c>
       <c r="K2" t="n">
-        <v>2.940202443545181</v>
+        <v>2.940202443545177</v>
       </c>
       <c r="L2" t="n">
-        <v>5.079776159107578</v>
+        <v>15.59806324409334</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1204103578024434</v>
+        <v>0.1204103578024469</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1233638614907733</v>
+        <v>0.1233638614907742</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1204103578024437</v>
+        <v>0.120410357802447</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1238929397977588</v>
+        <v>0.1238929397977575</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1238929397977581</v>
+        <v>0.1238929397977574</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1205944831698615</v>
+        <v>0.1205944831698627</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1204103578024437</v>
+        <v>0.120410357802447</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1211605604579089</v>
+        <v>0.1211605604579092</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1204103578024437</v>
+        <v>0.120410357802447</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1204103578024437</v>
+        <v>0.120410357802447</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1204103578024437</v>
+        <v>0.120410357802447</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.318304761460984</v>
+        <v>6.318304761460977</v>
       </c>
       <c r="C4" t="n">
-        <v>6.405177344603676</v>
+        <v>6.405177344603691</v>
       </c>
       <c r="D4" t="n">
-        <v>76.7141361381039</v>
+        <v>6.305049949564407</v>
       </c>
       <c r="E4" t="n">
-        <v>6.384356294071019</v>
+        <v>6.384356294071026</v>
       </c>
       <c r="F4" t="n">
-        <v>6.404142062177031</v>
+        <v>6.40414206217703</v>
       </c>
       <c r="G4" t="n">
-        <v>6.318488886828372</v>
+        <v>76.72221480872636</v>
       </c>
       <c r="H4" t="n">
-        <v>76.71244100422686</v>
+        <v>76.71244100422676</v>
       </c>
       <c r="I4" t="n">
-        <v>76.72278088601433</v>
+        <v>6.319054964116411</v>
       </c>
       <c r="J4" t="n">
-        <v>6.324141923139504</v>
+        <v>76.71472714365348</v>
       </c>
       <c r="K4" t="n">
-        <v>6.22178029741493</v>
+        <v>6.221780297414937</v>
       </c>
       <c r="L4" t="n">
-        <v>6.310252043172885</v>
+        <v>6.310252043172886</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4647805470766634</v>
+        <v>0.4647805470766652</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4655307497321277</v>
+        <v>0.4655307497321291</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4647553243895899</v>
+        <v>0.4647553243895895</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4656764483924842</v>
+        <v>0.4656764483924833</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4656764483924842</v>
+        <v>0.4656764483924833</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4649646724440796</v>
+        <v>0.464964672444082</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4647805470766628</v>
+        <v>0.4647805470766648</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4655307497321277</v>
+        <v>0.4655307497321291</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4647805470766628</v>
+        <v>0.4647805470766648</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4647805470766628</v>
+        <v>0.4647805470766648</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4647805470766628</v>
+        <v>0.4647805470766648</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5131049768384328</v>
+        <v>0.5131049768384346</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7911434841786227</v>
+        <v>0.7911434841786259</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8476185100668963</v>
+        <v>0.8476185100669024</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7153386119363037</v>
+        <v>0.7153386119363049</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5227396042107266</v>
+        <v>0.5227396042107277</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7903518663882377</v>
+        <v>0.7903518663882408</v>
       </c>
       <c r="H6" t="n">
-        <v>0.790167741020776</v>
+        <v>0.7901677410207799</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7909179436762853</v>
+        <v>0.7909179436762892</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7902221917511832</v>
+        <v>0.7902221917511889</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5079583937538855</v>
+        <v>0.5079583937538888</v>
       </c>
       <c r="L6" t="n">
-        <v>1.07958296578057</v>
+        <v>1.079582965780576</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.247702305914451</v>
+        <v>2.247702305914454</v>
       </c>
       <c r="C7" t="n">
-        <v>2.848756860522425</v>
+        <v>2.848756860522429</v>
       </c>
       <c r="D7" t="n">
-        <v>2.848006557031472</v>
+        <v>2.848006557031474</v>
       </c>
       <c r="E7" t="n">
-        <v>3.541494642173294</v>
+        <v>3.541494642173295</v>
       </c>
       <c r="F7" t="n">
-        <v>2.848756363849187</v>
+        <v>2.848756363849194</v>
       </c>
       <c r="G7" t="n">
-        <v>2.848190783234394</v>
+        <v>2.84819078323439</v>
       </c>
       <c r="H7" t="n">
-        <v>2.848006657866967</v>
+        <v>2.848006657866968</v>
       </c>
       <c r="I7" t="n">
-        <v>2.848756860522425</v>
+        <v>2.848756860522429</v>
       </c>
       <c r="J7" t="n">
-        <v>2.848006657866967</v>
+        <v>2.848006657866968</v>
       </c>
       <c r="K7" t="n">
         <v>2.50018791635777</v>
       </c>
       <c r="L7" t="n">
-        <v>2.848006657866967</v>
+        <v>2.848006657866968</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1408688580147525</v>
+        <v>0.1408688580147527</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02701381579792948</v>
+        <v>0.02701381579792902</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08394687964340643</v>
+        <v>0.08394687964340826</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02701381579792948</v>
+        <v>0.02701381579792902</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02701381579792948</v>
+        <v>0.02701381579792902</v>
       </c>
       <c r="G8" t="n">
-        <v>0.007098261748692276</v>
+        <v>0.007098261748694407</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.04872298171117456</v>
+        <v>-0.04872298171117376</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02701381579792948</v>
+        <v>0.02701381579792902</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0675708533060229</v>
+        <v>0.06757085330602416</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1140573457428141</v>
+        <v>0.1140573457428153</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08508589659386546</v>
+        <v>0.08508589659386623</v>
       </c>
     </row>
     <row r="9">
@@ -5943,34 +5943,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1679751822681171</v>
+        <v>0.1679751822681185</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1455027334391708</v>
+        <v>0.1455027334391719</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1447940255312527</v>
+        <v>0.1447940255312541</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1455027334391708</v>
+        <v>0.1455027334391719</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1455027334391708</v>
+        <v>0.1455027334391719</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1136836276267596</v>
+        <v>0.1136836276267611</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0909774839413619</v>
+        <v>0.09097748394136293</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1455027334391708</v>
+        <v>0.1455027334391719</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1381679171910272</v>
+        <v>0.1381679171910275</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1570590193389183</v>
+        <v>0.1570590193389189</v>
       </c>
       <c r="L9" t="n">
         <v>0.1453342796918852</v>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9738103776214667</v>
+        <v>0.9738103776215197</v>
       </c>
       <c r="C2" t="n">
         <v>11.261282838897</v>
       </c>
       <c r="D2" t="n">
-        <v>3.426276936508326</v>
+        <v>3.426276936508324</v>
       </c>
       <c r="E2" t="n">
         <v>11.261282838897</v>
@@ -6074,22 +6074,22 @@
         <v>11.261282838897</v>
       </c>
       <c r="G2" t="n">
-        <v>13.68287810816893</v>
+        <v>13.68287810816892</v>
       </c>
       <c r="H2" t="n">
-        <v>23.59525059989437</v>
+        <v>23.59525059989438</v>
       </c>
       <c r="I2" t="n">
         <v>11.261282838897</v>
       </c>
       <c r="J2" t="n">
-        <v>10.43528480254209</v>
+        <v>10.4352848025421</v>
       </c>
       <c r="K2" t="n">
-        <v>4.41330676105548</v>
+        <v>4.413306761055497</v>
       </c>
       <c r="L2" t="n">
-        <v>16.19750656167275</v>
+        <v>16.19750656167276</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1421940271475451</v>
+        <v>0.142194027147546</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1416464046020248</v>
+        <v>0.1416464046020246</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1421940271475451</v>
+        <v>0.142194027147546</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1425516922625363</v>
+        <v>0.1425516922625357</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1425516922625363</v>
+        <v>0.1425516922625357</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1422617524686404</v>
+        <v>0.1422617524686406</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1421940271475451</v>
+        <v>0.142194027147546</v>
       </c>
       <c r="I3" t="n">
         <v>0.142207464310221</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1421940271475451</v>
+        <v>0.142194027147546</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1421940271475451</v>
+        <v>0.142194027147546</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1421940271475451</v>
+        <v>0.142194027147546</v>
       </c>
     </row>
     <row r="4">
@@ -6139,34 +6139,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.820177142836793</v>
+        <v>82.41083219859837</v>
       </c>
       <c r="C4" t="n">
-        <v>6.902313781223252</v>
+        <v>6.902313781223254</v>
       </c>
       <c r="D4" t="n">
-        <v>82.40017027473155</v>
+        <v>82.40017027473151</v>
       </c>
       <c r="E4" t="n">
-        <v>6.879146722521153</v>
+        <v>6.879146722521156</v>
       </c>
       <c r="F4" t="n">
-        <v>6.905412226480188</v>
+        <v>6.905412226480185</v>
       </c>
       <c r="G4" t="n">
-        <v>6.820244868157912</v>
+        <v>82.41089992391943</v>
       </c>
       <c r="H4" t="n">
-        <v>82.40155006640386</v>
+        <v>6.811538693393043</v>
       </c>
       <c r="I4" t="n">
-        <v>6.820190579999466</v>
+        <v>82.41084563576086</v>
       </c>
       <c r="J4" t="n">
-        <v>82.40259053404365</v>
+        <v>82.4025905340437</v>
       </c>
       <c r="K4" t="n">
-        <v>6.703708252154938</v>
+        <v>6.70370825215494</v>
       </c>
       <c r="L4" t="n">
         <v>6.808406787934492</v>
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5310243012858874</v>
+        <v>0.5310243012858868</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5310377384485616</v>
+        <v>0.5310377384485602</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5309970903602499</v>
+        <v>0.5309970903602501</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5309700778377244</v>
+        <v>0.5309700778377238</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5309700778377244</v>
+        <v>0.5309700778377238</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5310920266069793</v>
+        <v>0.5310920266069801</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5310243012858874</v>
+        <v>0.5310243012858868</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5310377384485616</v>
+        <v>0.5310377384485602</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5310243012858874</v>
+        <v>0.5310243012858868</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5310243012858874</v>
+        <v>0.5310243012858868</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5310243012858874</v>
+        <v>0.5310243012858868</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6039695617829307</v>
+        <v>0.6039695617829313</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9301841567280642</v>
+        <v>0.9301841567280633</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9977701234204152</v>
+        <v>0.9977701234204177</v>
       </c>
       <c r="E6" t="n">
-        <v>0.840969491402737</v>
+        <v>0.8409694914027372</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6142978776678675</v>
+        <v>0.6142978776678664</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9302048746780046</v>
+        <v>0.9302048746780047</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9301371493568286</v>
+        <v>0.9301371493568291</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9301505865195854</v>
+        <v>0.9301505865195849</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9302012505799477</v>
+        <v>0.9302012505799474</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5979108313947736</v>
+        <v>0.5979108313947751</v>
       </c>
       <c r="L6" t="n">
-        <v>1.270846468215954</v>
+        <v>1.270846468215956</v>
       </c>
     </row>
     <row r="7">
@@ -6262,34 +6262,34 @@
         <v>3.100427179945928</v>
       </c>
       <c r="C7" t="n">
-        <v>3.932814413797213</v>
+        <v>3.932814413797214</v>
       </c>
       <c r="D7" t="n">
-        <v>3.932800810821376</v>
+        <v>3.932800810821377</v>
       </c>
       <c r="E7" t="n">
-        <v>4.893355028175503</v>
+        <v>4.893355028175502</v>
       </c>
       <c r="F7" t="n">
-        <v>3.93281365544994</v>
+        <v>3.932813655449941</v>
       </c>
       <c r="G7" t="n">
-        <v>3.932868701955642</v>
+        <v>3.932868701955643</v>
       </c>
       <c r="H7" t="n">
-        <v>3.932800976634558</v>
+        <v>3.932800976634562</v>
       </c>
       <c r="I7" t="n">
-        <v>3.932814413797213</v>
+        <v>3.932814413797214</v>
       </c>
       <c r="J7" t="n">
-        <v>3.932800976634558</v>
+        <v>3.932800976634562</v>
       </c>
       <c r="K7" t="n">
-        <v>3.450520260108856</v>
+        <v>3.450520260108854</v>
       </c>
       <c r="L7" t="n">
-        <v>3.932800976634558</v>
+        <v>3.932800976634562</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1940847823108272</v>
+        <v>0.1940847823108273</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0187925299597128</v>
+        <v>-0.01879252995971344</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1329769415799841</v>
+        <v>0.1329769415799844</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0187925299597128</v>
+        <v>-0.01879252995971344</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0187925299597128</v>
+        <v>-0.01879252995971344</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1120881549538524</v>
+        <v>-0.1120881549538519</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3193648312700987</v>
+        <v>-0.3193648312700985</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0187925299597128</v>
+        <v>-0.01879252995971344</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.01078913979672883</v>
+        <v>-0.01078913979672795</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1090582759344529</v>
+        <v>0.1090582759344526</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.221827280031133</v>
+        <v>-0.1154223559895262</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.202529573607947</v>
+        <v>0.2025295736079477</v>
       </c>
       <c r="C9" t="n">
-        <v>0.138215952705675</v>
+        <v>0.1382159527056748</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1776428267550468</v>
+        <v>0.1776428267550471</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1382159527056752</v>
+        <v>0.1382159527056748</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1382159527056752</v>
+        <v>0.1382159527056748</v>
       </c>
       <c r="G9" t="n">
-        <v>0.07771952162634842</v>
+        <v>0.07771952162634863</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.006100806919995039</v>
+        <v>-0.006100806919994858</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1382159527056752</v>
+        <v>0.1382159527056748</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1191705965006458</v>
+        <v>0.1191705965006457</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1679042464880541</v>
+        <v>0.167904246488054</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07671703978872184</v>
+        <v>0.07671703978872202</v>
       </c>
     </row>
   </sheetData>
@@ -6455,34 +6455,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.934262094514654</v>
+        <v>0.9342620945146534</v>
       </c>
       <c r="C2" t="n">
-        <v>8.511844238662562</v>
+        <v>8.511844238662565</v>
       </c>
       <c r="D2" t="n">
-        <v>2.461380163304673</v>
+        <v>2.461380163304672</v>
       </c>
       <c r="E2" t="n">
-        <v>8.511844238662562</v>
+        <v>8.511844238662565</v>
       </c>
       <c r="F2" t="n">
-        <v>8.511844238662562</v>
+        <v>8.511844238662565</v>
       </c>
       <c r="G2" t="n">
-        <v>8.988878822372921</v>
+        <v>8.988878822372952</v>
       </c>
       <c r="H2" t="n">
-        <v>12.70247271335751</v>
+        <v>12.7024727133575</v>
       </c>
       <c r="I2" t="n">
-        <v>8.511844238662562</v>
+        <v>8.511844238662565</v>
       </c>
       <c r="J2" t="n">
-        <v>6.3698101593966</v>
+        <v>6.369810159396607</v>
       </c>
       <c r="K2" t="n">
-        <v>2.385639812330807</v>
+        <v>2.385639812330806</v>
       </c>
       <c r="L2" t="n">
         <v>10.27265588918169</v>
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1252152583209571</v>
+        <v>0.1252152583209563</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1266015259975825</v>
+        <v>0.1266015259975824</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1252152583209571</v>
+        <v>0.1252152583209563</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1272116692090986</v>
+        <v>0.1272116692090988</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1272116692090988</v>
+        <v>0.1272116692090985</v>
       </c>
       <c r="G3" t="n">
         <v>0.1253554355928821</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1252152583209571</v>
+        <v>0.1252152583209563</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1256873527021025</v>
+        <v>0.125687352702103</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1252152583209571</v>
+        <v>0.1252152583209563</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1252152583209571</v>
+        <v>0.1252152583209563</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1252152583209571</v>
+        <v>0.1252152583209563</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.74334858560698</v>
+        <v>76.74334858560695</v>
       </c>
       <c r="C4" t="n">
-        <v>6.414379777657314</v>
+        <v>6.414379777657317</v>
       </c>
       <c r="D4" t="n">
-        <v>6.309577200948139</v>
+        <v>6.309576305766678</v>
       </c>
       <c r="E4" t="n">
-        <v>6.393316171408906</v>
+        <v>6.393316171408907</v>
       </c>
       <c r="F4" t="n">
-        <v>6.414836557607244</v>
+        <v>6.414836557607241</v>
       </c>
       <c r="G4" t="n">
-        <v>6.329356454211911</v>
+        <v>76.74348876287902</v>
       </c>
       <c r="H4" t="n">
-        <v>6.32435392029941</v>
+        <v>76.73471429435138</v>
       </c>
       <c r="I4" t="n">
-        <v>6.329688371321093</v>
+        <v>76.74382067998825</v>
       </c>
       <c r="J4" t="n">
-        <v>76.73644620519752</v>
+        <v>6.33586960343012</v>
       </c>
       <c r="K4" t="n">
-        <v>6.22856302737806</v>
+        <v>6.228563027378062</v>
       </c>
       <c r="L4" t="n">
-        <v>6.322853039867256</v>
+        <v>6.322853039867255</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4736852233319923</v>
+        <v>0.473685223331992</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4741573177131391</v>
+        <v>0.4741573177131399</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4736599864629666</v>
+        <v>0.4736599864629671</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4741498575291313</v>
+        <v>0.4741498575291307</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4741498575291313</v>
+        <v>0.4741498575291307</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4738254006039183</v>
+        <v>0.4738254006039178</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4736852233319923</v>
+        <v>0.473685223331992</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4741573177131391</v>
+        <v>0.4741573177131399</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4736852233319923</v>
+        <v>0.473685223331992</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4736852233319923</v>
+        <v>0.473685223331992</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4736852233319923</v>
+        <v>0.473685223331992</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.527816889926078</v>
+        <v>0.5278168899260774</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8124817229807059</v>
+        <v>0.8124817229807055</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8708417188690916</v>
+        <v>0.8708417188690928</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7347642994855871</v>
+        <v>0.7347642994855862</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5373055100108223</v>
+        <v>0.5373055100108235</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8120693611699991</v>
+        <v>0.8120693611699988</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8119291838980601</v>
+        <v>0.811929183898061</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8124012782792189</v>
+        <v>0.8124012782792179</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8119850200594118</v>
+        <v>0.8119850200594128</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5225393582068588</v>
+        <v>0.5225393582068587</v>
       </c>
       <c r="L6" t="n">
-        <v>1.108708231991746</v>
+        <v>1.108708231991749</v>
       </c>
     </row>
     <row r="7">
@@ -6658,34 +6658,34 @@
         <v>2.509254587984112</v>
       </c>
       <c r="C7" t="n">
-        <v>3.181364330473007</v>
+        <v>3.18136433047301</v>
       </c>
       <c r="D7" t="n">
-        <v>3.180892129200462</v>
+        <v>3.180892129200466</v>
       </c>
       <c r="E7" t="n">
-        <v>3.956419139458125</v>
+        <v>3.956419139458131</v>
       </c>
       <c r="F7" t="n">
-        <v>3.181363771044338</v>
+        <v>3.181363771044339</v>
       </c>
       <c r="G7" t="n">
-        <v>3.181032413363793</v>
+        <v>3.181032413363795</v>
       </c>
       <c r="H7" t="n">
-        <v>3.180892236091867</v>
+        <v>3.18089223609187</v>
       </c>
       <c r="I7" t="n">
-        <v>3.181364330473007</v>
+        <v>3.18136433047301</v>
       </c>
       <c r="J7" t="n">
-        <v>3.180892236091867</v>
+        <v>3.18089223609187</v>
       </c>
       <c r="K7" t="n">
-        <v>2.775954416187672</v>
+        <v>2.791742700095758</v>
       </c>
       <c r="L7" t="n">
-        <v>3.180892236091867</v>
+        <v>3.18089223609187</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1758988178198626</v>
+        <v>0.1758988178198628</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01277568595044616</v>
+        <v>0.01277568595044602</v>
       </c>
       <c r="D8" t="n">
         <v>0.1343511816176307</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01277568595044616</v>
+        <v>0.01277568595044602</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01277568595044616</v>
+        <v>0.01277568595044602</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.03826475080024568</v>
+        <v>-0.03826475080024586</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1311853888070971</v>
+        <v>-0.1311853888070967</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01277568595044616</v>
+        <v>0.01277568595044602</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04215065213432873</v>
+        <v>0.04215065213432878</v>
       </c>
       <c r="K8" t="n">
         <v>0.1370264358991947</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0278707626690745</v>
+        <v>-0.04647858594483111</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1852936041419396</v>
+        <v>0.1852936041419397</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1426271757159337</v>
+        <v>0.1426271757159338</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1683731200780245</v>
+        <v>0.1683731200780247</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1426271757159337</v>
+        <v>0.1426271757159338</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1426271757159337</v>
+        <v>0.1426271757159338</v>
       </c>
       <c r="G9" t="n">
-        <v>0.09813357431716037</v>
+        <v>0.09813357431716049</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0605236377480086</v>
+        <v>0.0605236377480087</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1426271757159337</v>
+        <v>0.1426271757159338</v>
       </c>
       <c r="J9" t="n">
         <v>0.1308770601190095</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1694641861920375</v>
+        <v>0.1694641861920376</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1024682051670029</v>
+        <v>0.09490078364375544</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.057376452676942</v>
+        <v>1.05737645267694</v>
       </c>
       <c r="C2" t="n">
-        <v>6.285629862530855</v>
+        <v>6.285629862530837</v>
       </c>
       <c r="D2" t="n">
-        <v>1.635104016210322</v>
+        <v>1.635104016210317</v>
       </c>
       <c r="E2" t="n">
-        <v>6.285629862530855</v>
+        <v>6.285629862530837</v>
       </c>
       <c r="F2" t="n">
-        <v>6.285629862530855</v>
+        <v>6.285629862530837</v>
       </c>
       <c r="G2" t="n">
-        <v>5.848258743992585</v>
+        <v>5.848258743992591</v>
       </c>
       <c r="H2" t="n">
-        <v>10.14350019899164</v>
+        <v>10.14350019899162</v>
       </c>
       <c r="I2" t="n">
-        <v>6.285629862530855</v>
+        <v>6.285629862530837</v>
       </c>
       <c r="J2" t="n">
-        <v>3.712817612385196</v>
+        <v>3.712817612385193</v>
       </c>
       <c r="K2" t="n">
-        <v>1.313979829268313</v>
+        <v>1.313979829268308</v>
       </c>
       <c r="L2" t="n">
-        <v>6.04168104074221</v>
+        <v>8.60106249160431</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1097539390624866</v>
+        <v>0.1097539390624843</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1119652851081286</v>
+        <v>0.1119652851081284</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1097539390624866</v>
+        <v>0.1097539390624843</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1124083053094799</v>
+        <v>0.1124083053094796</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1124083053094796</v>
+        <v>0.1124083053094797</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1099313927684223</v>
+        <v>0.109931392768422</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1097539390624866</v>
+        <v>0.1097539390624843</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1104600942969527</v>
+        <v>0.1104600942969523</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1097539390624866</v>
+        <v>0.1097539390624843</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1097539390624866</v>
+        <v>0.1097539390624843</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1097539390624866</v>
+        <v>0.1097539390624843</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.295406702229701</v>
+        <v>6.295406702229696</v>
       </c>
       <c r="C4" t="n">
-        <v>6.386445299036729</v>
+        <v>6.386445299036721</v>
       </c>
       <c r="D4" t="n">
-        <v>6.284475865102093</v>
+        <v>6.284475865102086</v>
       </c>
       <c r="E4" t="n">
-        <v>6.36602222639744</v>
+        <v>6.366022226397439</v>
       </c>
       <c r="F4" t="n">
-        <v>6.385797721381632</v>
+        <v>6.385797721381629</v>
       </c>
       <c r="G4" t="n">
-        <v>76.69028749169556</v>
+        <v>6.295584155935629</v>
       </c>
       <c r="H4" t="n">
-        <v>76.68115386599669</v>
+        <v>76.68115386599666</v>
       </c>
       <c r="I4" t="n">
-        <v>6.296112857464182</v>
+        <v>6.296112857464175</v>
       </c>
       <c r="J4" t="n">
-        <v>76.68261827353919</v>
+        <v>6.305538008288077</v>
       </c>
       <c r="K4" t="n">
-        <v>6.203085458912575</v>
+        <v>6.203085458912582</v>
       </c>
       <c r="L4" t="n">
-        <v>6.292987927282444</v>
+        <v>6.292987927282445</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.445021178178109</v>
+        <v>0.4450211781781078</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4457273334125748</v>
+        <v>0.445727333412574</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4449962529063849</v>
+        <v>0.4449962529063817</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4457176950425327</v>
+        <v>0.4457176950425323</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4457176950425327</v>
+        <v>0.4457176950425323</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4451986318840467</v>
+        <v>0.4451986318840447</v>
       </c>
       <c r="H5" t="n">
-        <v>0.445021178178109</v>
+        <v>0.4450211781781078</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4457273334125748</v>
+        <v>0.445727333412574</v>
       </c>
       <c r="J5" t="n">
-        <v>0.445021178178109</v>
+        <v>0.4450211781781078</v>
       </c>
       <c r="K5" t="n">
-        <v>0.445021178178109</v>
+        <v>0.4450211781781078</v>
       </c>
       <c r="L5" t="n">
-        <v>0.445021178178109</v>
+        <v>0.4450211781781078</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4861488086372704</v>
+        <v>0.4861488086372672</v>
       </c>
       <c r="C6" t="n">
         <v>0.7520022234654696</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8061864014675416</v>
+        <v>0.8061864014675395</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6794925706552972</v>
+        <v>0.6794925706552979</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4952664875351877</v>
+        <v>0.4952664875351878</v>
       </c>
       <c r="G6" t="n">
-        <v>0.751399245358349</v>
+        <v>0.7513992453583487</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7512217916524742</v>
+        <v>0.7512217916524712</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7519279468868811</v>
+        <v>0.7519279468868806</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7512738860515691</v>
+        <v>0.751273886051566</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4812249418930765</v>
+        <v>0.481224941893073</v>
       </c>
       <c r="L6" t="n">
-        <v>1.028112687417961</v>
+        <v>1.028112687417958</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.196134742285412</v>
+        <v>2.196134742285407</v>
       </c>
       <c r="C7" t="n">
-        <v>2.785120288197886</v>
+        <v>2.785120288197885</v>
       </c>
       <c r="D7" t="n">
-        <v>2.784413992148111</v>
+        <v>2.784413992148108</v>
       </c>
       <c r="E7" t="n">
-        <v>3.463981469824342</v>
+        <v>3.46398146982434</v>
       </c>
       <c r="F7" t="n">
-        <v>2.785119780690166</v>
+        <v>2.785119780690164</v>
       </c>
       <c r="G7" t="n">
-        <v>2.784591586669348</v>
+        <v>2.78459158666935</v>
       </c>
       <c r="H7" t="n">
-        <v>2.784414132963415</v>
+        <v>2.784414132963411</v>
       </c>
       <c r="I7" t="n">
-        <v>2.785120288197886</v>
+        <v>2.785120288197885</v>
       </c>
       <c r="J7" t="n">
-        <v>2.784414132963415</v>
+        <v>2.784414132963411</v>
       </c>
       <c r="K7" t="n">
-        <v>2.42973391631309</v>
+        <v>2.429733916313091</v>
       </c>
       <c r="L7" t="n">
-        <v>2.784414132963415</v>
+        <v>2.784414132963411</v>
       </c>
     </row>
     <row r="8">
@@ -7094,34 +7094,34 @@
         <v>0.155132930051764</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05876899542765249</v>
+        <v>0.05876899542765226</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1402669799149822</v>
+        <v>0.1402669799149819</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05876899542765249</v>
+        <v>0.05876899542765226</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05876899542765249</v>
+        <v>0.05876899542765226</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03223509121888054</v>
+        <v>0.0322350912188801</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.05884252829894066</v>
+        <v>-0.05884252829894034</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05876899542765249</v>
+        <v>0.05876899542765226</v>
       </c>
       <c r="J8" t="n">
-        <v>0.09185997356891581</v>
+        <v>0.09185997356891556</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1478624662736343</v>
+        <v>0.1478624662736339</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.01968881952231809</v>
+        <v>0.04870786868002955</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.166903415282752</v>
+        <v>0.1669034152827517</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1512165545996625</v>
+        <v>0.1512165545996622</v>
       </c>
       <c r="D9" t="n">
-        <v>0.16084960304551</v>
+        <v>0.1608496030455097</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1512165545996625</v>
+        <v>0.1512165545996622</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1512165545996625</v>
+        <v>0.1512165545996622</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1170012468850652</v>
+        <v>0.1170012468850649</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0799728280465328</v>
+        <v>0.07997282804653243</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1512165545996625</v>
+        <v>0.1512165545996622</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1411655065308522</v>
+        <v>0.141165506530852</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1639437825416672</v>
+        <v>0.1639437825416671</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1236548995783286</v>
+        <v>0.1236548995783284</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.935596775540825</v>
+        <v>1.935596775540818</v>
       </c>
       <c r="C2" t="n">
-        <v>11.24097633360986</v>
+        <v>11.24097633360988</v>
       </c>
       <c r="D2" t="n">
-        <v>5.366935205520275</v>
+        <v>5.366935205520274</v>
       </c>
       <c r="E2" t="n">
-        <v>11.24097633360986</v>
+        <v>11.24097633360988</v>
       </c>
       <c r="F2" t="n">
-        <v>11.24097633360986</v>
+        <v>11.24097633360988</v>
       </c>
       <c r="G2" t="n">
-        <v>11.25967116556026</v>
+        <v>11.25967116556023</v>
       </c>
       <c r="H2" t="n">
         <v>12.21602577534901</v>
       </c>
       <c r="I2" t="n">
-        <v>11.24097633360986</v>
+        <v>11.24097633360988</v>
       </c>
       <c r="J2" t="n">
-        <v>9.802263918356921</v>
+        <v>9.80226391835691</v>
       </c>
       <c r="K2" t="n">
-        <v>4.763451613095184</v>
+        <v>4.763451613095168</v>
       </c>
       <c r="L2" t="n">
-        <v>9.162610375396804</v>
+        <v>38.22942681152082</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1363881210936266</v>
+        <v>0.1363881210936265</v>
       </c>
       <c r="C3" t="n">
         <v>0.1385702295647688</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1363881210936266</v>
+        <v>0.1363881210936265</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1392690694197547</v>
+        <v>0.1392690694197544</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1392690694197547</v>
+        <v>0.1392690694197536</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1365542216370129</v>
+        <v>0.1365542216370123</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1363881210936266</v>
+        <v>0.1363881210936265</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1370273645063703</v>
+        <v>0.1370273645063701</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1363881210936266</v>
+        <v>0.1363881210936265</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1363881210936266</v>
+        <v>0.1363881210936265</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1363881210936266</v>
+        <v>0.1363881210936265</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.808100465057571</v>
+        <v>6.808100465057572</v>
       </c>
       <c r="C4" t="n">
-        <v>6.895829064712698</v>
+        <v>6.895829064712686</v>
       </c>
       <c r="D4" t="n">
-        <v>6.784711774524935</v>
+        <v>6.784711774524944</v>
       </c>
       <c r="E4" t="n">
-        <v>6.872834972064436</v>
+        <v>6.872834972064433</v>
       </c>
       <c r="F4" t="n">
-        <v>6.895194134319492</v>
+        <v>6.895194134319489</v>
       </c>
       <c r="G4" t="n">
-        <v>82.38115071380844</v>
+        <v>82.38115071380841</v>
       </c>
       <c r="H4" t="n">
-        <v>82.36950406739658</v>
+        <v>82.36950406739655</v>
       </c>
       <c r="I4" t="n">
-        <v>82.38162385667775</v>
+        <v>82.38162385667778</v>
       </c>
       <c r="J4" t="n">
-        <v>82.3725809804517</v>
+        <v>82.37258098045177</v>
       </c>
       <c r="K4" t="n">
         <v>6.6966026545627</v>
       </c>
       <c r="L4" t="n">
-        <v>6.794858072435636</v>
+        <v>6.794858072435635</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5156887312146384</v>
+        <v>0.515688731214638</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5163279746273829</v>
+        <v>0.5163279746273828</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5156615797736883</v>
+        <v>0.5156615797736881</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5163052061977337</v>
+        <v>0.5163052061977336</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5163052061977337</v>
+        <v>0.5163052061977336</v>
       </c>
       <c r="G5" t="n">
-        <v>0.515854831758026</v>
+        <v>0.5158548317580248</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5156887312146384</v>
+        <v>0.515688731214638</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5163279746273829</v>
+        <v>0.5163279746273828</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5156887312146384</v>
+        <v>0.515688731214638</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5156887312146384</v>
+        <v>0.515688731214638</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5156887312146384</v>
+        <v>0.515688731214638</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5781707633059302</v>
+        <v>0.5781707633059285</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8901011422417132</v>
+        <v>0.8901011422405744</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9539214029144333</v>
+        <v>0.9539214029144293</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8049709163045704</v>
+        <v>0.8049709163045707</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5886777399176822</v>
+        <v>0.5886777399176818</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8895544993464283</v>
+        <v>0.8895544993464272</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8893883988029491</v>
+        <v>0.8893883988029477</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8900276422157859</v>
+        <v>0.8900276422157833</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8894495619424124</v>
+        <v>0.8894495619424116</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5723897359518544</v>
+        <v>0.5723897359518542</v>
       </c>
       <c r="L6" t="n">
-        <v>1.214481242633033</v>
+        <v>1.214481242633027</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.030148633076928</v>
+        <v>3.030148633076923</v>
       </c>
       <c r="C7" t="n">
-        <v>3.844353464982982</v>
+        <v>3.844353464982986</v>
       </c>
       <c r="D7" t="n">
-        <v>3.84371414390188</v>
+        <v>3.843714143901876</v>
       </c>
       <c r="E7" t="n">
-        <v>4.783190114780483</v>
+        <v>4.78319011478048</v>
       </c>
       <c r="F7" t="n">
-        <v>3.844352889993415</v>
+        <v>3.84435288999341</v>
       </c>
       <c r="G7" t="n">
-        <v>3.843880322113627</v>
+        <v>3.843880322113626</v>
       </c>
       <c r="H7" t="n">
-        <v>3.843714221570241</v>
+        <v>3.84371422157025</v>
       </c>
       <c r="I7" t="n">
-        <v>3.844353464982982</v>
+        <v>3.844353464982986</v>
       </c>
       <c r="J7" t="n">
-        <v>3.843714221570241</v>
+        <v>3.84371422157025</v>
       </c>
       <c r="K7" t="n">
-        <v>3.37233109181181</v>
+        <v>3.372331091811807</v>
       </c>
       <c r="L7" t="n">
-        <v>3.843714221570241</v>
+        <v>3.84371422157025</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1618666254982379</v>
+        <v>0.161866625498238</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.02374962639848077</v>
+        <v>-0.02374962639848146</v>
       </c>
       <c r="D8" t="n">
-        <v>0.07891792579542328</v>
+        <v>0.07891792579542228</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.02374962639848077</v>
+        <v>-0.02374962639848146</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.02374962639848077</v>
+        <v>-0.02374962639848146</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0542327218418916</v>
+        <v>-0.05423272184189152</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0626092845364162</v>
+        <v>-0.06260928453641575</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.02374962639848077</v>
+        <v>-0.02374962639848146</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.006037562813863835</v>
+        <v>-0.006037562813863959</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09490350862254303</v>
+        <v>0.09490350862254311</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02610958177376049</v>
+        <v>0.02610958177376039</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1842278494442253</v>
+        <v>0.1842278494442247</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1330208559588489</v>
+        <v>0.1330208559588484</v>
       </c>
       <c r="D9" t="n">
-        <v>0.150446658534739</v>
+        <v>0.1504466585347382</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1330208559588489</v>
+        <v>0.1330208559588484</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1330208559588489</v>
+        <v>0.1330208559588484</v>
       </c>
       <c r="G9" t="n">
-        <v>0.09637744990544191</v>
+        <v>0.09637744990544146</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09304731854497247</v>
+        <v>0.09304731854497209</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1330208559588489</v>
+        <v>0.1330208559588484</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1159212113862658</v>
+        <v>0.1159212113862655</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1569599054726674</v>
+        <v>0.1569599054726669</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1290686927471591</v>
+        <v>-0.1174011554139562</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7816677952031362</v>
+        <v>0.7816677952031367</v>
       </c>
       <c r="C2" t="n">
-        <v>8.653798097605105</v>
+        <v>8.653798097605115</v>
       </c>
       <c r="D2" t="n">
-        <v>4.055356773767141</v>
+        <v>4.055356773767142</v>
       </c>
       <c r="E2" t="n">
-        <v>8.653798097605105</v>
+        <v>8.653798097605115</v>
       </c>
       <c r="F2" t="n">
-        <v>8.653798097605105</v>
+        <v>8.653798097605115</v>
       </c>
       <c r="G2" t="n">
-        <v>8.68420656646075</v>
+        <v>8.684206566460704</v>
       </c>
       <c r="H2" t="n">
-        <v>20.01715371401261</v>
+        <v>20.01715371401264</v>
       </c>
       <c r="I2" t="n">
-        <v>8.653798097605105</v>
+        <v>8.653798097605115</v>
       </c>
       <c r="J2" t="n">
-        <v>7.073155172853319</v>
+        <v>7.073155172853332</v>
       </c>
       <c r="K2" t="n">
-        <v>2.709423653727302</v>
+        <v>2.709423653727304</v>
       </c>
       <c r="L2" t="n">
-        <v>16.6105278682193</v>
+        <v>8.251767688993366</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1251160959910738</v>
+        <v>0.1251160959910753</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1270352716762625</v>
+        <v>0.1270352716762627</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1251160959910738</v>
+        <v>0.1251160959910753</v>
       </c>
       <c r="E3" t="n">
-        <v>0.127636289801656</v>
+        <v>0.1276362898016563</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1276362898016559</v>
+        <v>0.1276362898016562</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1252746608712633</v>
+        <v>0.1252746608712638</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1251160959910738</v>
+        <v>0.1251160959910753</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1257050473316259</v>
+        <v>0.1257050473316258</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1251160959910738</v>
+        <v>0.1251160959910753</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1251160959910738</v>
+        <v>0.1251160959910753</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1251160959910738</v>
+        <v>0.1251160959910753</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.74202006092014</v>
+        <v>76.74202006092013</v>
       </c>
       <c r="C4" t="n">
-        <v>6.414586642359975</v>
+        <v>6.414586642359977</v>
       </c>
       <c r="D4" t="n">
-        <v>6.312902561857101</v>
+        <v>6.312901754885079</v>
       </c>
       <c r="E4" t="n">
-        <v>6.393534306927027</v>
+        <v>6.39353430692703</v>
       </c>
       <c r="F4" t="n">
-        <v>6.414315756225554</v>
+        <v>6.41431575622555</v>
       </c>
       <c r="G4" t="n">
-        <v>6.33031065360643</v>
+        <v>76.74217862580031</v>
       </c>
       <c r="H4" t="n">
         <v>76.73441838248156</v>
       </c>
       <c r="I4" t="n">
-        <v>76.74260901226069</v>
+        <v>76.74260901226067</v>
       </c>
       <c r="J4" t="n">
-        <v>6.335184170508335</v>
+        <v>6.335184170508342</v>
       </c>
       <c r="K4" t="n">
-        <v>6.229128527027519</v>
+        <v>6.229128527027511</v>
       </c>
       <c r="L4" t="n">
-        <v>6.321421243734705</v>
+        <v>6.321421243734703</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4737975788391101</v>
+        <v>0.4737975788391123</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4743865301796612</v>
+        <v>0.4743865301796617</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4737723417296008</v>
+        <v>0.4737723417296033</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4743911174898875</v>
+        <v>0.4743911174898878</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4743911174898877</v>
+        <v>0.4743911174898878</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4739561437192986</v>
+        <v>0.4739561437192989</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4737975788391101</v>
+        <v>0.4737975788391123</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4743865301796612</v>
+        <v>0.4743865301796617</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4737975788391101</v>
+        <v>0.4737975788391123</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4737975788391101</v>
+        <v>0.4737975788391123</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4737975788391101</v>
+        <v>0.4737975788391123</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5274928277395254</v>
+        <v>0.5274928277395263</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8119421736121127</v>
+        <v>0.8119421736121111</v>
       </c>
       <c r="D6" t="n">
-        <v>0.870102567657082</v>
+        <v>0.8701025676570853</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7343175581756671</v>
+        <v>0.7343175581756655</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5370945939154749</v>
+        <v>0.5370945939154741</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8114198867109383</v>
+        <v>0.8114198867109371</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8112613218307608</v>
+        <v>0.8112613218307613</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8118502731713026</v>
+        <v>0.8118502731713029</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8113170904278445</v>
+        <v>0.8113170904278433</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5222216822793693</v>
+        <v>0.5222216822793685</v>
       </c>
       <c r="L6" t="n">
-        <v>1.107681242203034</v>
+        <v>1.107681242203032</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.50031013903832</v>
+        <v>2.500310139038321</v>
       </c>
       <c r="C7" t="n">
-        <v>3.170003206103784</v>
+        <v>3.170003206103785</v>
       </c>
       <c r="D7" t="n">
-        <v>3.169414028412247</v>
+        <v>3.169414028412251</v>
       </c>
       <c r="E7" t="n">
-        <v>3.942134139442552</v>
+        <v>3.942134139442553</v>
       </c>
       <c r="F7" t="n">
         <v>3.170002546669376</v>
       </c>
       <c r="G7" t="n">
-        <v>3.169572819643418</v>
+        <v>3.169572819643417</v>
       </c>
       <c r="H7" t="n">
-        <v>3.169414254763234</v>
+        <v>3.169414254763236</v>
       </c>
       <c r="I7" t="n">
-        <v>3.170003206103784</v>
+        <v>3.170003206103785</v>
       </c>
       <c r="J7" t="n">
-        <v>3.169414254763234</v>
+        <v>3.169414254763236</v>
       </c>
       <c r="K7" t="n">
-        <v>2.326892797068828</v>
+        <v>2.78173260713546</v>
       </c>
       <c r="L7" t="n">
-        <v>3.169414254763234</v>
+        <v>3.169414254763236</v>
       </c>
     </row>
     <row r="8">
@@ -7886,34 +7886,34 @@
         <v>0.1796247761187996</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01164206160555377</v>
+        <v>0.0116420616055535</v>
       </c>
       <c r="D8" t="n">
-        <v>0.09189956218826728</v>
+        <v>0.091899562188267</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01164206160555377</v>
+        <v>0.0116420616055535</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01164206160555377</v>
+        <v>0.0116420616055535</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.02367976757673215</v>
+        <v>-0.02367976757673312</v>
       </c>
       <c r="H8" t="n">
         <v>-0.2891133372868371</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01164206160555377</v>
+        <v>0.0116420616055535</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0337572972681456</v>
+        <v>0.03375729726814568</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1283011324233339</v>
+        <v>0.1283011324233337</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01994915364911504</v>
+        <v>0.01994915364911507</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.186707881558723</v>
+        <v>0.1867078815587226</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1423324119803571</v>
+        <v>0.1423324119803565</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1509806856470385</v>
+        <v>0.1509806856470384</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1423324119803571</v>
+        <v>0.1423324119803565</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1423324119803571</v>
+        <v>0.1423324119803565</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1040364734336208</v>
+        <v>0.1040364734336209</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.003755814764223042</v>
+        <v>-0.003755814764222987</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1423324119803571</v>
+        <v>0.1423324119803565</v>
       </c>
       <c r="J9" t="n">
-        <v>0.127358357823288</v>
+        <v>0.1273583578232879</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1658075967381862</v>
+        <v>0.165807596738186</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1218053231733345</v>
+        <v>0.1218053231733343</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen water use results.xlsx
+++ b/Results/Hydrogen/hydrogen water use results.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,321 +511,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.439624231261468</v>
+        <v>0.1991467017783181</v>
       </c>
       <c r="C2" t="n">
-        <v>11.12159826602231</v>
+        <v>0.2462457955761273</v>
       </c>
       <c r="D2" t="n">
-        <v>6.349099451425012</v>
+        <v>0.2020563218017847</v>
       </c>
       <c r="E2" t="n">
-        <v>11.12159826602231</v>
+        <v>0.2462457955761273</v>
       </c>
       <c r="F2" t="n">
-        <v>11.12159826602231</v>
+        <v>0.2462457955761273</v>
       </c>
       <c r="G2" t="n">
-        <v>11.62370516325139</v>
+        <v>0.2073168915820299</v>
       </c>
       <c r="H2" t="n">
-        <v>13.88600276223235</v>
+        <v>0.2084005240731018</v>
       </c>
       <c r="I2" t="n">
-        <v>11.12159826602231</v>
+        <v>0.2462457955761273</v>
       </c>
       <c r="J2" t="n">
-        <v>9.768892795319571</v>
+        <v>0.205106723657431</v>
       </c>
       <c r="K2" t="n">
-        <v>5.519665081932723</v>
+        <v>0.2012101897819229</v>
       </c>
       <c r="L2" t="n">
-        <v>5.166196394550684</v>
+        <v>0.2523322338047722</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1326954221235297</v>
+        <v>0.1974962216869131</v>
       </c>
       <c r="C3" t="n">
-        <v>0.134299435103481</v>
+        <v>0.2372043114611074</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1326954221235297</v>
+        <v>0.1974962216869131</v>
       </c>
       <c r="E3" t="n">
-        <v>0.135020792459265</v>
+        <v>0.2372043114611074</v>
       </c>
       <c r="F3" t="n">
-        <v>0.135020792459265</v>
+        <v>0.2372043114611074</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1328425964323179</v>
+        <v>0.1975827756847066</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1326954221235297</v>
+        <v>0.1974962216869131</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1332124444142258</v>
+        <v>0.2372043114611074</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1326954221235297</v>
+        <v>0.1974962216869131</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1326954221235297</v>
+        <v>0.1974962216869131</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1326954221235297</v>
+        <v>0.1974962216869131</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.258533098663348</v>
+        <v>3.439624231261474</v>
       </c>
       <c r="C4" t="n">
-        <v>7.350603112330774</v>
+        <v>11.12159826602233</v>
       </c>
       <c r="D4" t="n">
-        <v>7.235653301838506</v>
+        <v>6.349099451424995</v>
       </c>
       <c r="E4" t="n">
-        <v>7.326322319997771</v>
+        <v>11.12159826602233</v>
       </c>
       <c r="F4" t="n">
-        <v>7.350809588467324</v>
+        <v>11.12159826602233</v>
       </c>
       <c r="G4" t="n">
-        <v>88.0139274281717</v>
+        <v>11.62370516325138</v>
       </c>
       <c r="H4" t="n">
-        <v>88.00268980547104</v>
+        <v>13.88600276223236</v>
       </c>
       <c r="I4" t="n">
-        <v>88.01429727615353</v>
+        <v>11.12159826602233</v>
       </c>
       <c r="J4" t="n">
-        <v>88.00565904674765</v>
+        <v>9.768892795319589</v>
       </c>
       <c r="K4" t="n">
-        <v>7.14144426429487</v>
+        <v>5.519665081932724</v>
       </c>
       <c r="L4" t="n">
-        <v>7.242955024532695</v>
+        <v>5.166196394550696</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5333670001299307</v>
+        <v>0.1326954221235292</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5338840224206273</v>
+        <v>0.1342994351034822</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5333383863704655</v>
+        <v>0.1326954221235292</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5338289742157477</v>
+        <v>0.1350207924592664</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5338289742157477</v>
+        <v>0.1350207924592664</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5335141744387183</v>
+        <v>0.1328425964323178</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5333670001299307</v>
+        <v>0.1326954221235292</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5338840224206273</v>
+        <v>0.1332124444142266</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5333670001299307</v>
+        <v>0.1326954221235292</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5333670001299307</v>
+        <v>0.1326954221235292</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5333670001299307</v>
+        <v>0.1326954221235292</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5948421360649236</v>
+        <v>7.258533098663345</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9204113996044128</v>
+        <v>7.35060311233078</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9872391198765184</v>
+        <v>7.235653301838507</v>
       </c>
       <c r="E6" t="n">
-        <v>0.831512843904193</v>
+        <v>7.326322319997773</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6056455477046099</v>
+        <v>7.350809588467328</v>
       </c>
       <c r="G6" t="n">
-        <v>0.919994376513165</v>
+        <v>88.01392742817171</v>
       </c>
       <c r="H6" t="n">
-        <v>0.919847202204352</v>
+        <v>88.00268980547105</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9203642244950748</v>
+        <v>88.0142972761535</v>
       </c>
       <c r="J6" t="n">
-        <v>0.919911074974642</v>
+        <v>88.00565904674765</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5888050001077247</v>
+        <v>7.141444264294871</v>
       </c>
       <c r="L6" t="n">
-        <v>1.259342170231809</v>
+        <v>7.242955024532693</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.609862027412149</v>
+        <v>0.5333670001299305</v>
       </c>
       <c r="C7" t="n">
-        <v>4.585657795974369</v>
+        <v>0.5338840224206269</v>
       </c>
       <c r="D7" t="n">
-        <v>4.585140695944693</v>
+        <v>0.5333383863704647</v>
       </c>
       <c r="E7" t="n">
-        <v>5.711107969243984</v>
+        <v>0.5338289742157474</v>
       </c>
       <c r="F7" t="n">
-        <v>4.585657195650964</v>
+        <v>0.5338289742157474</v>
       </c>
       <c r="G7" t="n">
-        <v>4.585287947992464</v>
+        <v>0.5335141744387183</v>
       </c>
       <c r="H7" t="n">
-        <v>4.585140773683677</v>
+        <v>0.5333670001299305</v>
       </c>
       <c r="I7" t="n">
-        <v>4.585657795974369</v>
+        <v>0.5338840224206269</v>
       </c>
       <c r="J7" t="n">
-        <v>4.585140773683677</v>
+        <v>0.5333670001299305</v>
       </c>
       <c r="K7" t="n">
-        <v>3.357090765635855</v>
+        <v>0.5333670001299305</v>
       </c>
       <c r="L7" t="n">
-        <v>4.585140773683677</v>
+        <v>0.5333670001299305</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1263338467248802</v>
+        <v>0.5948421360649235</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.001383743702259518</v>
+        <v>0.9204113996044142</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06542128041424546</v>
+        <v>0.9872391198765192</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.001383743702259518</v>
+        <v>0.8315128439041946</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.001383743702259518</v>
+        <v>0.6056455477046104</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.04182941074571948</v>
+        <v>0.9199943765131656</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.06255020930605792</v>
+        <v>0.9198472022043527</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.001383743702259518</v>
+        <v>0.9203642244950766</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00296767047662938</v>
+        <v>0.919911074974643</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08320971260854661</v>
+        <v>0.5888050001077237</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.9701730720139556</v>
+        <v>1.25934217023181</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.609862027412149</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.585657795974369</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.585140695944693</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5.71110796924398</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.585657195650966</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.585287947992463</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.585140773683678</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.585657795974369</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.585140773683678</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.357090765635855</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.585140773683678</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.1263338467248802</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.00138374370225938</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.06542128041424625</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.00138374370225938</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.00138374370225938</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.04182941074572008</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.06255020930605806</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.00138374370225938</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.002967670476629084</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.08320971260854665</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.970173072013954</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.1667675943895594</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.1667675943895592</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.1376874701417768</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D11" t="n">
         <v>0.1419618026248569</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E11" t="n">
         <v>0.1376874701417768</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.1376874701417768</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.09838358379481724</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.09007856925249601</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>0.09838358379481787</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.09007856925249598</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.1376874701417768</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.1165956129310424</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.1492094639417718</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.1586872849558668</v>
+      <c r="J11" t="n">
+        <v>0.1165956129310421</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.1492094639417717</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.1586872849558667</v>
       </c>
     </row>
   </sheetData>
@@ -839,7 +919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,321 +987,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7118535288306262</v>
+        <v>0.1844364915092051</v>
       </c>
       <c r="C2" t="n">
-        <v>6.655692650504924</v>
+        <v>0.2300847082822353</v>
       </c>
       <c r="D2" t="n">
-        <v>2.820634643327075</v>
+        <v>0.1870893836770767</v>
       </c>
       <c r="E2" t="n">
-        <v>6.655692650504924</v>
+        <v>0.2300847082822353</v>
       </c>
       <c r="F2" t="n">
-        <v>6.655692650504924</v>
+        <v>0.2300847082822353</v>
       </c>
       <c r="G2" t="n">
-        <v>7.288786600455294</v>
+        <v>0.1924859989483621</v>
       </c>
       <c r="H2" t="n">
-        <v>12.91212733602359</v>
+        <v>0.1981481169561062</v>
       </c>
       <c r="I2" t="n">
-        <v>6.655692650504924</v>
+        <v>0.2300847082822353</v>
       </c>
       <c r="J2" t="n">
-        <v>5.065990580515675</v>
+        <v>0.1893336564424918</v>
       </c>
       <c r="K2" t="n">
-        <v>1.799225528864002</v>
+        <v>0.1858505796367238</v>
       </c>
       <c r="L2" t="n">
-        <v>5.164481121185355</v>
+        <v>0.1940467821629163</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1145712481990981</v>
+        <v>0.185424589932364</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1157740130120042</v>
+        <v>0.2241951416942319</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1145712481990981</v>
+        <v>0.185424589932364</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1163419360755726</v>
+        <v>0.2241951416942319</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1163419360755725</v>
+        <v>0.2241951416942319</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1147075538157959</v>
+        <v>0.1854379467409901</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1145712481990981</v>
+        <v>0.185424589932364</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1150171810686167</v>
+        <v>0.2241951416942319</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1145712481990981</v>
+        <v>0.185424589932364</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1145712481990981</v>
+        <v>0.185424589932364</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1145712481990981</v>
+        <v>0.185424589932364</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.309526125393175</v>
+        <v>0.7118535288306231</v>
       </c>
       <c r="C4" t="n">
-        <v>6.39363181461692</v>
+        <v>6.655692650504925</v>
       </c>
       <c r="D4" t="n">
-        <v>76.70396440073247</v>
+        <v>2.820634643327075</v>
       </c>
       <c r="E4" t="n">
-        <v>6.373020638388395</v>
+        <v>6.655692650504925</v>
       </c>
       <c r="F4" t="n">
-        <v>6.394357202734736</v>
+        <v>6.655692650504925</v>
       </c>
       <c r="G4" t="n">
-        <v>76.71280510656125</v>
+        <v>7.288786600455309</v>
       </c>
       <c r="H4" t="n">
-        <v>76.70350266186425</v>
+        <v>12.91212733602357</v>
       </c>
       <c r="I4" t="n">
-        <v>6.309972058262712</v>
+        <v>6.655692650504925</v>
       </c>
       <c r="J4" t="n">
-        <v>6.315093604000207</v>
+        <v>5.065990580515658</v>
       </c>
       <c r="K4" t="n">
-        <v>6.210976313201614</v>
+        <v>1.799225528864002</v>
       </c>
       <c r="L4" t="n">
-        <v>6.301523920819235</v>
+        <v>5.164481121185359</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4564729133722897</v>
+        <v>0.1145712481990978</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4569188462418085</v>
+        <v>0.1157740130120037</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4564479264436366</v>
+        <v>0.1145712481990978</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4569069855778615</v>
+        <v>0.116341936075572</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4569069855778615</v>
+        <v>0.1163419360755721</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4566092189889872</v>
+        <v>0.1147075538157958</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4564729133722897</v>
+        <v>0.1145712481990978</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4569188462418085</v>
+        <v>0.1150171810686163</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4564729133722897</v>
+        <v>0.1145712481990978</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4564729133722897</v>
+        <v>0.1145712481990978</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4564729133722897</v>
+        <v>0.1145712481990978</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.504958024666092</v>
+        <v>6.309526125393169</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7807390583243143</v>
+        <v>6.393631814616909</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8372960394462839</v>
+        <v>76.70396440073249</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7054431074730166</v>
+        <v>6.373020638388406</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5141371328314451</v>
+        <v>6.394357202734732</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7803552087567679</v>
+        <v>76.71280510656123</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7802189031400875</v>
+        <v>76.70350266186425</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7806648360095887</v>
+        <v>6.309972058262714</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7802729997487816</v>
+        <v>6.315093604000195</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4998449125336695</v>
+        <v>6.210976313201611</v>
       </c>
       <c r="L6" t="n">
-        <v>1.067751907606605</v>
+        <v>6.301523920819231</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.232140214137559</v>
+        <v>0.456472913372289</v>
       </c>
       <c r="C7" t="n">
-        <v>2.830055567786526</v>
+        <v>0.4569188462418089</v>
       </c>
       <c r="D7" t="n">
-        <v>2.82960949358798</v>
+        <v>0.4564479264436362</v>
       </c>
       <c r="E7" t="n">
-        <v>3.519521793887518</v>
+        <v>0.4569069855778613</v>
       </c>
       <c r="F7" t="n">
-        <v>2.830055016328391</v>
+        <v>0.4569069855778613</v>
       </c>
       <c r="G7" t="n">
-        <v>2.829745940533702</v>
+        <v>0.4566092189889876</v>
       </c>
       <c r="H7" t="n">
-        <v>2.829609634917014</v>
+        <v>0.456472913372289</v>
       </c>
       <c r="I7" t="n">
-        <v>2.830055567786526</v>
+        <v>0.4569188462418089</v>
       </c>
       <c r="J7" t="n">
-        <v>2.829609634917014</v>
+        <v>0.456472913372289</v>
       </c>
       <c r="K7" t="n">
-        <v>2.483433446631701</v>
+        <v>0.456472913372289</v>
       </c>
       <c r="L7" t="n">
-        <v>2.829609634917014</v>
+        <v>0.456472913372289</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1721194478490135</v>
+        <v>0.5049580246660925</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05434705816927196</v>
+        <v>0.7807390583243151</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1165527825626753</v>
+        <v>0.8372960394462835</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05434705816927196</v>
+        <v>0.7054431074730169</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05434705816927196</v>
+        <v>0.5141371328314449</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00458883898110295</v>
+        <v>0.7803552087567667</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1095200301691682</v>
+        <v>0.7802189031400879</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05434705816927196</v>
+        <v>0.780664836009589</v>
       </c>
       <c r="J8" t="n">
-        <v>0.07039512462822833</v>
+        <v>0.7802729997487817</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1425276679479086</v>
+        <v>0.4998449125336686</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07765472176835879</v>
+        <v>1.067751907606604</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.232140214137557</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.830055567786526</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.82960949358798</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.519521793887516</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.830055016328395</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.829745940533701</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.829609634917015</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.830055567786526</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.829609634917014</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.483433446631699</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.829609634917014</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.172119447849014</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.05434705816927195</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1165527825626759</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.05434705816927195</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.05434705816927195</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.004588838981103726</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.1095200301691672</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.05434705816927195</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.07039512462822838</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.1425276679479093</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.07765472176836009</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.1783826094603082</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.1783826094603088</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.1528032890046521</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.1557524918424414</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>0.1557524918424421</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.1528032890046521</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.1528032890046521</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.1101990785857037</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.06394737487717436</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>0.110199078585704</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0639473748771754</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.1528032890046521</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.1369948831519547</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.1663323434294177</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.1399894717486868</v>
+      <c r="J11" t="n">
+        <v>0.136994883151955</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.1663323434294178</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.1399894717486874</v>
       </c>
     </row>
   </sheetData>
@@ -1235,7 +1395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,321 +1463,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.51258613069282</v>
+        <v>0.2181151831434799</v>
       </c>
       <c r="C2" t="n">
-        <v>31.14700304910593</v>
+        <v>0.2534813682098506</v>
       </c>
       <c r="D2" t="n">
-        <v>4.161346424092906</v>
+        <v>0.2199797566524291</v>
       </c>
       <c r="E2" t="n">
-        <v>5.385823060346454</v>
+        <v>0.2260072779719856</v>
       </c>
       <c r="F2" t="n">
-        <v>5.385823060346454</v>
+        <v>0.2260072779719856</v>
       </c>
       <c r="G2" t="n">
-        <v>9.528743579374673</v>
+        <v>0.1983558001130535</v>
       </c>
       <c r="H2" t="n">
-        <v>11.78613593958423</v>
+        <v>0.2270870475163043</v>
       </c>
       <c r="I2" t="n">
-        <v>5.385823060346454</v>
+        <v>0.2260072779719856</v>
       </c>
       <c r="J2" t="n">
-        <v>7.272197841527303</v>
+        <v>0.2463085604178268</v>
       </c>
       <c r="K2" t="n">
-        <v>3.576855571447756</v>
+        <v>0.2234747568929548</v>
       </c>
       <c r="L2" t="n">
-        <v>22.88219238623095</v>
+        <v>0.2128213457691205</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.138478427067102</v>
+        <v>0.1860628948839604</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1543650625339988</v>
+        <v>0.2222832422259781</v>
       </c>
       <c r="D3" t="n">
-        <v>0.138478427067102</v>
+        <v>0.2176834076122205</v>
       </c>
       <c r="E3" t="n">
-        <v>0.139952164965647</v>
+        <v>0.2225093064286331</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1399521649656469</v>
+        <v>0.2225093064286331</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1384845533981125</v>
+        <v>0.1899727950217633</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1384784270671022</v>
+        <v>0.2176834076122205</v>
       </c>
       <c r="I3" t="n">
-        <v>0.138087751851694</v>
+        <v>0.2225093064286331</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1384784270671022</v>
+        <v>0.2412905511181147</v>
       </c>
       <c r="K3" t="n">
-        <v>0.138478427067102</v>
+        <v>0.2219029348406969</v>
       </c>
       <c r="L3" t="n">
-        <v>0.138478427067102</v>
+        <v>0.1925318082920539</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>81.06373347234387</v>
+        <v>31.51258613069287</v>
       </c>
       <c r="C4" t="n">
-        <v>6.846811482937483</v>
+        <v>31.14700304910603</v>
       </c>
       <c r="D4" t="n">
-        <v>6.697795672400777</v>
+        <v>4.161346424092906</v>
       </c>
       <c r="E4" t="n">
-        <v>6.771269933863173</v>
+        <v>5.385823060346439</v>
       </c>
       <c r="F4" t="n">
-        <v>6.801045541566104</v>
+        <v>5.385823060346439</v>
       </c>
       <c r="G4" t="n">
-        <v>6.713779929252857</v>
+        <v>9.528743579374712</v>
       </c>
       <c r="H4" t="n">
-        <v>81.06014079130672</v>
+        <v>11.78613593958425</v>
       </c>
       <c r="I4" t="n">
-        <v>6.713383127706468</v>
+        <v>5.385823060346439</v>
       </c>
       <c r="J4" t="n">
-        <v>81.0592261482302</v>
+        <v>7.272197841527304</v>
       </c>
       <c r="K4" t="n">
-        <v>6.611812573007168</v>
+        <v>3.576855571447756</v>
       </c>
       <c r="L4" t="n">
-        <v>6.710161362210495</v>
+        <v>22.88219238623095</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.501037616616849</v>
+        <v>0.138478427067102</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5023204149031735</v>
+        <v>0.154365062533999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5010113859166004</v>
+        <v>0.138478427067102</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5014795932909454</v>
+        <v>0.1399521649656465</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5014795932909454</v>
+        <v>0.1399521649656466</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5010437429478584</v>
+        <v>0.1384845533981116</v>
       </c>
       <c r="H5" t="n">
-        <v>0.501037616616849</v>
+        <v>0.138478427067102</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5006469414014421</v>
+        <v>0.1380877518516938</v>
       </c>
       <c r="J5" t="n">
-        <v>0.501037616616849</v>
+        <v>0.138478427067102</v>
       </c>
       <c r="K5" t="n">
-        <v>0.501037616616849</v>
+        <v>0.138478427067102</v>
       </c>
       <c r="L5" t="n">
-        <v>0.501037616616849</v>
+        <v>0.138478427067102</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5582012827884367</v>
+        <v>81.06373347234386</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8566984653851716</v>
+        <v>6.846811482937478</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9159734420130131</v>
+        <v>6.69779567240078</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7738810168502043</v>
+        <v>6.771269933863173</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5677160765136824</v>
+        <v>6.801045541566104</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8545342644950051</v>
+        <v>6.713779929252861</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8545281381641464</v>
+        <v>81.06014079130674</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8541374629485875</v>
+        <v>6.713383127706473</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8545863748298258</v>
+        <v>81.05922614823017</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5526968593199448</v>
+        <v>6.611812573007168</v>
       </c>
       <c r="L6" t="n">
-        <v>1.164066317004995</v>
+        <v>6.710161362210486</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.912316434754235</v>
+        <v>0.5010376166168481</v>
       </c>
       <c r="C7" t="n">
-        <v>3.693619253980628</v>
+        <v>0.5023204149031731</v>
       </c>
       <c r="D7" t="n">
-        <v>3.692336249129771</v>
+        <v>0.5010113859166008</v>
       </c>
       <c r="E7" t="n">
-        <v>4.592071269113797</v>
+        <v>0.5014795932909457</v>
       </c>
       <c r="F7" t="n">
-        <v>3.691945068715192</v>
+        <v>0.5014795932909457</v>
       </c>
       <c r="G7" t="n">
-        <v>3.692342582025329</v>
+        <v>0.5010437429478588</v>
       </c>
       <c r="H7" t="n">
-        <v>3.692336455694309</v>
+        <v>0.5010376166168481</v>
       </c>
       <c r="I7" t="n">
-        <v>3.691945780478897</v>
+        <v>0.5006469414014416</v>
       </c>
       <c r="J7" t="n">
-        <v>3.692336455694309</v>
+        <v>0.5010376166168481</v>
       </c>
       <c r="K7" t="n">
-        <v>3.24038970530661</v>
+        <v>0.5010376166168481</v>
       </c>
       <c r="L7" t="n">
-        <v>3.692336455694309</v>
+        <v>0.5010376166168481</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.5159576527335714</v>
+        <v>0.5582012827884352</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.4736856320672787</v>
+        <v>0.8566984653851715</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1255482921546074</v>
+        <v>0.9159734420130126</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1033043769630915</v>
+        <v>0.7738810168502039</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1033043769630915</v>
+        <v>0.5677160765136807</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.01982907376809934</v>
+        <v>0.8545342644950047</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.01884904215593358</v>
+        <v>0.8545281381641447</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1033043769630915</v>
+        <v>0.8541374629485873</v>
       </c>
       <c r="J8" t="n">
-        <v>0.08562074474926547</v>
+        <v>0.8545863748298257</v>
       </c>
       <c r="K8" t="n">
-        <v>0.143610572587019</v>
+        <v>0.5526968593199455</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2609662896058101</v>
+        <v>1.164066317004992</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.912316434754238</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.693619253980622</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.692336249129771</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.592071269113799</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.691945068715193</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.692342582025327</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.692336455694305</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.691945780478898</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.692336455694305</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.240389705306609</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.692336455694305</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.5159576527335722</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.4736856320672791</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1255482921546072</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.1033043769630914</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1033043769630913</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.01982907376810076</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.01884904215593405</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1033043769630914</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.08562074474926595</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.1436105725870176</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.2609662896058103</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>-0.1013064032292402</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.06318668751478593</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1780579855020244</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.1717686551815935</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.1717686551815935</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.1028952812147804</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.1194640290876018</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.1717686551815935</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.1754783024297619</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.1878514825645785</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.006478266012905306</v>
+      <c r="B11" t="n">
+        <v>-0.1013064032292406</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.06318668751478611</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1780579855020245</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1717686551815938</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1717686551815938</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1028952812147802</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.1194640290876016</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1717686551815938</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.1754783024297614</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.1878514825645776</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.006478266012904676</v>
       </c>
     </row>
   </sheetData>
@@ -1631,7 +1871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1699,321 +1939,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26.87624837199769</v>
+        <v>0.2065526538374483</v>
       </c>
       <c r="C2" t="n">
-        <v>25.76209792933401</v>
+        <v>0.2397753769622512</v>
       </c>
       <c r="D2" t="n">
-        <v>3.433094723222044</v>
+        <v>0.2158006092269459</v>
       </c>
       <c r="E2" t="n">
-        <v>3.859926473209593</v>
+        <v>0.2269622196183287</v>
       </c>
       <c r="F2" t="n">
-        <v>3.859926473209593</v>
+        <v>0.2269622196183287</v>
       </c>
       <c r="G2" t="n">
-        <v>7.294177192859902</v>
+        <v>0.1932819700242367</v>
       </c>
       <c r="H2" t="n">
-        <v>8.759883420382838</v>
+        <v>0.220984019613089</v>
       </c>
       <c r="I2" t="n">
-        <v>3.859926473209593</v>
+        <v>0.2269622196183287</v>
       </c>
       <c r="J2" t="n">
-        <v>5.035907294438378</v>
+        <v>0.2513142517917323</v>
       </c>
       <c r="K2" t="n">
-        <v>2.459873347612429</v>
+        <v>0.230048187266319</v>
       </c>
       <c r="L2" t="n">
-        <v>15.47557977994028</v>
+        <v>0.2082901211112396</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1327651491708655</v>
+        <v>0.1777148318068632</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1446769134324144</v>
+        <v>0.212656686632476</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1327651491708654</v>
+        <v>0.2140151217943824</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1492253812475904</v>
+        <v>0.2249046903371566</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1492253812475901</v>
+        <v>0.2249046903371566</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1328077448277207</v>
+        <v>0.1867889122264373</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1327651491708654</v>
+        <v>0.2140151217943824</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1325999138544263</v>
+        <v>0.2249046903371566</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1327651491708655</v>
+        <v>0.2484485322377087</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1327651491708654</v>
+        <v>0.2296507540455899</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1327651491708654</v>
+        <v>0.19434636894609</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.76578189773774</v>
+        <v>26.87624837199768</v>
       </c>
       <c r="C4" t="n">
-        <v>6.473198922361651</v>
+        <v>25.76209792933404</v>
       </c>
       <c r="D4" t="n">
-        <v>76.76347942331797</v>
+        <v>3.433094723222058</v>
       </c>
       <c r="E4" t="n">
-        <v>6.409329729042335</v>
+        <v>3.859926473209587</v>
       </c>
       <c r="F4" t="n">
-        <v>6.435575107539364</v>
+        <v>3.859926473209587</v>
       </c>
       <c r="G4" t="n">
-        <v>76.76582449339472</v>
+        <v>7.294177192859886</v>
       </c>
       <c r="H4" t="n">
-        <v>76.76718094209851</v>
+        <v>8.759883420382829</v>
       </c>
       <c r="I4" t="n">
-        <v>6.351001261388147</v>
+        <v>3.859926473209587</v>
       </c>
       <c r="J4" t="n">
-        <v>6.358736332975104</v>
+        <v>5.035907294438369</v>
       </c>
       <c r="K4" t="n">
-        <v>6.255937354030812</v>
+        <v>2.45987334761243</v>
       </c>
       <c r="L4" t="n">
-        <v>6.346755004634739</v>
+        <v>15.47557977994031</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4782484487262429</v>
+        <v>0.1327651491708622</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4795085285769676</v>
+        <v>0.1446769134324144</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4782237286953442</v>
+        <v>0.1327651491708622</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4830857920777325</v>
+        <v>0.1492253812475902</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4830857920777325</v>
+        <v>0.14922538124759</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4782910443830968</v>
+        <v>0.1328077448277214</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4782484487262429</v>
+        <v>0.1327651491708622</v>
       </c>
       <c r="I5" t="n">
-        <v>0.478083213409803</v>
+        <v>0.1325999138544268</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4782484487262429</v>
+        <v>0.1327651491708622</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4782484487262429</v>
+        <v>0.1327651491708622</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4782484487262429</v>
+        <v>0.1327651491708622</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5302104860085226</v>
+        <v>76.76578189773778</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8189715355371507</v>
+        <v>6.473198922361664</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8714485973337975</v>
+        <v>76.76347942331799</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7397271898901386</v>
+        <v>6.409329729042336</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5420032902093841</v>
+        <v>6.435575107539361</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8128855164629424</v>
+        <v>76.76582449339475</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8128429208068028</v>
+        <v>76.76718094209849</v>
       </c>
       <c r="I6" t="n">
-        <v>0.812677685489647</v>
+        <v>6.351001261388149</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8128984660846411</v>
+        <v>6.358736332975101</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5249604434354859</v>
+        <v>6.255937354030813</v>
       </c>
       <c r="L6" t="n">
-        <v>1.108076132208395</v>
+        <v>6.346755004634741</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.453714945889836</v>
+        <v>0.4782484487262408</v>
       </c>
       <c r="C7" t="n">
-        <v>3.109946878782845</v>
+        <v>0.4795085285769677</v>
       </c>
       <c r="D7" t="n">
-        <v>3.108686642004116</v>
+        <v>0.4782237286953429</v>
       </c>
       <c r="E7" t="n">
-        <v>3.864344306151412</v>
+        <v>0.4830857920777321</v>
       </c>
       <c r="F7" t="n">
-        <v>3.108520966520036</v>
+        <v>0.4830857920777321</v>
       </c>
       <c r="G7" t="n">
-        <v>3.108729394588965</v>
+        <v>0.4782910443830966</v>
       </c>
       <c r="H7" t="n">
-        <v>3.108686798932111</v>
+        <v>0.4782484487262408</v>
       </c>
       <c r="I7" t="n">
-        <v>3.108521563615677</v>
+        <v>0.4780832134098026</v>
       </c>
       <c r="J7" t="n">
-        <v>3.108686798932111</v>
+        <v>0.4782484487262408</v>
       </c>
       <c r="K7" t="n">
-        <v>2.729193469003374</v>
+        <v>0.4782484487262408</v>
       </c>
       <c r="L7" t="n">
-        <v>3.108686798932111</v>
+        <v>0.4782484487262408</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.4541500058592491</v>
+        <v>0.5302104860085187</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.3946561694398136</v>
+        <v>0.8189715355371484</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1341980926772343</v>
+        <v>0.8714485973337974</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1355986892530431</v>
+        <v>0.7397271898901382</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1355986892530431</v>
+        <v>0.5420032902093841</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01790183161302242</v>
+        <v>0.8128855164629407</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02912395165459515</v>
+        <v>0.8128429208067983</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1355986892530431</v>
+        <v>0.8126776854896471</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1355971541960868</v>
+        <v>0.8128984660846408</v>
       </c>
       <c r="K8" t="n">
-        <v>0.173819623221495</v>
+        <v>0.5249604434354855</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1285058707677876</v>
+        <v>1.108076132208391</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.453714945889832</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.109946878782844</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.108686642004115</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.864344306151411</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.108520966520035</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.108729394588965</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.108686798932111</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.108521563615676</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.108686798932111</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.72919346900337</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.108686798932111</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.454150005859249</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.394656169439814</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1341980926772305</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.1355986892530428</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1355986892530428</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01790183161302186</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.02912395165459454</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1355986892530428</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.1355971541960854</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.1738196232214915</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.1285058707677887</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>-0.08094786093439318</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.03655390794187817</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1794836066168638</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.186327704523719</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.186327704523719</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.1164378101339429</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.1368579479862873</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.186327704523719</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.199966515146793</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.2046448448181022</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.06139132317238483</v>
+      <c r="B11" t="n">
+        <v>-0.08094786093439441</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.03655390794187826</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1794836066168626</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1863277045237185</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1863277045237185</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1164378101339421</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.1368579479862862</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1863277045237185</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.199966515146789</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2046448448180972</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.06139132317238465</v>
       </c>
     </row>
   </sheetData>
@@ -2027,7 +2347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2095,321 +2415,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24.73508748989613</v>
+        <v>0.1967402042019022</v>
       </c>
       <c r="C2" t="n">
-        <v>23.06506662457045</v>
+        <v>0.2271728824073691</v>
       </c>
       <c r="D2" t="n">
-        <v>2.994876042036948</v>
+        <v>0.2089868908771622</v>
       </c>
       <c r="E2" t="n">
-        <v>2.860892284464396</v>
+        <v>0.2217276208844776</v>
       </c>
       <c r="F2" t="n">
-        <v>2.860892284464396</v>
+        <v>0.2217276208844776</v>
       </c>
       <c r="G2" t="n">
-        <v>6.178776269820399</v>
+        <v>0.1865493045844679</v>
       </c>
       <c r="H2" t="n">
-        <v>6.953570353833179</v>
+        <v>0.2127896151762091</v>
       </c>
       <c r="I2" t="n">
-        <v>2.860892284464396</v>
+        <v>0.2217276208844776</v>
       </c>
       <c r="J2" t="n">
-        <v>3.73869676958522</v>
+        <v>0.248691964177119</v>
       </c>
       <c r="K2" t="n">
-        <v>1.904947391413651</v>
+        <v>0.2270260479944445</v>
       </c>
       <c r="L2" t="n">
-        <v>11.37688235967189</v>
+        <v>0.2008489977809318</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1297091303454118</v>
+        <v>0.1702223293294097</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1399544474196147</v>
+        <v>0.2029808752876168</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1297091303454118</v>
+        <v>0.2076214884632592</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1485641955031667</v>
+        <v>0.2207679915103773</v>
       </c>
       <c r="F3" t="n">
-        <v>0.148564195503167</v>
+        <v>0.2207679915103773</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1297552238740875</v>
+        <v>0.1812456704053208</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1297091303454118</v>
+        <v>0.2076214884632592</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1295701762468545</v>
+        <v>0.2207679915103773</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1297091303454118</v>
+        <v>0.2472632865461106</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1297091303454118</v>
+        <v>0.2272447402146686</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1297091303454118</v>
+        <v>0.1910574513720451</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.340918053472508</v>
+        <v>24.73508748989615</v>
       </c>
       <c r="C4" t="n">
-        <v>6.459958837214288</v>
+        <v>23.06506662457049</v>
       </c>
       <c r="D4" t="n">
-        <v>6.329308444727283</v>
+        <v>2.994876042036962</v>
       </c>
       <c r="E4" t="n">
-        <v>6.400273928905199</v>
+        <v>2.860892284464397</v>
       </c>
       <c r="F4" t="n">
-        <v>6.425929326720244</v>
+        <v>2.860892284464397</v>
       </c>
       <c r="G4" t="n">
-        <v>76.75007734322222</v>
+        <v>6.17877626982038</v>
       </c>
       <c r="H4" t="n">
-        <v>76.75392831738584</v>
+        <v>6.953570353833202</v>
       </c>
       <c r="I4" t="n">
-        <v>76.74989229559507</v>
+        <v>2.860892284464397</v>
       </c>
       <c r="J4" t="n">
-        <v>76.74924894087522</v>
+        <v>3.738696769585227</v>
       </c>
       <c r="K4" t="n">
-        <v>6.246738888559136</v>
+        <v>1.90494739141366</v>
       </c>
       <c r="L4" t="n">
-        <v>6.335940129756302</v>
+        <v>11.37688235967189</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4732848649879634</v>
+        <v>0.1297091303454122</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4744993475914952</v>
+        <v>0.1399544474196141</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4732595213872446</v>
+        <v>0.1297091303454122</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4790502297284866</v>
+        <v>0.1485641955031676</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4790502297284866</v>
+        <v>0.1485641955031677</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4733309585166383</v>
+        <v>0.1297552238740877</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4732848649879634</v>
+        <v>0.1297091303454122</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4731459108894047</v>
+        <v>0.1295701762468547</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4732848649879634</v>
+        <v>0.1297091303454122</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4732848649879634</v>
+        <v>0.1297091303454122</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4732848649879634</v>
+        <v>0.1297091303454122</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5232147970132044</v>
+        <v>6.340918053472508</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8107589173253034</v>
+        <v>6.459958837214289</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8619954248724209</v>
+        <v>6.329308444727275</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7320499877301103</v>
+        <v>6.400273928905202</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5355076663877267</v>
+        <v>6.425929326720246</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8038579004793605</v>
+        <v>76.75007734322222</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8038118069520317</v>
+        <v>76.75392831738584</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8036728528521275</v>
+        <v>76.749892295595</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8038669521899846</v>
+        <v>76.74924894087522</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5180025635020493</v>
+        <v>6.246738888559134</v>
       </c>
       <c r="L6" t="n">
-        <v>1.096918846871883</v>
+        <v>6.335940129756302</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.214015271017558</v>
+        <v>0.4732848649879642</v>
       </c>
       <c r="C7" t="n">
-        <v>2.804960187616981</v>
+        <v>0.4744993475914962</v>
       </c>
       <c r="D7" t="n">
-        <v>2.803745572552442</v>
+        <v>0.4732595213872456</v>
       </c>
       <c r="E7" t="n">
-        <v>3.484142359889744</v>
+        <v>0.4790502297284889</v>
       </c>
       <c r="F7" t="n">
-        <v>2.803606200666801</v>
+        <v>0.4790502297284889</v>
       </c>
       <c r="G7" t="n">
-        <v>2.803791798542136</v>
+        <v>0.4733309585166397</v>
       </c>
       <c r="H7" t="n">
-        <v>2.80374570501346</v>
+        <v>0.4732848649879642</v>
       </c>
       <c r="I7" t="n">
-        <v>2.803606750914896</v>
+        <v>0.4731459108894062</v>
       </c>
       <c r="J7" t="n">
-        <v>2.80374570501346</v>
+        <v>0.4732848649879642</v>
       </c>
       <c r="K7" t="n">
-        <v>2.44819064159165</v>
+        <v>0.4732848649879642</v>
       </c>
       <c r="L7" t="n">
-        <v>2.80374570501346</v>
+        <v>0.4732848649879642</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.4111604507785595</v>
+        <v>0.5232147970132066</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.3404578193460734</v>
+        <v>0.8107589173253048</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1383664852721201</v>
+        <v>0.8619954248724248</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1554609700163891</v>
+        <v>0.7320499877301118</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1554609700163891</v>
+        <v>0.5355076663877274</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03864698058137439</v>
+        <v>0.8038579004793617</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06148078385761918</v>
+        <v>0.8038118069520306</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1554609700163891</v>
+        <v>0.8036728528521287</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1643355279341254</v>
+        <v>0.8038669521899868</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1847667552433425</v>
+        <v>0.5180025635020512</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.04546115484777317</v>
+        <v>1.096918846871884</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.214015271017563</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.804960187616991</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.803745572552452</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.484142359889753</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.803606200666809</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.803791798542144</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.803745705013463</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.803606750914903</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.803745705013463</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.448190641591656</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.803745705013463</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.4111604507785593</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.3404578193460728</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1383664852721208</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.1554609700163897</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1554609700163897</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.03864698058137533</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.06148078385761958</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1554609700163897</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.1643355279341272</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.1847667552433478</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.04546115484777266</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>-0.0677908135042132</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.02009345548732284</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1774756437225924</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.1920127179835838</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.1920127179835838</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.1216664462795107</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.1462951288578508</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.1920127179835838</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.2109595697335783</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.2076984294631838</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.09323227821083832</v>
+      <c r="B11" t="n">
+        <v>-0.06779081350421275</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.02009345548732239</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1774756437225932</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1920127179835845</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1920127179835845</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1216664462795112</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.1462951288578513</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1920127179835845</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.2109595697335797</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2076984294631884</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.09323227821083899</v>
       </c>
     </row>
   </sheetData>
@@ -2423,7 +2823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2491,321 +2891,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.81470464908815</v>
+        <v>0.248359545292089</v>
       </c>
       <c r="C2" t="n">
-        <v>35.08388161014173</v>
+        <v>0.2756312165429312</v>
       </c>
       <c r="D2" t="n">
-        <v>3.295046119469534</v>
+        <v>0.2264551047235404</v>
       </c>
       <c r="E2" t="n">
-        <v>4.805547517367089</v>
+        <v>0.2416985971343221</v>
       </c>
       <c r="F2" t="n">
-        <v>4.805547517367089</v>
+        <v>0.2416985971343221</v>
       </c>
       <c r="G2" t="n">
-        <v>8.732529400572705</v>
+        <v>0.2088817706616802</v>
       </c>
       <c r="H2" t="n">
-        <v>15.17799135064065</v>
+        <v>0.2378809851096249</v>
       </c>
       <c r="I2" t="n">
-        <v>4.805547517367089</v>
+        <v>0.2416985971343221</v>
       </c>
       <c r="J2" t="n">
-        <v>7.55527422726776</v>
+        <v>0.2639267087721547</v>
       </c>
       <c r="K2" t="n">
-        <v>3.134076738781791</v>
+        <v>0.2443882673012558</v>
       </c>
       <c r="L2" t="n">
-        <v>23.49723536925033</v>
+        <v>0.2276986228734637</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1462122988859561</v>
+        <v>0.2174822683280309</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1638606180693062</v>
+        <v>0.2404073434060298</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1462122988859561</v>
+        <v>0.2251651928992403</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1719007804427286</v>
+        <v>0.2390203710254072</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1719007804427286</v>
+        <v>0.2390203710254072</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1462581816832842</v>
+        <v>0.2014662841130876</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1462122988859561</v>
+        <v>0.2251651928992403</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1460594071208085</v>
+        <v>0.2390203710254072</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1462122988859561</v>
+        <v>0.2588177608224782</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1462122988859561</v>
+        <v>0.2435760577331905</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1462122988859561</v>
+        <v>0.2069722808603912</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.726915301106692</v>
+        <v>30.81470464908817</v>
       </c>
       <c r="C4" t="n">
-        <v>6.868763560247974</v>
+        <v>35.0838816101417</v>
       </c>
       <c r="D4" t="n">
-        <v>6.710027236842297</v>
+        <v>3.295046119469533</v>
       </c>
       <c r="E4" t="n">
-        <v>6.787498685857435</v>
+        <v>4.805547517367171</v>
       </c>
       <c r="F4" t="n">
-        <v>6.815932200112885</v>
+        <v>4.805547517367171</v>
       </c>
       <c r="G4" t="n">
-        <v>6.726961183904015</v>
+        <v>8.732529400572696</v>
       </c>
       <c r="H4" t="n">
-        <v>81.07697134665212</v>
+        <v>15.17799135064065</v>
       </c>
       <c r="I4" t="n">
-        <v>81.07808236244108</v>
+        <v>4.805547517367171</v>
       </c>
       <c r="J4" t="n">
-        <v>6.735527261833595</v>
+        <v>7.55527422726777</v>
       </c>
       <c r="K4" t="n">
-        <v>6.625292793614184</v>
+        <v>3.134076738781786</v>
       </c>
       <c r="L4" t="n">
-        <v>6.723586492141636</v>
+        <v>23.49723536925033</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5146954679153961</v>
+        <v>0.1462122988859551</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5161574967846561</v>
+        <v>0.1638606180693022</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5146695440811668</v>
+        <v>0.1462122988859551</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5220454404022935</v>
+        <v>0.1719007804427287</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5220454404022935</v>
+        <v>0.1719007804427287</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5147413507127253</v>
+        <v>0.1462581816832844</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5146954679153961</v>
+        <v>0.1462122988859551</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5145425761502468</v>
+        <v>0.1460594071208088</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5146954679153961</v>
+        <v>0.1462122988859551</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5146954679153961</v>
+        <v>0.1462122988859551</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5146954679153961</v>
+        <v>0.1462122988859551</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5718758024452734</v>
+        <v>6.726915301106691</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8830143287816513</v>
+        <v>6.868763560248013</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9369974908436568</v>
+        <v>6.710027236842286</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7979181318466303</v>
+        <v>6.787498685857439</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5858002597201954</v>
+        <v>6.815932200112888</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8743358305695093</v>
+        <v>6.726961183904012</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8742899477717535</v>
+        <v>81.0769713466521</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8741370560070338</v>
+        <v>81.07808236244107</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8743493807207355</v>
+        <v>6.735527261833589</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5662583044457413</v>
+        <v>6.625292793614177</v>
       </c>
       <c r="L6" t="n">
-        <v>1.190186809934959</v>
+        <v>6.723586492141624</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.912287153493609</v>
+        <v>0.51469546791539</v>
       </c>
       <c r="C7" t="n">
-        <v>3.692628939619454</v>
+        <v>0.5161574967846642</v>
       </c>
       <c r="D7" t="n">
-        <v>3.691166626755366</v>
+        <v>0.5146695440811607</v>
       </c>
       <c r="E7" t="n">
-        <v>4.58982352218321</v>
+        <v>0.5220454404022952</v>
       </c>
       <c r="F7" t="n">
-        <v>3.691013246958818</v>
+        <v>0.5220454404022952</v>
       </c>
       <c r="G7" t="n">
-        <v>3.691212793547511</v>
+        <v>0.5147413507127224</v>
       </c>
       <c r="H7" t="n">
-        <v>3.691166910750184</v>
+        <v>0.51469546791539</v>
       </c>
       <c r="I7" t="n">
-        <v>3.691014018985042</v>
+        <v>0.514542576150248</v>
       </c>
       <c r="J7" t="n">
-        <v>3.691166910750183</v>
+        <v>0.51469546791539</v>
       </c>
       <c r="K7" t="n">
-        <v>3.239880801051978</v>
+        <v>0.51469546791539</v>
       </c>
       <c r="L7" t="n">
-        <v>3.691166910750183</v>
+        <v>0.51469546791539</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.4688273106779933</v>
+        <v>0.571875802445271</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.54396340248728</v>
+        <v>0.8830143287816559</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1531359023831042</v>
+        <v>0.9369974908436627</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1331790276453616</v>
+        <v>0.7979181318466316</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1331790276453616</v>
+        <v>0.5858002597201967</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009608488110972018</v>
+        <v>0.8743358305695121</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.08042223661382228</v>
+        <v>0.8742899477717524</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1331790276453616</v>
+        <v>0.8741370560070358</v>
       </c>
       <c r="J8" t="n">
-        <v>0.09701789943959681</v>
+        <v>0.874349380720736</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1755583540278175</v>
+        <v>0.5662583044457403</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2587399368448147</v>
+        <v>1.190186809934959</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.912287153493618</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.692628939619456</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.691166626755373</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.589823522183219</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.691013246958825</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.691212793547515</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.691166910750189</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.691014018985048</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.691166910750189</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.239880801051979</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.691166910750189</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.4688273106779928</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.5439634024872796</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1531359023831046</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.1331790276453619</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1331790276453619</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.009608488110972507</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.08042223661382258</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1331790276453619</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.09701789943959831</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.1755583540278262</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.258739936844815</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>-0.06391350029450783</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.08125997247977894</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1936815479949686</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.1935404486000527</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.1935404486000527</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.121585862066199</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.09883773083182465</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.1935404486000527</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.1903072562173783</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.2134399953557439</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.01579807968081709</v>
+      <c r="B11" t="n">
+        <v>-0.06391350029450761</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.08125997247977852</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1936815479949692</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1935404486000535</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1935404486000535</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1215858620662003</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.098837730831825</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1935404486000535</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.19030725621738</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2134399953557495</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.01579807968081757</v>
       </c>
     </row>
   </sheetData>
@@ -2819,7 +3299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,321 +3367,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.24284021624031</v>
+        <v>0.2274643017656016</v>
       </c>
       <c r="C2" t="n">
-        <v>25.94408674137239</v>
+        <v>0.2428890918829885</v>
       </c>
       <c r="D2" t="n">
-        <v>2.051989558327119</v>
+        <v>0.214390445209427</v>
       </c>
       <c r="E2" t="n">
-        <v>3.292189369532506</v>
+        <v>0.2324870656137124</v>
       </c>
       <c r="F2" t="n">
-        <v>3.292189369532506</v>
+        <v>0.2324870656137124</v>
       </c>
       <c r="G2" t="n">
-        <v>5.910601428314033</v>
+        <v>0.1946641033134557</v>
       </c>
       <c r="H2" t="n">
-        <v>16.94389484033477</v>
+        <v>0.2297481236317959</v>
       </c>
       <c r="I2" t="n">
-        <v>3.292189369532506</v>
+        <v>0.2324870656137124</v>
       </c>
       <c r="J2" t="n">
-        <v>4.519074754632888</v>
+        <v>0.2573651521213403</v>
       </c>
       <c r="K2" t="n">
-        <v>1.854704315786538</v>
+        <v>0.2391220152228556</v>
       </c>
       <c r="L2" t="n">
-        <v>12.49280973234907</v>
+        <v>0.2095816544352059</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1358554524261274</v>
+        <v>0.2031186161603571</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1505539702387416</v>
+        <v>0.215584785203518</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1358554524261274</v>
+        <v>0.2141924768604479</v>
       </c>
       <c r="E3" t="n">
-        <v>0.167611391058878</v>
+        <v>0.2311493455743254</v>
       </c>
       <c r="F3" t="n">
-        <v>0.167611391058878</v>
+        <v>0.2311493455743254</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1359437110230351</v>
+        <v>0.1897615795750842</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1358554524261274</v>
+        <v>0.2141924768604479</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1359726367049809</v>
+        <v>0.2311493455743254</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1358554524261274</v>
+        <v>0.255156569530714</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1358554524261274</v>
+        <v>0.239558175427481</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1358554524261274</v>
+        <v>0.1987342959999931</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.352210650780775</v>
+        <v>23.24284021624032</v>
       </c>
       <c r="C4" t="n">
-        <v>6.477985774789691</v>
+        <v>25.94408674137237</v>
       </c>
       <c r="D4" t="n">
-        <v>76.7611953702209</v>
+        <v>2.051989558327118</v>
       </c>
       <c r="E4" t="n">
-        <v>6.414504768154183</v>
+        <v>3.292189369532507</v>
       </c>
       <c r="F4" t="n">
-        <v>6.438932034782988</v>
+        <v>3.292189369532507</v>
       </c>
       <c r="G4" t="n">
-        <v>6.352298909377658</v>
+        <v>5.910601428314047</v>
       </c>
       <c r="H4" t="n">
-        <v>76.77233806941383</v>
+        <v>16.94389484033479</v>
       </c>
       <c r="I4" t="n">
-        <v>76.76184038030991</v>
+        <v>3.292189369532507</v>
       </c>
       <c r="J4" t="n">
-        <v>76.76211805267224</v>
+        <v>4.519074754632887</v>
       </c>
       <c r="K4" t="n">
-        <v>6.258889439512564</v>
+        <v>1.85470431578654</v>
       </c>
       <c r="L4" t="n">
-        <v>6.348030132420069</v>
+        <v>12.49280973234907</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4825823413820202</v>
+        <v>0.135855452426127</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4839288784260702</v>
+        <v>0.1505539702387415</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4825569195392517</v>
+        <v>0.135855452426127</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4918811563242194</v>
+        <v>0.1676113910588787</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4918811563242194</v>
+        <v>0.1676113910588789</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4826705999789293</v>
+        <v>0.1359437110230347</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4825823413820202</v>
+        <v>0.135855452426127</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4826995256608754</v>
+        <v>0.1359726367049817</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4825823413820202</v>
+        <v>0.135855452426127</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4825823413820202</v>
+        <v>0.135855452426127</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4825823413820202</v>
+        <v>0.135855452426127</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.531598261402866</v>
+        <v>6.352210650780777</v>
       </c>
       <c r="C6" t="n">
-        <v>0.82434489298668</v>
+        <v>6.477985774789695</v>
       </c>
       <c r="D6" t="n">
-        <v>0.872719860274212</v>
+        <v>76.7611953702209</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7449000083129582</v>
+        <v>6.414504768154183</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5461638522753552</v>
+        <v>6.438932034782988</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8142224526873423</v>
+        <v>6.352298909377661</v>
       </c>
       <c r="H6" t="n">
-        <v>0.814134194092731</v>
+        <v>76.77233806941383</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8142513783692883</v>
+        <v>76.76184038030991</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8141897203775407</v>
+        <v>76.76211805267224</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5263500114099838</v>
+        <v>6.258889439512579</v>
       </c>
       <c r="L6" t="n">
-        <v>1.109266600944494</v>
+        <v>6.34803013242007</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.432676107765425</v>
+        <v>0.4825823413820197</v>
       </c>
       <c r="C7" t="n">
-        <v>3.082750428141293</v>
+        <v>0.4839288784260702</v>
       </c>
       <c r="D7" t="n">
-        <v>3.081403607167098</v>
+        <v>0.4825569195392518</v>
       </c>
       <c r="E7" t="n">
-        <v>3.830138065749107</v>
+        <v>0.4918811563242201</v>
       </c>
       <c r="F7" t="n">
-        <v>3.081520387636246</v>
+        <v>0.4918811563242201</v>
       </c>
       <c r="G7" t="n">
-        <v>3.081492149694153</v>
+        <v>0.482670599978929</v>
       </c>
       <c r="H7" t="n">
-        <v>3.081403891097246</v>
+        <v>0.4825823413820197</v>
       </c>
       <c r="I7" t="n">
-        <v>3.081521075376092</v>
+        <v>0.4826995256608757</v>
       </c>
       <c r="J7" t="n">
-        <v>3.081403891097246</v>
+        <v>0.4825823413820197</v>
       </c>
       <c r="K7" t="n">
-        <v>2.705528346264487</v>
+        <v>0.4825823413820197</v>
       </c>
       <c r="L7" t="n">
-        <v>3.081403891097246</v>
+        <v>0.4825823413820197</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.3428932635610042</v>
+        <v>0.5315982614028665</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.3960516272805267</v>
+        <v>0.8243448929866805</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1680661343369823</v>
+        <v>0.8727198602742122</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1555539752870349</v>
+        <v>0.7449000083129598</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1555539752870349</v>
+        <v>0.5461638522753557</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0536343044320796</v>
+        <v>0.8142224526873429</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1468090116485307</v>
+        <v>0.8141341940927316</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1555539752870349</v>
+        <v>0.8142513783692903</v>
       </c>
       <c r="J8" t="n">
-        <v>0.154268822090308</v>
+        <v>0.8141897203775421</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1984232892821576</v>
+        <v>0.5263500114099836</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0612155443047682</v>
+        <v>1.109266600944493</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.432676107765425</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.082750428141296</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.0814036071671</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.83013806574911</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.081520387636248</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.081492149694157</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.081403891097248</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.081521075376097</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.081403891097248</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.705528346264491</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.081403891097248</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.3428932635610042</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.3960516272805263</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1680661343369824</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.1555539752870351</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1555539752870351</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.05363430443208006</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.146809011648531</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1555539752870351</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.1542688220903072</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.1984232892821591</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.06121554430476798</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>-0.0209728435442346</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.03540742496684581</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1934028123653185</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.1980909312248446</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.1980909312248446</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.1327257593115021</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.06549129591672742</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.1980909312248446</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.2114609055257822</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.2204055109376292</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.0913036486855508</v>
+      <c r="B11" t="n">
+        <v>-0.02097284354423468</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.03540742496684698</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1934028123653184</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1980909312248445</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1980909312248445</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1327257593115026</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.06549129591672739</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1980909312248445</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.2114609055257825</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2204055109376293</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.09130364868555099</v>
       </c>
     </row>
   </sheetData>
@@ -3215,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3283,321 +3843,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.23237525578735</v>
+        <v>0.2169496191021966</v>
       </c>
       <c r="C2" t="n">
-        <v>18.46029996164138</v>
+        <v>0.2102473644641817</v>
       </c>
       <c r="D2" t="n">
-        <v>1.955762135466052</v>
+        <v>0.2067930257600198</v>
       </c>
       <c r="E2" t="n">
-        <v>2.228753001965655</v>
+        <v>0.2227196386049044</v>
       </c>
       <c r="F2" t="n">
-        <v>2.228753001965655</v>
+        <v>0.2227196386049044</v>
       </c>
       <c r="G2" t="n">
-        <v>4.284928090237121</v>
+        <v>0.1845106934270854</v>
       </c>
       <c r="H2" t="n">
-        <v>12.20022516018548</v>
+        <v>0.2172976779941119</v>
       </c>
       <c r="I2" t="n">
-        <v>2.228753001965655</v>
+        <v>0.2227196386049044</v>
       </c>
       <c r="J2" t="n">
-        <v>3.317447179745303</v>
+        <v>0.2552908161685711</v>
       </c>
       <c r="K2" t="n">
-        <v>1.332616340614077</v>
+        <v>0.2305262767687947</v>
       </c>
       <c r="L2" t="n">
-        <v>6.445622033449754</v>
+        <v>0.1941130318880296</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1391335276045327</v>
+        <v>0.1982515030112802</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1596259300411809</v>
+        <v>0.1911189513371528</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1391335276045327</v>
+        <v>0.2066331514019931</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1611177525187243</v>
+        <v>0.2225178687200937</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1611177525187243</v>
+        <v>0.2225178687200938</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1392236609644558</v>
+        <v>0.1813666493439352</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1391335276045327</v>
+        <v>0.2066331514019931</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1392771244287599</v>
+        <v>0.2225178687200938</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1391335276045327</v>
+        <v>0.2544547618069287</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1391335276045327</v>
+        <v>0.2314863116332199</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1391335276045327</v>
+        <v>0.1893501221223592</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.74753729326967</v>
+        <v>18.23237525578736</v>
       </c>
       <c r="C4" t="n">
-        <v>6.458948571685498</v>
+        <v>18.46029996164141</v>
       </c>
       <c r="D4" t="n">
-        <v>6.332126941167284</v>
+        <v>1.955762135466064</v>
       </c>
       <c r="E4" t="n">
-        <v>6.405191874601216</v>
+        <v>2.228753001965665</v>
       </c>
       <c r="F4" t="n">
-        <v>6.429499245542001</v>
+        <v>2.228753001965665</v>
       </c>
       <c r="G4" t="n">
-        <v>76.74762742662936</v>
+        <v>4.284928090237146</v>
       </c>
       <c r="H4" t="n">
-        <v>6.339676092467684</v>
+        <v>12.2002251601855</v>
       </c>
       <c r="I4" t="n">
-        <v>76.74768089009362</v>
+        <v>2.228753001965665</v>
       </c>
       <c r="J4" t="n">
-        <v>6.351296519635558</v>
+        <v>3.317447179745307</v>
       </c>
       <c r="K4" t="n">
-        <v>6.251075060226341</v>
+        <v>1.332616340614094</v>
       </c>
       <c r="L4" t="n">
-        <v>6.337626322371222</v>
+        <v>6.445622033449767</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4816504379433283</v>
+        <v>0.1391335276045446</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4828111053386921</v>
+        <v>0.1596259300411793</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4816223378003942</v>
+        <v>0.1391335276045446</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4884067960851827</v>
+        <v>0.1611177525187241</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4884067960851827</v>
+        <v>0.1611177525187241</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4817405713032424</v>
+        <v>0.1392236609644556</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4816504379433283</v>
+        <v>0.1391335276045446</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4817940347675511</v>
+        <v>0.1392771244287605</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4816504379433283</v>
+        <v>0.1391335276045445</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4816504379433283</v>
+        <v>0.1391335276045446</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4816504379433283</v>
+        <v>0.1391335276045446</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5306957422698271</v>
+        <v>76.74753729326969</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8209713771538735</v>
+        <v>6.458948571685501</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8720142562721964</v>
+        <v>6.332126941167288</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7419489045733169</v>
+        <v>6.40519187460122</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5437620581097938</v>
+        <v>6.429499245542001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8134849044163217</v>
+        <v>76.74762742662939</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8133947710598944</v>
+        <v>6.339676092467688</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8135383678806251</v>
+        <v>76.74768089009352</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8134503293099907</v>
+        <v>6.351296519635557</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5254444626867533</v>
+        <v>6.251075060226344</v>
       </c>
       <c r="L6" t="n">
-        <v>1.108697545347566</v>
+        <v>6.337626322371245</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.188809715128929</v>
+        <v>0.4816504379433352</v>
       </c>
       <c r="C7" t="n">
-        <v>2.771576181157965</v>
+        <v>0.4828111053386925</v>
       </c>
       <c r="D7" t="n">
-        <v>2.770415310004593</v>
+        <v>0.481622337800402</v>
       </c>
       <c r="E7" t="n">
-        <v>3.441718969122906</v>
+        <v>0.4884067960851829</v>
       </c>
       <c r="F7" t="n">
-        <v>2.770558537098842</v>
+        <v>0.4884067960851829</v>
       </c>
       <c r="G7" t="n">
-        <v>2.770505647122524</v>
+        <v>0.4817405713032468</v>
       </c>
       <c r="H7" t="n">
-        <v>2.770415513762599</v>
+        <v>0.4816504379433352</v>
       </c>
       <c r="I7" t="n">
-        <v>2.770559110586829</v>
+        <v>0.4817940347675504</v>
       </c>
       <c r="J7" t="n">
-        <v>2.770415513762599</v>
+        <v>0.4816504379433352</v>
       </c>
       <c r="K7" t="n">
-        <v>2.433430744192423</v>
+        <v>0.4816504379433352</v>
       </c>
       <c r="L7" t="n">
-        <v>2.770415513762599</v>
+        <v>0.4816504379433352</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.229426862623811</v>
+        <v>0.53069574226983</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2429941011833173</v>
+        <v>0.8209713771538734</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1627812377070043</v>
+        <v>0.8720142562721981</v>
       </c>
       <c r="E8" t="n">
-        <v>0.172532982012048</v>
+        <v>0.7419489045733161</v>
       </c>
       <c r="F8" t="n">
-        <v>0.172532982012048</v>
+        <v>0.5437620581097935</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0836671050407624</v>
+        <v>0.8134849044163202</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.05236313255968056</v>
+        <v>0.8133947710598961</v>
       </c>
       <c r="I8" t="n">
-        <v>0.172532982012048</v>
+        <v>0.8135383678806257</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1813302611186188</v>
+        <v>0.8134503293100009</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2029632122863688</v>
+        <v>0.5254444626867592</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05687967600106755</v>
+        <v>1.108697545347561</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.188809715128932</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.771576181157968</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.770415310004593</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.441718969122907</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.770558537098843</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.770505647122528</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.770415513762608</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.77055911058683</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.770415513762608</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.433430744192416</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.770415513762608</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.2294268626238095</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.2429941011833175</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1627812377070057</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.1725329820120479</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1725329820120479</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.08366710504076524</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.05236313255967748</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1725329820120479</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.181330261118621</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.2029632122863716</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.05687967600106571</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.02235459980814685</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.01272454213115452</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1868402652810461</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.1999763558603615</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.1999763558603615</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.1400570894191658</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0994535434193649</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.1999763558603615</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.2220189353214339</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.2175481756682478</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.1338385567445735</v>
+      <c r="B11" t="n">
+        <v>0.02235459980814761</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.01272454213115426</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1868402652810433</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1999763558603616</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1999763558603616</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1400570894191696</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.09945354341936802</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1999763558603616</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.2220189353214337</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2175481756682536</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.1338385567445776</v>
       </c>
     </row>
   </sheetData>
@@ -3611,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3679,321 +4319,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.28574012372844</v>
+        <v>0.2569768643390443</v>
       </c>
       <c r="C2" t="n">
-        <v>34.44664993509612</v>
+        <v>0.2777626504429387</v>
       </c>
       <c r="D2" t="n">
-        <v>2.506323844104069</v>
+        <v>0.2266058727620282</v>
       </c>
       <c r="E2" t="n">
-        <v>4.714031495958487</v>
+        <v>0.2436482155194683</v>
       </c>
       <c r="F2" t="n">
-        <v>4.714031495958487</v>
+        <v>0.2436482155194682</v>
       </c>
       <c r="G2" t="n">
-        <v>8.594733064544306</v>
+        <v>0.2111834320722042</v>
       </c>
       <c r="H2" t="n">
-        <v>14.95423915548302</v>
+        <v>0.2386799107922412</v>
       </c>
       <c r="I2" t="n">
-        <v>4.714031495958487</v>
+        <v>0.2436482155194682</v>
       </c>
       <c r="J2" t="n">
-        <v>6.376977613286511</v>
+        <v>0.2650349656571016</v>
       </c>
       <c r="K2" t="n">
-        <v>2.791504839028549</v>
+        <v>0.2470692715449541</v>
       </c>
       <c r="L2" t="n">
-        <v>24.51606542264501</v>
+        <v>0.2309073917996832</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1466612766503034</v>
+        <v>0.2267971141648202</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1632631611715462</v>
+        <v>0.2432538925167815</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1466612766503034</v>
+        <v>0.2261858724640289</v>
       </c>
       <c r="E3" t="n">
-        <v>0.176700189908589</v>
+        <v>0.2410850739112446</v>
       </c>
       <c r="F3" t="n">
-        <v>0.176700189908589</v>
+        <v>0.2410850739112446</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1467131957766288</v>
+        <v>0.2039383484084586</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1466612766503034</v>
+        <v>0.2261858724640289</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1465440266048826</v>
+        <v>0.2410850739112446</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1466612766503034</v>
+        <v>0.2611907751254962</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1466612766503034</v>
+        <v>0.2466658420196511</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1466612766503034</v>
+        <v>0.2092128223718745</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.725692546726555</v>
+        <v>30.28574012372844</v>
       </c>
       <c r="C4" t="n">
-        <v>6.866558870852853</v>
+        <v>34.44664993509615</v>
       </c>
       <c r="D4" t="n">
-        <v>6.707556952996337</v>
+        <v>2.506323844104071</v>
       </c>
       <c r="E4" t="n">
-        <v>6.787168578069131</v>
+        <v>4.714031495958504</v>
       </c>
       <c r="F4" t="n">
-        <v>6.815154506834849</v>
+        <v>4.714031495958504</v>
       </c>
       <c r="G4" t="n">
-        <v>6.725744465852893</v>
+        <v>8.594733064544386</v>
       </c>
       <c r="H4" t="n">
-        <v>81.07696603189292</v>
+        <v>14.95423915548301</v>
       </c>
       <c r="I4" t="n">
-        <v>6.725575296681141</v>
+        <v>4.714031495958504</v>
       </c>
       <c r="J4" t="n">
-        <v>6.734055004395605</v>
+        <v>6.376977613286532</v>
       </c>
       <c r="K4" t="n">
-        <v>6.623701006830934</v>
+        <v>2.791504839028545</v>
       </c>
       <c r="L4" t="n">
-        <v>6.722811399695058</v>
+        <v>24.51606542264502</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5169122000373708</v>
+        <v>0.1466612766503034</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5183680287040686</v>
+        <v>0.1632631611715498</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5168864509726188</v>
+        <v>0.1466612766503034</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5254975138331751</v>
+        <v>0.1767001899085889</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5254975138331751</v>
+        <v>0.1767001899085895</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5169641191636967</v>
+        <v>0.1467131957766315</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5169122000373708</v>
+        <v>0.1466612766503034</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5167949499919487</v>
+        <v>0.1465440266048831</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5169122000373708</v>
+        <v>0.1466612766503034</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5169122000373708</v>
+        <v>0.1466612766503034</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5169122000373708</v>
+        <v>0.1466612766503034</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5745319097544502</v>
+        <v>6.725692546726552</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8890227202226642</v>
+        <v>6.866558870852857</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9423241744604205</v>
+        <v>6.707556952996334</v>
       </c>
       <c r="E6" t="n">
-        <v>0.803242574072901</v>
+        <v>6.78716857806913</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5892776979915725</v>
+        <v>6.815154506834849</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8792098944455938</v>
+        <v>6.72574446585289</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8791579753187063</v>
+        <v>81.07696603189292</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8790407252738416</v>
+        <v>6.725575296681138</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8792178429611456</v>
+        <v>6.734055004395596</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5688733242021573</v>
+        <v>6.623701006830935</v>
       </c>
       <c r="L6" t="n">
-        <v>1.197365373116327</v>
+        <v>6.722811399695056</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.910911979707612</v>
+        <v>0.5169122000373698</v>
       </c>
       <c r="C7" t="n">
-        <v>3.691095437178526</v>
+        <v>0.5183680287040705</v>
       </c>
       <c r="D7" t="n">
-        <v>3.689639327867419</v>
+        <v>0.5168864509726186</v>
       </c>
       <c r="E7" t="n">
-        <v>4.588156319499299</v>
+        <v>0.5254975138331761</v>
       </c>
       <c r="F7" t="n">
-        <v>3.689521592691737</v>
+        <v>0.5254975138331761</v>
       </c>
       <c r="G7" t="n">
-        <v>3.689691527638166</v>
+        <v>0.516964119163697</v>
       </c>
       <c r="H7" t="n">
-        <v>3.689639608511836</v>
+        <v>0.5169122000373698</v>
       </c>
       <c r="I7" t="n">
-        <v>3.689522358466416</v>
+        <v>0.5167949499919486</v>
       </c>
       <c r="J7" t="n">
-        <v>3.689639608511836</v>
+        <v>0.5169122000373698</v>
       </c>
       <c r="K7" t="n">
-        <v>3.238441644045554</v>
+        <v>0.5169122000373698</v>
       </c>
       <c r="L7" t="n">
-        <v>3.689639608511836</v>
+        <v>0.5169122000373698</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.4476952704921637</v>
+        <v>0.5745319097544502</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.5268128120983628</v>
+        <v>0.889022720222667</v>
       </c>
       <c r="D8" t="n">
-        <v>0.172363308584434</v>
+        <v>0.9423241744604218</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1373171823950311</v>
+        <v>0.8032425740729027</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1373171823950311</v>
+        <v>0.5892776979915736</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01515130293544995</v>
+        <v>0.8792098944455911</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.07485988016463174</v>
+        <v>0.879157975318709</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1373171823950311</v>
+        <v>0.8790407252738426</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1252229444961593</v>
+        <v>0.8792178429611471</v>
       </c>
       <c r="K8" t="n">
-        <v>0.186510931689807</v>
+        <v>0.5688733242021589</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2768715602034478</v>
+        <v>1.19736537311633</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.910911979707613</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.691095437178525</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.689639327867416</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.588156319499302</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.689521592691738</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.689691527638169</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.689639608511832</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.68952235846642</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.689639608511832</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.238441644045556</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.689639608511832</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.4476952704921642</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.5268128120983616</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1723633085844346</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.1373171823950312</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1373171823950312</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.015151302935449</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.07485988016463142</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1373171823950312</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.1252229444961611</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.1865109316898065</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.2768715602034484</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>-0.04991932015957471</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.07262015421393057</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.2021164346744781</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.1964334941909419</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.1964334941909419</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.1252847247533671</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="B11" t="n">
+        <v>-0.04991932015957568</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.07262015421392928</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.202116434674479</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1964334941909416</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1964334941909416</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1252847247533682</v>
+      </c>
+      <c r="H11" t="n">
         <v>0.1017031339703109</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.1964334941909419</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.2031691694169867</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.2196985956425498</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.009737448668895723</v>
+      <c r="I11" t="n">
+        <v>0.1964334941909416</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.2031691694169883</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2196985956425521</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.009737448668895789</v>
       </c>
     </row>
   </sheetData>
@@ -4007,7 +4727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4075,321 +4795,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.79674557890818</v>
+        <v>0.3070499473808615</v>
       </c>
       <c r="C2" t="n">
-        <v>24.50526679126413</v>
+        <v>0.2438452557237556</v>
       </c>
       <c r="D2" t="n">
-        <v>2.243367361856426</v>
+        <v>0.2152261765820316</v>
       </c>
       <c r="E2" t="n">
-        <v>3.109356983650831</v>
+        <v>0.2353993434802795</v>
       </c>
       <c r="F2" t="n">
-        <v>3.109356983650831</v>
+        <v>0.2353993434802795</v>
       </c>
       <c r="G2" t="n">
-        <v>5.88046566099208</v>
+        <v>0.2047418090017151</v>
       </c>
       <c r="H2" t="n">
-        <v>15.40880326332603</v>
+        <v>0.2287538146766832</v>
       </c>
       <c r="I2" t="n">
-        <v>3.109356983650831</v>
+        <v>0.2353993434802795</v>
       </c>
       <c r="J2" t="n">
-        <v>4.429681094316272</v>
+        <v>0.261922420689453</v>
       </c>
       <c r="K2" t="n">
-        <v>1.866531213560365</v>
+        <v>0.2474840114343504</v>
       </c>
       <c r="L2" t="n">
-        <v>13.30627862131534</v>
+        <v>0.213185197307883</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1333469041433896</v>
+        <v>0.2856016728106427</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1439061270313195</v>
+        <v>0.2181863105785312</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1333469041433896</v>
+        <v>0.2147819891527194</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1720136229570539</v>
+        <v>0.2342894647461575</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1720136229570539</v>
+        <v>0.2342894647461575</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1334327628047198</v>
+        <v>0.2000014087746542</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1333469041433896</v>
+        <v>0.2147819891527194</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1334440452113219</v>
+        <v>0.2342894647461575</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1333469041433896</v>
+        <v>0.259854644048025</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1333469041433896</v>
+        <v>0.2480061502741013</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1333469041433896</v>
+        <v>0.2015171726032677</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.75857894332596</v>
+        <v>21.7967455789082</v>
       </c>
       <c r="C4" t="n">
-        <v>6.471307259692434</v>
+        <v>24.50526679126413</v>
       </c>
       <c r="D4" t="n">
-        <v>6.3360094545196</v>
+        <v>2.243367361856424</v>
       </c>
       <c r="E4" t="n">
-        <v>6.411815957315865</v>
+        <v>3.10935698365082</v>
       </c>
       <c r="F4" t="n">
-        <v>6.435951711578246</v>
+        <v>3.10935698365082</v>
       </c>
       <c r="G4" t="n">
-        <v>6.348511760857961</v>
+        <v>5.880465660992129</v>
       </c>
       <c r="H4" t="n">
-        <v>76.76855981498385</v>
+        <v>15.40880326332602</v>
       </c>
       <c r="I4" t="n">
-        <v>76.75867608439398</v>
+        <v>3.10935698365082</v>
       </c>
       <c r="J4" t="n">
-        <v>6.357381742186295</v>
+        <v>4.429681094316272</v>
       </c>
       <c r="K4" t="n">
-        <v>6.255856120576954</v>
+        <v>1.866531213560359</v>
       </c>
       <c r="L4" t="n">
-        <v>6.344928293065855</v>
+        <v>13.30627862131534</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4823595038696946</v>
+        <v>0.1333469041433984</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4836704506047088</v>
+        <v>0.1439061270313207</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4823350720384171</v>
+        <v>0.1333469041433984</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4936380428558415</v>
+        <v>0.1720136229570544</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4936380428558415</v>
+        <v>0.1720136229570545</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4824453625310233</v>
+        <v>0.133432762804722</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4823595038696946</v>
+        <v>0.1333469041433984</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4824566449376256</v>
+        <v>0.1334440452113222</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4823595038696946</v>
+        <v>0.1333469041433967</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4823595038696946</v>
+        <v>0.1333469041433984</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4823595038696946</v>
+        <v>0.1333469041433984</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5314797251907507</v>
+        <v>76.75857894332601</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8285821088724226</v>
+        <v>6.471307259692439</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8755973317175135</v>
+        <v>6.336009454519601</v>
       </c>
       <c r="E6" t="n">
-        <v>0.748273174207683</v>
+        <v>6.411815957315863</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5472962989775575</v>
+        <v>6.435951711578252</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8165829771695214</v>
+        <v>6.348511760857967</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8164971185101609</v>
+        <v>76.76855981498385</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8165942595761254</v>
+        <v>76.758676084394</v>
       </c>
       <c r="J6" t="n">
-        <v>0.816553132456328</v>
+        <v>6.357381742186299</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5261853807945615</v>
+        <v>6.255856120576963</v>
       </c>
       <c r="L6" t="n">
-        <v>1.114221618470443</v>
+        <v>6.344928293065858</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.430975590644078</v>
+        <v>0.48235950386969</v>
       </c>
       <c r="C7" t="n">
-        <v>3.081656850391164</v>
+        <v>0.4836704506047101</v>
       </c>
       <c r="D7" t="n">
-        <v>3.080345649758574</v>
+        <v>0.4823350720384152</v>
       </c>
       <c r="E7" t="n">
-        <v>3.829801563585962</v>
+        <v>0.4936380428558434</v>
       </c>
       <c r="F7" t="n">
-        <v>3.080442385554539</v>
+        <v>0.4936380428558434</v>
       </c>
       <c r="G7" t="n">
-        <v>3.080431762317484</v>
+        <v>0.4824453625310248</v>
       </c>
       <c r="H7" t="n">
-        <v>3.080345903656156</v>
+        <v>0.48235950386969</v>
       </c>
       <c r="I7" t="n">
-        <v>3.080443044724083</v>
+        <v>0.4824566449376266</v>
       </c>
       <c r="J7" t="n">
-        <v>3.080345903656156</v>
+        <v>0.48235950386969</v>
       </c>
       <c r="K7" t="n">
-        <v>2.262672833188039</v>
+        <v>0.48235950386969</v>
       </c>
       <c r="L7" t="n">
-        <v>3.080345903656156</v>
+        <v>0.48235950386969</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.226343413719693</v>
+        <v>0.5314797251907429</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.3593968279549215</v>
+        <v>0.8285821088724211</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1638896290053637</v>
+        <v>0.8755973317175154</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1630136118483965</v>
+        <v>0.7482731742076829</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1630136118483965</v>
+        <v>0.5472962989775587</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06449425711101772</v>
+        <v>0.8165829771695218</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.113272855091008</v>
+        <v>0.816497118510162</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1630136118483965</v>
+        <v>0.8165942595761274</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1609460067967527</v>
+        <v>0.8165531324563258</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2064877875565376</v>
+        <v>0.5261853807945609</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.07567349621345267</v>
+        <v>1.114221618470446</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.430975590644079</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.081656850391166</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.080345649758577</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.829801563585966</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.080442385554543</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.080431762317483</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.080345903656158</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.08044304472409</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.080345903656158</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.262672833188045</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.080345903656158</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.2263434137196887</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.3593968279549212</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1638896290053626</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.1630136118483966</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1630136118483966</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.06449425711101667</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.1132728550910108</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1630136118483966</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.1609460067967539</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.2064877875565366</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.07567349621345108</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.07411330153737414</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.01895691295721474</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1920699905306552</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.202968603269132</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.202968603269132</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.1430856231590907</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.07948781509702769</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.202968603269132</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.2169186755369984</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.2285930240866851</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.08706255964202976</v>
+      <c r="B11" t="n">
+        <v>0.07411330153737147</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.01895691295721535</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1920699905306562</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.2029686032691327</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2029686032691327</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1430856231590894</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.07948781509702646</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2029686032691327</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.2169186755370002</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2285930240866864</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.08706255964202639</v>
       </c>
     </row>
   </sheetData>
@@ -4403,7 +5203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4471,321 +5271,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.56323573392874</v>
+        <v>0.4920598536327687</v>
       </c>
       <c r="C2" t="n">
-        <v>19.49045220533285</v>
+        <v>0.2202602505496576</v>
       </c>
       <c r="D2" t="n">
-        <v>2.250973647433744</v>
+        <v>0.2059830136503172</v>
       </c>
       <c r="E2" t="n">
-        <v>2.216901702127076</v>
+        <v>0.2232063226066221</v>
       </c>
       <c r="F2" t="n">
-        <v>2.216901702127076</v>
+        <v>0.2232063226066221</v>
       </c>
       <c r="G2" t="n">
-        <v>4.532030104334916</v>
+        <v>0.2107972586018169</v>
       </c>
       <c r="H2" t="n">
-        <v>11.76299656493493</v>
+        <v>0.215685902271388</v>
       </c>
       <c r="I2" t="n">
-        <v>2.216901702127076</v>
+        <v>0.2232063226066221</v>
       </c>
       <c r="J2" t="n">
-        <v>3.374418687264197</v>
+        <v>0.2537576101043474</v>
       </c>
       <c r="K2" t="n">
-        <v>1.499619719946263</v>
+        <v>0.2349055945779701</v>
       </c>
       <c r="L2" t="n">
-        <v>7.532431484942081</v>
+        <v>0.1967860672047461</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1345585301547509</v>
+        <v>0.4773359495166562</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1502200360167555</v>
+        <v>0.2000810787001982</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1345585301547509</v>
+        <v>0.20544144732266</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1625825782126966</v>
+        <v>0.22300743986296</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1625825782126966</v>
+        <v>0.22300743986296</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1346314062753515</v>
+        <v>0.2077670387626075</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1345585301547509</v>
+        <v>0.20544144732266</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1345846856891028</v>
+        <v>0.22300743986296</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1345585301547509</v>
+        <v>0.2528132949022661</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1345585301547509</v>
+        <v>0.2357188783079205</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1345585301547509</v>
+        <v>0.1909169702993194</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.74353586683694</v>
+        <v>18.56323573392873</v>
       </c>
       <c r="C4" t="n">
-        <v>6.456569703934898</v>
+        <v>19.49045220533282</v>
       </c>
       <c r="D4" t="n">
-        <v>6.329607991970727</v>
+        <v>2.250973647433749</v>
       </c>
       <c r="E4" t="n">
-        <v>6.402653284730219</v>
+        <v>2.216901702127078</v>
       </c>
       <c r="F4" t="n">
-        <v>6.426690854578577</v>
+        <v>2.216901702127078</v>
       </c>
       <c r="G4" t="n">
-        <v>6.339073266917763</v>
+        <v>4.532030104335036</v>
       </c>
       <c r="H4" t="n">
-        <v>76.7551381062631</v>
+        <v>11.76299656493493</v>
       </c>
       <c r="I4" t="n">
-        <v>6.339026546331524</v>
+        <v>2.216901702127078</v>
       </c>
       <c r="J4" t="n">
-        <v>76.74337373066105</v>
+        <v>3.374418687264202</v>
       </c>
       <c r="K4" t="n">
-        <v>6.248546996318279</v>
+        <v>1.49961971994626</v>
       </c>
       <c r="L4" t="n">
-        <v>6.335125657967446</v>
+        <v>7.532431484942066</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4782597973865622</v>
+        <v>0.1345585301547491</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4794452175143887</v>
+        <v>0.150220036016757</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4782325792099664</v>
+        <v>0.1345585301547491</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4867267850603602</v>
+        <v>0.1625825782126965</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4867267850603602</v>
+        <v>0.1625825782126965</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4783326735071649</v>
+        <v>0.13463140627535</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4782597973865622</v>
+        <v>0.1345585301547491</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4782859529209137</v>
+        <v>0.1345846856891025</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4782597973865622</v>
+        <v>0.1345585301547491</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4782597973865622</v>
+        <v>0.1345585301547491</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4782597973865622</v>
+        <v>0.1345585301547491</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5253733875085758</v>
+        <v>76.74353586683691</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8158011537160932</v>
+        <v>6.456569703934885</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8647382936768595</v>
+        <v>6.329607991970722</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7368951049421559</v>
+        <v>6.402653284730219</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5393609780237595</v>
+        <v>6.426690854578582</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8065272054518121</v>
+        <v>6.339073266917763</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8064543293341445</v>
+        <v>76.75513810626315</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8064804848655611</v>
+        <v>6.339026546331525</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8065095696194413</v>
+        <v>76.74337373066103</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5201521647206508</v>
+        <v>6.248546996318278</v>
       </c>
       <c r="L6" t="n">
-        <v>1.100066876518038</v>
+        <v>6.335125657967447</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.189834888509453</v>
+        <v>0.4782597973865615</v>
       </c>
       <c r="C7" t="n">
-        <v>2.773677270646922</v>
+        <v>0.4794452175143875</v>
       </c>
       <c r="D7" t="n">
-        <v>2.772491646412444</v>
+        <v>0.478232579209962</v>
       </c>
       <c r="E7" t="n">
-        <v>3.444890877154032</v>
+        <v>0.4867267850603604</v>
       </c>
       <c r="F7" t="n">
-        <v>2.772517426671106</v>
+        <v>0.4867267850603604</v>
       </c>
       <c r="G7" t="n">
-        <v>2.772564726639701</v>
+        <v>0.4783326735071637</v>
       </c>
       <c r="H7" t="n">
-        <v>2.772491850519105</v>
+        <v>0.4782597973865615</v>
       </c>
       <c r="I7" t="n">
-        <v>2.772518006053454</v>
+        <v>0.4782859529209141</v>
       </c>
       <c r="J7" t="n">
-        <v>2.772491850519105</v>
+        <v>0.4782597973865615</v>
       </c>
       <c r="K7" t="n">
-        <v>2.421201433257643</v>
+        <v>0.4782597973865615</v>
       </c>
       <c r="L7" t="n">
-        <v>2.772491850519105</v>
+        <v>0.4782597973865615</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04176656312889183</v>
+        <v>0.5253733875085743</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2585394677163773</v>
+        <v>0.8158011537160925</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1543205280215445</v>
+        <v>0.8647382936768597</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1732405636354435</v>
+        <v>0.7368951049421573</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1732405636354435</v>
+        <v>0.5393609780237596</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1041511237281435</v>
+        <v>0.8065272054518101</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0442048170164297</v>
+        <v>0.8064543293341442</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1732405636354435</v>
+        <v>0.806480484865562</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1783064656586379</v>
+        <v>0.8065095696194422</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2030723736255987</v>
+        <v>0.5201521647206521</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03546675915810382</v>
+        <v>1.100066876518036</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.189834888509453</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.773677270646927</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.772491646412444</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.444890877154037</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.772517426671108</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.772564726639701</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.772491850519105</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.772518006053458</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.772491850519105</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.42120143325764</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.772491850519105</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.04176656312889086</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.2585394677163774</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1543205280215447</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.1732405636354438</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1732405636354438</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.1041511237281432</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.04420481701643131</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1732405636354438</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.1783064656586361</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.2030723736255939</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.03546675915810504</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.2938743947490621</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.0115864403931549</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1827228324556065</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.2005622353254783</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.2005622353254783</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.1636516870568078</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.1020960564216615</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.2005622353254783</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.2198567653593198</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.2200513309092744</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.126055725745066</v>
+      <c r="B11" t="n">
+        <v>0.2938743947490613</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.01158644039315338</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1827228324556063</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.2005622353254784</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2005622353254784</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1636516870568072</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.102096056421662</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2005622353254784</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.2198567653593183</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2200513309092732</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.1260557257450646</v>
       </c>
     </row>
   </sheetData>
@@ -4799,7 +5679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4867,321 +5747,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.70532674384672</v>
+        <v>0.2010714103802563</v>
       </c>
       <c r="C2" t="n">
-        <v>10.90484588386029</v>
+        <v>0.2519738980925271</v>
       </c>
       <c r="D2" t="n">
-        <v>5.618512043260413</v>
+        <v>0.20423951851306</v>
       </c>
       <c r="E2" t="n">
-        <v>10.90484588386029</v>
+        <v>0.2519738980925271</v>
       </c>
       <c r="F2" t="n">
-        <v>10.90484588386029</v>
+        <v>0.2519738980925271</v>
       </c>
       <c r="G2" t="n">
-        <v>10.95471983319387</v>
+        <v>0.2101161759360717</v>
       </c>
       <c r="H2" t="n">
-        <v>12.91651369996433</v>
+        <v>0.2108813954078709</v>
       </c>
       <c r="I2" t="n">
-        <v>10.90484588386029</v>
+        <v>0.2519738980925271</v>
       </c>
       <c r="J2" t="n">
-        <v>7.753204000752302</v>
+        <v>0.2061499495022477</v>
       </c>
       <c r="K2" t="n">
-        <v>4.970815362863648</v>
+        <v>0.2035231355866419</v>
       </c>
       <c r="L2" t="n">
-        <v>35.3435469540038</v>
+        <v>0.2333078512181743</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1339233690897061</v>
+        <v>0.2000237076701067</v>
       </c>
       <c r="C3" t="n">
-        <v>0.136055521313233</v>
+        <v>0.2419950837311905</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1339233690897061</v>
+        <v>0.2000237076701067</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1367452493170459</v>
+        <v>0.2419950837311905</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1367452493170459</v>
+        <v>0.2419950837311905</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1340955314355511</v>
+        <v>0.2002353207655835</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1339233690897061</v>
+        <v>0.2000237076701067</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1346001200363502</v>
+        <v>0.2419950837311905</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1339233690897061</v>
+        <v>0.2000237076701067</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1339233690897061</v>
+        <v>0.2000237076701067</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1339233690897061</v>
+        <v>0.2000237076701067</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.802112330887377</v>
+        <v>2.705326743846696</v>
       </c>
       <c r="C4" t="n">
-        <v>6.890528693572319</v>
+        <v>10.90484588386033</v>
       </c>
       <c r="D4" t="n">
-        <v>6.780333217722753</v>
+        <v>5.618512043260434</v>
       </c>
       <c r="E4" t="n">
-        <v>6.867723410710639</v>
+        <v>10.90484588386033</v>
       </c>
       <c r="F4" t="n">
-        <v>6.889677362212414</v>
+        <v>10.90484588386033</v>
       </c>
       <c r="G4" t="n">
-        <v>6.802284493233229</v>
+        <v>10.95471983319386</v>
       </c>
       <c r="H4" t="n">
-        <v>82.35967190382887</v>
+        <v>12.91651369996435</v>
       </c>
       <c r="I4" t="n">
-        <v>82.37115156619828</v>
+        <v>10.90484588386033</v>
       </c>
       <c r="J4" t="n">
-        <v>6.804508706933245</v>
+        <v>7.753204000752321</v>
       </c>
       <c r="K4" t="n">
-        <v>6.692305870471017</v>
+        <v>4.970815362863658</v>
       </c>
       <c r="L4" t="n">
-        <v>6.788095595629558</v>
+        <v>35.34354695400374</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5115120796661317</v>
+        <v>0.1339233690897068</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5121888306127782</v>
+        <v>0.1360555213132339</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5114850211536865</v>
+        <v>0.1339233690897068</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5121129208213906</v>
+        <v>0.1367452493170465</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5121129208213906</v>
+        <v>0.1367452493170464</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5116842420119767</v>
+        <v>0.1340955314355508</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5115120796661317</v>
+        <v>0.1339233690897068</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5121888306127782</v>
+        <v>0.1346001200363511</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5115120796661317</v>
+        <v>0.1339233690897068</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5115120796661317</v>
+        <v>0.1339233690897068</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5115120796661317</v>
+        <v>0.1339233690897068</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5716518752795984</v>
+        <v>6.802112330887378</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8806699357080148</v>
+        <v>6.890528693572319</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9439032046005804</v>
+        <v>6.780333217722757</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7963378641558081</v>
+        <v>6.86772341071064</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5820727301919892</v>
+        <v>6.889677362212413</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8801433491842353</v>
+        <v>6.802284493233237</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8799711868382964</v>
+        <v>82.35967190382887</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8806479377850329</v>
+        <v>82.37115156619826</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8800317803767835</v>
+        <v>6.804508706933236</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5659246857804032</v>
+        <v>6.692305870471018</v>
       </c>
       <c r="L6" t="n">
-        <v>1.202036488963474</v>
+        <v>6.788095595629558</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.011464469107857</v>
+        <v>0.5115120796661369</v>
       </c>
       <c r="C7" t="n">
-        <v>3.821080927408416</v>
+        <v>0.5121888306127818</v>
       </c>
       <c r="D7" t="n">
-        <v>3.82040410530715</v>
+        <v>0.511485021153688</v>
       </c>
       <c r="E7" t="n">
-        <v>4.754579440438872</v>
+        <v>0.5121129208213936</v>
       </c>
       <c r="F7" t="n">
-        <v>3.821080373294888</v>
+        <v>0.5121129208213936</v>
       </c>
       <c r="G7" t="n">
-        <v>3.820576338807621</v>
+        <v>0.5116842420119808</v>
       </c>
       <c r="H7" t="n">
-        <v>3.820404176461776</v>
+        <v>0.5115120796661369</v>
       </c>
       <c r="I7" t="n">
-        <v>3.821080927408416</v>
+        <v>0.5121888306127818</v>
       </c>
       <c r="J7" t="n">
-        <v>3.820404176461776</v>
+        <v>0.5115120796661369</v>
       </c>
       <c r="K7" t="n">
-        <v>3.351701303142401</v>
+        <v>0.5115120796661369</v>
       </c>
       <c r="L7" t="n">
-        <v>3.820404176461776</v>
+        <v>0.5115120796661369</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1409281500614069</v>
+        <v>0.5716518752796022</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.01739112161231481</v>
+        <v>0.8806699357080157</v>
       </c>
       <c r="D8" t="n">
-        <v>0.07459393395709699</v>
+        <v>0.9439032046005865</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.01739112161231481</v>
+        <v>0.7963378641558113</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.01739112161231481</v>
+        <v>0.5820727301919922</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.04280252451234409</v>
+        <v>0.8801433491842415</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0596209934013504</v>
+        <v>0.8799711868383003</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01739112161231481</v>
+        <v>0.8806479377850382</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03579569310923969</v>
+        <v>0.8800317803767861</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08966214721502411</v>
+        <v>0.5659246857804062</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5234320600049159</v>
+        <v>1.20203648896348</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.011464469107862</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.821080927408416</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.820404105307153</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.754579440438869</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.821080373294889</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.820576338807621</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.820404176461777</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.821080927408416</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.820404176461777</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.3517013031424</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.820404176461777</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.1409281500614065</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.01739112161231429</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.07459393395709611</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.01739112161231429</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.01739112161231429</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.04280252451234322</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.05962099340135112</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.01739112161231429</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.0357956931092405</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.08966214721502454</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.5234320600049166</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.1741827433419278</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.1339523480464417</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1471685717526681</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.1339523480464417</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.1339523480464417</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.09953318181895685</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.09274222898178937</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.1339523480464417</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.131425679513425</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.1533082738781529</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.1620360944070451</v>
+      <c r="B11" t="n">
+        <v>0.1741827433419287</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.1339523480464422</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1471685717526688</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1339523480464422</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1339523480464422</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.09953318181895743</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0927422289817898</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1339523480464422</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.1314256795134248</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.1533082738781537</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.1620360944070461</v>
       </c>
     </row>
   </sheetData>
@@ -5195,7 +6155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5263,321 +6223,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.247130452331414</v>
+        <v>0.1959317622142212</v>
       </c>
       <c r="C2" t="n">
-        <v>9.2703882102505</v>
+        <v>0.2470233688666922</v>
       </c>
       <c r="D2" t="n">
-        <v>4.826965699331532</v>
+        <v>0.1990426290231908</v>
       </c>
       <c r="E2" t="n">
-        <v>9.2703882102505</v>
+        <v>0.2470233688666922</v>
       </c>
       <c r="F2" t="n">
-        <v>9.2703882102505</v>
+        <v>0.2470233688666922</v>
       </c>
       <c r="G2" t="n">
-        <v>8.767781490032066</v>
+        <v>0.2038751856234858</v>
       </c>
       <c r="H2" t="n">
-        <v>9.480120824729195</v>
+        <v>0.2033552436383631</v>
       </c>
       <c r="I2" t="n">
-        <v>9.2703882102505</v>
+        <v>0.2470233688666922</v>
       </c>
       <c r="J2" t="n">
-        <v>6.515377363364002</v>
+        <v>0.2005672202196181</v>
       </c>
       <c r="K2" t="n">
-        <v>3.920624751474533</v>
+        <v>0.1981336533370108</v>
       </c>
       <c r="L2" t="n">
-        <v>20.43826984150618</v>
+        <v>0.2153710379124101</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1269783441924913</v>
+        <v>0.1951924720422351</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1299288723538272</v>
+        <v>0.237958850344192</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1269783441924912</v>
+        <v>0.1951924720422351</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1305088300992694</v>
+        <v>0.237958850344192</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1305088300992695</v>
+        <v>0.237958850344192</v>
       </c>
       <c r="G3" t="n">
-        <v>0.127172415710612</v>
+        <v>0.1954983306921632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1269783441924912</v>
+        <v>0.1951924720422351</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1277933547763803</v>
+        <v>0.237958850344192</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1269783441924912</v>
+        <v>0.1951924720422351</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1269783441924912</v>
+        <v>0.1951924720422351</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1269783441924912</v>
+        <v>0.1951924720422351</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.331593084549692</v>
+        <v>2.247130452331433</v>
       </c>
       <c r="C4" t="n">
-        <v>6.418556847620956</v>
+        <v>9.270388210250522</v>
       </c>
       <c r="D4" t="n">
-        <v>6.316406060451587</v>
+        <v>4.826965699331534</v>
       </c>
       <c r="E4" t="n">
-        <v>6.397461290145311</v>
+        <v>9.270388210250522</v>
       </c>
       <c r="F4" t="n">
-        <v>6.417073209328366</v>
+        <v>9.270388210250522</v>
       </c>
       <c r="G4" t="n">
-        <v>6.331787156067772</v>
+        <v>8.767781490032059</v>
       </c>
       <c r="H4" t="n">
-        <v>76.7302404327212</v>
+        <v>9.480120824729212</v>
       </c>
       <c r="I4" t="n">
-        <v>76.74104171893494</v>
+        <v>9.270388210250522</v>
       </c>
       <c r="J4" t="n">
-        <v>6.337178416030533</v>
+        <v>6.515377363363998</v>
       </c>
       <c r="K4" t="n">
-        <v>6.234037452751229</v>
+        <v>3.920624751474538</v>
       </c>
       <c r="L4" t="n">
-        <v>6.322626350117829</v>
+        <v>20.43826984150617</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4749755086177314</v>
+        <v>0.1269783441924915</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4757905192016197</v>
+        <v>0.1299288723538269</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4749501770827879</v>
+        <v>0.1269783441924913</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4758479646583106</v>
+        <v>0.130508830099269</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4758479646583105</v>
+        <v>0.1305088300992694</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4751695801358504</v>
+        <v>0.1271724157106113</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4749755086177314</v>
+        <v>0.1269783441924913</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4757905192016197</v>
+        <v>0.1277933547763797</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4749755086177314</v>
+        <v>0.1269783441924913</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4749755086177314</v>
+        <v>0.1269783441924913</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4749755086177314</v>
+        <v>0.1269783441924913</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5272302648058531</v>
+        <v>6.331593084549694</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8104396519100103</v>
+        <v>6.418556847620958</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8680091910505809</v>
+        <v>6.316406060451586</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7332243851065359</v>
+        <v>6.397461290145314</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5370416120358555</v>
+        <v>6.417073209328367</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8096764484259592</v>
+        <v>6.331787156067774</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8094823769077371</v>
+        <v>76.73024043272122</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8102973874917272</v>
+        <v>76.74104171893488</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8095378474941505</v>
+        <v>6.337178416030531</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5219872869194481</v>
+        <v>6.234037452751229</v>
       </c>
       <c r="L6" t="n">
-        <v>1.104318309496205</v>
+        <v>6.322626350117825</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.499564627062842</v>
+        <v>0.4749755086177306</v>
       </c>
       <c r="C7" t="n">
-        <v>3.168690004364129</v>
+        <v>0.4757905192016195</v>
       </c>
       <c r="D7" t="n">
-        <v>3.167874943772688</v>
+        <v>0.4749501770827877</v>
       </c>
       <c r="E7" t="n">
-        <v>3.939905369301889</v>
+        <v>0.47584796465831</v>
       </c>
       <c r="F7" t="n">
-        <v>3.168689538299938</v>
+        <v>0.4758479646583099</v>
       </c>
       <c r="G7" t="n">
-        <v>3.168069065298361</v>
+        <v>0.4751695801358506</v>
       </c>
       <c r="H7" t="n">
-        <v>3.167874993780245</v>
+        <v>0.4749755086177307</v>
       </c>
       <c r="I7" t="n">
-        <v>3.168690004364129</v>
+        <v>0.4757905192016195</v>
       </c>
       <c r="J7" t="n">
-        <v>3.167874993780245</v>
+        <v>0.4749755086177307</v>
       </c>
       <c r="K7" t="n">
-        <v>2.780653321614079</v>
+        <v>0.4749755086177307</v>
       </c>
       <c r="L7" t="n">
-        <v>3.167874993780245</v>
+        <v>0.4749755086177307</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1434888631378151</v>
+        <v>0.527230264805852</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.001535903851205492</v>
+        <v>0.8104396519100089</v>
       </c>
       <c r="D8" t="n">
-        <v>0.07834965608197426</v>
+        <v>0.8680091910505798</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.001535903851205492</v>
+        <v>0.7332243851065328</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.001535903851205492</v>
+        <v>0.5370416120358542</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.01524764953487582</v>
+        <v>0.8096764484259574</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.008137771406575803</v>
+        <v>0.8094823769077353</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.001535903851205492</v>
+        <v>0.810297387491726</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04751110401043358</v>
+        <v>0.8095378474941483</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09744543074321997</v>
+        <v>0.521987286919447</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2568864054921712</v>
+        <v>1.104318309496202</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.499564627062841</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.168690004364131</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.167874943772692</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.939905369301891</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.168689538299938</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.168069065298361</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.167874993780242</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.168690004364131</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.167874993780242</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.780653321614077</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.167874993780242</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.1434888631378144</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.001535903851205406</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.07834965608197431</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.001535903851205406</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.001535903851205406</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.01524764953487561</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.008137771406575588</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.001535903851205406</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.04751110401043336</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.09744543074321979</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.2568864054921715</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>0.1724064553930859</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C11" t="n">
         <v>0.1380524924832892</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.1458787754053114</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>0.145878775405311</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.1380524924832892</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.1380524924832892</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G11" t="n">
         <v>0.1079850930125933</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H11" t="n">
         <v>0.1108393348941155</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I11" t="n">
         <v>0.1380524924832892</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.1333717271325536</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.1536584380446221</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.1503337153844229</v>
+      <c r="J11" t="n">
+        <v>0.1333717271325534</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.1536584380446218</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.1503337153844223</v>
       </c>
     </row>
   </sheetData>
@@ -5591,7 +6631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5659,321 +6699,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.074281276725833</v>
+        <v>0.190066841319483</v>
       </c>
       <c r="C2" t="n">
-        <v>7.842661517065317</v>
+        <v>0.2382202671049315</v>
       </c>
       <c r="D2" t="n">
-        <v>4.254049723494</v>
+        <v>0.1927853661411634</v>
       </c>
       <c r="E2" t="n">
-        <v>7.842661517065317</v>
+        <v>0.2382202671049315</v>
       </c>
       <c r="F2" t="n">
-        <v>7.842661517065317</v>
+        <v>0.2382202671049315</v>
       </c>
       <c r="G2" t="n">
-        <v>7.440897490698586</v>
+        <v>0.1967559254319873</v>
       </c>
       <c r="H2" t="n">
-        <v>10.62074098886567</v>
+        <v>0.1993340342613686</v>
       </c>
       <c r="I2" t="n">
-        <v>7.842661517065317</v>
+        <v>0.2382202671049315</v>
       </c>
       <c r="J2" t="n">
-        <v>5.404323889710499</v>
+        <v>0.1936104019717462</v>
       </c>
       <c r="K2" t="n">
-        <v>2.940202443545177</v>
+        <v>0.1913500019172368</v>
       </c>
       <c r="L2" t="n">
-        <v>15.59806324409334</v>
+        <v>0.1928073639595054</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1204103578024469</v>
+        <v>0.1894216147684022</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1233638614907742</v>
+        <v>0.2307871878387087</v>
       </c>
       <c r="D3" t="n">
-        <v>0.120410357802447</v>
+        <v>0.1894216147684022</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1238929397977575</v>
+        <v>0.2307871878387087</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1238929397977574</v>
+        <v>0.2307871878387087</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1205944831698627</v>
+        <v>0.1896734616884465</v>
       </c>
       <c r="H3" t="n">
-        <v>0.120410357802447</v>
+        <v>0.1894216147684022</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1211605604579092</v>
+        <v>0.2307871878387087</v>
       </c>
       <c r="J3" t="n">
-        <v>0.120410357802447</v>
+        <v>0.1894216147684022</v>
       </c>
       <c r="K3" t="n">
-        <v>0.120410357802447</v>
+        <v>0.1894216147684022</v>
       </c>
       <c r="L3" t="n">
-        <v>0.120410357802447</v>
+        <v>0.1894216147684022</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.318304761460977</v>
+        <v>2.074281276725832</v>
       </c>
       <c r="C4" t="n">
-        <v>6.405177344603691</v>
+        <v>7.842661517065331</v>
       </c>
       <c r="D4" t="n">
-        <v>6.305049949564407</v>
+        <v>4.254049723493997</v>
       </c>
       <c r="E4" t="n">
-        <v>6.384356294071026</v>
+        <v>7.842661517065331</v>
       </c>
       <c r="F4" t="n">
-        <v>6.40414206217703</v>
+        <v>7.842661517065331</v>
       </c>
       <c r="G4" t="n">
-        <v>76.72221480872636</v>
+        <v>7.440897490698587</v>
       </c>
       <c r="H4" t="n">
-        <v>76.71244100422676</v>
+        <v>10.62074098886566</v>
       </c>
       <c r="I4" t="n">
-        <v>6.319054964116411</v>
+        <v>7.842661517065331</v>
       </c>
       <c r="J4" t="n">
-        <v>76.71472714365348</v>
+        <v>5.404323889710497</v>
       </c>
       <c r="K4" t="n">
-        <v>6.221780297414937</v>
+        <v>2.940202443545181</v>
       </c>
       <c r="L4" t="n">
-        <v>6.310252043172886</v>
+        <v>15.59806324409337</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4647805470766652</v>
+        <v>0.1204103578024437</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4655307497321291</v>
+        <v>0.123363861490774</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4647553243895895</v>
+        <v>0.1204103578024437</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4656764483924833</v>
+        <v>0.123892939797757</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4656764483924833</v>
+        <v>0.123892939797757</v>
       </c>
       <c r="G5" t="n">
-        <v>0.464964672444082</v>
+        <v>0.1205944831698619</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4647805470766648</v>
+        <v>0.1204103578024437</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4655307497321291</v>
+        <v>0.1211605604579088</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4647805470766648</v>
+        <v>0.1204103578024437</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4647805470766648</v>
+        <v>0.1204103578024437</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4647805470766648</v>
+        <v>0.1204103578024437</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5131049768384346</v>
+        <v>6.318304761460979</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7911434841786259</v>
+        <v>6.405177344603681</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8476185100669024</v>
+        <v>6.305049949564404</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7153386119363049</v>
+        <v>6.384356294071016</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5227396042107277</v>
+        <v>6.404142062177029</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7903518663882408</v>
+        <v>76.72221480872641</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7901677410207799</v>
+        <v>76.71244100422676</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7909179436762892</v>
+        <v>6.319054964116413</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7902221917511889</v>
+        <v>76.71472714365346</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5079583937538888</v>
+        <v>6.221780297414933</v>
       </c>
       <c r="L6" t="n">
-        <v>1.079582965780576</v>
+        <v>6.310252043172886</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.247702305914454</v>
+        <v>0.4647805470766647</v>
       </c>
       <c r="C7" t="n">
-        <v>2.848756860522429</v>
+        <v>0.46553074973213</v>
       </c>
       <c r="D7" t="n">
-        <v>2.848006557031474</v>
+        <v>0.4647553243895905</v>
       </c>
       <c r="E7" t="n">
-        <v>3.541494642173295</v>
+        <v>0.4656764483924834</v>
       </c>
       <c r="F7" t="n">
-        <v>2.848756363849194</v>
+        <v>0.4656764483924834</v>
       </c>
       <c r="G7" t="n">
-        <v>2.84819078323439</v>
+        <v>0.4649646724440815</v>
       </c>
       <c r="H7" t="n">
-        <v>2.848006657866968</v>
+        <v>0.4647805470766646</v>
       </c>
       <c r="I7" t="n">
-        <v>2.848756860522429</v>
+        <v>0.46553074973213</v>
       </c>
       <c r="J7" t="n">
-        <v>2.848006657866968</v>
+        <v>0.4647805470766646</v>
       </c>
       <c r="K7" t="n">
-        <v>2.50018791635777</v>
+        <v>0.4647805470766646</v>
       </c>
       <c r="L7" t="n">
-        <v>2.848006657866968</v>
+        <v>0.4647805470766646</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1408688580147527</v>
+        <v>0.5131049768384355</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02701381579792902</v>
+        <v>0.7911434841786257</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08394687964340826</v>
+        <v>0.8476185100669037</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02701381579792902</v>
+        <v>0.715338611936305</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02701381579792902</v>
+        <v>0.5227396042107281</v>
       </c>
       <c r="G8" t="n">
-        <v>0.007098261748694407</v>
+        <v>0.7903518663882411</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.04872298171117376</v>
+        <v>0.7901677410207786</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02701381579792902</v>
+        <v>0.7909179436762899</v>
       </c>
       <c r="J8" t="n">
-        <v>0.06757085330602416</v>
+        <v>0.7902221917511866</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1140573457428153</v>
+        <v>0.5079583937538901</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08508589659386623</v>
+        <v>1.079582965780576</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.247702305914453</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.848756860522429</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.848006557031474</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.541494642173295</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.848756363849193</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.848190783234393</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.84800665786697</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.848756860522429</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.84800665786697</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.500187916357771</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.84800665786697</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.1408688580147525</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.02701381579792878</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.08394687964340639</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.02701381579792878</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.02701381579792878</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.007098261748693104</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.04872298171117505</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.02701381579792878</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.06757085330602339</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.1140573457428144</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.08508589659386522</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.1679751822681185</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.1455027334391719</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1447940255312541</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.1455027334391719</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.1455027334391719</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.1136836276267611</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.09097748394136293</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.1455027334391719</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.1381679171910275</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="B11" t="n">
+        <v>0.1679751822681178</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.1455027334391715</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1447940255312531</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1455027334391715</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1455027334391715</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1136836276267599</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.09097748394136262</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1455027334391715</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.1381679171910276</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.1570590193389189</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.1453342796918852</v>
+      <c r="L11" t="n">
+        <v>0.1453342796918853</v>
       </c>
     </row>
   </sheetData>
@@ -5987,7 +7107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6055,321 +7175,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9738103776215197</v>
+        <v>0.2104491589275458</v>
       </c>
       <c r="C2" t="n">
-        <v>11.261282838897</v>
+        <v>0.2606430779291854</v>
       </c>
       <c r="D2" t="n">
-        <v>3.426276936508324</v>
+        <v>0.2133666743463122</v>
       </c>
       <c r="E2" t="n">
-        <v>11.261282838897</v>
+        <v>0.2606430779291854</v>
       </c>
       <c r="F2" t="n">
-        <v>11.261282838897</v>
+        <v>0.2606430779291854</v>
       </c>
       <c r="G2" t="n">
-        <v>13.68287810816892</v>
+        <v>0.2248074546897096</v>
       </c>
       <c r="H2" t="n">
-        <v>23.59525059989438</v>
+        <v>0.2354399888457569</v>
       </c>
       <c r="I2" t="n">
-        <v>11.261282838897</v>
+        <v>0.2606430779291854</v>
       </c>
       <c r="J2" t="n">
-        <v>10.4352848025421</v>
+        <v>0.2203084692736327</v>
       </c>
       <c r="K2" t="n">
-        <v>4.413306761055497</v>
+        <v>0.2145111631723005</v>
       </c>
       <c r="L2" t="n">
-        <v>16.19750656167276</v>
+        <v>0.2306156932886747</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.142194027147546</v>
+        <v>0.2114903424237269</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1416464046020246</v>
+        <v>0.2502761903751787</v>
       </c>
       <c r="D3" t="n">
-        <v>0.142194027147546</v>
+        <v>0.2114903424237269</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1425516922625357</v>
+        <v>0.2502761903751787</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1425516922625357</v>
+        <v>0.2502761903751787</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1422617524686406</v>
+        <v>0.2111797634409385</v>
       </c>
       <c r="H3" t="n">
-        <v>0.142194027147546</v>
+        <v>0.2114903424237269</v>
       </c>
       <c r="I3" t="n">
-        <v>0.142207464310221</v>
+        <v>0.2502761903751787</v>
       </c>
       <c r="J3" t="n">
-        <v>0.142194027147546</v>
+        <v>0.2114903424237269</v>
       </c>
       <c r="K3" t="n">
-        <v>0.142194027147546</v>
+        <v>0.2114903424237269</v>
       </c>
       <c r="L3" t="n">
-        <v>0.142194027147546</v>
+        <v>0.2114903424237269</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>82.41083219859837</v>
+        <v>0.9738103776214684</v>
       </c>
       <c r="C4" t="n">
-        <v>6.902313781223254</v>
+        <v>11.26128283889701</v>
       </c>
       <c r="D4" t="n">
-        <v>82.40017027473151</v>
+        <v>3.426276936508326</v>
       </c>
       <c r="E4" t="n">
-        <v>6.879146722521156</v>
+        <v>11.26128283889701</v>
       </c>
       <c r="F4" t="n">
-        <v>6.905412226480185</v>
+        <v>11.26128283889701</v>
       </c>
       <c r="G4" t="n">
-        <v>82.41089992391943</v>
+        <v>13.68287810816893</v>
       </c>
       <c r="H4" t="n">
-        <v>6.811538693393043</v>
+        <v>23.59525059989436</v>
       </c>
       <c r="I4" t="n">
-        <v>82.41084563576086</v>
+        <v>11.26128283889701</v>
       </c>
       <c r="J4" t="n">
-        <v>82.4025905340437</v>
+        <v>10.43528480254212</v>
       </c>
       <c r="K4" t="n">
-        <v>6.70370825215494</v>
+        <v>4.413306761055487</v>
       </c>
       <c r="L4" t="n">
-        <v>6.808406787934492</v>
+        <v>16.19750656167272</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5310243012858868</v>
+        <v>0.1421940271475459</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5310377384485602</v>
+        <v>0.1416464046020245</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5309970903602501</v>
+        <v>0.1421940271475459</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5309700778377238</v>
+        <v>0.1425516922625356</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5309700778377238</v>
+        <v>0.1425516922625356</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5310920266069801</v>
+        <v>0.1422617524686406</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5310243012858868</v>
+        <v>0.142194027147546</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5310377384485602</v>
+        <v>0.1422074643102212</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5310243012858868</v>
+        <v>0.1421940271475459</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5310243012858868</v>
+        <v>0.1421940271475459</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5310243012858868</v>
+        <v>0.1421940271475459</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6039695617829313</v>
+        <v>82.41083219859834</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9301841567280633</v>
+        <v>6.902313781223252</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9977701234204177</v>
+        <v>82.40017027473149</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8409694914027372</v>
+        <v>6.879146722521155</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6142978776678664</v>
+        <v>6.905412226480185</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9302048746780047</v>
+        <v>82.41089992391944</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9301371493568291</v>
+        <v>6.811538693393042</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9301505865195849</v>
+        <v>82.41084563576092</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9302012505799474</v>
+        <v>82.40259053404368</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5979108313947751</v>
+        <v>6.703708252154938</v>
       </c>
       <c r="L6" t="n">
-        <v>1.270846468215956</v>
+        <v>6.808406787934492</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.100427179945928</v>
+        <v>0.5310243012858875</v>
       </c>
       <c r="C7" t="n">
-        <v>3.932814413797214</v>
+        <v>0.5310377384485605</v>
       </c>
       <c r="D7" t="n">
-        <v>3.932800810821377</v>
+        <v>0.530997090360251</v>
       </c>
       <c r="E7" t="n">
-        <v>4.893355028175502</v>
+        <v>0.5309700778377232</v>
       </c>
       <c r="F7" t="n">
-        <v>3.932813655449941</v>
+        <v>0.5309700778377232</v>
       </c>
       <c r="G7" t="n">
-        <v>3.932868701955643</v>
+        <v>0.5310920266069808</v>
       </c>
       <c r="H7" t="n">
-        <v>3.932800976634562</v>
+        <v>0.5310243012858875</v>
       </c>
       <c r="I7" t="n">
-        <v>3.932814413797214</v>
+        <v>0.5310377384485605</v>
       </c>
       <c r="J7" t="n">
-        <v>3.932800976634562</v>
+        <v>0.5310243012858875</v>
       </c>
       <c r="K7" t="n">
-        <v>3.450520260108854</v>
+        <v>0.5310243012858875</v>
       </c>
       <c r="L7" t="n">
-        <v>3.932800976634562</v>
+        <v>0.5310243012858875</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1940847823108273</v>
+        <v>0.6039695617829319</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.01879252995971344</v>
+        <v>0.930184156728064</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1329769415799844</v>
+        <v>0.9977701234204176</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.01879252995971344</v>
+        <v>0.8409694914027377</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.01879252995971344</v>
+        <v>0.6142978776678676</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1120881549538519</v>
+        <v>0.9302048746780058</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3193648312700985</v>
+        <v>0.93013714935683</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01879252995971344</v>
+        <v>0.9301505865195854</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.01078913979672795</v>
+        <v>0.930201250579948</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1090582759344526</v>
+        <v>0.5979108313947751</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1154223559895262</v>
+        <v>1.270846468215955</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.100427179945924</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.93281441379721</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.932800810821376</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.893355028175502</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.932813655449937</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.93286870195564</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.932800976634556</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.93281441379721</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.932800976634556</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.450520260108854</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.932800976634556</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.1940847823108276</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.01879252995971258</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1329769415799846</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.01879252995971258</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.01879252995971258</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.1120881549538519</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.3193648312700985</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.01879252995971258</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.01078913979672818</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.1090582759344536</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.1154223559895261</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>0.2025295736079477</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.1382159527056748</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1776428267550471</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.1382159527056748</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.1382159527056748</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.07771952162634863</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.006100806919994858</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.1382159527056748</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.1191705965006457</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.167904246488054</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.07671703978872202</v>
+      <c r="C11" t="n">
+        <v>0.1382159527056752</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1776428267550475</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1382159527056752</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1382159527056752</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.07771952162634882</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.006100806919994747</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1382159527056752</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.119170596500646</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.1679042464880545</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.07671703978872239</v>
       </c>
     </row>
   </sheetData>
@@ -6383,7 +7583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6451,321 +7651,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9342620945146534</v>
+        <v>0.1938163450681111</v>
       </c>
       <c r="C2" t="n">
-        <v>8.511844238662565</v>
+        <v>0.2440998235311818</v>
       </c>
       <c r="D2" t="n">
-        <v>2.461380163304672</v>
+        <v>0.1958001678806717</v>
       </c>
       <c r="E2" t="n">
-        <v>8.511844238662565</v>
+        <v>0.2440998235311818</v>
       </c>
       <c r="F2" t="n">
-        <v>8.511844238662565</v>
+        <v>0.2440998235311818</v>
       </c>
       <c r="G2" t="n">
-        <v>8.988878822372952</v>
+        <v>0.2041109782393877</v>
       </c>
       <c r="H2" t="n">
-        <v>12.7024727133575</v>
+        <v>0.2087706713087482</v>
       </c>
       <c r="I2" t="n">
-        <v>8.511844238662565</v>
+        <v>0.2440998235311818</v>
       </c>
       <c r="J2" t="n">
-        <v>6.369810159396607</v>
+        <v>0.2002556426622132</v>
       </c>
       <c r="K2" t="n">
-        <v>2.385639812330806</v>
+        <v>0.1956739847710429</v>
       </c>
       <c r="L2" t="n">
-        <v>10.27265588918169</v>
+        <v>0.2046059519575993</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1252152583209563</v>
+        <v>0.1946299853659777</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1266015259975824</v>
+        <v>0.2357909323412747</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1252152583209563</v>
+        <v>0.1946299853659777</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1272116692090988</v>
+        <v>0.2357909323412747</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1272116692090985</v>
+        <v>0.2357909323412747</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1253554355928821</v>
+        <v>0.1946509891202052</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1252152583209563</v>
+        <v>0.1946299853659777</v>
       </c>
       <c r="I3" t="n">
-        <v>0.125687352702103</v>
+        <v>0.2357909323412747</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1252152583209563</v>
+        <v>0.1946299853659777</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1252152583209563</v>
+        <v>0.1946299853659777</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1252152583209563</v>
+        <v>0.1946299853659777</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.74334858560695</v>
+        <v>0.9342620945146537</v>
       </c>
       <c r="C4" t="n">
-        <v>6.414379777657317</v>
+        <v>8.51184423866256</v>
       </c>
       <c r="D4" t="n">
-        <v>6.309576305766678</v>
+        <v>2.46138016330467</v>
       </c>
       <c r="E4" t="n">
-        <v>6.393316171408907</v>
+        <v>8.51184423866256</v>
       </c>
       <c r="F4" t="n">
-        <v>6.414836557607241</v>
+        <v>8.51184423866256</v>
       </c>
       <c r="G4" t="n">
-        <v>76.74348876287902</v>
+        <v>8.988878822372918</v>
       </c>
       <c r="H4" t="n">
-        <v>76.73471429435138</v>
+        <v>12.70247271335751</v>
       </c>
       <c r="I4" t="n">
-        <v>76.74382067998825</v>
+        <v>8.51184423866256</v>
       </c>
       <c r="J4" t="n">
-        <v>6.33586960343012</v>
+        <v>6.369810159396589</v>
       </c>
       <c r="K4" t="n">
-        <v>6.228563027378062</v>
+        <v>2.385639812330805</v>
       </c>
       <c r="L4" t="n">
-        <v>6.322853039867255</v>
+        <v>10.27265588918168</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.473685223331992</v>
+        <v>0.1252152583209567</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4741573177131399</v>
+        <v>0.1266015259975824</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4736599864629671</v>
+        <v>0.1252152583209567</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4741498575291307</v>
+        <v>0.1272116692090987</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4741498575291307</v>
+        <v>0.1272116692090987</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4738254006039178</v>
+        <v>0.1253554355928828</v>
       </c>
       <c r="H5" t="n">
-        <v>0.473685223331992</v>
+        <v>0.1252152583209567</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4741573177131399</v>
+        <v>0.1256873527021026</v>
       </c>
       <c r="J5" t="n">
-        <v>0.473685223331992</v>
+        <v>0.1252152583209567</v>
       </c>
       <c r="K5" t="n">
-        <v>0.473685223331992</v>
+        <v>0.1252152583209567</v>
       </c>
       <c r="L5" t="n">
-        <v>0.473685223331992</v>
+        <v>0.1252152583209567</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5278168899260774</v>
+        <v>76.74334858560697</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8124817229807055</v>
+        <v>6.414379777657317</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8708417188690928</v>
+        <v>6.309576305766675</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7347642994855862</v>
+        <v>6.393316171408907</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5373055100108235</v>
+        <v>6.414836557607249</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8120693611699988</v>
+        <v>76.7434887628791</v>
       </c>
       <c r="H6" t="n">
-        <v>0.811929183898061</v>
+        <v>76.73471429435139</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8124012782792179</v>
+        <v>76.74382067998823</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8119850200594128</v>
+        <v>6.335869603430113</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5225393582068587</v>
+        <v>6.228563027378065</v>
       </c>
       <c r="L6" t="n">
-        <v>1.108708231991749</v>
+        <v>6.322853039867249</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.509254587984112</v>
+        <v>0.4736852233319918</v>
       </c>
       <c r="C7" t="n">
-        <v>3.18136433047301</v>
+        <v>0.4741573177131392</v>
       </c>
       <c r="D7" t="n">
-        <v>3.180892129200466</v>
+        <v>0.4736599864629668</v>
       </c>
       <c r="E7" t="n">
-        <v>3.956419139458131</v>
+        <v>0.4741498575291309</v>
       </c>
       <c r="F7" t="n">
-        <v>3.181363771044339</v>
+        <v>0.4741498575291309</v>
       </c>
       <c r="G7" t="n">
-        <v>3.181032413363795</v>
+        <v>0.4738254006039178</v>
       </c>
       <c r="H7" t="n">
-        <v>3.18089223609187</v>
+        <v>0.4736852233319918</v>
       </c>
       <c r="I7" t="n">
-        <v>3.18136433047301</v>
+        <v>0.4741573177131392</v>
       </c>
       <c r="J7" t="n">
-        <v>3.18089223609187</v>
+        <v>0.4736852233319918</v>
       </c>
       <c r="K7" t="n">
-        <v>2.791742700095758</v>
+        <v>0.4736852233319918</v>
       </c>
       <c r="L7" t="n">
-        <v>3.18089223609187</v>
+        <v>0.4736852233319918</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1758988178198628</v>
+        <v>0.5278168899260776</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01277568595044602</v>
+        <v>0.8124817229807039</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1343511816176307</v>
+        <v>0.8708417188690921</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01277568595044602</v>
+        <v>0.7347642994855861</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01277568595044602</v>
+        <v>0.5373055100108216</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.03826475080024586</v>
+        <v>0.8120693611699985</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1311853888070967</v>
+        <v>0.8119291838980591</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01277568595044602</v>
+        <v>0.8124012782792164</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04215065213432878</v>
+        <v>0.8119850200594113</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1370264358991947</v>
+        <v>0.5225393582068584</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.04647858594483111</v>
+        <v>1.108708231991746</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.50925458798411</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.181364330473005</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.180892129200465</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.956419139458129</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.181363771044338</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.181032413363792</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.180892236091868</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.181364330473005</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.180892236091868</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.791742700095756</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.180892236091868</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.1758988178198629</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01277568595044615</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.134351181617631</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01277568595044615</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01277568595044615</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.03826475080024541</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.1311853888070964</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01277568595044615</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.04215065213432894</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.1370264358991945</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.04647858594483114</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.1852936041419397</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.1426271757159338</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1683731200780247</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.1426271757159338</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.1426271757159338</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.09813357431716049</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0605236377480087</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.1426271757159338</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.1308770601190095</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="B11" t="n">
+        <v>0.1852936041419396</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.1426271757159336</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1683731200780248</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1426271757159336</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1426271757159336</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.09813357431716027</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.06052363774800887</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1426271757159336</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.1308770601190098</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.1694641861920376</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.09490078364375544</v>
+      <c r="L11" t="n">
+        <v>0.09490078364375526</v>
       </c>
     </row>
   </sheetData>
@@ -6779,7 +8059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6847,321 +8127,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.05737645267694</v>
+        <v>0.1771229364395616</v>
       </c>
       <c r="C2" t="n">
-        <v>6.285629862530837</v>
+        <v>0.2238411619967513</v>
       </c>
       <c r="D2" t="n">
-        <v>1.635104016210317</v>
+        <v>0.1778331788895292</v>
       </c>
       <c r="E2" t="n">
-        <v>6.285629862530837</v>
+        <v>0.2238411619967513</v>
       </c>
       <c r="F2" t="n">
-        <v>6.285629862530837</v>
+        <v>0.2238411619967513</v>
       </c>
       <c r="G2" t="n">
-        <v>5.848258743992591</v>
+        <v>0.1832310116650852</v>
       </c>
       <c r="H2" t="n">
-        <v>10.14350019899162</v>
+        <v>0.1875518646522395</v>
       </c>
       <c r="I2" t="n">
-        <v>6.285629862530837</v>
+        <v>0.2238411619967513</v>
       </c>
       <c r="J2" t="n">
-        <v>3.712817612385193</v>
+        <v>0.1801744245263077</v>
       </c>
       <c r="K2" t="n">
-        <v>1.313979829268308</v>
+        <v>0.1774713878871201</v>
       </c>
       <c r="L2" t="n">
-        <v>8.60106249160431</v>
+        <v>0.1856109645055551</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1097539390624843</v>
+        <v>0.1775932587989964</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1119652851081284</v>
+        <v>0.218382399250404</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1097539390624843</v>
+        <v>0.1775932587989964</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1124083053094796</v>
+        <v>0.218382399250404</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1124083053094797</v>
+        <v>0.218382399250404</v>
       </c>
       <c r="G3" t="n">
-        <v>0.109931392768422</v>
+        <v>0.1777939943206815</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1097539390624843</v>
+        <v>0.1775932587989964</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1104600942969523</v>
+        <v>0.218382399250404</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1097539390624843</v>
+        <v>0.1775932587989964</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1097539390624843</v>
+        <v>0.1775932587989964</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1097539390624843</v>
+        <v>0.1775932587989964</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.295406702229696</v>
+        <v>1.057376452676937</v>
       </c>
       <c r="C4" t="n">
-        <v>6.386445299036721</v>
+        <v>6.28562986253086</v>
       </c>
       <c r="D4" t="n">
-        <v>6.284475865102086</v>
+        <v>1.635104016210315</v>
       </c>
       <c r="E4" t="n">
-        <v>6.366022226397439</v>
+        <v>6.28562986253086</v>
       </c>
       <c r="F4" t="n">
-        <v>6.385797721381629</v>
+        <v>6.28562986253086</v>
       </c>
       <c r="G4" t="n">
-        <v>6.295584155935629</v>
+        <v>5.8482587439926</v>
       </c>
       <c r="H4" t="n">
-        <v>76.68115386599666</v>
+        <v>10.14350019899163</v>
       </c>
       <c r="I4" t="n">
-        <v>6.296112857464175</v>
+        <v>6.28562986253086</v>
       </c>
       <c r="J4" t="n">
-        <v>6.305538008288077</v>
+        <v>3.712817612385196</v>
       </c>
       <c r="K4" t="n">
-        <v>6.203085458912582</v>
+        <v>1.31397982926831</v>
       </c>
       <c r="L4" t="n">
-        <v>6.292987927282445</v>
+        <v>8.601062491604315</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4450211781781078</v>
+        <v>0.1097539390624843</v>
       </c>
       <c r="C5" t="n">
-        <v>0.445727333412574</v>
+        <v>0.1119652851081286</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4449962529063817</v>
+        <v>0.1097539390624843</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4457176950425323</v>
+        <v>0.1124083053094793</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4457176950425323</v>
+        <v>0.1124083053094793</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4451986318840447</v>
+        <v>0.1099313927684215</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4450211781781078</v>
+        <v>0.1097539390624843</v>
       </c>
       <c r="I5" t="n">
-        <v>0.445727333412574</v>
+        <v>0.1104600942969524</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4450211781781078</v>
+        <v>0.1097539390624843</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4450211781781078</v>
+        <v>0.1097539390624843</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4450211781781078</v>
+        <v>0.1097539390624843</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4861488086372672</v>
+        <v>6.295406702229706</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7520022234654696</v>
+        <v>6.386445299036724</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8061864014675395</v>
+        <v>6.284475865102082</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6794925706552979</v>
+        <v>6.366022226397442</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4952664875351878</v>
+        <v>6.385797721381629</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7513992453583487</v>
+        <v>6.295584155935633</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7512217916524712</v>
+        <v>76.68115386599666</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7519279468868806</v>
+        <v>6.29611285746418</v>
       </c>
       <c r="J6" t="n">
-        <v>0.751273886051566</v>
+        <v>6.305538008288071</v>
       </c>
       <c r="K6" t="n">
-        <v>0.481224941893073</v>
+        <v>6.203085458912568</v>
       </c>
       <c r="L6" t="n">
-        <v>1.028112687417958</v>
+        <v>6.29298792728244</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.196134742285407</v>
+        <v>0.4450211781781069</v>
       </c>
       <c r="C7" t="n">
-        <v>2.785120288197885</v>
+        <v>0.4457273334125749</v>
       </c>
       <c r="D7" t="n">
-        <v>2.784413992148108</v>
+        <v>0.4449962529063807</v>
       </c>
       <c r="E7" t="n">
-        <v>3.46398146982434</v>
+        <v>0.4457176950425324</v>
       </c>
       <c r="F7" t="n">
-        <v>2.785119780690164</v>
+        <v>0.4457176950425324</v>
       </c>
       <c r="G7" t="n">
-        <v>2.78459158666935</v>
+        <v>0.4451986318840446</v>
       </c>
       <c r="H7" t="n">
-        <v>2.784414132963411</v>
+        <v>0.4450211781781069</v>
       </c>
       <c r="I7" t="n">
-        <v>2.785120288197885</v>
+        <v>0.4457273334125749</v>
       </c>
       <c r="J7" t="n">
-        <v>2.784414132963411</v>
+        <v>0.4450211781781069</v>
       </c>
       <c r="K7" t="n">
-        <v>2.429733916313091</v>
+        <v>0.4450211781781069</v>
       </c>
       <c r="L7" t="n">
-        <v>2.784414132963411</v>
+        <v>0.4450211781781069</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.155132930051764</v>
+        <v>0.486148808637267</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05876899542765226</v>
+        <v>0.7520022234654686</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1402669799149819</v>
+        <v>0.8061864014675364</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05876899542765226</v>
+        <v>0.6794925706552969</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05876899542765226</v>
+        <v>0.4952664875351874</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0322350912188801</v>
+        <v>0.7513992453583456</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.05884252829894034</v>
+        <v>0.7512217916524668</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05876899542765226</v>
+        <v>0.7519279468868828</v>
       </c>
       <c r="J8" t="n">
-        <v>0.09185997356891556</v>
+        <v>0.7512738860515635</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1478624662736339</v>
+        <v>0.4812249418930743</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04870786868002955</v>
+        <v>1.028112687417952</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.196134742285408</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.785120288197886</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.784413992148111</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.463981469824343</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.785119780690167</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.78459158666935</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.784414132963413</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.785120288197886</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.784414132963412</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.42973391631309</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.784414132963412</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.1551329300517637</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.05876899542765215</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1402669799149817</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.05876899542765215</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.05876899542765215</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.03223509121888015</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.05884252829894045</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.05876899542765215</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.09185997356891541</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.1478624662736337</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.04870786868002928</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.1669034152827517</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.1512165545996622</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1608496030455097</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.1512165545996622</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.1512165545996622</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.1170012468850649</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.07997282804653243</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.1512165545996622</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.141165506530852</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.1639437825416671</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.1236548995783284</v>
+      <c r="B11" t="n">
+        <v>0.1669034152827513</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.1512165545996616</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1608496030455093</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1512165545996616</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1512165545996616</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1170012468850648</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.07997282804653197</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1512165545996616</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.1411655065308512</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.1639437825416668</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.1236548995783279</v>
       </c>
     </row>
   </sheetData>
@@ -7175,7 +8535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7243,321 +8603,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.935596775540818</v>
+        <v>0.2027717224586413</v>
       </c>
       <c r="C2" t="n">
-        <v>11.24097633360988</v>
+        <v>0.2552299326251714</v>
       </c>
       <c r="D2" t="n">
-        <v>5.366935205520274</v>
+        <v>0.206732454255758</v>
       </c>
       <c r="E2" t="n">
-        <v>11.24097633360988</v>
+        <v>0.2552299326251714</v>
       </c>
       <c r="F2" t="n">
-        <v>11.24097633360988</v>
+        <v>0.2552299326251714</v>
       </c>
       <c r="G2" t="n">
-        <v>11.25967116556023</v>
+        <v>0.2133276935621813</v>
       </c>
       <c r="H2" t="n">
-        <v>12.21602577534901</v>
+        <v>0.213728445987438</v>
       </c>
       <c r="I2" t="n">
-        <v>11.24097633360988</v>
+        <v>0.2552299326251714</v>
       </c>
       <c r="J2" t="n">
-        <v>9.80226391835691</v>
+        <v>0.2108620251615893</v>
       </c>
       <c r="K2" t="n">
-        <v>4.763451613095168</v>
+        <v>0.2059722100643176</v>
       </c>
       <c r="L2" t="n">
-        <v>38.22942681152082</v>
+        <v>0.2093824532882423</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1363881210936265</v>
+        <v>0.2026221049145255</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1385702295647688</v>
+        <v>0.2448398696946732</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1363881210936265</v>
+        <v>0.2026221049145255</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1392690694197544</v>
+        <v>0.2448398696946732</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1392690694197536</v>
+        <v>0.2448398696946732</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1365542216370123</v>
+        <v>0.2027989804554843</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1363881210936265</v>
+        <v>0.2026221049145255</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1370273645063701</v>
+        <v>0.2448398696946732</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1363881210936265</v>
+        <v>0.2026221049145255</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1363881210936265</v>
+        <v>0.2026221049145255</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1363881210936265</v>
+        <v>0.2026221049145255</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.808100465057572</v>
+        <v>1.935596775540816</v>
       </c>
       <c r="C4" t="n">
-        <v>6.895829064712686</v>
+        <v>11.24097633360986</v>
       </c>
       <c r="D4" t="n">
-        <v>6.784711774524944</v>
+        <v>5.36693520552029</v>
       </c>
       <c r="E4" t="n">
-        <v>6.872834972064433</v>
+        <v>11.24097633360986</v>
       </c>
       <c r="F4" t="n">
-        <v>6.895194134319489</v>
+        <v>11.24097633360986</v>
       </c>
       <c r="G4" t="n">
-        <v>82.38115071380841</v>
+        <v>11.25967116556023</v>
       </c>
       <c r="H4" t="n">
-        <v>82.36950406739655</v>
+        <v>12.21602577534901</v>
       </c>
       <c r="I4" t="n">
-        <v>82.38162385667778</v>
+        <v>11.24097633360986</v>
       </c>
       <c r="J4" t="n">
-        <v>82.37258098045177</v>
+        <v>9.802263918356903</v>
       </c>
       <c r="K4" t="n">
-        <v>6.6966026545627</v>
+        <v>4.763451613095173</v>
       </c>
       <c r="L4" t="n">
-        <v>6.794858072435635</v>
+        <v>38.22942681152089</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.515688731214638</v>
+        <v>0.1363881210936261</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5163279746273828</v>
+        <v>0.1385702295647683</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5156615797736881</v>
+        <v>0.1363881210936261</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5163052061977336</v>
+        <v>0.139269069419754</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5163052061977336</v>
+        <v>0.139269069419754</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5158548317580248</v>
+        <v>0.136554221637012</v>
       </c>
       <c r="H5" t="n">
-        <v>0.515688731214638</v>
+        <v>0.1363881210936261</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5163279746273828</v>
+        <v>0.1370273645063698</v>
       </c>
       <c r="J5" t="n">
-        <v>0.515688731214638</v>
+        <v>0.1363881210936261</v>
       </c>
       <c r="K5" t="n">
-        <v>0.515688731214638</v>
+        <v>0.1363881210936261</v>
       </c>
       <c r="L5" t="n">
-        <v>0.515688731214638</v>
+        <v>0.1363881210936261</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5781707633059285</v>
+        <v>6.808100465057576</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8901011422405744</v>
+        <v>6.895829064712686</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9539214029144293</v>
+        <v>6.784711774524951</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8049709163045707</v>
+        <v>6.872834972064432</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5886777399176818</v>
+        <v>6.895194134319491</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8895544993464272</v>
+        <v>82.38115071380838</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8893883988029477</v>
+        <v>82.36950406739655</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8900276422157833</v>
+        <v>82.38162385667771</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8894495619424116</v>
+        <v>82.37258098045179</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5723897359518542</v>
+        <v>6.696602654562697</v>
       </c>
       <c r="L6" t="n">
-        <v>1.214481242633027</v>
+        <v>6.794858072435635</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.030148633076923</v>
+        <v>0.5156887312146381</v>
       </c>
       <c r="C7" t="n">
-        <v>3.844353464982986</v>
+        <v>0.5163279746273821</v>
       </c>
       <c r="D7" t="n">
-        <v>3.843714143901876</v>
+        <v>0.5156615797736882</v>
       </c>
       <c r="E7" t="n">
-        <v>4.78319011478048</v>
+        <v>0.5163052061977337</v>
       </c>
       <c r="F7" t="n">
-        <v>3.84435288999341</v>
+        <v>0.5163052061977337</v>
       </c>
       <c r="G7" t="n">
-        <v>3.843880322113626</v>
+        <v>0.5158548317580258</v>
       </c>
       <c r="H7" t="n">
-        <v>3.84371422157025</v>
+        <v>0.5156887312146381</v>
       </c>
       <c r="I7" t="n">
-        <v>3.844353464982986</v>
+        <v>0.5163279746273821</v>
       </c>
       <c r="J7" t="n">
-        <v>3.84371422157025</v>
+        <v>0.5156887312146381</v>
       </c>
       <c r="K7" t="n">
-        <v>3.372331091811807</v>
+        <v>0.5156887312146381</v>
       </c>
       <c r="L7" t="n">
-        <v>3.84371422157025</v>
+        <v>0.5156887312146381</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.161866625498238</v>
+        <v>0.5781707633059293</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.02374962639848146</v>
+        <v>0.8901011422405736</v>
       </c>
       <c r="D8" t="n">
-        <v>0.07891792579542228</v>
+        <v>0.9539214029144309</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.02374962639848146</v>
+        <v>0.8049709163045696</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.02374962639848146</v>
+        <v>0.588677739917682</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.05423272184189152</v>
+        <v>0.8895544993464262</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.06260928453641575</v>
+        <v>0.8893883988029475</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.02374962639848146</v>
+        <v>0.8900276422157838</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.006037562813863959</v>
+        <v>0.8894495619424093</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09490350862254311</v>
+        <v>0.5723897359518531</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02610958177376039</v>
+        <v>1.214481242633027</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.030148633076924</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.844353464982981</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.843714143901875</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.783190114780483</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.844352889993412</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.843880322113624</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.843714221570237</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.844353464982981</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.843714221570237</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.372331091811808</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.843714221570237</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.1618666254982375</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.02374962639848097</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.07891792579542178</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.02374962639848097</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.02374962639848097</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.05423272184189194</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.06260928453641657</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.02374962639848097</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.006037562813864604</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.09490350862254252</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.02610958177375976</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.1842278494442247</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.1330208559588484</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>0.1842278494442248</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.133020855958848</v>
+      </c>
+      <c r="D11" t="n">
         <v>0.1504466585347382</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.1330208559588484</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.1330208559588484</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.09637744990544146</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.09304731854497209</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.1330208559588484</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.1159212113862655</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="E11" t="n">
+        <v>0.133020855958848</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.133020855958848</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.09637744990544111</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.09304731854497213</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.133020855958848</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.1159212113862654</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.1569599054726669</v>
       </c>
-      <c r="L9" t="n">
-        <v>-0.1174011554139562</v>
+      <c r="L11" t="n">
+        <v>-0.1174011554139566</v>
       </c>
     </row>
   </sheetData>
@@ -7571,7 +9011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7639,321 +9079,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7816677952031367</v>
+        <v>0.1934598977714971</v>
       </c>
       <c r="C2" t="n">
-        <v>8.653798097605115</v>
+        <v>0.2444541344088028</v>
       </c>
       <c r="D2" t="n">
-        <v>4.055356773767142</v>
+        <v>0.1976479537618739</v>
       </c>
       <c r="E2" t="n">
-        <v>8.653798097605115</v>
+        <v>0.2444541344088028</v>
       </c>
       <c r="F2" t="n">
-        <v>8.653798097605115</v>
+        <v>0.2444541344088028</v>
       </c>
       <c r="G2" t="n">
-        <v>8.684206566460704</v>
+        <v>0.2033554396543899</v>
       </c>
       <c r="H2" t="n">
-        <v>20.01715371401264</v>
+        <v>0.2162735368278515</v>
       </c>
       <c r="I2" t="n">
-        <v>8.653798097605115</v>
+        <v>0.2444541344088028</v>
       </c>
       <c r="J2" t="n">
-        <v>7.073155172853332</v>
+        <v>0.2004805417651833</v>
       </c>
       <c r="K2" t="n">
-        <v>2.709423653727304</v>
+        <v>0.1959120343911454</v>
       </c>
       <c r="L2" t="n">
-        <v>8.251767688993366</v>
+        <v>0.2110024296262716</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1251160959910753</v>
+        <v>0.1944642682553245</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1270352716762627</v>
+        <v>0.2360838356164356</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1251160959910753</v>
+        <v>0.1944642682553245</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1276362898016563</v>
+        <v>0.2360838356164356</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1276362898016562</v>
+        <v>0.2360838356164356</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1252746608712638</v>
+        <v>0.1946021458245542</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1251160959910753</v>
+        <v>0.1944642682553245</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1257050473316258</v>
+        <v>0.2360838356164356</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1251160959910753</v>
+        <v>0.1944642682553245</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1251160959910753</v>
+        <v>0.1944642682553245</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1251160959910753</v>
+        <v>0.1944642682553245</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.74202006092013</v>
+        <v>0.7816677952031355</v>
       </c>
       <c r="C4" t="n">
-        <v>6.414586642359977</v>
+        <v>8.653798097605108</v>
       </c>
       <c r="D4" t="n">
-        <v>6.312901754885079</v>
+        <v>4.055356773767132</v>
       </c>
       <c r="E4" t="n">
-        <v>6.39353430692703</v>
+        <v>8.653798097605108</v>
       </c>
       <c r="F4" t="n">
-        <v>6.41431575622555</v>
+        <v>8.653798097605108</v>
       </c>
       <c r="G4" t="n">
-        <v>76.74217862580031</v>
+        <v>8.684206566460739</v>
       </c>
       <c r="H4" t="n">
-        <v>76.73441838248156</v>
+        <v>20.01715371401266</v>
       </c>
       <c r="I4" t="n">
-        <v>76.74260901226067</v>
+        <v>8.653798097605108</v>
       </c>
       <c r="J4" t="n">
-        <v>6.335184170508342</v>
+        <v>7.073155172853325</v>
       </c>
       <c r="K4" t="n">
-        <v>6.229128527027511</v>
+        <v>2.7094236537273</v>
       </c>
       <c r="L4" t="n">
-        <v>6.321421243734703</v>
+        <v>8.251767688993347</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4737975788391123</v>
+        <v>0.1251160959910737</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4743865301796617</v>
+        <v>0.1270352716762634</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4737723417296033</v>
+        <v>0.1251160959910737</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4743911174898878</v>
+        <v>0.1276362898016561</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4743911174898878</v>
+        <v>0.1276362898016563</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4739561437192989</v>
+        <v>0.1252746608712632</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4737975788391123</v>
+        <v>0.1251160959910737</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4743865301796617</v>
+        <v>0.1257050473316258</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4737975788391123</v>
+        <v>0.1251160959910737</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4737975788391123</v>
+        <v>0.1251160959910737</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4737975788391123</v>
+        <v>0.1251160959910737</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5274928277395263</v>
+        <v>76.74202006092014</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8119421736121111</v>
+        <v>6.414586642359973</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8701025676570853</v>
+        <v>6.312901754885077</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7343175581756655</v>
+        <v>6.393534306927026</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5370945939154741</v>
+        <v>6.414315756225553</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8114198867109371</v>
+        <v>76.74217862580026</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8112613218307613</v>
+        <v>76.73441838248156</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8118502731713029</v>
+        <v>76.7426090122607</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8113170904278433</v>
+        <v>6.335184170508336</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5222216822793685</v>
+        <v>6.229128527027512</v>
       </c>
       <c r="L6" t="n">
-        <v>1.107681242203032</v>
+        <v>6.321421243734705</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.500310139038321</v>
+        <v>0.4737975788391106</v>
       </c>
       <c r="C7" t="n">
-        <v>3.170003206103785</v>
+        <v>0.4743865301796611</v>
       </c>
       <c r="D7" t="n">
-        <v>3.169414028412251</v>
+        <v>0.4737723417296021</v>
       </c>
       <c r="E7" t="n">
-        <v>3.942134139442553</v>
+        <v>0.4743911174898884</v>
       </c>
       <c r="F7" t="n">
-        <v>3.170002546669376</v>
+        <v>0.4743911174898884</v>
       </c>
       <c r="G7" t="n">
-        <v>3.169572819643417</v>
+        <v>0.4739561437192991</v>
       </c>
       <c r="H7" t="n">
-        <v>3.169414254763236</v>
+        <v>0.4737975788391106</v>
       </c>
       <c r="I7" t="n">
-        <v>3.170003206103785</v>
+        <v>0.4743865301796611</v>
       </c>
       <c r="J7" t="n">
-        <v>3.169414254763236</v>
+        <v>0.4737975788391106</v>
       </c>
       <c r="K7" t="n">
-        <v>2.78173260713546</v>
+        <v>0.4737975788391106</v>
       </c>
       <c r="L7" t="n">
-        <v>3.169414254763236</v>
+        <v>0.4737975788391106</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1796247761187996</v>
+        <v>0.527492827739526</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0116420616055535</v>
+        <v>0.8119421736121128</v>
       </c>
       <c r="D8" t="n">
-        <v>0.091899562188267</v>
+        <v>0.8701025676570848</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0116420616055535</v>
+        <v>0.7343175581756676</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0116420616055535</v>
+        <v>0.5370945939154768</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.02367976757673312</v>
+        <v>0.811419886710938</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2891133372868371</v>
+        <v>0.8112613218307619</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0116420616055535</v>
+        <v>0.8118502731713025</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03375729726814568</v>
+        <v>0.8113170904278445</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1283011324233337</v>
+        <v>0.5222216822793693</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01994915364911507</v>
+        <v>1.107681242203035</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.500310139038316</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.170003206103776</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.169414028412242</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.942134139442546</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.170002546669367</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.169572819643419</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.16941425476323</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.170003206103776</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.16941425476323</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.781732607135461</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.16941425476323</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.1796247761187993</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01164206160555357</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.09189956218826685</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01164206160555357</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01164206160555357</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.02367976757673072</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.2891133372868369</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01164206160555357</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.03375729726814535</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.1283011324233339</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01994915364911496</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.1867078815587226</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.1423324119803565</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1509806856470384</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.1423324119803565</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.1423324119803565</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.1040364734336209</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.003755814764222987</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.1423324119803565</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.1273583578232879</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="B11" t="n">
+        <v>0.1867078815587227</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.142332411980357</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1509806856470386</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.142332411980357</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.142332411980357</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1040364734336207</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.00375581476422307</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.142332411980357</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.1273583578232878</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.165807596738186</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.1218053231733343</v>
+      <c r="L11" t="n">
+        <v>0.1218053231733345</v>
       </c>
     </row>
   </sheetData>
